--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -481,10 +481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-06-24  ·  Window 2025-12-24 to 2026-06-24  ·  NC + SC</t>
+          <t>Week of 2026-07-02  ·  Window 2026-01-02 to 2026-07-02  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24  (Inaugural / Baseline — Week 1)</t>
+          <t>2026-07-02  (Week 2)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24 to 2026-06-24  (trailing 6 months)</t>
+          <t>2026-01-02 to 2026-07-02  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -553,112 +553,148 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Qualifying (ranked) deals</t>
+          <t>Qualifying (ranked) deals — this week</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Markets to Watch</t>
+          <t>Qualifying (ranked) deals — cumulative (all weeks)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Excluded / Noise</t>
+          <t>Markets to Watch — this week</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Markets to Watch — cumulative (all weeks)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Top market</t>
+          <t>Excluded / Noise — this week</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 92</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Top SC market</t>
+          <t>Excluded / Noise — cumulative (all weeks)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Blythewood / N. Columbia (Richland) — Scout Motors, score 85</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Key takeaway</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Charlotte is the standout high-income story (SMBC $165k + Capital Group); Triangle life-sciences (AbbVie, Genentech) is the #2 cluster; biggest SC headcount (Ferrara, Suniva) is workforce-tier.</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Window note</t>
+          <t>Top market</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months reaches back to 2025-12-24 — adds Genentech (Jan) &amp; Siemens Energy (Feb). The Nov-2025 cluster (Novartis, Aspida, Vulcan, Maersk, Pacific Life) is STILL out (&gt;6 mo back).</t>
+          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Data-quality note</t>
+          <t>Top new find</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>NC deals carry stated wages; SC deals mostly do not — SC income tiers inferred &amp; flagged. No numbers invented.</t>
+          <t>Rock Hill / Palmetto Research Park (York, SC) — Octapharma, score 90 (NEW)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Key takeaway</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Octapharma's $1.49B Rock Hill campus is the largest find since this report began; Charlotte's SMBC/Capital Group/Citigroup all converted from announced to leased/open this week; Novartis graduates into Ranked via a new April facility phase; JetZero's hiring ramp is confirmed delayed a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Window note</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Window rolled forward to 2026-01-02 - 2026-07-02; all 6 baseline (2026-06-24) Ranked entries remain in scope, none rolled out of window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Data-quality note</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>NC deals carry stated wages; SC deals mostly do not, except Octapharma this week (two stated wage bands from its incentive filing). WebFetch (direct page fetch) returned HTTP 403 on all tested domains this week — findings rest on WebSearch-surfaced content and verified URLs rather than a second-pass raw fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>Week-over-week</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Baseline established; all qualifying entries = NEW. Carry-over projects (Scout, JetZero, Genentech) flagged via in-window milestones/expansions.</t>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>3 New (Octapharma, Novartis, Citigroup), 2 Updated (Capital Group wage/lease, JetZero delay), 1 Gaining Momentum (SMBC lease), 3 Repeated (Scout Motors, AbbVie, Genentech), 1 Removed from Watch (TigerDC Project Spero, withdrawn).</t>
         </is>
       </c>
     </row>
@@ -673,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -793,7 +829,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -812,7 +848,7 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>SMBC Group — 2nd US HQ / bank operations</t>
+          <t>SMBC Group — 2nd US HQ / bank operations (lease signed)</t>
         </is>
       </c>
       <c r="G2" s="6" t="n">
@@ -825,7 +861,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>$165,316 avg (stated; vs county $90,706)</t>
+          <t>$165,316 avg (stated; unchanged)</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -845,17 +881,17 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>New office / HQ-tier ops expansion</t>
+          <t>Ops expansion + lease-signing milestone</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/04/07/governor-stein-announces-2000-new-jobs-japans-smbc-group-selects-charlotte-bank-operations-expansion</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/04/07/governor-stein-announces-2000-new-jobs-japans-smbc-group-selects-charlotte-bank-operations-expansion ; https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
@@ -870,7 +906,7 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth. Lease signing de-risks timeline.</t>
         </is>
       </c>
     </row>
@@ -879,16 +915,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Blythewood / N. Columbia</t>
+          <t>Rock Hill / Palmetto Research Park</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Richland</t>
+          <t>York</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -898,65 +934,65 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (hiring ramp)</t>
+          <t>Octapharma — new US HQ/lab + manufacturing campus (Project Palmetto Rock)</t>
         </is>
       </c>
       <c r="G3" s="6" t="n">
-        <v>4000</v>
+        <v>1552</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Auto mfg + salaried eng.</t>
+          <t>Biopharma HQ/lab + manufacturing</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
+          <t>$141,502 avg HQ/lab (564 jobs, stated) / $102,752 avg mfg (688 jobs, stated)</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mix supports above-median HH income</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>$2.0B (+$25M training center)</t>
+          <t>$1.49B ($190M HQ/lab + $1.29B mfg)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>State/local package (2023); $25M readySC</t>
+          <t>Fee-in-lieu of ad valorem tax; special source revenue credits; multi-county park designation</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>Hiring ramp + training-center milestone</t>
+          <t>New HQ + manufacturing campus</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
+          <t>https://www.wrhi.com/2026/06/global-biopharmaceutical-company-eyes-rock-hill-site-for-1-5-billion-facility-and-1252-jobs-213471 ; https://www.wrhi.com/2026/06/york-county-council-passes-second-reading-of-1-5-billion-biopharma-deal-data-center-moratorium-213788 ; https://www.postandcourier.com/york-county/news/rock-hill-plasma-panthers-octapharma-billion/article_fbd570b1-6451-406b-bb8c-92a53fad0d7c.html</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>High (project/milestone); Med (wage)</t>
+          <t>High (facts); Med (final commitment)</t>
         </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>Suburban</t>
+          <t>Suburban / urban-adjacent</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+          <t>Largest find of the cycle; blended $103K-$141.5K wages support strong Class-A rental + for-sale demand in Rock Hill/York Co.; 300 relocating Charlotte staff imply cross-border household movement.</t>
         </is>
       </c>
     </row>
@@ -965,84 +1001,84 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Durham / RTP</t>
+          <t>Blythewood / N. Columbia</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Richland</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>AbbVie — biopharma manufacturing campus</t>
+          <t>Scout Motors — EV assembly plant (hiring ramp)</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>734</v>
+        <v>4000</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Adv. mfg / R&amp;D / lab</t>
+          <t>Auto mfg + salaried eng.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>$118,041 avg (stated; vs county $102,817)</t>
+          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>$1.4B</t>
+          <t>$2.0B (+$25M training center)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+          <t>State/local package (2023); $25M readySC</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>New facility (greenfield, 185 ac)</t>
+          <t>Hiring ramp + training-center milestone (unchanged from prior week)</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (project/milestone); Med (wage)</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Suburban-urban</t>
+          <t>Suburban</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
         </is>
       </c>
     </row>
@@ -1051,16 +1087,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Durham / RTP</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1070,65 +1106,65 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (groundbreaking)</t>
+          <t>AbbVie — biopharma manufacturing campus</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>14500</v>
+        <v>734</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Aerospace mfg + eng.</t>
+          <t>Adv. mfg / R&amp;D / lab</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>$89,340 avg (stated, 2025 selection)</t>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated (2025)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>$4.7B</t>
+          <t>$1.4B</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr</t>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking of megaproject</t>
+          <t>New facility (greenfield, 185 ac) — unchanged</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project</t>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Med (timeline)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Suburban</t>
+          <t>Suburban-urban</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>Transformational long-term: multi-yr construction then 14,500 jobs; broad rental + for-sale across Guilford + Randolph/Alamance commuter shed.</t>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
         </is>
       </c>
     </row>
@@ -1137,16 +1173,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs / SW Wake</t>
+          <t>Durham / Wake (Morrisville)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Durham &amp; Wake</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1156,20 +1192,20 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
+          <t>Novartis — 7th US facility / Morrisville API manufacturing building</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Biologics/API mfg + R&amp;D</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
+          <t>$111,161 avg (stated; exceeds Durham $97,531 and Wake $76,643 avgs)</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1179,27 +1215,27 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B (doubled from ~$700M)</t>
+          <t>~$991M cumulative ($771M orig. + $220M new API bldg)</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
+          <t>JDIG up to $7.56M / 12 yr (original award)</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>Expansion of committed project</t>
+          <t>New phase — additional facility as part of $23B national plan</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+          <t>https://www.globenewswire.com/news-release/2026/04/30/3284676/0/en/Novartis-finalizes-US-manufacturing-and-R-D-expansion-plan-with-seventh-new-facility.html ; https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
@@ -1214,7 +1250,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median. Near-term 1,500+ construction workforce.</t>
+          <t>$111K avg wage across 700+ jobs reinforces Durham/Wake as the report's deepest life-sciences cluster alongside AbbVie and Genentech.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1259,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -1242,7 +1278,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Capital Group — East Coast operations hub</t>
+          <t>Capital Group — East Coast operations hub (lease signed; wage confirmed)</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
@@ -1250,17 +1286,17 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Office — finance/tech</t>
+          <t>Software/Data/AI Engineering, Investment Ops, GBS</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$194,141 avg (stated, per JDIG filing — newly confirmed)</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred ~$190k (from ~$116M payroll / 600 jobs; roles all $100k+ in CLT)</t>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k last week)</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -1270,37 +1306,295 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+          <t>JDIG up to $17.17M / 12 yr; ~$1M local incentive</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>New facility / operations hub</t>
+          <t>New facility / operations hub + lease-signing milestone</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/03/26/governor-stein-announces-capital-group-will-establish-major-operations-hub-charlotte</t>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/26/governor-stein-announces-capital-group-will-establish-major-operations-hub-charlotte ; https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>High (jobs); Med (wage)</t>
+          <t>High (jobs and wage both now stated)</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>Urban-suburban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+          <t>Highest confirmed avg wage in the report ($194,141); strongly supports luxury/high-end housing demand in Uptown/South End.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B (doubled from ~$700M)</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project — unchanged</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking; hiring delayed 1 year)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025 selection)</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking + confirmed hiring-timeline delay</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project ; https://www.carolinajournal.com/jetzero-delays-hiring-timeline-amid-budget-holdup/ ; https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Still potentially transformational long-term but push demand curve back ~1 year; model 2028+ for meaningful Guilford Co. absorption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Ballantyne (South Charlotte)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup / Citi — office grand opening</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Finance, Risk Mgmt, Compliance, Private Bank Wealth Mgmt</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>State JDIG &gt;$8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Material in-window milestone: grand opening of previously announced office</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/16/governor-stein-celebrates-grand-opening-citi-charlotte-office ; https://www.bankingdive.com/news/citi-opening-charlotte-office-510-jobs-north-carolina/752586/</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Solid Ballantyne/south Charlotte rental and starter-home demand from ~$132K-avg finance roles.</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2456,1050 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Gaining Momentum</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations (lease signed)</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Ops expansion + lease-signing milestone</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed 2026-05-04 (~200K SF, 301 S. College St); occupancy fall 2026; hiring 2028-2032</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/04/07/governor-stein-announces-2000-new-jobs-japans-smbc-group-selects-charlotte-bank-operations-expansion ; https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W8" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth. Lease signing de-risks timeline.</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr">
+        <is>
+          <t>Score raised from 92 to 94 on lease-signing certainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / Palmetto Research Park</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — new US HQ/lab + manufacturing campus (Project Palmetto Rock)</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical / plasma manufacturing</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>New HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>1552</v>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,252 new + 300 relocating from Charlotte)</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ/lab (564 jobs, stated) / $102,752 avg mfg (688 jobs, stated)</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>$1.49B ($190M HQ/lab + $1.29B mfg)</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu of ad valorem tax; special source revenue credits; multi-county park designation</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>1st reading 2026-06-15 (7-0); 2nd reading 2026-06-29 (7-0); construction could start 2027; ~10-yr build-out</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrhi.com/2026/06/global-biopharmaceutical-company-eyes-rock-hill-site-for-1-5-billion-facility-and-1252-jobs-213471 ; https://www.wrhi.com/2026/06/york-county-council-passes-second-reading-of-1-5-billion-biopharma-deal-data-center-moratorium-213788 ; https://www.postandcourier.com/york-county/news/rock-hill-plasma-panthers-octapharma-billion/article_fbd570b1-6451-406b-bb8c-92a53fad0d7c.html</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (final commitment)</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma HQ/lab + manufacturing</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>Suburban / urban-adjacent</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
+        <is>
+          <t>Largest find of the cycle; blended $103K-$141.5K wages support strong Class-A rental + for-sale demand in Rock Hill/York Co.; 300 relocating Charlotte staff imply cross-border household movement.</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr">
+        <is>
+          <t>Site is the former Carolina Panthers HQ/practice facility at Palmetto Research Park; Novant Health separately building $300M medical campus on adjacent 25 acres of same tract (see Watch).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (hiring ramp)</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Hiring ramp + training-center milestone (unchanged from prior week)</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Projected (600+ hired)</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Production targeted end-2026; 4,000 at full capacity ~2030-31</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>High (project/milestone); Med (wage)</t>
+        </is>
+      </c>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone found in this week's window; April 20 milestone remains valid within trailing 6-month window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac) — unchanged</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U11" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this week; steady.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Wake (Morrisville)</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — 7th US facility / Morrisville API manufacturing building</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>New phase — additional facility as part of $23B national plan</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Projected (280 Durham + 100 Wake + growing; total by end of 2030)</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated; exceeds Durham $97,531 and Wake $76,643 avgs)</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>~$991M cumulative ($771M orig. + $220M new API bldg)</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $7.56M / 12 yr (original award)</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Morrisville API site opens 2028</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/04/30/3284676/0/en/Novartis-finalizes-US-manufacturing-and-R-D-expansion-plan-with-seventh-new-facility.html ; https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>Biologics/API mfg + R&amp;D</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W12" s="6" t="inlineStr">
+        <is>
+          <t>$111K avg wage across 700+ jobs reinforces Durham/Wake as the report's deepest life-sciences cluster alongside AbbVie and Genentech.</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr">
+        <is>
+          <t>Original Nov 2025 announcement was pre-window/excluded last week; the April 30, 2026 'seventh facility' update (new building, new capital, first stated wage) is the qualifying in-window event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub (lease signed; wage confirmed)</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub + lease-signing milestone</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated, per JDIG filing — newly confirmed)</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k last week)</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.17M / 12 yr; ~$1M local incentive</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed 2026-05-22 (196,940 SF, One Independence Center); hiring begins 2027 over 5 yr; Hampton Roads VA office closing by end of 2027</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/26/governor-stein-announces-capital-group-will-establish-major-operations-hub-charlotte ; https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs and wage both now stated)</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>Software/Data/AI Engineering, Investment Ops, GBS</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W13" s="6" t="inlineStr">
+        <is>
+          <t>Highest confirmed avg wage in the report ($194,141); strongly supports luxury/high-end housing demand in Uptown/South End.</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>Wage upgraded from Estimated/Inferred to stated this week via JDIG filing; score raised from 78 to 81.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project — unchanged</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total; +100 in-window, +1,500 construction)</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B (doubled from ~$700M)</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Operational by 2029</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median.</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this week; steady.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking; hiring delayed 1 year)</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking + confirmed hiring-timeline delay</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025 selection)</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking 2026-06-15; hiring target extended from 2026-12-31 to 2027-12-31 amid state-budget holdup; $133.9M state infrastructure allocation ~2026-06-30</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project ; https://www.carolinajournal.com/jetzero-delays-hiring-timeline-amid-budget-holdup/ ; https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>Still potentially transformational long-term but push demand curve back ~1 year; model 2028+ for meaningful Guilford Co. absorption.</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>Score lowered from 82 to 74 on confirmed 1-year hiring delay (project-certainty discount).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Ballantyne (South Charlotte)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup / Citi — office grand opening</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Material in-window milestone: grand opening of previously announced office</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>State JDIG &gt;$8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Original announcement 2025-07-08 (out of window); grand opening 2026-03-16; investment completion targeted by 2027-12-31</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/16/governor-stein-celebrates-grand-opening-citi-charlotte-office ; https://www.bankingdive.com/news/citi-opening-charlotte-office-510-jobs-north-carolina/752586/</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Finance, Risk Mgmt, Compliance, Private Bank Wealth Mgmt</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
+          <t>Solid Ballantyne/south Charlotte rental and starter-home demand from ~$132K-avg finance roles.</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Excluded last week on the reasoning that a grand opening 'tied to a prior-year commitment' wasn't a new award; included this week for consistency with how Scout Motors/JetZero/Genentech milestones were already treated.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2173,7 +3511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3368,6 +4706,1618 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred ~$89K blended (sub-$100K)</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Still under 500 jobs; wage inferred sub-$100k</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-06/usa-rare-earth-inc-selects-cherokee-county-first-south-carolina-operation</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co.</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Suniva — solar-cell plant</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred $55K-$80K production/technician, up to ~$117.9K senior eng.</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>500+ but wage still not disclosed/inferred sub-$100k blended</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-04/suniva-inc-selects-laurens-county-first-south-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500 white-collar HQ; no update this week</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy — new mfg + corporate site</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; workforce-tier</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>500+ but wage undisclosed, workforce-tier; county outside core SC list but tracked for continuity</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-04/ferrara-candy-company-selects-orangeburg-county-first-south-carolina-operation</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>High (facts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Boeing — 787 engineering relocation + production ramp</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>~300 (of 1,000 total 5-yr)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>$1.0B (base, pre-window)</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred eng. $100K-$150K+, mfg/mechanic $55K-$85K</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Base $1B/1,000-job project pre-window; in-window signal is ~300-role WA-to-SC eng relocation + confirmed production ramp (5 to 8 787s/mo)</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/ ; https://www.postandcourier.com/business/aerospace/boeing-charleston-sc-787-dreamliner-seattle-jobs/article_78c746b5-ae9d-4bdd-b12c-a811626108be.html</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>BMW Group — Plant Woodruff EV battery / iX5 completion</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>300 (2022-disclosed)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>$1.7B (total, incl. Plant Spartanburg)</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred production $46K-$62K, battery tech/eng $65K-$95K+</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Jobs count is old; in-window signal is 6/30/26 investment-completion milestone ahead of iX5 production</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.spartanburg.com/news/2026/07/bmw-group-completes-1-7-billion-investment-in-south-carolina-operations-premieres-all-new-bmw-x5-in-spartanburg-sc/</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Ridgeville / Camp Hall</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials — battery-materials recycling</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (target)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Operations began just pre-window (~Nov 2025); no distinct in-window headcount figure found</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>2025-11 (pre-window; flagged)</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.redwoodmaterials.com/news/redwood-begins-critical-materials-recovery-in-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Lake Wylie</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>QTS 'Project Cobra' — data-center campus</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>12 direct</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Up to $1B (phased)</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>N/A — only 12 direct jobs disclosed</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Massive capex, minimal disclosed jobs; in-window milestone is a zoning-ordinance overhaul</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/qts-to-build-data-center-in-york-county-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Still pre-window (2025-10-13); no in-window construction/hiring milestone located</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/google-to-invest-9billion-dollars-in-south-carolina-data-center-expansion/101-6999f41c-efd3-4663-9bd1-c18414f7efd0</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>High (capex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>$165M (Carolinas-wide)</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; no update this week</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Pickens</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>FN America — 2nd production facility</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>~176</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>$33M</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; no 2026 update found</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / Palmetto Research Park</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Novant Health — new medical campus</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>$300M</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; on the same 209-acre tract as Octapharma (Ranked #2)</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/06/09/rock-hill-approves-300m-development-failed-panthers-site/</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Uptown Charlotte</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Life — interim office opening</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>300-301</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>$12.3M</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>$176,250 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500 (prior-tracked); interim office opened early 2026 ahead of 2028 permanent move</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2025/10/28/governor-stein-announces-301-new-jobs-insurance-giant-pacific-life-selects-charlotte</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>SouthPark (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — consolidated office</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>400 new (site total 1,000)</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; likely $100k+ (commercial/investment banking)</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; wage not disclosed</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Coinbase — office + hiring commitment</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>130+</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred $101K-$250K (job-board data)</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Well sub-500; exact announcement date unconfirmed</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>2026 (unconfirmed)</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>https://cointelegraph.com/news/coinbase-expands-charlotte-hiring-130-employees-fintech-growth</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>North Hills (Raleigh)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant — global HQ</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>$170,531-$189,479 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Well sub-500; exceptional wage; HQ opened March 2026 (in-window milestone)</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260305697057/en/Ralliant-Opens-Global-Headquarters-in-Raleigh-North-Carolina</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred ~$87K (sub-$100K)</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>In-window but split across 3 metros, no single 500+ site</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Knightdale / Wendell</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred ~$72,617 avg (sub-$100K)</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; wage now more specifically estimated</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; no 2026 update found</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.areadevelopment.com/newsitems/4-14-2026/lumentum-greensboro-north-carolina.shtml</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; solid WNC signal</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; recruiting confirmed launched 4/16/26</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; no 2026 update found</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>https://myfox8.com/news/north-carolina/piedmont-triad/john-deere-factory-bringing-150-jobs-to-piedmont-triad/</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / Asheville / Durham</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover, Buncombe, Durham</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>GE Aerospace — 4-community equipment/capacity upgrade</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Mostly not disclosed</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>$163M (NC total)</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Capex confirmed at existing sites in 3 of 4 subregions; jobs largely undisclosed</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/ge-aerospace-investing-163-million-across-four-nc-communities/</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Salisbury</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>'Project Rack' — distribution facility (company undisclosed)</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>~$41M</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred sub-$100K entry-level distribution</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; company identity confidential</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.salisburypost.com/2026/06/06/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed real via 6/29/26 public-hearing milestone; outside core priority-county list but retained for continuity</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/energy-environment/2026-06-29/public-hearing-planned-for-amazon-and-duke-energy-data-center-project-in-richmond-county</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (52 projects)</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Aggregate pipeline; no single new project crystallized to 500+</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3379,7 +6329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3509,7 +6459,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Pre-window (&gt;6 mo back); June 2026 was groundbreaking follow-up</t>
+          <t>Pre-window (&gt;6 mo back); June 2026 item was groundbreaking follow-up</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -4185,6 +7135,1896 @@
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TigerDC 'Project Spero'</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>WITHDRAWN — county council denied incentive; company pulled the $3B project. Was in prior-week Watch list; removed this week.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/news/spartanburg-project-spero-data-center-withdrawn/article_bfb9e61e-2282-4d22-9806-7aa4a934be27.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>VinFast</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Co. (Moncure)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>7,500 orig. -&gt; ~1,400</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>State of NC sued VinFast over missed construction/hiring deadlines; hiring plan cut ~82%. Negative/contraction signal, not a growth item.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/raleigh/2026/05/21/north-carolina-sues-vinfast-to-take-back-control-of-chatham-county-land</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro (Guilford)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>500 req. by 12/31/26 vs 1,761 orig.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2026 (ongoing)</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Facility idle since 2024 ribbon-cutting; zero aircraft produced; at risk of lease default, not growing.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>SAS Institute</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Cary (Wake)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>-300</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>LAYOFF — excluded per rules</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/technology/sas-cuts-300-jobs-across-the-company-june-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Maersk</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; update this week is a confirmed 1-yr hiring-ramp delay (2027-2029 vs 2026-2028) — negative momentum on an already-excluded item.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sedc.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (original announcement)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Durham/Morrisville</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; superseded this week by the 2026-04-30 '7th facility' update, now in Ranked table.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/novartis-expand-us-manufacturing-footprint-durham-and-wake-counties-adding-700-jobs-771-million</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window (&gt;6 mo back); no in-window update found</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/financial-services-company-expand-durham-headquarters-1000-new-jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Benson (Johnston)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; training-program milestone undated, could not confirm in-window date</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>https://vulcanelements.com/vulcan-elements-selects-benson-north-carolina-for-1-billion-magnet-facility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Life (original announcement)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; now tracked via Watch (interim office milestone) instead</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2025/10/28/governor-stein-announces-301-new-jobs-insurance-giant-pacific-life-selects-charlotte</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Boeing (base $1B/1,000-job commitment)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window groundbreaking; now tracked via Watch (eng. relocation + production ramp) instead</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>https://boeing.mediaroom.com/2025-11-07-Boeing-South-Carolina-Breaks-Ground-on-787-Site-Expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Salisbury (Rowan)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>1,181</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; wage $62K (&lt;$100K)</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/30/jabil-selects-rowan-county-nearly-1200-new-jobs-and-500-million-multi-year-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Charlotte HQ</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (Plaza Midwood)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window (separate project from the Blythewood, SC plant); no in-window milestone found — recommend rechecking for a 2026 groundbreaking/hiring start.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2025/11/12/governor-stein-announces-a-new-headquarters-for-scout-motors-creating-1200-jobs-in-mecklenburg-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery NC</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Liberty (Randolph)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>5,100 cum.</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>2021-2023 / GO 2025-11-12</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Out of window; ~$20.77/hr median</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>https://abc11.com/post/toyota-nc-plant-investing-139-billion-creating-5100-jobs-randolph-county-north-carolina/18148348/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>BuildOps</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh (Wake)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window + sub-500</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/24/governor-stein-announces-software-company-buildops-will-create-291-jobs-raleigh</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>AvidXchange</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>1,229</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>2018-12-18</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2018 news re-surfacing in 2026 search indexes</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/governor-cooper-announces-1229-new-jobs-avidxchange-expands-mecklenburg-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (Morrisville)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>2019-12-17</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2019 news</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/microsoft-create-500-new-jobs-wake-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>RTP (Wake)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>2012-07-23</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2012 news; also sub-500</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/netapp-create-460-jobs-wake-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Honda Aircraft</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro (Guilford)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>280 / 419</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news; no 2026 update</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2023/07/11/governor-cooper-announces-honda-aircraft-company-will-create-280-jobs-major-greensboro-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>DEHN Inc.</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Mooresville (Iredell)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Recycled; sub-500 + $66,120 wage (&lt;$100K)</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2024/01/23/german-electrical-engineering-and-manufacturing-company-selects-iredell-county-us-headquarters-and</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Red Bull / Rauch</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Concord (Cabarrus)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>2021-07/08</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2021 news; ~$50K wage</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>https://edpnc.com/news/red-bull-and-rauch-to-build-a-multimillion-dollar-beverage-manufacturing-hub/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Kroger fulfillment center</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Concord (Cabarrus)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2021 news; low-wage logistics</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2021/12/08/governor-cooper-announces-kroger-will-build-high-tech-customer-fulfillment-center-cabarrus-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>RTP (Wake)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2023 news</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>https://news.biobuzz.io/2025/07/16/eli-lilly-invests-450-million-to-expand-rtp-manufacturing-site/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Apple RTP campus</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>RTP (Wake)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Recycled/stale; project reported paused since 2024, no 2026 reactivation found</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>https://abc11.com/post/apple-nc-east-coast-hub-on-hold-research-triangle-park-3-years-later-1-billion-project/14997218/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Pallidus</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill (York)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>2023-02-07</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news; also sub-500</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sccommerce.com/news/pallidus-relocating-corporate-headquarters-and-manufacturing-operations-york-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>IKO Industries</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co.</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>180-200</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news; sub-500</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2023-02/iko-establishing-south-carolina-operations-chester-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Live Oak Bank</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington (New Hanover)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2022 news; sub-500</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2022/09/07/live-oak-bank-add-200-new-jobs-new-hanover-county-25-million-expansion-wilmington</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Vantaca</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover Co.</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news; well sub-500</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>FIT Precast</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Gastonia (Gaston)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Wage would qualify (~$102K) but job count far below the 500 threshold</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/114420-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Walmart fulfillment center</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Kings Mountain (Gaston)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; date/wage not independently source-verified this cycle</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Textum OPCO LLC</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>McAdenville (Gaston)</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Far below threshold</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Snider Fleet Solutions</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Indian Land (Lancaster)</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; dormant since 2023, no 2026 update found (prior-tracked, explicitly rechecked)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2023-05/snider-fleet-solutions-relocating-headquarters-lancaster-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Corvid Technologies</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Mooresville (Iredell)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2018 news; possible undated 2026 ribbon-cutting — recommend rechecking</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>https://patch.com/north-carolina/mooresville/corvid-bring-367-jobs-headquarters-mooresville</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Albemarle Corp.</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co.</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>300+</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>2021/2023</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; wage ~$93K just under $100K; could not verify a 2026 production-start milestone</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/albemarle-picks-s-c-for-lithium-plant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Movement Mortgage</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Indian Land (Lancaster)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Vague commentary, no numbers, no credible dedicated 2026 source</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Red Ventures</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Indian Land / Fort Mill (Lancaster)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; date not independently verified</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sccommerce.com/news/red-ventures-expanding-lancaster-county-headquarters-adding-200-jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>NACA (Neighborhood Assistance Corp of America)</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (Mecklenburg)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>1,014</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Source URL returned HTTP 403 repeatedly; date could not be verified; likely sub-$100K counselor/processor roles</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/mecklenburg-county-finance-service-center-add-1014-jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>HII / Newport News Shipbuilding</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek (Berkeley)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds (n/d)</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Vague, no hard job number disclosed</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Wilson Co.</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Real &amp; in-window but Wilson County is outside this report's priority-county list; flagged for awareness only</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/01/09/governor-stein-announces-johnson-johnson-will-build-second-major-facility-wilson-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Envision AESC</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Florence Co.</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>~1,600</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed 2026</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Feeds BMW Spartanburg supply chain but Florence Co. is outside the Upstate/Midlands/Lowcountry scope list</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtw.com/growthtracker/aesc-restarts-clock-on-construction-of-1-6b-florence-plant-after-six-month-hiatus/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Goodyear plant</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Fayetteville (Cumberland)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>LAYOFF/CLOSURE (excluded per rules)</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/fayetteville-cumberland-industrial-jobs-may-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co. data center moratorium</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co.</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Policy action, not a jobs announcement; logged for regional context</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/06/19/york-county-discusses-project-palmetto-rock-chester-county-data-center-moratorium-rock-hill-juneteenth-celebration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Silfab Solar</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Fort Mill (York)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Wage ~$60-79K (&lt;$100K); in-window legal milestone (2026-01-26 court dismissal) doesn't change the wage disqualifier</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>https://pv-magazine-usa.com/2026/01/26/south-carolina-county-court-dismisses-challenge-to-silfab-solar-manufacturing-facility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>E&amp;J Gallo Winery</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co.</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>~496</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Old project; recent items are facility recognition only</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2021-06/e-j-gallo-winery-establishing-new-east-coast-facility-chester-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Apple / JPMorgan / BofA / Truist branches</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>No specific qualifying job count; branch-network/speculative commentary</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Wake Forest Innovation Quarter Phase II</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Winston-Salem (Forsyth)</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>General district growth; no single named-company 500+ job announcement</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -4201,7 +9041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4261,7 +9101,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>SMBC, AbbVie, JetZero, BorgWarner (stated wages + JDIG)</t>
+          <t>SMBC, AbbVie, JetZero, BorgWarner, Novartis, J&amp;J (stated wages + JDIG)</t>
         </is>
       </c>
     </row>
@@ -4288,7 +9128,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>SMBC, Capital Group, JetZero</t>
+          <t>SMBC, Capital Group, JetZero, Citigroup</t>
         </is>
       </c>
     </row>
@@ -4430,34 +9270,34 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Trade &amp; Industry Dev / Carolina Journal</t>
+          <t>GlobeNewswire / Novartis press</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>company_primary</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradeandindustrydev.com/</t>
+          <t>https://www.globenewswire.com/</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>NC/SC</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Siemens Energy $421M/500-job NC expansion (Feb 2026)</t>
+          <t>Novartis 7th-facility / Morrisville API announcement (Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>WRAL / WRAL TechWire</t>
+          <t>Trade &amp; Industry Dev / Carolina Journal</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -4467,24 +9307,24 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/</t>
+          <t>https://www.tradeandindustrydev.com/</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>NC Triangle</t>
+          <t>NC/SC</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>AbbVie salary/incentive detail</t>
+          <t>Siemens Energy $421M/500-job NC expansion (Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>WIS / WLTX (Columbia)</t>
+          <t>Carolina Journal</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -4494,24 +9334,24 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>https://www.wistv.com/</t>
+          <t>https://www.carolinajournal.com/</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>SC Midlands</t>
+          <t>NC statewide</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors hiring milestone, wages</t>
+          <t>JetZero hiring-timeline delay, state budget allocation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Charlotte Business Journal / Axios Charlotte</t>
+          <t>WRAL / WRAL TechWire</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -4521,24 +9361,24 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>https://charlotte.axios.com/</t>
+          <t>https://www.wral.com/</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Charlotte metro</t>
+          <t>NC Triangle</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Capital Group corroboration</t>
+          <t>AbbVie salary/incentive detail, Novartis, SAS layoffs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Area Development</t>
+          <t>WIS / WLTX (Columbia)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -4548,24 +9388,24 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>https://www.areadevelopment.com/</t>
+          <t>https://www.wistv.com/</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>National site-selection</t>
+          <t>SC Midlands</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Scout Motors hiring milestone, wages</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Post &amp; Courier</t>
+          <t>Charlotte Business Journal / Axios Charlotte</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -4575,152 +9415,476 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/</t>
+          <t>https://www.axios.com/local/charlotte/</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>SC statewide</t>
+          <t>Charlotte metro</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>QTS York County</t>
+          <t>SMBC lease, Capital Group, JPMorgan SouthPark</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Asheville Chamber</t>
+          <t>CRE News</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>regional_edo</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>https://www.ashevillechamber.org/</t>
+          <t>https://crenews.com/</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Buncombe NC</t>
+          <t>Charlotte CRE</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Eaton expansion</t>
+          <t>Capital Group lease at One Independence Center</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Charlotte Regional Business Alliance</t>
+          <t>Banking Dive</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>regional_edo</t>
+          <t>trade_journal</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>https://charlotteregion.com/</t>
+          <t>https://www.bankingdive.com/</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>CLT 15-county bi-state</t>
+          <t>National banking</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>IKO/Chester cross-check</t>
+          <t>Citigroup Charlotte office opening</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>York County Economic Development</t>
+          <t>Area Development</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>regional_edo</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>https://www.yorkcountyed.com/</t>
+          <t>https://www.areadevelopment.com/</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>York Co. SC</t>
+          <t>National site-selection</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Pallidus (excluded)</t>
+          <t>Lumentum, Octapharma</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Upstate SC Alliance / Fox Carolina</t>
+          <t>Post &amp; Courier</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>regional_edo/journal</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>https://www.upstatescalliance.com/</t>
+          <t>https://www.postandcourier.com/</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Upstate SC</t>
+          <t>SC statewide</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Siemens Smart Infra</t>
+          <t>QTS York County, Octapharma, Boeing, TigerDC withdrawal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>WRHI (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>regional_journal</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrhi.com/</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>York Co., SC</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma public identification, York County Council votes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>WBTV / QC News</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte metro / Rock Hill</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Novant Health Rock Hill, Chester Co. moratorium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>SC statewide</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Boeing Charleston momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>DataCenterDynamics</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>National data centers</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>QTS York Co., TigerDC withdrawal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg.com / Greenville.com</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.spartanburg.com/</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Upstate SC</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>BMW Group investment-completion milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>BusinessWire</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>wire_service</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant Raleigh HQ opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Salisbury Post</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.salisburypost.com/</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Rowan Co., NC</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>'Project Rack' distribution facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>WFAE</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>public_radio</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / NC</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>AWS Hamlet public hearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Asheville Chamber</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>regional_edo</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe NC</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Eaton expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte Regional Business Alliance</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>regional_edo</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>https://charlotteregion.com/</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>CLT 15-county bi-state</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>IKO/Chester cross-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>York County Economic Development</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>regional_edo</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.yorkcountyed.com/</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>York Co. SC</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Pallidus (excluded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Upstate SC Alliance / Fox Carolina</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>regional_edo/journal</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.upstatescalliance.com/</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Upstate SC</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infra</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>Business NC</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>https://businessnc.com/</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>NC statewide</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Siemens Energy (excluded, pre-window)</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy, GE Aerospace, Albemarle, FIT Precast</t>
         </is>
       </c>
     </row>
@@ -4735,7 +9899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4816,7 +9980,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Capex size + lock-in (incentive-backed, under construction)</t>
+          <t>Capex size + lock-in (incentive-backed, under construction, leased); confirmed delays discount this factor</t>
         </is>
       </c>
     </row>
@@ -4846,7 +10010,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Reinforcement of a market across reports (baseline = low)</t>
+          <t>Reinforcement of a market across reports; confirmed milestones (leases, groundbreakings) score higher than static repeats</t>
         </is>
       </c>
     </row>
@@ -4892,71 +10056,71 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>2,000 jobs + stated $165k + top-tier employer + urban Class-A fit; new (low momentum).</t>
+          <t>2,000 jobs + stated $165k + top-tier employer + urban Class-A fit; lease signed 5/4/26 raises project-certainty score from 92 to 94.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors (Blythewood)</t>
+          <t>Octapharma (Rock Hill)</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>4,000 jobs + $2B locked-in + active hiring; wage mixed/workforce-to-salaried.</t>
+          <t>1,552 total jobs + two stated wage bands ($141.5K/$102.8K) + $1.49B; discounted slightly for a not-yet-fully-finalized county vote.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AbbVie (Durham)</t>
+          <t>Scout Motors (Blythewood)</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>734 jobs + stated $118k + $1.4B top-pharma certainty; strong MF fit.</t>
+          <t>4,000 jobs + $2B locked-in + active hiring; wage mixed/workforce-to-salaried; unchanged from prior week.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>JetZero (Greensboro)</t>
+          <t>AbbVie (Durham)</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>14,500 jobs (max) + $4.7B; wage $89k (&lt;$100k) + budget/timeline execution risk discount.</t>
+          <t>734 jobs + stated $118k + $1.4B top-pharma certainty; strong MF fit; unchanged from prior week.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Genentech (Holly Springs)</t>
+          <t>Novartis (Durham/Wake)</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Site crosses 500 jobs + stated ~$120k + ~$2B (doubled) top-pharma certainty; in-window increment is +100, slight discount.</t>
+          <t>700+ jobs + newly stated $111,161 avg + ~$991M cumulative investment; new in-window 'seventh facility' milestone.</t>
         </is>
       </c>
     </row>
@@ -4967,11 +10131,56 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>600 jobs + inferred ~$190k (discounted vs stated) + urban fit; new.</t>
+          <t>600 jobs + now-stated $194,141 (highest in report) + signed lease; raised from 78 to 81 on wage confirmation + lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Site crosses 500 jobs + stated ~$120k + ~$2B (doubled) top-pharma certainty; unchanged from prior week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>14,500 jobs (max) + $4.7B; wage $89k (&lt;$100k) + CONFIRMED 1-year hiring delay discounts project certainty further (was 82, now 74).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup (Ballantyne)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>510 jobs + stated $131,832 + confirmed grand-opening milestone; added this week for consistency with how other milestone-based entries were scored.</t>
         </is>
       </c>
     </row>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -481,10 +481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-07-02  ·  Window 2026-01-02 to 2026-07-02  ·  NC + SC</t>
+          <t>Week of 2026-07-06  ·  Window 2026-01-06 to 2026-07-06  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02  (Week 2)</t>
+          <t>2026-07-06  (Week 2)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-01-02 to 2026-07-02  (trailing 6 months)</t>
+          <t>2026-01-06 to 2026-07-06  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -553,148 +553,124 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Qualifying (ranked) deals — this week</t>
+          <t>Qualifying (ranked) deals this week</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qualifying (ranked) deals — cumulative (all weeks)</t>
+          <t>Qualifying (ranked) deals — cumulative</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Markets to Watch — this week</t>
+          <t>Markets to Watch this week</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Markets to Watch — cumulative (all weeks)</t>
+          <t>Excluded / Noise this week</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Excluded / Noise — this week</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Excluded / Noise — cumulative (all weeks)</t>
+          <t>Top market</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 93</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Top new market</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 88</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Top market</t>
+          <t>Key takeaway</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 94</t>
+          <t>Octapharma is the first SC deal in this dataset with two stated six-figure wage tiers; SMBC/Scout/Capital Group all cleared real occupancy/production milestones; JetZero is a mixed signal (funding secured, hiring delayed a year); Boom Supersonic flagged as a downside risk.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Top new find</t>
+          <t>Window note</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / Palmetto Research Park (York, SC) — Octapharma, score 90 (NEW)</t>
+          <t>Trailing 6 months now runs 2026-01-06 to 2026-07-06. Novartis (Durham/Morrisville) re-enters scope via an in-window investment-increase milestone despite its original announcement predating the window.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Key takeaway</t>
+          <t>Data-quality note</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Octapharma's $1.49B Rock Hill campus is the largest find since this report began; Charlotte's SMBC/Capital Group/Citigroup all converted from announced to leased/open this week; Novartis graduates into Ranked via a new April facility phase; JetZero's hiring ramp is confirmed delayed a year.</t>
+          <t>Several primary state press-release domains returned HTTP 403 to direct fetch this cycle; facts corroborated against 2+ independent secondary outlets where that occurred. Two unverifiable claims (Barclays, Energizer) found only on non-authoritative blogs were excluded rather than reported.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Window note</t>
+          <t>Week-over-week</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Window rolled forward to 2026-01-02 - 2026-07-02; all 6 baseline (2026-06-24) Ranked entries remain in scope, none rolled out of window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Data-quality note</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>NC deals carry stated wages; SC deals mostly do not, except Octapharma this week (two stated wage bands from its incentive filing). WebFetch (direct page fetch) returned HTTP 403 on all tested domains this week — findings rest on WebSearch-surfaced content and verified URLs rather than a second-pass raw fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Week-over-week</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>3 New (Octapharma, Novartis, Citigroup), 2 Updated (Capital Group wage/lease, JetZero delay), 1 Gaining Momentum (SMBC lease), 3 Repeated (Scout Motors, AbbVie, Genentech), 1 Removed from Watch (TigerDC Project Spero, withdrawn).</t>
+          <t>6 of 6 baseline-ranked deals remain qualifying (none removed); 3 gaining momentum, 2 repeated, 1 mixed-update; 2 new entries (Octapharma, Novartis).</t>
         </is>
       </c>
     </row>
@@ -709,892 +685,1398 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
+          <t>report_date</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>market_submarket</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>county</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>company_project</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>job_count</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>job_type</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>salary_wage_stated</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>salary_inferred</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>capital_investment</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>incentives</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>announcement_type</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>source_date</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>urban_suburban_rural</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>housing_demand_implication</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Charlotte / Uptown</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Mecklenburg</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>SMBC Group — 2nd US HQ / bank operations (lease signed)</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Office / HQ banking</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>$165,316 avg (stated; unchanged)</t>
-        </is>
-      </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
           <t>N/A — stated</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>$50.5M</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>Ops expansion + lease-signing milestone</t>
-        </is>
-      </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
+          <t>New office / HQ-tier ops expansion</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/04/07/governor-stein-announces-2000-new-jobs-japans-smbc-group-selects-charlotte-bank-operations-expansion</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (hiring ramp)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Hiring ramp + training-center milestone</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>High (project/milestone); Med (wage)</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025 selection)</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking of megaproject</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (timeline)</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>Transformational long-term: multi-yr construction then 14,500 jobs; broad rental + for-sale across Guilford + Randolph/Alamance commuter shed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B (doubled from ~$700M)</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median. Near-term 1,500+ construction workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred ~$190k (from ~$116M payroll / 600 jobs; roles all $100k+ in CLT)</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/26/governor-stein-announces-capital-group-will-establish-major-operations-hub-charlotte</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Med (wage)</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/04/07/governor-stein-announces-2000-new-jobs-japans-smbc-group-selects-charlotte-bank-operations-expansion ; https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth. Lease signing de-risks timeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Rock Hill / Palmetto Research Park</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="C9" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>York</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Octapharma — new US HQ/lab + manufacturing campus (Project Palmetto Rock)</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1552</v>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Biopharma HQ/lab + manufacturing</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>$141,502 avg HQ/lab (564 jobs, stated) / $102,752 avg mfg (688 jobs, stated)</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>N/A — stated</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>$1.49B ($190M HQ/lab + $1.29B mfg)</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Fee-in-lieu of ad valorem tax; special source revenue credits; multi-county park designation</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>New HQ + manufacturing campus</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; City of Rock Hill forgoes its share; Rock Hill Schools share cut to 31.9%</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>New US HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wrhi.com/2026/06/global-biopharmaceutical-company-eyes-rock-hill-site-for-1-5-billion-facility-and-1252-jobs-213471 ; https://www.wrhi.com/2026/06/york-county-council-passes-second-reading-of-1-5-billion-biopharma-deal-data-center-moratorium-213788 ; https://www.postandcourier.com/york-county/news/rock-hill-plasma-panthers-octapharma-billion/article_fbd570b1-6451-406b-bb8c-92a53fad0d7c.html</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>High (facts); Med (final commitment)</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>Suburban / urban-adjacent</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>Largest find of the cycle; blended $103K-$141.5K wages support strong Class-A rental + for-sale demand in Rock Hill/York Co.; 300 relocating Charlotte staff imply cross-border household movement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/rock-hill-plasma-panthers-octapharma-billion/article_fbd570b1-6451-406b-bb8c-92a53fad0d7c.html</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (deal certainty)</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>85</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C10" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Blythewood / N. Columbia</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Richland</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Scout Motors — EV assembly plant (hiring ramp)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n">
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (production milestone)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Auto mfg + salaried eng.</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>$30-$37.50/hr line (stated, news); salaried higher</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Estimated/Inferred mix supports above-median HH income</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>$2.0B (+$25M training center)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>State/local package (2023); $25M readySC</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Hiring ramp + training-center milestone (unchanged from prior week)</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>High (project/milestone); Med (wage)</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>First vehicle body welded / production ramp</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/june-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>Suburban</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="S10" s="6" t="inlineStr">
         <is>
           <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="C11" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Durham / RTP</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Durham</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>AbbVie — biopharma manufacturing campus</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>734</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Adv. mfg / R&amp;D / lab</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>$118,041 avg (stated; vs county $102,817)</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>N/A — stated</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>$1.4B</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>New facility (greenfield, 185 ac) — unchanged</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Suburban-urban</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Durham / Wake (Morrisville)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C12" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (funding secured; hiring delayed)</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025 selection)</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr; NEW: $133.9M state budget infrastructure allocation</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>State infrastructure funding + hiring-timeline revision</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale, but push absorption modeling out ~12 months to 2028-2029.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B (doubled from ~$700M)</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub (lease signed)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred ~$190k (from ~$116M payroll / 600 jobs; roles all $100k+ in CLT)</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Med (wage)</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Durham &amp; Wake</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Novartis — 7th US facility / Morrisville API manufacturing building</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API manufacturing building (investment increase)</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>700</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Biologics/API mfg + R&amp;D</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>$111,161 avg (stated; exceeds Durham $97,531 and Wake $76,643 avgs)</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Lab/manufacturing/API production</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated; exceeds Durham avg $97,531 and Wake avg $76,643)</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>N/A — stated</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>~$991M cumulative ($771M orig. + $220M new API bldg)</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>JDIG up to $7.56M / 12 yr (original award)</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>New phase — additional facility as part of $23B national plan</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. new $220M)</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>Investment increase on existing 700-job project</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>https://www.globenewswire.com/news-release/2026/04/30/3284676/0/en/Novartis-finalizes-US-manufacturing-and-R-D-expansion-plan-with-seventh-new-facility.html ; https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>Suburban</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>$111K avg wage across 700+ jobs reinforces Durham/Wake as the report's deepest life-sciences cluster alongside AbbVie and Genentech.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>81</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Mecklenburg</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Capital Group — East Coast operations hub (lease signed; wage confirmed)</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Software/Data/AI Engineering, Investment Ops, GBS</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>$194,141 avg (stated, per JDIG filing — newly confirmed)</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>N/A — now stated (was Estimated/Inferred ~$190k last week)</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>$60M</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>JDIG up to $17.17M / 12 yr; ~$1M local incentive</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>New facility / operations hub + lease-signing milestone</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/03/26/governor-stein-announces-capital-group-will-establish-major-operations-hub-charlotte ; https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>High (jobs and wage both now stated)</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Highest confirmed avg wage in the report ($194,141); strongly supports luxury/high-end housing demand in Uptown/South End.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Holly Springs / SW Wake</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Wake</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Adv. biomanufacturing</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>~$2.0B (doubled from ~$700M)</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>Expansion of committed project — unchanged</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Greensboro / PTI Airport</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Guilford</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>JetZero — aerospace plant (groundbreaking; hiring delayed 1 year)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Aerospace mfg + eng.</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>$89,340 avg (stated, 2025 selection)</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated (2025)</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>$4.7B</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Groundbreaking + confirmed hiring-timeline delay</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project ; https://www.carolinajournal.com/jetzero-delays-hiring-timeline-amid-budget-holdup/ ; https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>High (facts); Low (timeline)</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>Still potentially transformational long-term but push demand curve back ~1 year; model 2028+ for meaningful Guilford Co. absorption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Ballantyne (South Charlotte)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Mecklenburg</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Citigroup / Citi — office grand opening</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Finance, Risk Mgmt, Compliance, Private Bank Wealth Mgmt</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>$131,832 avg (stated)</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>$16.1M</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>State JDIG &gt;$8.9M / 10 yr</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>Material in-window milestone: grand opening of previously announced office</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/03/16/governor-stein-celebrates-grand-opening-citi-charlotte-office ; https://www.bankingdive.com/news/citi-opening-charlotte-office-510-jobs-north-carolina/752586/</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>Solid Ballantyne/south Charlotte rental and starter-home demand from ~$132K-avg finance roles.</t>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in the Wake/Durham corridor; supports continued upper-income housing absorption around Morrisville/RTP.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2459,7 +2941,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -2471,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -2490,7 +2972,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>SMBC Group — 2nd US HQ / bank operations (lease signed)</t>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -2500,7 +2982,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Ops expansion + lease-signing milestone</t>
+          <t>Lease signed / active hiring milestone</t>
         </is>
       </c>
       <c r="K8" s="6" t="n">
@@ -2513,7 +2995,7 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>$165,316 avg (stated; unchanged)</t>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
@@ -2533,7 +3015,7 @@
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>Lease signed 2026-05-04 (~200K SF, 301 S. College St); occupancy fall 2026; hiring 2028-2032</t>
+          <t>Leased former One Wells Fargo Center; hiring 70+ roles; first workers fall 2026</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -2543,7 +3025,7 @@
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/04/07/governor-stein-announces-2000-new-jobs-japans-smbc-group-selects-charlotte-bank-operations-expansion ; https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
@@ -2563,19 +3045,19 @@
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
-          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth. Lease signing de-risks timeline.</t>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
         </is>
       </c>
       <c r="X8" s="6" t="inlineStr">
         <is>
-          <t>Score raised from 92 to 94 on lease-signing certainty.</t>
+          <t>Real-estate + hiring milestone confirms April announcement is executing.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -2587,11 +3069,11 @@
         <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill / Palmetto Research Park</t>
+          <t>Rock Hill / York Co.</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2606,30 +3088,30 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — new US HQ/lab + manufacturing campus (Project Palmetto Rock)</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Biopharmaceutical / plasma manufacturing</t>
+          <t>Biopharmaceutical (plasma fractionation)</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>New HQ + manufacturing campus</t>
+          <t>New US HQ + manufacturing campus</t>
         </is>
       </c>
       <c r="K9" s="6" t="n">
-        <v>1552</v>
+        <v>1500</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Projected (1,252 new + 300 relocating from Charlotte)</t>
+          <t>Projected (1,200 new + 300 relocated)</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>$141,502 avg HQ/lab (564 jobs, stated) / $102,752 avg mfg (688 jobs, stated)</t>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -2639,17 +3121,17 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>$1.49B ($190M HQ/lab + $1.29B mfg)</t>
+          <t>$1.5B</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu of ad valorem tax; special source revenue credits; multi-county park designation</t>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; City of Rock Hill forgoes its share; Rock Hill Schools share cut to 31.9%</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>1st reading 2026-06-15 (7-0); 2nd reading 2026-06-29 (7-0); construction could start 2027; ~10-yr build-out</t>
+          <t>2nd reading approved 2026-06-29 (5-2); construction could start late 2026, build-out ~10 yrs</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -2659,51 +3141,51 @@
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrhi.com/2026/06/global-biopharmaceutical-company-eyes-rock-hill-site-for-1-5-billion-facility-and-1252-jobs-213471 ; https://www.wrhi.com/2026/06/york-county-council-passes-second-reading-of-1-5-billion-biopharma-deal-data-center-moratorium-213788 ; https://www.postandcourier.com/york-county/news/rock-hill-plasma-panthers-octapharma-billion/article_fbd570b1-6451-406b-bb8c-92a53fad0d7c.html</t>
+          <t>https://www.postandcourier.com/york-county/news/rock-hill-plasma-panthers-octapharma-billion/article_fbd570b1-6451-406b-bb8c-92a53fad0d7c.html</t>
         </is>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Med (final commitment)</t>
+          <t>High (facts); Med (deal certainty)</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
-          <t>Biopharma HQ/lab + manufacturing</t>
+          <t>Office/HQ + biopharma mfg</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>Suburban / urban-adjacent</t>
+          <t>Suburban</t>
         </is>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>Largest find of the cycle; blended $103K-$141.5K wages support strong Class-A rental + for-sale demand in Rock Hill/York Co.; 300 relocating Charlotte staff imply cross-border household movement.</t>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
         </is>
       </c>
       <c r="X9" s="6" t="inlineStr">
         <is>
-          <t>Site is the former Carolina Panthers HQ/practice facility at Palmetto Research Park; Novant Health separately building $300M medical campus on adjacent 25 acres of same tract (see Watch).</t>
+          <t>First SC deal in this dataset with two stated six-figure wage tiers. Tax-share amendment is a real execution risk flagged by local press.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>Gaining Momentum</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -2722,7 +3204,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (hiring ramp)</t>
+          <t>Scout Motors — EV assembly plant (production milestone)</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -2732,7 +3214,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Hiring ramp + training-center milestone (unchanged from prior week)</t>
+          <t>First vehicle body welded / production ramp</t>
         </is>
       </c>
       <c r="K10" s="6" t="n">
@@ -2765,22 +3247,22 @@
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>Production targeted end-2026; 4,000 at full capacity ~2030-31</t>
+          <t>First Traveler body welded June 2026; production targeted end-2026</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
-          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
+          <t>https://blog.scoutmotors.com/june-2026-scout-motors-production-center-update/</t>
         </is>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>High (project/milestone); Med (wage)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -2800,14 +3282,14 @@
       </c>
       <c r="X10" s="6" t="inlineStr">
         <is>
-          <t>No new milestone found in this week's window; April 20 milestone remains valid within trailing 6-month window.</t>
+          <t>First-ever vehicle-body weld is a materially lower-risk milestone than training-center opening alone.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -2848,7 +3330,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>New facility (greenfield, 185 ac) — unchanged</t>
+          <t>New facility (greenfield, 185 ac)</t>
         </is>
       </c>
       <c r="K11" s="6" t="n">
@@ -2916,35 +3398,35 @@
       </c>
       <c r="X11" s="6" t="inlineStr">
         <is>
-          <t>No new milestone this week; steady.</t>
+          <t>No new in-window milestone found this cycle; project remains on track.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated (mixed)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Durham / Wake (Morrisville)</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Durham &amp; Wake</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -2954,70 +3436,70 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Novartis — 7th US facility / Morrisville API manufacturing building</t>
+          <t>JetZero — aerospace plant (funding secured; hiring delayed)</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Biopharmaceutical / life sciences mfg</t>
+          <t>Aerospace / advanced manufacturing</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>New phase — additional facility as part of $23B national plan</t>
+          <t>State infrastructure funding + hiring-timeline revision</t>
         </is>
       </c>
       <c r="K12" s="6" t="n">
-        <v>700</v>
+        <v>14500</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>Projected (280 Durham + 100 Wake + growing; total by end of 2030)</t>
+          <t>Projected</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>$111,161 avg (stated; exceeds Durham $97,531 and Wake $76,643 avgs)</t>
+          <t>$89,340 avg (stated, 2025 selection)</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>N/A — stated (2025)</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>~$991M cumulative ($771M orig. + $220M new API bldg)</t>
+          <t>$4.7B</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $7.56M / 12 yr (original award)</t>
+          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr; NEW: $133.9M state budget infrastructure allocation</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>Morrisville API site opens 2028</t>
+          <t>Hiring deadline pushed from 12/31/2026 to 12/31/2027; ramp now 2028-2029</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/04/30/3284676/0/en/Novartis-finalizes-US-manufacturing-and-R-D-expansion-plan-with-seventh-new-facility.html ; https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); Low (timeline)</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>Biologics/API mfg + R&amp;D</t>
+          <t>Aerospace mfg + eng.</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
@@ -3027,40 +3509,40 @@
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>$111K avg wage across 700+ jobs reinforces Durham/Wake as the report's deepest life-sciences cluster alongside AbbVie and Genentech.</t>
+          <t>Same long-run scale, but push absorption modeling out ~12 months to 2028-2029.</t>
         </is>
       </c>
       <c r="X12" s="6" t="inlineStr">
         <is>
-          <t>Original Nov 2025 announcement was pre-window/excluded last week; the April 30, 2026 'seventh facility' update (new building, new capital, first stated wage) is the qualifying in-window event.</t>
+          <t>Mixed signal: state funding is a positive, but company's own hiring deadline slipped a full year due to the same budget delay.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Repeated</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Holly Springs / SW Wake</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -3070,113 +3552,113 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Capital Group — East Coast operations hub (lease signed; wage confirmed)</t>
+          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Investment mgmt / finance + tech</t>
+          <t>Biopharma / life sciences mfg</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>New facility / operations hub + lease-signing milestone</t>
+          <t>Expansion of committed project</t>
         </is>
       </c>
       <c r="K13" s="6" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>Projected</t>
+          <t>Projected (site total; +100 in-window, +1,500 construction)</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>$194,141 avg (stated, per JDIG filing — newly confirmed)</t>
+          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>N/A — now stated (was Estimated/Inferred ~$190k last week)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>$60M</t>
+          <t>~$2.0B (doubled from ~$700M)</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $17.17M / 12 yr; ~$1M local incentive</t>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Lease signed 2026-05-22 (196,940 SF, One Independence Center); hiring begins 2027 over 5 yr; Hampton Roads VA office closing by end of 2027</t>
+          <t>Operational by 2029</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/03/26/governor-stein-announces-capital-group-will-establish-major-operations-hub-charlotte ; https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>High (jobs and wage both now stated)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>Software/Data/AI Engineering, Investment Ops, GBS</t>
+          <t>Adv. biomanufacturing</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Suburban</t>
         </is>
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>Highest confirmed avg wage in the report ($194,141); strongly supports luxury/high-end housing demand in Uptown/South End.</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median.</t>
         </is>
       </c>
       <c r="X13" s="6" t="inlineStr">
         <is>
-          <t>Wage upgraded from Estimated/Inferred to stated this week via JDIG filing; score raised from 78 to 81.</t>
+          <t>No new in-window milestone found this cycle beyond January investment-doubling story.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>Gaining Momentum</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs / SW Wake</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -3186,113 +3668,113 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Genentech — biomanufacturing expansion (investment doubled to ~$2B)</t>
+          <t>Capital Group — East Coast operations hub (lease signed)</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Biopharma / life sciences mfg</t>
+          <t>Investment mgmt / finance + tech</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Expansion of committed project — unchanged</t>
+          <t>New facility / operations hub</t>
         </is>
       </c>
       <c r="K14" s="6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>Projected (site total; +100 in-window, +1,500 construction)</t>
+          <t>Projected</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, original 2025 tranche; ~$120k, 56% above Wake avg)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>Estimated/Inferred ~$190k (from ~$116M payroll / 600 jobs; roles all $100k+ in CLT)</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B (doubled from ~$700M)</t>
+          <t>$60M</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $9.85M / 12 yr (original 420-job award; no new incentive on the +100)</t>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>Operational by 2029</t>
+          <t>Leased 196,940 sq ft at One Independence Center, Uptown</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (jobs); Med (wage)</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Office — finance/tech</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>Suburban</t>
+          <t>Urban-suburban</t>
         </is>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay); ~$120k wage well above county median.</t>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
         </is>
       </c>
       <c r="X14" s="6" t="inlineStr">
         <is>
-          <t>No new milestone this week; steady.</t>
+          <t>Large Uptown lease confirms the operations hub is real estate now, not just an announcement.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New (newly in-window)</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Durham / Morrisville</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Durham &amp; Wake</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -3302,70 +3784,70 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (groundbreaking; hiring delayed 1 year)</t>
+          <t>Novartis — API manufacturing building (investment increase)</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Aerospace / advanced manufacturing</t>
+          <t>Pharmaceutical / biologics &amp; small-molecule mfg</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking + confirmed hiring-timeline delay</t>
+          <t>Investment increase on existing 700-job project</t>
         </is>
       </c>
       <c r="K15" s="6" t="n">
-        <v>14500</v>
+        <v>700</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Projected</t>
+          <t>Confirmed (part of pre-window 2025-11-19 package)</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>$89,340 avg (stated, 2025 selection)</t>
+          <t>$111,161 avg (stated; exceeds Durham avg $97,531 and Wake avg $76,643)</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated (2025)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>$4.7B</t>
+          <t>~$991M (incl. new $220M)</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr</t>
+          <t>Part of original $771M package incentives</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking 2026-06-15; hiring target extended from 2026-12-31 to 2027-12-31 amid state-budget holdup; $133.9M state infrastructure allocation ~2026-06-30</t>
+          <t>New 56,200 sq ft API building announced 2026-04-30; facility opening 2027-2028</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project ; https://www.carolinajournal.com/jetzero-delays-hiring-timeline-amid-budget-holdup/ ; https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Low (timeline)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>Aerospace mfg + eng.</t>
+          <t>Lab/manufacturing/API production</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
@@ -3375,128 +3857,12 @@
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>Still potentially transformational long-term but push demand curve back ~1 year; model 2028+ for meaningful Guilford Co. absorption.</t>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in the Wake/Durham corridor; supports continued upper-income housing absorption around Morrisville/RTP.</t>
         </is>
       </c>
       <c r="X15" s="6" t="inlineStr">
         <is>
-          <t>Score lowered from 82 to 74 on confirmed 1-year hiring delay (project-certainty discount).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Ballantyne (South Charlotte)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Mecklenburg</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Citigroup / Citi — office grand opening</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Banking / financial services</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Material in-window milestone: grand opening of previously announced office</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>$131,832 avg (stated)</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>$16.1M</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>State JDIG &gt;$8.9M / 10 yr</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>Original announcement 2025-07-08 (out of window); grand opening 2026-03-16; investment completion targeted by 2027-12-31</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/03/16/governor-stein-celebrates-grand-opening-citi-charlotte-office ; https://www.bankingdive.com/news/citi-opening-charlotte-office-510-jobs-north-carolina/752586/</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>Finance, Risk Mgmt, Compliance, Private Bank Wealth Mgmt</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="W16" s="6" t="inlineStr">
-        <is>
-          <t>Solid Ballantyne/south Charlotte rental and starter-home demand from ~$132K-avg finance roles.</t>
-        </is>
-      </c>
-      <c r="X16" s="6" t="inlineStr">
-        <is>
-          <t>Excluded last week on the reasoning that a grand opening 'tied to a prior-year commitment' wasn't a new award; included this week for consistency with how Scout Motors/JetZero/Genentech milestones were already treated.</t>
+          <t>Excluded at baseline as pre-window (orig. 2025-11-19); this in-window investment-increase milestone brings it back into scope per report rules.</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4709,7 +5075,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -4744,12 +5110,12 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred ~$89K blended (sub-$100K)</t>
+          <t>$24.50-$63/hr (newly stated)</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>Still under 500 jobs; wage inferred sub-$100k</t>
+          <t>Still just under 500 jobs; wage newly disclosed this cycle</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -4759,29 +5125,29 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2026-06/usa-rare-earth-inc-selects-cherokee-county-first-south-carolina-operation</t>
+          <t>https://scdailygazette.com/2026/06/02/</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Laurens Co.</t>
+          <t>Orangeburg / I-26</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Orangeburg</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -4791,59 +5157,59 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Suniva — solar-cell plant</t>
+          <t>Ferrara Candy — groundbreaking held</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>1,000 (10 yr)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>$350M</t>
+          <t>$675M</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred $55K-$80K production/technician, up to ~$117.9K senior eng.</t>
+          <t>Not disclosed; confectionery = workforce-tier</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>500+ but wage still not disclosed/inferred sub-$100k blended</t>
+          <t>Groundbreaking held 2026-05-20; still fails high-income intent</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2026-04/suniva-inc-selects-laurens-county-first-south-carolina-manufacturing-facility</t>
+          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Columbia / BullStreet</t>
+          <t>Laurens Co.</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Richland</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -4853,59 +5219,59 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>AMAROK — new HQ (perimeter security)</t>
+          <t>Suniva — solar-cell plant</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>564</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>$69M</t>
+          <t>$350M</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Stated $23-$53/hr = workforce-tier</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Sub-500 white-collar HQ; no update this week</t>
+          <t>No update found this cycle; unchanged workforce-tier read</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+          <t>https://governor.sc.gov/news/2026-04/suniva-inc-selects-laurens-county-first-south-carolina-manufacturing-facility</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg / I-26</t>
+          <t>Columbia / BullStreet</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg</t>
+          <t>Richland</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -4915,431 +5281,431 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Ferrara Candy — new mfg + corporate site</t>
+          <t>AMAROK — new HQ (perimeter security)</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>1,000 (10 yr)</t>
+          <t>296</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>$675M</t>
+          <t>$69M</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; workforce-tier</t>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>500+ but wage undisclosed, workforce-tier; county outside core SC list but tracked for continuity</t>
+          <t>Richland County Council approved incentive package 2026-03-03</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2026-04/ferrara-candy-company-selects-orangeburg-county-first-south-carolina-operation</t>
+          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>High (facts)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Greensboro</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Boeing — 787 engineering relocation + production ramp</t>
+          <t>Lumentum — AI/data-center optics</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>~300 (of 1,000 total 5-yr)</t>
+          <t>~400</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>$1.0B (base, pre-window)</t>
+          <t>Hundreds of millions</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred eng. $100K-$150K+, mfg/mechanic $55K-$85K</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>Base $1B/1,000-job project pre-window; in-window signal is ~300-role WA-to-SC eng relocation + confirmed production ramp (5 to 8 787s/mo)</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/ ; https://www.postandcourier.com/business/aerospace/boeing-charleston-sc-787-dreamliner-seattle-jobs/article_78c746b5-ae9d-4bdd-b12c-a811626108be.html</t>
+          <t>https://www.areadevelopment.com/newsitems/4-14-2026/lumentum-greensboro-north-carolina.shtml</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Woodruff</t>
+          <t>Hendersonville</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>BMW Group — Plant Woodruff EV battery / iX5 completion</t>
+          <t>BorgWarner — vertical-integration expansion</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>300 (2022-disclosed)</t>
+          <t>378</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>$1.7B (total, incl. Plant Spartanburg)</t>
+          <t>$100M</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred production $46K-$62K, battery tech/eng $65K-$95K+</t>
+          <t>$67,047 avg (stated; below $100k)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Jobs count is old; in-window signal is 6/30/26 investment-completion milestone ahead of iX5 production</t>
+          <t>A 2026-05-27 follow-up mention was found but not corroborated with detail this cycle — recheck next report</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>https://www.spartanburg.com/news/2026/07/bmw-group-completes-1-7-billion-investment-in-south-carolina-operations-premieres-all-new-bmw-x5-in-spartanburg-sc/</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Ridgeville / Camp Hall</t>
+          <t>Asheville / Arden</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Berkeley</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Redwood Materials — battery-materials recycling</t>
+          <t>Eaton — Low Voltage Assembly expansion</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>1,500 (target)</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>$3.5B</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>'high-wage' but figure Not disclosed (Inferred mid-$60k-$80k)</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Operations began just pre-window (~Nov 2025); no distinct in-window headcount figure found</t>
+          <t>Confirmed as the 7th Helene-recovery manufacturer expansion (725+ cumulative jobs, $388M+ across 7 deals)</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>2025-11 (pre-window; flagged)</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>https://www.redwoodmaterials.com/news/redwood-begins-critical-materials-recovery-in-south-carolina/</t>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Low-Medium</t>
+          <t>High (jobs); Low (wage)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Lake Wylie</t>
+          <t>Charlotte / Raleigh / Rural Hall</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Multi</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>QTS 'Project Cobra' — data-center campus</t>
+          <t>Siemens Energy — $421M NC expansion</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>12 direct</t>
+          <t>500 (statewide)</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Up to $1B (phased)</t>
+          <t>$421M</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>N/A — only 12 direct jobs disclosed</t>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Massive capex, minimal disclosed jobs; in-window milestone is a zoning-ordinance overhaul</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/qts-to-build-data-center-in-york-county-south-carolina/</t>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High (totals); Low (wage/split)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Berkeley / Dorchester</t>
+          <t>Raleigh / Wendell / Knightdale</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Berkeley &amp; Dorchester</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Google — data-center expansion</t>
+          <t>Siemens AG — power devices for AI/data centers</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>$9B</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Still pre-window (2025-10-13); no in-window construction/hiring milestone located</t>
+          <t>Site detail confirmed: 100 Raleigh by YE2026, 50 new Wendell site, 200+ Wendell HQ by 2028</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/google-to-invest-9billion-dollars-in-south-carolina-data-center-expansion/101-6999f41c-efd3-4663-9bd1-c18414f7efd0</t>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>High (capex)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Kernersville</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Forsyth</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Siemens Smart Infrastructure</t>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>~150</t>
+          <t>150+</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>$165M (Carolinas-wide)</t>
+          <t>$70M</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; no update this week</t>
+          <t>Re-confirmed Jan 2026 w/ White House mention; construction later 2026, production 2030</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+          <t>https://myfox8.com/news/north-carolina/piedmont-triad/john-deere-factory-bringing-150-jobs-to-piedmont-triad/</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Spartanburg Co.</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Pickens</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -5349,54 +5715,54 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>FN America — 2nd production facility</t>
+          <t>TigerDC 'Project Spero' — data center</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>~176</t>
+          <t>~50 FTE (Phase I)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>$33M</t>
+          <t>$3B</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$100,000 avg (newly stated)</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; no 2026 update found</t>
+          <t>Wage newly disclosed this cycle (~2x county avg)</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
+          <t>https://www.upstatescalliance.com/data-resources/media-center/</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med-High (capex/wage)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill / Palmetto Research Park</t>
+          <t>York Co.</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -5411,307 +5777,307 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Novant Health — new medical campus</t>
+          <t>QTS 'Project Cobra' — data-center campus</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>~200 FTE (+~1,000 constr.)</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>$300M</t>
+          <t>up to $8B</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$80k median (stated)</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; on the same 209-acre tract as Octapharma (Ranked #2)</t>
+          <t>Investment grown to ~$8B; June 2026 county moratorium discussion tied partly to this project</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>https://www.wbtv.com/2026/06/09/rock-hill-approves-300m-development-failed-panthers-site/</t>
+          <t>https://www.postandcourier.com/york-county/news/qts-data-center-york-clover-meeting/article_d3095fdb-8572-4510-9974-681459f18cd9.html</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med (capex figure varies by source)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Uptown Charlotte</t>
+          <t>Indian Land</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Pacific Life — interim office opening</t>
+          <t>Snider Fleet Solutions — corporate office relo</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>300-301</t>
+          <t>167</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>$12.3M</t>
+          <t>$6.9M</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>$176,250 avg (stated)</t>
+          <t>Not disclosed; corporate/HQ roles</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Sub-500 (prior-tracked); interim office opened early 2026 ahead of 2028 permanent move</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2025/10/28/governor-stein-announces-301-new-jobs-insurance-giant-pacific-life-selects-charlotte</t>
+          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>SouthPark (Charlotte)</t>
+          <t>Berkeley / Dorchester</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Berkeley &amp; Dorchester</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Chase — consolidated office</t>
+          <t>Google — data-center expansion</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>400 new (site total 1,000)</t>
+          <t>~160 apprentices (FTE n/d)</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed; likely $100k+ (commercial/investment banking)</t>
-        </is>
-      </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; wage not disclosed</t>
+          <t>No new in-window milestone found this cycle</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High (capex)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Pickens</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Coinbase — office + hiring commitment</t>
+          <t>FN America — 2nd production facility</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>130+</t>
+          <t>~176</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
+          <t>$33M</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>Estimated/Inferred $101K-$250K (job-board data)</t>
-        </is>
-      </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Well sub-500; exact announcement date unconfirmed</t>
+          <t>No 2026 milestone found; appears to have gone quiet — Losing Relevance</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>2026 (unconfirmed)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>https://cointelegraph.com/news/coinbase-expands-charlotte-hiring-130-employees-fintech-growth</t>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>Low-Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>North Hills (Raleigh)</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Ralliant — global HQ</t>
+          <t>Siemens Smart Infrastructure</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>~150</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>$2.1M</t>
+          <t>$165M</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>$170,531-$189,479 avg (stated)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Well sub-500; exceptional wage; HQ opened March 2026 (in-window milestone)</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260305697057/en/Ralliant-Opens-Global-Headquarters-in-Raleigh-North-Carolina</t>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / Raleigh / Rural Hall</t>
+          <t>Hamlet</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -5721,54 +6087,54 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Siemens Energy — $421M NC expansion</t>
+          <t>AWS/Amazon — AI/cloud campus</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>500 (statewide)</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>$421M</t>
+          <t>$10B</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred ~$87K (sub-$100K)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>In-window but split across 3 metros, no single 500+ site</t>
+          <t>Still unverified; needs direct confirmation</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+          <t>https://www.aboutamazon.com/</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low (needs verification)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Knightdale / Wendell</t>
+          <t>Wake Co. (aggregate)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5783,59 +6149,59 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Siemens AG — power devices for AI/data centers</t>
+          <t>County jobs pipeline (52 projects)</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>~11,000 (pipeline)</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>part of $165M</t>
+          <t>$11B</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred ~$72,617 avg (sub-$100K)</t>
+          <t>Mixed (office-skewed)</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; wage now more specifically estimated</t>
+          <t>A second, possibly overlapping aggregate figure (~30 projects/8,000 jobs/$5.6B) surfaced this cycle — flagged for reconciliation</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Greensboro</t>
+          <t>Charlotte / SouthPark</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -5845,59 +6211,59 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Lumentum — AI/data-center optics</t>
+          <t>JPMorgan Chase — new office (1,000-employee bldg)</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>~400</t>
+          <t>400 new by 2028</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Hundreds of millions</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$105k Estimated/Inferred (PayScale avg)</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; no 2026 update found</t>
+          <t>Sub-500 new jobs; wage inferred</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>https://www.areadevelopment.com/newsitems/4-14-2026/lumentum-greensboro-north-carolina.shtml</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorganchase-charlotte-hiring-workforce-banking-competition</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Hendersonville</t>
+          <t>Charlotte (CLT airport)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -5907,37 +6273,37 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>BorgWarner — vertical-integration expansion</t>
+          <t>Averitt — logistics campus</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>$100M</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>$67,047 avg (stated; below $100k)</t>
+          <t>$81,769 avg (stated)</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; solid WNC signal</t>
+          <t>Sub-500; wage below $100k</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+          <t>https://news.mecknc.gov/averitt-announces-major-new-commitment-mecklenburg-county</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -5949,17 +6315,17 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Asheville / Arden</t>
+          <t>Rowan County</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -5969,59 +6335,59 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Eaton — Low Voltage Assembly expansion</t>
+          <t>"Project Rack" (company undisclosed)</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$41M</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>'Above-average starting' Estimated/Inferred sub-$100k</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; recruiting confirmed launched 4/16/26</t>
+          <t>Sub-500; wage tier unclear; company undisclosed</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+          <t>https://www.salisburypost.com/2026/06/06/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Kernersville</t>
+          <t>Rowan / Kannapolis</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Forsyth</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -6031,59 +6397,59 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>John Deere — excavator plant</t>
+          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>150+</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>$70M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$55k-$150k range (DHL postings)</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; no 2026 update found</t>
+          <t>Jobs undisclosed; capex-heavy lease</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>https://myfox8.com/news/north-carolina/piedmont-triad/john-deere-factory-bringing-150-jobs-to-piedmont-triad/</t>
+          <t>https://www.wbtv.com/2026/04/29/google-leases-massive-facility-near-rowan-cabarrus-county-line/</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Wilmington / Asheville / Durham</t>
+          <t>Raleigh / North Hills</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>New Hanover, Buncombe, Durham</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -6093,59 +6459,59 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>GE Aerospace — 4-community equipment/capacity upgrade</t>
+          <t>Ralliant Corp. — global HQ launch</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Mostly not disclosed</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>$163M (NC total)</t>
+          <t>$2.1M</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$170k-$189k avg (stated)</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Capex confirmed at existing sites in 3 of 4 subregions; jobs largely undisclosed</t>
+          <t>Sub-500 but very high wage; HQ opened March 2026, active hiring ramp</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/ge-aerospace-investing-163-million-across-four-nc-communities/</t>
+          <t>https://www.wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Siler City</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -6155,59 +6521,59 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>'Project Rack' — distribution facility (company undisclosed)</t>
+          <t>Wolfspeed — silicon-carbide fab</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>1,800 (proj.)</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>~$41M</t>
+          <t>$5.0B</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred sub-$100K entry-level distribution</t>
+          <t>$77,753 avg (stated)</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; company identity confidential</t>
+          <t>500+ jobs but wage sub-$100k; full occupancy targeted March 2026, production June 2026, 200+ hired</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>https://www.salisburypost.com/2026/06/06/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
+          <t>https://www.chathamedc.org/news/wolfspeed-siler-city/</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Hamlet</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -6217,54 +6583,54 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>AWS/Amazon — AI/cloud campus</t>
+          <t>Vulcan Elements — magnet factory</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1,000 (proj.)</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>$10B</t>
+          <t>$918.4M</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$81,932 avg (stated)</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Confirmed real via 6/29/26 public-hearing milestone; outside core priority-county list but retained for continuity</t>
+          <t>500+ jobs but wage sub-$100k; JCC training cohorts begin summer 2026</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-summer (training start)</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>https://www.wfae.org/energy-environment/2026-06-29/public-hearing-planned-for-amazon-and-duke-energy-data-center-project-in-richmond-county</t>
+          <t>https://www.wunc.org/economy/2025-11-18/vulcan-elements-worlds-largest-magnet-factory-outside-china-benson</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Wake Co. (aggregate)</t>
+          <t>Wake County (statewide)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6279,42 +6645,786 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>County jobs pipeline (52 projects)</t>
+          <t>WakeMed / Atrium Health — proposed merger</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>~11,000 (pipeline)</t>
+          <t>3,300 (statewide, 5 yr)</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>$11B</t>
+          <t>$2.0B (Wake Co. portion)</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Mixed (office-skewed)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Aggregate pipeline; no single new project crystallized to 500+</t>
+          <t>Huge but wage/geography unclear; still under regulatory/public review</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+          <t>https://abc11.com/post/nc-wakemed-atrium-merge-creating-2b-investment-wake-county-3300-health-care-jobs/19016838/</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>~$500M (site, existing)</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>RISK FLAG: hangar reportedly largely idle; contractual hiring cliff this year or lease may terminate</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/greensboro-s-50-million-supersonic-ghost-hangar-puts-state-on-the-clock/</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed NC-specific)</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington-specific job count not disclosed</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Sub-$100k wage; equipment arrival end 2026, first parts mid-2027</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>2025-01 (orig.); 2026 milestone</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county/</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>$20M</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>$55,133 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Sub-$100k wage</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25 (orig.)</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Jobs undisclosed for this milestone (production start early 2026)</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>2026-01 (est.)</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.neimagazine.com/news/ge-hitachi-allocates-50m-to-enhance-safety-at-north-carolina-factory/</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>$40-60M</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Mixed)</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; wage not disclosed</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.airsysnorthamerica.com/</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; wage not disclosed</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.growlaurenscounty.com/</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Sub-100k wage; county border ambiguous (Anderson per state, Pickens per local coverage)</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wltx.com/</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Jobs entirely undisclosed; company 'still developing projections'</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.scbio.org/</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (unchanged)</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>$1.0B (existing)</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed ($54-64k assemblers; eng. likely higher)</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Rate ramp 7-&gt;10/month during 2026 confirms hiring plan active; wage mixed</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/air-transport/aircraft-propulsion/boeing-formally-launches-787-facilities-expansion</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal Phase 2</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mixed, some 6-figure specialist roles)</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>Direct count sub-500; wage unclear</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>https://www.joc.com/article/charlestons-leatherman-terminal-eyes-second-berth-by-late-2026-6066963</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — 1-yr anniversary</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>~250 (estimate)</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500; figure not re-confirmed this cycle</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.berkeleyobserver.com/</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -6329,7 +7439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6459,7 +7569,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Pre-window (&gt;6 mo back); June 2026 item was groundbreaking follow-up</t>
+          <t>Pre-window (&gt;6 mo back); June 2026 was groundbreaking follow-up</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -6728,37 +7838,37 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Amazon robotics FC</t>
+          <t>Google SC data centers</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Pender Co.</t>
+          <t>Berkeley/Dorchester</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>1,000+</t>
+          <t>jobs n/d</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Pre-window + logistics wages (&lt; $100k)</t>
+          <t>Pre-window (2025-10-13) + jobs undisclosed (also in Watch)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/amazon-adding-1000-jobs-at-new-pender-county-center/</t>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
         </is>
       </c>
     </row>
@@ -6770,12 +7880,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Toyota Battery NC</t>
+          <t>Amazon robotics FC</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Liberty (Randolph)</t>
+          <t>Pender Co.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -6785,22 +7895,22 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>5,100 cum.</t>
+          <t>1,000+</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Out of window; ~$20.77/hr median</t>
+          <t>Pre-window + logistics wages (&lt; $100k)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>https://abc11.com/post/toyota-nc-plant-investing-139-billion-creating-5100-jobs-randolph-county-north-carolina/18148348/</t>
+          <t>https://businessnc.com/amazon-adding-1000-jobs-at-new-pender-county-center/</t>
         </is>
       </c>
     </row>
@@ -6812,37 +7922,37 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors (original selection)</t>
+          <t>Toyota Battery NC</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Blythewood</t>
+          <t>Liberty (Randolph)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>5,100 cum.</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2021-2023</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Superseded by in-window hiring milestone (now ranked #2)</t>
+          <t>Out of window; ~$20.77/hr median</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2023-03/scout-motors-selects-south-carolina-production-site-plans-create-4000-jobs</t>
+          <t>https://abc11.com/post/toyota-nc-plant-investing-139-billion-creating-5100-jobs-randolph-county-north-carolina/18148348/</t>
         </is>
       </c>
     </row>
@@ -6854,37 +7964,37 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Goodyear plant</t>
+          <t>Scout Motors (original selection)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Fayetteville (Cumberland)</t>
+          <t>Blythewood</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>LAYOFF/CLOSURE (excluded per rules)</t>
+          <t>2023 selection — superseded here by the in-window hiring milestone (now ranked #2/#3)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/fayetteville-cumberland-industrial-jobs-may-2026/</t>
+          <t>https://governor.sc.gov/news/2023-03/scout-motors-selects-south-carolina-production-site-plans-create-4000-jobs</t>
         </is>
       </c>
     </row>
@@ -6896,12 +8006,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Ralliant</t>
+          <t>Goodyear plant</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Raleigh (Wake)</t>
+          <t>Fayetteville (Cumberland)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -6911,22 +8021,22 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Pre-window + sub-500 (high wage $189k)</t>
+          <t>LAYOFF/CLOSURE (excluded per rules)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/03/11/governor-stein-announces-180-jobs-global-technology-company-selects-wake-county-new-headquarters</t>
+          <t>https://www.wral.com/business/fayetteville-cumberland-industrial-jobs-may-2026/</t>
         </is>
       </c>
     </row>
@@ -6938,7 +8048,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>BuildOps</t>
+          <t>Ralliant</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -6953,22 +8063,22 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Pre-window + sub-500</t>
+          <t>Pre-window + sub-500 (high wage $189k)</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/24/governor-stein-announces-software-company-buildops-will-create-291-jobs-raleigh</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/03/11/governor-stein-announces-180-jobs-global-technology-company-selects-wake-county-new-headquarters</t>
         </is>
       </c>
     </row>
@@ -6980,37 +8090,37 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Pallidus</t>
+          <t>BuildOps</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>York Co.</t>
+          <t>Raleigh (Wake)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>291</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Old project recycled</t>
+          <t>Pre-window + sub-500</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>https://www.yorkcountyed.com/news-media/announcements/pallidus-relocating-corporate-headquarters-and-manufacturing-operations-to-york-county</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/24/governor-stein-announces-software-company-buildops-will-create-291-jobs-raleigh</t>
         </is>
       </c>
     </row>
@@ -7022,12 +8132,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>E&amp;J Gallo Winery</t>
+          <t>Pallidus</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Chester Co.</t>
+          <t>York Co.</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -7037,22 +8147,22 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>~496</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Old project; recent items facility recognition</t>
+          <t>Old project recycled</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2021-06/e-j-gallo-winery-establishing-new-east-coast-facility-chester-county</t>
+          <t>https://www.yorkcountyed.com/news-media/announcements/pallidus-relocating-corporate-headquarters-and-manufacturing-operations-to-york-county</t>
         </is>
       </c>
     </row>
@@ -7064,7 +8174,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>IKO North America</t>
+          <t>E&amp;J Gallo Winery</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -7079,22 +8189,22 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>~180</t>
+          <t>~496</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Grand opening of 2023 project; sub-500</t>
+          <t>Old project; recent items facility recognition</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>https://charlotteregion.com/news/global-roofing-manufacturer-investing-363m-creating-180-jobs-in-chester-county/</t>
+          <t>https://governor.sc.gov/news/2021-06/e-j-gallo-winery-establishing-new-east-coast-facility-chester-county</t>
         </is>
       </c>
     </row>
@@ -7106,96 +8216,96 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Apple / JPMorgan / BofA / Truist branches</t>
+          <t>IKO North America</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chester Co.</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>~180</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>various</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>No specific qualifying job count; branch-network/speculative</t>
+          <t>Grand opening of 2023 project; sub-500</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://charlotteregion.com/news/global-roofing-manufacturer-investing-363m-creating-180-jobs-in-chester-county/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TigerDC 'Project Spero'</t>
+          <t>Apple / JPMorgan / BofA / Truist branches</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg Co.</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>various</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>WITHDRAWN — county council denied incentive; company pulled the $3B project. Was in prior-week Watch list; removed this week.</t>
+          <t>No specific qualifying job count; branch-network/speculative</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/spartanburg/news/spartanburg-project-spero-data-center-withdrawn/article_bfb9e61e-2282-4d22-9806-7aa4a934be27.html</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>VinFast</t>
+          <t>Wegmans</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Chatham Co. (Moncure)</t>
+          <t>Charlotte area (Ballantyne)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -7205,39 +8315,39 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>7,500 orig. -&gt; ~1,400</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>State of NC sued VinFast over missed construction/hiring deadlines; hiring plan cut ~82%. Negative/contraction signal, not a growth item.</t>
+          <t>In-window but low-wage-only retail (~$14-16/hr)</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/raleigh/2026/05/21/north-carolina-sues-vinfast-to-take-back-control-of-chatham-county-land</t>
+          <t>https://www.wbtv.com/2026/01/15/wegmans-bring-450-jobs-new-charlotte-area-store-how-apply/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Boom Supersonic</t>
+          <t>PSA Airlines</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Greensboro (Guilford)</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -7247,39 +8357,39 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>500 req. by 12/31/26 vs 1,761 orig.</t>
+          <t>~400</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>2026 (ongoing)</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Facility idle since 2024 ribbon-cutting; zero aircraft produced; at risk of lease default, not growing.</t>
+          <t>HQ grand opening of a prior Ohio-closure-driven relocation; mixed/mostly sub-$100k except pilots</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/19/governor-stein-celebrates-psa-airlines-headquarters-grand-opening-charlotte-highlights-only</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>SAS Institute</t>
+          <t>Maersk</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Cary (Wake)</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -7289,39 +8399,39 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>-300</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>LAYOFF — excluded per rules</t>
+          <t>Pre-window; in-window 'milestone' is a 1-year hiring delay (2027-2029), not qualifying forward movement</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/technology/sas-cuts-300-jobs-across-the-company-june-2026/</t>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Maersk</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charlotte / South End</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -7331,39 +8441,39 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>301</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; update this week is a confirmed 1-yr hiring-ramp delay (2027-2029 vs 2026-2028) — negative momentum on an already-excluded item.</t>
+          <t>Pre-window + sub-500; in-window milestone is only an interim-office opening</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>https://www.sedc.org/</t>
+          <t>https://www.pacificlife.com/press-releases/pacific-life-announces-footprint-expansion-to-charlotte-north-carolina.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Novartis (original announcement)</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Durham/Morrisville</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -7373,39 +8483,39 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; superseded this week by the 2026-04-30 '7th facility' update, now in Ranked table.</t>
+          <t>Withdrew from state JDIG citing ~30-job hiring shortfall vs. 204-job target — negative reversal</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/novartis-expand-us-manufacturing-footprint-durham-and-wake-counties-adding-700-jobs-771-million</t>
+          <t>https://www.wilmingtonbiz.com/banking_and_finance/2026/05/13/live_oak_bank_pulls_out_of_state_incentive_program_citing_projected_hiring_shortfall/27496</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Aspida Financial</t>
+          <t>Technimark</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Asheboro (Randolph)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -7415,39 +8525,39 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Pre-window (&gt;6 mo back); no in-window update found</t>
+          <t>State terminated JDIG for missed hiring targets — negative reversal</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/financial-services-company-expand-durham-headquarters-1000-new-jobs</t>
+          <t>https://www.wral.com/news/nccapitol/north-carolina-terminates-incentives-six-companies-1500-jobs-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Hoffman &amp; Hoffman</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Benson (Johnston)</t>
+          <t>Greensboro (Guilford)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -7457,34 +8567,34 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; training-program milestone undated, could not confirm in-window date</t>
+          <t>Announced 13 days before window opens</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>https://vulcanelements.com/vulcan-elements-selects-benson-north-carolina-for-1-billion-magnet-facility/</t>
+          <t>https://www.areadevelopment.com/newsItems/12-24-2025/hoffman-hoffman-greensboro-north-carolina.shtml</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Pacific Life (original announcement)</t>
+          <t>AssetMark Financial Holdings</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7499,123 +8609,123 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>252</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; now tracked via Watch (interim office milestone) instead</t>
+          <t>Pre-window; no in-window update despite high wage ($110,518)</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2025/10/28/governor-stein-announces-301-new-jobs-insurance-giant-pacific-life-selects-charlotte</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/07/08/governor-stein-announces-financial-services-firm-assetmark-will-create-252-jobs-charlotte</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Boeing (base $1B/1,000-job commitment)</t>
+          <t>Fit Precast</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Gaston Co.</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Pre-window groundbreaking; now tracked via Watch (eng. relocation + production ramp) instead</t>
+          <t>Pre-window + sub-200 jobs despite high wage ($104,000)</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>https://boeing.mediaroom.com/2025-11-07-Boeing-South-Carolina-Breaks-Ground-on-787-Site-Expansion</t>
+          <t>https://businessnc.com/114420-2/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Silfab Solar</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Salisbury (Rowan)</t>
+          <t>York Co.</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>1,181</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; wage $62K (&lt;$100K)</t>
+          <t>Pre-window; no in-window milestone found</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/30/jabil-selects-rowan-county-nearly-1200-new-jobs-and-500-million-multi-year-investment</t>
+          <t>https://pv-magazine-usa.com/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — Charlotte HQ</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Charlotte (Plaza Midwood)</t>
+          <t>Salisbury (Rowan)</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -7625,39 +8735,39 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>1,181</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Pre-window (separate project from the Blythewood, SC plant); no in-window milestone found — recommend rechecking for a 2026 groundbreaking/hiring start.</t>
+          <t>Pre-window; wage $62,034 (&lt;$100k)</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2025/11/12/governor-stein-announces-a-new-headquarters-for-scout-motors-creating-1200-jobs-in-mecklenburg-county</t>
+          <t>https://governor.nc.gov/news/press-releases/2025/06/30/jabil-selects-rowan-county-nearly-1200-new-jobs-and-500-million-multi-year-investment</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Toyota Battery NC</t>
+          <t>MetOx International</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Liberty (Randolph)</t>
+          <t>Chatham Co.</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -7667,39 +8777,39 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>5,100 cum.</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>2021-2023 / GO 2025-11-12</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Out of window; ~$20.77/hr median</t>
+          <t>Pre-window; wage $75,132 (&lt;$100k)</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>https://abc11.com/post/toyota-nc-plant-investing-139-billion-creating-5100-jobs-randolph-county-north-carolina/18148348/</t>
+          <t>https://www.commerce.nc.gov/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>BuildOps</t>
+          <t>Amgen (2nd facility)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Raleigh (Wake)</t>
+          <t>Holly Springs (Wake)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -7709,39 +8819,39 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>370</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Pre-window + sub-500</t>
+          <t>Pre-window; wage &gt;$91k but &lt;$100k</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/24/governor-stein-announces-software-company-buildops-will-create-291-jobs-raleigh</t>
+          <t>https://www.commerce.nc.gov/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>AvidXchange</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Durham/Wake (RTP)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -7751,39 +8861,39 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>1,229</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>2018-12-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Recycled 2018 news re-surfacing in 2026 search indexes</t>
+          <t>Pre-window; no job figure disclosed</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/governor-cooper-announces-1229-new-jobs-avidxchange-expands-mecklenburg-county</t>
+          <t>https://www.biogen.com/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Crystal Window &amp; Door Systems</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Wake Co. (Morrisville)</t>
+          <t>Johnston Co.</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -7793,39 +8903,39 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>501</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>2019-12-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Recycled 2019 news</t>
+          <t>Pre-window; meets job count but wage $56,061 (&lt;$100k)</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/microsoft-create-500-new-jobs-wake-county</t>
+          <t>https://www.commerce.nc.gov/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Novo Nordisk (2nd facility)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>RTP (Wake)</t>
+          <t>Clayton (Johnston)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -7835,39 +8945,39 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Recycled 2012 news; also sub-500</t>
+          <t>Pre-window; wage ~$65-70k (&lt;$100k)</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/netapp-create-460-jobs-wake-county</t>
+          <t>https://www.commerce.nc.gov/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Honda Aircraft</t>
+          <t>Apple RTP campus extension</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Greensboro (Guilford)</t>
+          <t>Wake Co.</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -7877,39 +8987,39 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>280 / 419</t>
+          <t>2,700+</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Recycled old news; no 2026 update</t>
+          <t>Pre-window; no in-window construction start confirmed</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2023/07/11/governor-cooper-announces-honda-aircraft-company-will-create-280-jobs-major-greensboro-investment</t>
+          <t>https://www.apple.com/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>DEHN Inc.</t>
+          <t>Pendo</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Mooresville (Iredell)</t>
+          <t>Raleigh (Wake)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -7919,39 +9029,39 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>-90</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Recycled; sub-500 + $66,120 wage (&lt;$100K)</t>
+          <t>Layoff — excluded per rules</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2024/01/23/german-electrical-engineering-and-manufacturing-company-selects-iredell-county-us-headquarters-and</t>
+          <t>https://www.pendo.io/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Red Bull / Rauch</t>
+          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Concord (Cabarrus)</t>
+          <t>Raleigh (Wake)</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -7961,39 +9071,39 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>1,500 (claimed)</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>2021-07/08</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Recycled 2021 news; ~$50K wage</t>
+          <t>Unverifiable — only source is a non-authoritative relocation/SEO blog; no corroboration found</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>https://edpnc.com/news/red-bull-and-rauch-to-build-a-multimillion-dollar-beverage-manufacturing-hub/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Kroger fulfillment center</t>
+          <t>"Energizer Holdings HQ relocation to Apex" (unverified)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Concord (Cabarrus)</t>
+          <t>Apex (Wake)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -8003,81 +9113,81 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>~75 (claimed)</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Recycled 2021 news; low-wage logistics</t>
+          <t>Unverifiable — same non-authoritative source issue; Energizer's own newsroom shows no such announcement</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2021/12/08/governor-cooper-announces-kroger-will-build-high-tech-customer-fulfillment-center-cabarrus-county</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>GITI Tire</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>RTP (Wake)</t>
+          <t>Chester Co.</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1,700 cum.</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2015-2017</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Recycled 2023 news</t>
+          <t>Legacy project; no in-window milestone despite ongoing hiring</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>https://news.biobuzz.io/2025/07/16/eli-lilly-invests-450-million-to-expand-rtp-manufacturing-site/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Apple RTP campus</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>RTP (Wake)</t>
+          <t>Concord (Cabarrus)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -8087,185 +9197,185 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>~600</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Recycled/stale; project reported paused since 2024, no 2026 reactivation found</t>
+          <t>Legacy announcement/groundbreaking; wage &gt;$70k (&lt;$100k); no in-window update</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>https://abc11.com/post/apple-nc-east-coast-hub-on-hold-research-triangle-park-3-years-later-1-billion-project/14997218/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Pallidus</t>
+          <t>Windsor Windows &amp; Doors</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill (York)</t>
+          <t>Monroe (Union)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Recycled old news; also sub-500</t>
+          <t>Facility largely complete by 2024; no in-window figures disclosed</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>https://www.sccommerce.com/news/pallidus-relocating-corporate-headquarters-and-manufacturing-operations-york-county</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>IKO Industries</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Chester Co.</t>
+          <t>Mecklenburg Co.</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>180-200</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Recycled old news; sub-500</t>
+          <t>Land acquired Nov. 2024; rezoning approved but zero jobs figure ever disclosed</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2023-02/iko-establishing-south-carolina-operations-chester-county</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Live Oak Bank</t>
+          <t>Duke Energy gas plant</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Wilmington (New Hanover)</t>
+          <t>Anderson Co.</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>125 permanent</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Recycled 2022 news; sub-500</t>
+          <t>Below the 200-job Watch floor despite a 2,200-job, multi-year construction surge (2027-2031)</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2022/09/07/live-oak-bank-add-200-new-jobs-new-hanover-county-25-million-expansion-wilmington</t>
+          <t>https://www.foxcarolina.com/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Vantaca</t>
+          <t>GE Vernova / EnerSys / Woodward / Isuzu N.A. (legacy Upstate deals)</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>New Hanover Co.</t>
+          <t>Greenville/Spartanburg Cos.</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>500-700 each</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Recycled old news; well sub-500</t>
+          <t>All pre-window; no confirmed 2026 groundbreaking/hiring-ramp milestone found</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -8277,59 +9387,59 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>FIT Precast</t>
+          <t>Sub-200-job Upstate SC items (Huwell, Coastal Precast, Hydrite, United Composite, DartPoints, DMA Industries, Carbotech, AFL/Fujikura, Project Moc-1, Advanced Metalworks)</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Gastonia (Gaston)</t>
+          <t>Various Upstate</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>10-100 each</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Wage would qualify (~$102K) but job count far below the 500 threshold</t>
+          <t>Below Watch floor regardless of window; Project Moc-1 has $2.76B capex but only 27 jobs</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/114420-2/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Walmart fulfillment center</t>
+          <t>Sub-200-job Triad/Piedmont items (DePalo Foods, Textum OPCO, Cheerwine, ChenMed, Alamance Foods, Nature's Value, WH Farms, 7 Cinematics)</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Kings Mountain (Gaston)</t>
+          <t>Various Triad</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -8339,692 +9449,20 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10-183 each</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>unconfirmed</t>
+          <t>2021-2026</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Sub-500; date/wage not independently source-verified this cycle</t>
+          <t>Below Watch floor and/or wage well under $100k</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Textum OPCO LLC</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>McAdenville (Gaston)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>Far below threshold</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>https://www.commerce.nc.gov/news/press-releases</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Snider Fleet Solutions</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Indian Land (Lancaster)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Sub-500; dormant since 2023, no 2026 update found (prior-tracked, explicitly rechecked)</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.sc.gov/news/2023-05/snider-fleet-solutions-relocating-headquarters-lancaster-county</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Corvid Technologies</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Mooresville (Iredell)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>2018-03</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>Recycled 2018 news; possible undated 2026 ribbon-cutting — recommend rechecking</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>https://patch.com/north-carolina/mooresville/corvid-bring-367-jobs-headquarters-mooresville</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Albemarle Corp.</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Chester Co.</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>300+</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>2021/2023</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Sub-500; wage ~$93K just under $100K; could not verify a 2026 production-start milestone</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>https://businessnc.com/albemarle-picks-s-c-for-lithium-plant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Movement Mortgage</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Indian Land (Lancaster)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>Vague commentary, no numbers, no credible dedicated 2026 source</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Red Ventures</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Indian Land / Fort Mill (Lancaster)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>unconfirmed</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>Sub-500; date not independently verified</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>https://www.sccommerce.com/news/red-ventures-expanding-lancaster-county-headquarters-adding-200-jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>NACA (Neighborhood Assistance Corp of America)</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Charlotte (Mecklenburg)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>1,014</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>unconfirmed</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>Source URL returned HTTP 403 repeatedly; date could not be verified; likely sub-$100K counselor/processor roles</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/mecklenburg-county-finance-service-center-add-1014-jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>HII / Newport News Shipbuilding</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Goose Creek (Berkeley)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Hundreds (n/d)</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Vague, no hard job number disclosed</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Johnson &amp; Johnson</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Wilson Co.</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Real &amp; in-window but Wilson County is outside this report's priority-county list; flagged for awareness only</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/01/09/governor-stein-announces-johnson-johnson-will-build-second-major-facility-wilson-county</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Envision AESC</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Florence Co.</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>~1,600</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>unconfirmed 2026</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Feeds BMW Spartanburg supply chain but Florence Co. is outside the Upstate/Midlands/Lowcountry scope list</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wbtw.com/growthtracker/aesc-restarts-clock-on-construction-of-1-6b-florence-plant-after-six-month-hiatus/</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Goodyear plant</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Fayetteville (Cumberland)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>LAYOFF/CLOSURE (excluded per rules)</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wral.com/business/fayetteville-cumberland-industrial-jobs-may-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Chester Co. data center moratorium</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Chester Co.</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Policy action, not a jobs announcement; logged for regional context</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wbtv.com/2026/06/19/york-county-discusses-project-palmetto-rock-chester-county-data-center-moratorium-rock-hill-juneteenth-celebration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Silfab Solar</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Fort Mill (York)</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>Wage ~$60-79K (&lt;$100K); in-window legal milestone (2026-01-26 court dismissal) doesn't change the wage disqualifier</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>https://pv-magazine-usa.com/2026/01/26/south-carolina-county-court-dismisses-challenge-to-silfab-solar-manufacturing-facility/</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>E&amp;J Gallo Winery</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Chester Co.</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>~496</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Old project; recent items are facility recognition only</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.sc.gov/news/2021-06/e-j-gallo-winery-establishing-new-east-coast-facility-chester-county</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Apple / JPMorgan / BofA / Truist branches</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>various</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>No specific qualifying job count; branch-network/speculative commentary</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Wake Forest Innovation Quarter Phase II</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Winston-Salem (Forsyth)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>General district growth; no single named-company 500+ job announcement</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -9041,7 +9479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9101,7 +9539,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>SMBC, AbbVie, JetZero, BorgWarner, Novartis, J&amp;J (stated wages + JDIG)</t>
+          <t>SMBC, AbbVie, JetZero, BorgWarner (stated wages + JDIG)</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9566,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>SMBC, Capital Group, JetZero, Citigroup</t>
+          <t>SMBC, Capital Group, JetZero, PSA Airlines</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9647,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Ferrara, Suniva, AMAROK, Scout (project)</t>
+          <t>Ferrara, Suniva, AMAROK, Scout (project), Octapharma context</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9708,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GlobeNewswire / Novartis press</t>
+          <t>Scout Motors company blog</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -9280,7 +9718,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/</t>
+          <t>https://blog.scoutmotors.com/</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -9290,7 +9728,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Novartis 7th-facility / Morrisville API announcement (Apr 2026)</t>
+          <t>June 2026 production-center update (first vehicle body weld)</t>
         </is>
       </c>
     </row>
@@ -9317,14 +9755,14 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Siemens Energy $421M/500-job NC expansion (Feb 2026)</t>
+          <t>Siemens Energy $421M/500-job NC expansion; JetZero hiring delay + $133.9M funding</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Carolina Journal</t>
+          <t>WRAL / WRAL TechWire</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -9334,24 +9772,24 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>https://www.carolinajournal.com/</t>
+          <t>https://www.wral.com/</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>NC statewide</t>
+          <t>NC Triangle</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>JetZero hiring-timeline delay, state budget allocation</t>
+          <t>AbbVie salary/incentive detail; Novartis $220M expansion; Siemens AG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>WRAL / WRAL TechWire</t>
+          <t>WIS / WLTX (Columbia)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -9361,24 +9799,24 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/</t>
+          <t>https://www.wistv.com/</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>NC Triangle</t>
+          <t>SC Midlands</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>AbbVie salary/incentive detail, Novartis, SAS layoffs</t>
+          <t>Scout Motors hiring milestone, wages; AMAROK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>WIS / WLTX (Columbia)</t>
+          <t>Charlotte Business Journal / Axios Charlotte</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -9388,24 +9826,24 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>https://www.wistv.com/</t>
+          <t>https://charlotte.axios.com/</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>SC Midlands</t>
+          <t>Charlotte metro</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors hiring milestone, wages</t>
+          <t>Capital Group corroboration; SMBC lease; JPMorgan Chase; Pacific Life</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Charlotte Business Journal / Axios Charlotte</t>
+          <t>Area Development</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -9415,24 +9853,24 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/</t>
+          <t>https://www.areadevelopment.com/</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Charlotte metro</t>
+          <t>National site-selection</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>SMBC lease, Capital Group, JPMorgan SouthPark</t>
+          <t>Lumentum; Hoffman &amp; Hoffman</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>CRE News</t>
+          <t>Post &amp; Courier</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -9442,132 +9880,132 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>https://crenews.com/</t>
+          <t>https://www.postandcourier.com/</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Charlotte CRE</t>
+          <t>SC statewide</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Capital Group lease at One Independence Center</t>
+          <t>QTS York County; Octapharma Rock Hill; SC Ports; AMAROK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Banking Dive</t>
+          <t>Asheville Chamber</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>trade_journal</t>
+          <t>regional_edo</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>https://www.bankingdive.com/</t>
+          <t>https://www.ashevillechamber.org/</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>National banking</t>
+          <t>Buncombe NC</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Citigroup Charlotte office opening</t>
+          <t>Eaton expansion; post-Helene recovery context</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Area Development</t>
+          <t>Charlotte Regional Business Alliance</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>regional_edo</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>https://www.areadevelopment.com/</t>
+          <t>https://charlotteregion.com/</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>National site-selection</t>
+          <t>CLT 15-county bi-state</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Lumentum, Octapharma</t>
+          <t>IKO/Chester cross-check</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Post &amp; Courier</t>
+          <t>York County Economic Development</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>regional_edo</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/</t>
+          <t>https://www.yorkcountyed.com/</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>SC statewide</t>
+          <t>York Co. SC</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>QTS York County, Octapharma, Boeing, TigerDC withdrawal</t>
+          <t>Pallidus (excluded); Octapharma context</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>WRHI (Rock Hill)</t>
+          <t>Upstate SC Alliance / Fox Carolina</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>regional_journal</t>
+          <t>regional_edo/journal</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrhi.com/</t>
+          <t>https://www.upstatescalliance.com/</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>York Co., SC</t>
+          <t>Upstate SC</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Octapharma public identification, York County Council votes</t>
+          <t>Siemens Smart Infra; TigerDC Project Spero</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>WBTV / QC News</t>
+          <t>Business NC</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -9577,24 +10015,24 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>https://www.wbtv.com/</t>
+          <t>https://businessnc.com/</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Charlotte metro / Rock Hill</t>
+          <t>NC statewide</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Novant Health Rock Hill, Chester Co. moratorium</t>
+          <t>Siemens Energy; Pratt &amp; Whitney; Maersk delay; Capital Group lease</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>SC Daily Gazette</t>
+          <t>Fort Mill Sun / WRHI / WSOC-TV / QC News</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -9604,51 +10042,51 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/</t>
+          <t>https://www.fortmillsun.com/</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>SC statewide</t>
+          <t>Charlotte-metro SC (York Co.)</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Boeing Charleston momentum</t>
+          <t>Octapharma 'Project Palmetto Rock' council vote + controversy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DataCenterDynamics</t>
+          <t>Commercial Real Estate Direct</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>trade_journal</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/</t>
+          <t>https://crenews.com/</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>National data centers</t>
+          <t>National CRE</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>QTS York Co., TigerDC withdrawal</t>
+          <t>Capital Group lease at One Independence Center</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg.com / Greenville.com</t>
+          <t>Salisbury Post</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -9658,233 +10096,179 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>https://www.spartanburg.com/</t>
+          <t>https://www.salisburypost.com/</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Upstate SC</t>
+          <t>Rowan Co. NC</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>BMW Group investment-completion milestone</t>
+          <t>Project Rack; Google/DHL Kannapolis lease</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>BusinessWire</t>
+          <t>Hoodline</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>wire_service</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/</t>
+          <t>https://hoodline.com/</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>NC (Triad/Triangle)</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Ralliant Raleigh HQ opening</t>
+          <t>Boom Supersonic risk flag; Ralliant HQ launch</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Salisbury Post</t>
+          <t>Chatham County EDC</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>regional_edo</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>https://www.salisburypost.com/</t>
+          <t>https://www.chathamedc.org/</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Rowan Co., NC</t>
+          <t>Chatham Co. NC</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>'Project Rack' distribution facility</t>
+          <t>Wolfspeed Siler City milestone</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>WFAE</t>
+          <t>WUNC</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>public_radio</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>https://www.wfae.org/</t>
+          <t>https://www.wunc.org/</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / NC</t>
+          <t>NC Triangle</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>AWS Hamlet public hearing</t>
+          <t>Vulcan Elements training milestone; WakeMed/Atrium merger</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Asheville Chamber</t>
+          <t>ABC11 / NC Health News</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>regional_edo</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>https://www.ashevillechamber.org/</t>
+          <t>https://abc11.com/</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Buncombe NC</t>
+          <t>NC Triangle</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Eaton expansion</t>
+          <t>WakeMed/Atrium Health merger proposal</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Charlotte Regional Business Alliance</t>
+          <t>Aviation Week / Manufacturing Dive</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>regional_edo</t>
+          <t>trade_journal</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>https://charlotteregion.com/</t>
+          <t>https://aviationweek.com/</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>CLT 15-county bi-state</t>
+          <t>National aerospace</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>IKO/Chester cross-check</t>
+          <t>Boeing 787 production-rate ramp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>York County Economic Development</t>
+          <t>WilmingtonBiz</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>regional_edo</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>https://www.yorkcountyed.com/</t>
+          <t>https://www.wilmingtonbiz.com/</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>York Co. SC</t>
+          <t>New Hanover Co. NC</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Pallidus (excluded)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Upstate SC Alliance / Fox Carolina</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>regional_edo/journal</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>https://www.upstatescalliance.com/</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Upstate SC</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Siemens Smart Infra</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Business NC</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>https://businessnc.com/</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>NC statewide</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Siemens Energy, GE Aerospace, Albemarle, FIT Precast</t>
+          <t>Amazon-Corning fiber optics; Live Oak Bank JDIG withdrawal</t>
         </is>
       </c>
     </row>
@@ -9899,12 +10283,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9980,7 +10365,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Capex size + lock-in (incentive-backed, under construction, leased); confirmed delays discount this factor</t>
+          <t>Capex size + lock-in (incentive-backed, under construction)</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10395,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Reinforcement of a market across reports; confirmed milestones (leases, groundbreakings) score higher than static repeats</t>
+          <t>Reinforcement of a market across reports (new = low; gaining-momentum = higher)</t>
         </is>
       </c>
     </row>
@@ -10028,22 +10413,27 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Per-deal score rationale</t>
+          <t>Per-deal score rationale (all weeks)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>report_date</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>company_project</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>score_rationale</t>
         </is>
@@ -10052,135 +10442,280 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>SMBC Group (Charlotte)</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>2,000 jobs + stated $165k + top-tier employer + urban Class-A fit; lease signed 5/4/26 raises project-certainty score from 92 to 94.</t>
+      <c r="C12" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>2,000 jobs + stated $165k + top-tier employer + urban Class-A fit; new (low momentum).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Octapharma (Rock Hill)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>1,552 total jobs + two stated wage bands ($141.5K/$102.8K) + $1.49B; discounted slightly for a not-yet-fully-finalized county vote.</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>4,000 jobs + $2B locked-in + active hiring; wage mixed/workforce-to-salaried.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors (Blythewood)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>85</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>4,000 jobs + $2B locked-in + active hiring; wage mixed/workforce-to-salaried; unchanged from prior week.</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>734 jobs + stated $118k + $1.4B top-pharma certainty; strong MF fit.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>AbbVie (Durham)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>734 jobs + stated $118k + $1.4B top-pharma certainty; strong MF fit; unchanged from prior week.</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>14,500 jobs (max) + $4.7B; wage $89k (&lt;$100k) + budget/timeline execution risk discount.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Novartis (Durham/Wake)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>700+ jobs + newly stated $111,161 avg + ~$991M cumulative investment; new in-window 'seventh facility' milestone.</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Site crosses 500 jobs + stated ~$120k + ~$2B (doubled) top-pharma certainty; in-window increment is +100, slight discount.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
           <t>Capital Group (Charlotte)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>81</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>600 jobs + now-stated $194,141 (highest in report) + signed lease; raised from 78 to 81 on wage confirmation + lease.</t>
+      <c r="C17" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>600 jobs + inferred ~$190k (discounted vs stated) + urban fit; new.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Genentech (Holly Springs)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Site crosses 500 jobs + stated ~$120k + ~$2B (doubled) top-pharma certainty; unchanged from prior week.</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged fundamentals + lease/hiring milestone reinforces momentum (+1).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>JetZero (Greensboro)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>14,500 jobs (max) + $4.7B; wage $89k (&lt;$100k) + CONFIRMED 1-year hiring delay discounts project certainty further (was 82, now 74).</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>1,500+ jobs + two stated six-figure wage tiers (rare for SC) + $1.5B; discounted for tax-share controversy/execution risk.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Citigroup (Ballantyne)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>510 jobs + stated $131,832 + confirmed grand-opening milestone; added this week for consistency with how other milestone-based entries were scored.</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>First vehicle body welded is a lower-risk production milestone than training-center opening alone (+1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>State funding secured (+) but company's own hiring deadline slipped a full year (-); net -1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Uptown lease signed reinforces momentum (+1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>700 jobs + stated $111,161 + top-pharma certainty; newly in-window via investment-increase milestone, low repeat-momentum score as first-time-ranked.</t>
         </is>
       </c>
     </row>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-07-06  ·  Window 2026-01-06 to 2026-07-06  ·  NC + SC</t>
+          <t>Week of 2026-07-13  ·  Window 2026-01-13 to 2026-07-13  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06  (Week 2)</t>
+          <t>2026-07-13  (Week 3)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-01-06 to 2026-07-06  (trailing 6 months)</t>
+          <t>2026-01-13 to 2026-07-13  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Top new market</t>
+          <t>Top mover</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 88</t>
+          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 87 — county-level 3rd reading approved 4-3 but Rock Hill City Council's vote on amended tax-share terms remains outstanding</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Octapharma is the first SC deal in this dataset with two stated six-figure wage tiers; SMBC/Scout/Capital Group all cleared real occupancy/production milestones; JetZero is a mixed signal (funding secured, hiring delayed a year); Boom Supersonic flagged as a downside risk.</t>
+          <t>No brand-new qualifying (500+ job / $100k+ wage) deal was found in any of the five sub-regions this cycle — all 8 ranked entries carry forward. JetZero's groundbreaking is real construction progress even as its hiring ramp slips further (full target now 2037). SC Ports' decision to pause Leatherman Terminal operations Aug. 1 and Boom Supersonic's looming Dec. 31 hiring deadline are the cycle's clearest downside signals; TigerDC's $3.0B Spartanburg data center was formally withdrawn.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-01-06 to 2026-07-06. Novartis (Durham/Morrisville) re-enters scope via an in-window investment-increase milestone despite its original announcement predating the window.</t>
+          <t>Trailing 6 months now runs 2026-01-13 to 2026-07-13.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Several primary state press-release domains returned HTTP 403 to direct fetch this cycle; facts corroborated against 2+ independent secondary outlets where that occurred. Two unverifiable claims (Barclays, Energizer) found only on non-authoritative blogs were excluded rather than reported.</t>
+          <t>Two near-miss candidates (Maersk — wage now disclosed at $100,962 but milestone is a hiring delay; Citigroup — grand opening tied to a pre-window commitment) were excluded for consistency with this dataset's established milestone rules rather than admitted on job count/wage alone.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>6 of 6 baseline-ranked deals remain qualifying (none removed); 3 gaining momentum, 2 repeated, 1 mixed-update; 2 new entries (Octapharma, Novartis).</t>
+          <t>8 of 8 prior-ranked deals remain qualifying (none removed, none newly added); 1 gaining momentum (Scout Motors), 2 updated-mixed (Octapharma, JetZero), 1 updated (Capital Group, wage confirmation), 4 repeated (SMBC, AbbVie, Genentech, Novartis).</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2080,734 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>Final (3rd reading) county approval; city-level consent still pending</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/07/10/york-county-council-approves-project-palmetto-rock-deal-rock-hill-city-council-vote-deal/</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (deal certainty)</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>Hiring event announced; companywide headcount update</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/columbia/business/scout-motors-blythewood-factory-construction-sc/article_66a10144-3603-47f1-9b23-2f8415835b8f.html</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>Wage figure confirmed (stated, not inferred)</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2091,7 +2819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3866,6 +4594,934 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Leased former One Wells Fargo Center; hiring 70+ roles; first workers fall 2026</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; project remains on track for fall 2026 first arrivals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Updated (mixed)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Final (3rd reading) county approval; city-level consent still pending</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>York County Council 3rd reading approved 2026-07-08 (4-3, narrower than 2nd reading's 5-2); Rock Hill City Council has not yet voted on the revised terms as of 2026-07-13; Planning Commission recommended rezoning 2026-07-08</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/07/10/york-county-council-approves-project-palmetto-rock-deal-rock-hill-city-council-vote-deal/</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (deal certainty)</t>
+        </is>
+      </c>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W17" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>County-level approval advanced but on a narrower vote; Rock Hill City Council's outstanding vote on the amended tax-share terms is the key unresolved risk heading into next cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Gaining Momentum</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Hiring event announced; companywide headcount update</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Projected (~1,400 hired companywide; 600+ in SC)</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Pre-hire/interview events for 70+ maintenance-tech roles begin 2026-07-29; customer vehicle deliveries now more likely 2028 vs. earlier end-2026 framing</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/columbia/business/scout-motors-blythewood-factory-construction-sc/article_66a10144-3603-47f1-9b23-2f8415835b8f.html</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>Active hiring push continues (new interview events, ~1,400 hired companywide) even as customer-delivery timeline slips toward 2028 — near-term housing-demand driver (hiring) remains strong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Wage figure confirmed (stated, not inferred)</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>12-yr JDIG term; lease term began 2026-05-22</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="inlineStr">
+        <is>
+          <t>Wage figure upgraded from Estimated/Inferred (~$190k, payroll math) to a stated $194,141 avg (NC Commerce JDIG record) — removes prior wage-confidence discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Operational by 2029</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+        </is>
+      </c>
+      <c r="X21" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Updated (mixed)</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking held 2026-06-15; zero jobs now projected for 2027; hiring ramp begins 2028-2029 (3,020 jobs by end 2029); full 14,500+ target now due by 2037 (pushed from 2036)</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking actually occurred — first physical construction milestone — but the state's own JDIG amendment confirms the hiring ramp is now pushed out even further than last cycle's estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Facility opening targeted 2027-2028</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3877,7 +5533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7428,6 +9084,2548 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>Still just under 500 jobs; no threshold-crossing update found this cycle (high-priority check)</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy — groundbreaking held</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone since May 2026 groundbreaking; first lines targeted Q1 2029</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co.</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Suniva — solar-cell plant</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Stated $23-$53/hr = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; operations targeted spring/summer 2027</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Ribbon-cutting/opening ceremony held late April 2026 for the 240,000 sq ft facility; production ramp still targeted mid-2028</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>https://myfox8.com/news/north-carolina/greensboro/lumentum-holdings-opens-new-manufacturing-facility-in-greensboro/</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Now corroborated via official NC Commerce/Governor press releases dated 2026-05-26, resolving prior cycle's uncorroborated flag</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>'high-tech, high-wage' but figure Not disclosed (Inferred mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>Eaton recruiting at WNC Career Expo 2026-04-16; confirmed as 7th Helene-recovery manufacturer expansion</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; Mecklenburg-specific allocation for this tranche remains unclear (conflated with a 2024 tranche in some coverage)</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals uncertain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>New 101,000 sq ft Wendell facility coming online July 2026; Knightdale targeting 100 jobs by end 2026; expanded Wendell campus (+200 jobs) by 2028</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>Reaffirmed 2026-01-28 via White House-linked event; construction underway on west campus, facility slated to open within the next year</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>https://greensboro.com/news/local/business/development/article_f8077494-ba1d-526b-a82a-9d8425f0acbe.html</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>York Co.</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>QTS "Project Cobra" — data-center campus</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>~200 FTE (+~1,000 constr.)</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>up to $8B</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>~$80k median (stated)</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>York County's proposed nine-month data-center moratorium reached 3rd reading/public hearing 2026-07-13 (same day as this report); outcome not yet known — could affect QTS's remaining unpermitted buildings</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrhi.com/2026/06/york-county-council-approves-data-center-moratorium-first-reading-advances-1-5-billion-biopharmaceutical-project-213500</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>Med (regulatory outcome pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Indian Land</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Snider Fleet Solutions — corporate office relo</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>$6.9M</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; corporate/HQ roles</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Re-examined this cycle: underlying announcement traces to 2023 with no 2026 developments found at all — likely a stale carryover; recommend removal next cycle absent a genuine update</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>2023 (orig.)</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>Low (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>~160 apprentices (FTE n/d)</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; original Oct. 2025 announcement remains the latest news</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>High (capex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Pickens</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>FN America — 2nd production facility</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>~176</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>$33M</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>Second consecutive cycle with no momentum found; flag for possible removal next report</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Still unverified; outside this cycle's five assigned research regions — needs direct confirmation next cycle</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aboutamazon.com/</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>Low (needs verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>RECONCILED this cycle: the previously-flagged second figure (~30 projects/8,000-10,800 jobs/$5.6B) is confirmed to be the closed, prior EDGE 6 campaign (concluded ~Sept 2024) — sequential, not duplicative, with the current $11B/11,000-job EDGE 7 pipeline</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — new office (1,000-employee bldg)</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>400 new by 2028</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred (job-posting range)</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>"Project Rack" (company undisclosed)</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>'Above-average starting' Estimated/Inferred sub-$100k</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; Q1 2027 operations start still targeted</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.salisburypost.com/2026/06/06/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (DHL postings)</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; jobs still undisclosed</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>https://www.salisburypost.com/2026/05/02/not-a-data-center-google-leases-rowan-county-side-kannapolis-industrial-site/</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant Corp. — global HQ launch</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>$170k-$189k avg (stated)</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Siler City</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed — silicon-carbide fab</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>1,800 (proj.)</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>$5.0B</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>$77,753 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Post-bankruptcy ramp described by the company as 'more measured/disciplined' — original full-occupancy March 2026 target appears to have slipped; SiC crystal growth/wafer shipments to Mohawk Valley (NY) underway</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>2026-Q1 (10-Q)</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0000895419/000089541926000030/wolf-20260329.htm</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>Med (financial distress clouds trajectory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>'Hundreds of workers already on site' per current coverage; JCC training cohorts begin summer 2026 as originally scheduled</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>2026-summer (training start)</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/sponsored/fifth-third-bank/the-next-industrial-revolution-how-vulcan-elements-makes-nc-the-backbone-of-vital-global-market/</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — proposed merger</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. Commissioners' vote (delayed 90 days from 2026-05-04, targeted ~early Aug 2026) still not scheduled as of this report; opposition mounting (cost-impact study, Patients Union, NC Justice Center, NAACP)</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04 (delay announced)</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wakemed-atrium-merger-costs-opposition-july-2026/</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar, existing)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>RISK ESCALATING: hangar still largely idle as of June 2026; CEO says production starts 'in about two years'; company separately pursuing a Colorado data-center initiative, raising questions about Greensboro focus; deadline now 6 months away with no positive movement</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>High (risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed NC-specific)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (newly disclosed; sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Wage now disclosed (exceeds $65k) but still sub-$100k; per-site (incl. Wilmington-specific) job allocation still not broken out</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.corning.com/worldwide/en/about-us/news-events/news-releases/2026/06/amazon-announces-agreement-with-corning-to-boost-us-fiber-optics-manufacturing-creating-1000-advanced-manufacturing-jobs-in-north-carolina.html</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>On track: first equipment arrival end of 2026, first parts production mid-2027, hiring ramp begins mid-2027</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>2026 (equipment arrival timeline)</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/engines/2026/04/rtx-says-gtf-groundings-are-coming-down-thanks-to-maintenance-ramp/</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>$20M</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>$55,133 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle despite targeted searches</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25 (orig.)</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>GNF4 fuel fabrication began early 2026; lead-use assemblies scheduled for deployment in commercial reactors during 2026 — genuine in-window production milestones, jobs still undisclosed</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>2026 (fabrication start)</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>https://www.world-nuclear-news.org/articles/global-nuclear-fuel-unveils-new-gnf4-product</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>$40-60M</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Mixed)</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturing-operations start slipped from 2026 to early 2027; HQ campus itself already opened</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>~2026 (HQ opening); early 2027 (mfg slip)</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Operations confirmed online as of April 2026</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>No update on headcount found this cycle</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (unchanged)</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>$1.0B (existing)</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed ($54-64k assemblers; eng. likely higher)</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Rate confirmed at 8/month as of Jan 2026 (up from 5/month a year prior); full 10/month target now more likely 2027 than fully sustained through 2026</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal Phase 2 (OPERATIONS PAUSED)</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect (unchanged projection)</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B (terminal, existing)</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mixed, some 6-figure specialist roles)</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>REVERSAL: SC Ports announced 2026-06-25 it will pause ALL Leatherman Terminal operations starting Aug. 1, 2026, citing high ILA labor costs and weak container volume; cargo consolidates to Wando Welch/North Charleston terminals; Phase 2 wharf construction reportedly continues toward 2027 completion but no operations-resumption timeline given</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>High (risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — 1-yr anniversary</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>~250 (estimate, not re-confirmed)</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>One-year operations anniversary reached 2026-01-22; company reports exceeding production targets, but no updated job-count figure surfaced</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>5,100 (proj. total); 3,000+ now employed</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>$13.9B</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>$62,234 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: employment crossed 3,000+ workers (Feb 2026 milestone); all-EV battery line targeted to launch later 2026, plug-in hybrid line mid-2027; scale of hiring velocity in a rural county may pressure workforce housing despite sub-$100k wage</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfmynews2.com/article/news/local/major-milestone-over-3000-people-now-work-at-the-toyota-battery-plant/83-b192b700-91b7-42f4-837e-33d0c01ee96e</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark Strategies "Project Moc-1" — AI/HPC data center</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>~150 FT at full operation (revised up from ~27); 400-600 temporary construction</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>$2.8B</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: jobs figure revised upward; contested public hearing held 2026-06-25 (SCDES comment period through 2026-07-31); power-capacity expansion request (48MW-&gt;450MW) under review</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/news/spartanburg-sc-data-center-northmark-power-tax/article_c3e02eef-fe42-4fda-9bd6-df50ec79a3ed.html</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>Med (contested/evolving)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (AI/data-center power supply chain)</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired 2025, ~300 more targeted by end 2026</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville); part of $600M multi-site plan</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed — production/technician roles ~$45-56k; specialist/eng. roles $91k-$226k (Glassdoor); bulk of new hires likely sub-$100k</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: in-window (2026-06-27) hiring-ramp confirmation; original Jan-2025 investment announcement was pre-window</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension (incentive-timeline extension)</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: NC Economic Investment Committee granted a four-year extension on hiring/investment timelines (April 2026) restarting the 2021 deal (up to $845M in potential tax benefits if targets met); no active construction found</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/apple-delays-construction-on-552-million-rtp-campus/</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med (long-delayed, no active construction)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7439,7 +11637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9468,6 +13666,636 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Maersk North American HQ</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; in-window milestone remains a 1-year hiring delay (2027-2029) confirmed again this cycle; wage now disclosed at $100,962 (just above $100k) but a delay is not qualifying forward movement per report rules</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; in-window milestone (3/16/26 grand opening) ties to a prior-year commitment, not a new 500+ award — consistent with this dataset's baseline-report exclusion rule</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>TigerDC "Project Spero" (WITHDRAWN)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>~50 FTE (Phase I)</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>REVERSAL: Spartanburg County Council voted down the tax incentive; TigerDC formally withdrew the $3.0B project — removed from Watch tier this cycle</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/02/27/company-withdraws-ai-data-center-spartanburg-county-consideration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>PSA Airlines</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT)</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>~400-450 (mix reloc.+new; ~250 net new)</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update; net new local roles (~250) remain well below 500-job threshold; wage mixed/mostly sub-$100k except pilots</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>https://psaairlines.com/psa-airlines-celebrates-grand-opening-of-charlotte-headquarters-underscoring-economic-and-workforce-impact-across-north-carolina/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors HQ (Plaza Midwood)</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; no confirmed dated in-window milestone found (only vague 'spring/summer 2026 build-out' reporting) — recheck next cycle for a concrete groundbreaking/permit date</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.detroitnews.com/story/business/autos/2025/11/14/scout-motors-rolls-into-charlotte-5-key-things-about-the-automaker/87270881007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Bosch — Dorchester Co. electric motors</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Dorchester</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>n/d (workforce 1,500-&gt;1,800)</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Incremental headcount growth only; expansion physically paused due to EV slowdown; no discrete new-jobs announcement found</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/business/bosch-dorchester-electric-vehicles-rivian-expansion/article_265b1c36-ab6c-11ef-b047-3b784368d210.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Compass Datacenters</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Statesville (Iredell)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>~250</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Announcement and rezoning both pre-window; no new 2026 milestone found</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Southeastern Container</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Enka-Candler (Buncombe)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>In-window but far below the 200-job Watch floor</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Amazon robotics fulfillment center</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Pender/New Hanover</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; fulfillment-center wages well under $100k, no offsetting wage signal found</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Walmart — Mebane distribution center</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Alamance</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; wage $35,374 (well under $100k)</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>"3 medical textile manufacturers" (unnamed)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Winston-Salem (Forsyth)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>600+ (aspirational)</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Speculative — no specific company named; aspirational recruitment target only, not a qualifying announcement</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh (Wake)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (claimed)</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Re-checked this cycle: still unverifiable — only source is a non-authoritative relocation-marketing content site; no corroboration from Barclays, WRAL, Triangle Business Journal, NC Commerce, or Governor's office</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Novo Nordisk speculative Four Oaks expansion</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>~500 (speculative)</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>2025-10 (cancelled)</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Project cancelled after an annexation vote in Oct. 2025; also pre-window</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Numerous sub-200-job items (Shamrock Technologies, Meiden America Switchgear, Coastal Precast, Hydrite Chemical, Huwell US, Milliken Cherokee, DartPoints, Advanced Metalworks, Eastern Engineered Wood, DMA Industries, United Composite, Aran USA, Carbotech, Peabody Engineering, ZF Chassis, Idealworks, Transcom)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Various Upstate SC</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>13-450 each</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>2021-2026</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Below Watch floor regardless of window, or recycled old news (Transcom 2021, Bosch/Anderson 2022) with no in-window update</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Numerous sub-200-job items (SHL Medical, ATP Adhesives, Cardiff Products USA, The Nuclear Company, Carolina Renewable Products, AVM Group, Red Metals, Bittermilk Bottling, Modus21, Hoffman &amp; Hoffman Lexington, Eastover Chips, Leonardo DRS, Nucor Berkeley galvanizing)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Various Midlands/Lowcountry</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>12-220 each</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>2022-2026</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Below Watch floor and/or recycled old news with no in-window update</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9479,7 +14307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10272,6 +15100,222 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SC statewide</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth wage detail; Leatherman Terminal pause; Boeing rate-ramp</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Live5News / Berkeley Observer</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Charleston/Lowcountry SC</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>HII one-year anniversary; SC Ports Leatherman pause</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>SEC EDGAR filings</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>primary_filing</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 10-Q rate-ramp confirmation; Wolfspeed 10-Q post-bankruptcy status</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Post and Courier — Spartanburg/Greenville bureaus</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Upstate SC</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>TigerDC withdrawal; NorthMark Project Moc-1; AIRSYS timeline slip; GE Vernova; Suniva</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>World Nuclear News</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.world-nuclear-news.org/</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>National nuclear</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi GNF4 fuel-line fabrication start</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>WFMY News 2</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfmynews2.com/</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>NC Triad</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery Manufacturing NC 3,000-employee milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Corning press releases</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>https://www.corning.com/</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning fiber-optics partnership wage/job detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>WBTV / Fort Mill Sun (Charlotte-metro follow-up)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte metro &amp; York Co. SC</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma 3rd-reading vote; Maersk/Citigroup verification</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10283,7 +15327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10719,6 +15763,166 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>County-level 3rd reading approved but on a narrower 4-3 vote; Rock Hill City Council's vote on the amended tax-share terms remains outstanding — net -1 for continued execution uncertainty despite forward progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Active hiring push continues (new July 29 interview events, ~1,400 hired companywide); unchanged despite a mild timeline slip in customer deliveries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Wage figure upgraded from Estimated/Inferred to a stated $194,141 avg (NC Commerce JDIG record); +2 for removed wage-confidence discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking held (tangible positive) but JDIG amendment confirms hiring ramp pushed out further (full target now 2037 vs. 2036); net -2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-07-13  ·  Window 2026-01-13 to 2026-07-13  ·  NC + SC</t>
+          <t>Week of 2026-07-20  ·  Window 2026-01-20 to 2026-07-20  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13  (Week 3)</t>
+          <t>2026-07-20  (Week 4)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-01-13 to 2026-07-13  (trailing 6 months)</t>
+          <t>2026-01-20 to 2026-07-20  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 87 — county-level 3rd reading approved 4-3 but Rock Hill City Council's vote on amended tax-share terms remains outstanding</t>
+          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 88 (+1) — Rock Hill School Board voted 5-2 to back the amended tax-share terms; Rock Hill City Council's own vote remains outstanding</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>No brand-new qualifying (500+ job / $100k+ wage) deal was found in any of the five sub-regions this cycle — all 8 ranked entries carry forward. JetZero's groundbreaking is real construction progress even as its hiring ramp slips further (full target now 2037). SC Ports' decision to pause Leatherman Terminal operations Aug. 1 and Boom Supersonic's looming Dec. 31 hiring deadline are the cycle's clearest downside signals; TigerDC's $3.0B Spartanburg data center was formally withdrawn.</t>
+          <t>Second consecutive cycle with zero brand-new qualifying (500+ job / $100k+ wage) deals across all five sub-regions — all 8 ranked entries carry forward. JetZero gained an execution-certainty boost when Gov. Stein signed the FY2026-27 state budget (2026-07-07), releasing the previously-frozen $133.9M JDIG-linked funding. A data-quality correction: last week's Scout Motors '2026-07-29 hiring event' could not be corroborated as genuinely 2026-dated (it traces to matching 2025 wage/role details) and is now flagged unverified rather than carried forward as confirmed. Genentech's sole dated milestone (2026-01-20) now sits exactly at the trailing-6-month window boundary — watch for it to age out next cycle absent a new update. SC Ports' Leatherman Terminal pause remains on track for Aug. 1 with no reversal found.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-01-13 to 2026-07-13.</t>
+          <t>Trailing 6 months now runs 2026-01-20 to 2026-07-20.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Two near-miss candidates (Maersk — wage now disclosed at $100,962 but milestone is a hiring delay; Citigroup — grand opening tied to a pre-window commitment) were excluded for consistency with this dataset's established milestone rules rather than admitted on job count/wage alone.</t>
+          <t>Scout Motors' previously-reported 2026-07-29 pre-hire event could not be independently corroborated this cycle as a genuinely 2026-dated announcement — the wage/role details match 2025-07-10 and 2025-07-25 stories precisely. Treated as unverified/likely a dating error rather than confirmed. Two Watch-tier items (Snider Fleet Solutions, FN America) were dropped this cycle after 2-3 consecutive quiet cycles with zero forward movement; four new Watch-tier items were added (Isuzu North America, EPC Power Corp., BMW Plant Woodruff, Southern Glazer's Wine &amp; Spirits) — all clear the 500-job bar in Isuzu's/Southern Glazer's case but fail the $100k wage bar.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>8 of 8 prior-ranked deals remain qualifying (none removed, none newly added); 1 gaining momentum (Scout Motors), 2 updated-mixed (Octapharma, JetZero), 1 updated (Capital Group, wage confirmation), 4 repeated (SMBC, AbbVie, Genentech, Novartis).</t>
+          <t>8 of 8 prior-ranked deals remain qualifying (none removed, none newly added); 1 gaining momentum (Octapharma, +1), 1 updated (AbbVie — county incentive hearing), 1 updated (JetZero, +1 — state budget funding release), 5 repeated (SMBC, Scout Motors, Capital Group, Genentech, Novartis).</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2083,7 +2083,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -2174,7 +2174,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -2265,7 +2265,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2356,7 +2356,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -2447,7 +2447,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
@@ -2538,7 +2538,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -2629,7 +2629,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -2720,7 +2720,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -2803,6 +2803,734 @@
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill School Board endorsement of amended tax-share terms; City Council vote still outstanding</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fortmillsun.com/2026/07/13/rock-hill-schools-board-urges-city-to-accept-county-tax-allocations/</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (deal certainty)</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>Hiring event announced; companywide headcount update</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/scout-motors-plant-blythewood-update/101-c64d17ed-4b85-4fae-b866-e7e1a08021f1</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>County incentive hearing (procedural step, no scale change)</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>https://abc11.com/post/abbvie-pharmaceutical-project-moves-forward-durham/19500900/</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>Wage figure confirmed (stated, not inferred)</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
         <is>
           <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
         </is>
@@ -2819,7 +3547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4597,7 +5325,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -4713,7 +5441,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -4829,7 +5557,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -4945,7 +5673,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5061,7 +5789,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -5177,7 +5905,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -5293,7 +6021,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -5409,7 +6137,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -5517,6 +6245,934 @@
         </is>
       </c>
       <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Leased former One Wells Fargo Center; hiring 70+ roles; first workers fall 2026</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle (second consecutive quiet cycle); project remains on track for fall 2026 first arrivals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Gaining Momentum</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill School Board endorsement of amended tax-share terms; City Council vote still outstanding</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>York County Council 3rd reading approved 2026-07-08 (4-3); Rock Hill School Board voted 5-2 on 2026-07-13 to back the amended tax-share structure and urge City Council to accept it; Rock Hill City Council has still not voted as of 2026-07-20 (unconfirmed reporting points to an Aug. 10, 2026 council agenda — not independently verified)</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fortmillsun.com/2026/07/13/rock-hill-schools-board-urges-city-to-accept-county-tax-allocations/</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (deal certainty)</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X25" s="6" t="inlineStr">
+        <is>
+          <t>School board's 5-2 endorsement removes one point of local opposition, but Rock Hill City Council's outstanding vote on the amended tax-share terms remains the key unresolved risk; +1 for continued forward momentum with no new negative signal this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Hiring event announced; companywide headcount update</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Projected (~1,400 hired companywide; 600+ in SC)</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Companywide headcount holds at ~1,400 (~600 in SC), confirmed via WLTX and Scout's own blog as of mid-July 2026; production still targeted late 2027, customer deliveries trending 2028</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/scout-motors-plant-blythewood-update/101-c64d17ed-4b85-4fae-b866-e7e1a08021f1</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W26" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION: last week's report cited a 2026-07-29 pre-hire event for 70+ maintenance techs; this cycle's research found the wage/role details trace precisely to a 2025-07-10 WISTV story and a 2025-07-25 SC Daily Gazette story, with no distinctly-dated 2026 version found — that specific claim is now treated as unverified/likely a dating error and is not carried forward. Headcount and the active-hiring trend remain independently confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>County incentive hearing (procedural step, no scale change)</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Durham County Board of Commissioners held a public hearing 2026-07-13 on a proposed $15M county incentive package (on top of the ~$26M state EIC incentive approved in April); no vote outcome reported yet</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>https://abc11.com/post/abbvie-pharmaceutical-project-moves-forward-durham/19500900/</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X27" s="6" t="inlineStr">
+        <is>
+          <t>Procedural incentive step, not a scale change; construction start still targeted this year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Wage figure confirmed (stated, not inferred)</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>12-yr JDIG term; lease term began 2026-05-22</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W28" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+      <c r="X28" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Operational by 2029</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W29" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+        </is>
+      </c>
+      <c r="X29" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; the sole dated milestone (2026-01-20 investment doubling) sits exactly at this week's window boundary (2026-01-20 to 2026-07-20) — still inclusive, but flagged as at risk of aging out of the window next cycle absent a new update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking held 2026-06-15; zero jobs still projected for 2027; hiring ramp begins 2028-2029 (3,020 jobs by end 2029); full 14,500+ target due by 2037; Governor Stein signed the FY2026-27 state budget on 2026-07-07, releasing the previously-frozen $133.9M JDIG-linked infrastructure allocation (on top of $118.1M already allotted) — company communications called it 'all systems go'</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="U30" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W30" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
+        </is>
+      </c>
+      <c r="X30" s="6" t="inlineStr">
+        <is>
+          <t>+1 for confirmed release of state incentive funding (an execution-certainty signal), though the hiring-ramp timeline itself is unchanged from last cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Facility opening targeted 2027-2028</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V31" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr">
         <is>
           <t>No new in-window milestone found this cycle.</t>
         </is>
@@ -5533,7 +7189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9087,7 +10743,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -9149,7 +10805,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -9211,7 +10867,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -9273,7 +10929,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -9335,7 +10991,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -9397,7 +11053,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -9459,7 +11115,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -9521,7 +11177,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -9583,7 +11239,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -9645,7 +11301,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -9707,7 +11363,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -9769,7 +11425,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -9831,7 +11487,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -9893,7 +11549,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -9955,7 +11611,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -10017,7 +11673,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -10079,7 +11735,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -10141,7 +11797,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -10203,7 +11859,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -10265,7 +11921,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -10327,7 +11983,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -10389,7 +12045,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -10451,7 +12107,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -10513,7 +12169,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -10575,7 +12231,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -10637,7 +12293,7 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -10699,7 +12355,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -10761,7 +12417,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -10823,7 +12479,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -10885,7 +12541,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -10947,7 +12603,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -11009,7 +12665,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -11071,7 +12727,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -11133,7 +12789,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -11195,7 +12851,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -11257,7 +12913,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -11319,7 +12975,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -11381,7 +13037,7 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -11443,7 +13099,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -11505,7 +13161,7 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -11567,7 +13223,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -11623,6 +13279,2672 @@
       <c r="L98" s="6" t="inlineStr">
         <is>
           <t>Low-Med (long-delayed, no active construction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Still just under 500 jobs; no threshold-crossing update found this cycle (high-priority check)</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy — groundbreaking held</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone since May 2026 groundbreaking; first lines targeted Q1 2029</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co.</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Suniva — solar-cell plant</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>Stated $23-$53/hr = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; operations targeted spring/summer 2027</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>Ribbon-cutting/opening ceremony held late April 2026 for the 240,000 sq ft facility; production ramp still targeted mid-2028</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>https://myfox8.com/news/north-carolina/greensboro/lumentum-holdings-opens-new-manufacturing-facility-in-greensboro/</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>Now corroborated via official NC Commerce/Governor press releases dated 2026-05-26, resolving prior cycle's uncorroborated flag</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>'high-tech, high-wage' but figure Not disclosed (Inferred mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>Eaton recruiting at WNC Career Expo 2026-04-16; confirmed as 7th Helene-recovery manufacturer expansion</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; Mecklenburg-specific allocation for this tranche remains unclear (conflated with a 2024 tranche in some coverage)</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals uncertain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>New 101,000 sq ft Wendell facility coming online July 2026; Knightdale targeting 100 jobs by end 2026; expanded Wendell campus (+200 jobs) by 2028</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>Reaffirmed 2026-01-28 via White House-linked event; construction underway on west campus, facility slated to open within the next year</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>https://greensboro.com/news/local/business/development/article_f8077494-ba1d-526b-a82a-9d8425f0acbe.html</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>York Co.</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>QTS "Project Cobra" — data-center campus</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>~200 FTE (+~1,000 constr.)</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>up to $8B</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>~$80k median (stated)</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>York County's nine-month data-center moratorium received FINAL passage 2026-07-14 (6-0); it bars new site plans/special exceptions/CUPs for data centers in unincorporated York Co. through ~April 2027 but explicitly exempts projects with vested rights — QTS's under-construction buildings are understood to be unaffected</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrhi.com/2026/07/york-county-council-approves-nine-month-data-center-moratorium-214184</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>~160 apprentices (FTE n/d)</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; original Oct. 2025 announcement remains the latest news</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>High (capex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>Still unverified; outside this cycle's five assigned research regions — needs direct confirmation next cycle</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aboutamazon.com/</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>Low (needs verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>RECONCILED this cycle: the previously-flagged second figure (~30 projects/8,000-10,800 jobs/$5.6B) is confirmed to be the closed, prior EDGE 6 campaign (concluded ~Sept 2024) — sequential, not duplicative, with the current $11B/11,000-job EDGE 7 pipeline</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — new office (1,000-employee bldg)</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>400 new by 2028</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred (job-posting range)</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters Inc. — "Project Rack" distribution hub (identity confirmed)</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>200+ (per 2026-07-17 announcement; county incentive filing cited 258)</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>$57,351 avg for ~70 skilled roles (stated); bulk of the 200+ workforce likely lower (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>Company identity confirmed 2026-07-17: American Eagle Outfitters Inc., $41M, 472,890 sq ft distribution hub at Innovation Logistics Center, 1415 Peeler Road, Salisbury; Q1 2027 ops start unchanged</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (DHL postings)</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; jobs still undisclosed</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>https://www.salisburypost.com/2026/05/02/not-a-data-center-google-leases-rowan-county-side-kannapolis-industrial-site/</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant Corp. — global HQ launch</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>$170k-$189k avg (stated)</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Siler City</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed — silicon-carbide fab</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>1,800 (proj.)</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>$5.0B</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>$77,753 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>Post-bankruptcy ramp described by the company as 'more measured/disciplined' — original full-occupancy March 2026 target appears to have slipped; SiC crystal growth/wafer shipments to Mohawk Valley (NY) underway</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>2026-Q1 (10-Q)</t>
+        </is>
+      </c>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0000895419/000089541926000030/wolf-20260329.htm</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>Med (financial distress clouds trajectory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>'Hundreds of workers already on site' per current coverage; JCC training cohorts begin summer 2026 as originally scheduled</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>2026-summer (training start)</t>
+        </is>
+      </c>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/sponsored/fifth-third-bank/the-next-industrial-revolution-how-vulcan-elements-makes-nc-the-backbone-of-vital-global-market/</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — proposed merger</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>Vote still not scheduled as of 2026-07-20; the 90-day delay from 2026-05-04 points to early August 2026; opposition continues (Brown University School of Public Health cost-impact report, community groups)</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04 (delay announced)</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wakemed-atrium-merger-costs-opposition-july-2026/</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar, existing)</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>No positive or negative movement found this cycle; hangar still largely idle, and the Dec. 31, 2026 500-employee deadline is now roughly five months away with no confirmed hiring progress</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>High (risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed NC-specific)</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (newly disclosed; sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>Wage now disclosed (exceeds $65k) but still sub-$100k; per-site (incl. Wilmington-specific) job allocation still not broken out</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>https://www.corning.com/worldwide/en/about-us/news-events/news-releases/2026/06/amazon-announces-agreement-with-corning-to-boost-us-fiber-optics-manufacturing-creating-1000-advanced-manufacturing-jobs-in-north-carolina.html</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>On track: first equipment arrival end of 2026, first parts production mid-2027, hiring ramp begins mid-2027</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>2026 (equipment arrival timeline)</t>
+        </is>
+      </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/engines/2026/04/rtx-says-gtf-groundings-are-coming-down-thanks-to-maintenance-ramp/</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>$20M</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>$55,133 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle despite targeted searches</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25 (orig.)</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+        </is>
+      </c>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>GNF4 fuel fabrication began early 2026; lead-use assemblies scheduled for deployment in commercial reactors during 2026 — genuine in-window production milestones, jobs still undisclosed</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>2026 (fabrication start)</t>
+        </is>
+      </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>https://www.world-nuclear-news.org/articles/global-nuclear-fuel-unveils-new-gnf4-product</t>
+        </is>
+      </c>
+      <c r="L126" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>$40-60M</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Mixed)</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturing-operations start slipped from 2026 to early 2027; HQ campus itself already opened</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>~2026 (HQ opening); early 2027 (mfg slip)</t>
+        </is>
+      </c>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>Operations confirmed online as of April 2026</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>No update on headcount found this cycle</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
+        </is>
+      </c>
+      <c r="L130" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (unchanged)</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>$1.0B (existing)</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed ($54-64k assemblers; eng. likely higher)</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>Rate confirmed holding steady at 8/month as of the Farnborough Airshow (mid-July 2026); 10/month target reaffirmed 'over the next year' — consistent with, not accelerating beyond, prior framing</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>https://leehamnews.com/2026/07/16/bca-riding-recovery-momentum-into-farnborough-air-show/</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal Phase 2 (OPERATIONS PAUSED)</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect (unchanged projection)</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B (terminal, existing)</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mixed, some 6-figure specialist roles)</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>No reversal found; pause remains on track for Aug. 1, 2026 start (~5% of container volume / 5 weekly MSC calls affected); cargo shifting to Wando Welch/North Charleston terminals; no operations-resumption timeline given</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+        </is>
+      </c>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>High (risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — 1-yr anniversary</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>~250 (estimate, not re-confirmed)</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>One-year operations anniversary reached 2026-01-22; company reports exceeding production targets, but no updated job-count figure surfaced</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>5,100 (proj. total); 3,000+ now employed</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>$13.9B</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>$62,234 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: employment crossed 3,000+ workers (Feb 2026 milestone); all-EV battery line targeted to launch later 2026, plug-in hybrid line mid-2027; scale of hiring velocity in a rural county may pressure workforce housing despite sub-$100k wage</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfmynews2.com/article/news/local/major-milestone-over-3000-people-now-work-at-the-toyota-battery-plant/83-b192b700-91b7-42f4-837e-33d0c01ee96e</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark Strategies "Project Moc-1" — AI/HPC data center</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>~150 FT at full operation (revised up from ~27); 400-600 temporary construction</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>$2.8B</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>SCDES air-permit comment period remains open through 2026-07-31; residents and the SC Environmental Law Center filed a lawsuit challenging the county's 'minor development' approval (hearing scheduled 2026-07-30 in Columbia); Spartanburg County Council separately gave first-reading approval to a one-year moratorium on new data-center proposals</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/07/08/lawsuit-targets-spartanburg-county-data-center-project-demands-public-planning-review/</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>Med (contested/evolving; litigation adds new risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (AI/data-center power supply chain)</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired 2025, ~300 more targeted by end 2026</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville); part of $600M multi-site plan</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed — production/technician roles ~$45-56k; specialist/eng. roles $91k-$226k (Glassdoor); bulk of new hires likely sub-$100k</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: in-window (2026-06-27) hiring-ramp confirmation; original Jan-2025 investment announcement was pre-window</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
+        </is>
+      </c>
+      <c r="L136" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension (incentive-timeline extension)</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: NC Economic Investment Committee granted a four-year extension on hiring/investment timelines (April 2026) restarting the 2021 deal (up to $845M in potential tax benefits if targets met); no active construction found</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/apple-delays-construction-on-552-million-rtp-campus/</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med (long-delayed, no active construction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu North America Corp. — production facility (medium-duty trucks)</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k (Assembly Operator postings $52k-$72k; Quality Eng. $66k-$85k)</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>$283M JBIC/MUFG construction loan disbursed 2026-06-30; direct-hire event for 150+ positions held 2026-07-08 at Greenville Tech; production starts 2027, capacity 50,000 units/yr by 2030</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>https://www.automotiveworld.com/news/isuzu-secures-us283m-loan-for-south-carolina-plant/</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Fountain Inn</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>EPC Power Corp. — power-conversion/inverter manufacturing facility</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (site-specific)</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k (Mfg/Test/Eng Tech postings $47k-$66k; Production Mgr $95k-$120k)</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>Facility opened 2026-07-15, ramping to full capacity within the month; serves AI data-center and grid-infrastructure customers</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/07/15/epc-power-opens-facility-upstate-produce-critical-ai-data-center-technology/</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>BMW Group — Plant Woodruff high-voltage battery assembly</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>~300 (Woodruff-specific, part of $1.7B total)</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>$700M (Woodruff portion of $1.7B)</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k (~$43,169 avg per ZipRecruiter)</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>Completion celebrated 2026-07-01/07-02 ('Home of X' event, new BMW X5 premiere); iX5 EV production starts late 2026</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>https://www.press.bmwgroup.com/global/article/detail/T0458864EN/</t>
+        </is>
+      </c>
+      <c r="L140" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>West Columbia</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits — distribution facility</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>500+ (stated)</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>$80M</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred sub-$100k (warehouse/distribution roles typically $35k-$55k)</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>412,500 sq ft facility on 85 acres opened 2026-02-10/02-11 (originally planned fall 2026, opened early)</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/columbia/business/wine-liquor-distributor-facility-west-columbia/article_60829410-b73e-47b4-9f46-f9c2dc79317c.html</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11637,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13669,7 +17991,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -13711,7 +18033,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -13753,7 +18075,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -13795,7 +18117,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -13837,7 +18159,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -13879,7 +18201,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -13921,7 +18243,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -13963,7 +18285,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -14005,7 +18327,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -14047,7 +18369,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -14089,7 +18411,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -14131,7 +18453,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -14173,7 +18495,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -14215,7 +18537,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -14257,7 +18579,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -14293,6 +18615,426 @@
       <c r="H63" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Snider Fleet Solutions</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Indian Land</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed stale after 3 cycles tracked on Watch — all coverage traces to 2023 relocation, completed/operational by June 2023; no 2026 developments found — removed from Watch tier</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>FN America</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Liberty (Pickens)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>~176</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Third consecutive quiet cycle with zero forward movement — removed from Watch tier per the report's 2-cycle flag</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Reynolds American — Tobaccoville Operations Center</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Tobaccoville (Forsyth)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Site-specific 200-job figure is pre-window (Dec 2025); a March 2026 $3.2B multi-site reinvestment announcement is in-window but not broken out by site; wage (~$47k-$55k) well under $100k regardless</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfmynews2.com/article/news/local/reynolds-announces-200-new-jobs-coming-tobaccoville-operations-center/83-230e6897-51d9-4eeb-83e2-f486f0a759c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>AdvanceTEC</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Clayton/Smithfield (Johnston)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>160 jobs below the 200-job Watch floor; wage ~$90,000 also below the $100k bar despite the in-window groundbreaking</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/07/french-cleanroom-giant-drops-160-high-paying-jobs-into-johnston-county/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>FUJIFILM Diosynth Biotechnologies expansion</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs (Wake)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news — original announcement dated 2024-04-11, well outside the 6-month window; no in-window update found</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2024/04/11/fujifilm-diosynth-biotechnologies-expands-holly-springs-facility-create-one-largest-end-end-cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Cielo Digital Infrastructure "Project Kingfisher"</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Gaffney (Cherokee)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>$2.1B capex but only 30 confirmed jobs — far below the 200-job Watch floor despite being described as the largest-ever Cherokee County investment</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/briefs/cherokee-county-inks-2-1b-deal-with-data-center-developer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Multiple recycled Lowcountry items (Volvo Ridgeville XC60/hybrid expansion, Mercedes-Benz Ladson CKD expansion, Roper St. Francis $1.2B hospital campus)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley/Dorchester/Charleston</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>various (2025)</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>All trace to pre-window announcements (Sept 2025, Dec 2025, and June 2025 respectively) with no in-window milestone found despite active search this cycle</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>ProKidney — Greensboro manufacturing plant (WITHDRAWN)</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro (Guilford)</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>330 (orig., never tracked)</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>Company ended its pursuit of the Greensboro plant and sold the site (June 2026) — closure/withdrawal noted for completeness only; never previously tracked since it never met the qualifying bar</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>https://journalnow.com/news/local/business/health-care/prokidney-greensboro-manufacturing-plant/article_e77df70a-d8c9-11ef-82c8-a347d4b0b442.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh (Wake)</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (claimed)</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Re-checked again this cycle across Barclays newsroom, NC Governor, Wake County, EDPNC, and NC Commerce — still no authoritative primary source, only recirculating non-authoritative blog/social posts</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Frontier Scientific Solutions</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington (New Hanover)</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>~80 (current)</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Current headcount (~80) is well below even the 200-job Watch floor; CEO's 'likely exceed 500' figure is a speculative, undated future-phase projection, not a confirmed commitment — noted for context only</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/03/18/amazon_facility_regional_projects_forecast_to_bring_hundreds_of_jobs_to_wilmington_area/27315</t>
         </is>
       </c>
     </row>
@@ -14307,7 +19049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15316,6 +20058,411 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Fort Mill Sun (Rock Hill school board)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fortmillsun.com/2026/07/13/</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte-metro SC (York Co.)</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — Rock Hill School Board 5-2 endorsement</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ABC11 / AOL / Yahoo News mirrors</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>https://abc11.com/</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>NC Triangle</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — Durham County incentive hearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Carolina Journal (state budget)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>NC statewide</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — FY2026-27 budget signing, $133.9M JDIG funding release</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>WLTX (Columbia)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wltx.com/</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>SC Midlands</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — mid-July headcount reconfirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>NC Governor's Office (Rowan)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>state_primary</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/07/17/</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>NC statewide</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters — Rowan Co. distribution hub (Project Rack identity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>WRHI (York County moratorium)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>regional_edo/journal</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrhi.com/</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>York Co. SC</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>York County data-center moratorium final passage</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Fox Carolina (Spartanburg litigation)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Upstate SC</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark Project Moc-1 lawsuit; EPC Power opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Automotive World</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.automotiveworld.com/</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>National automotive</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu North America — Piedmont SC loan/hiring event</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>BMW Group press office</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.press.bmwgroup.com/</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>BMW Plant Woodruff completion event</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Post and Courier — Columbia bureau (Southern Glazer's)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/columbia/</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>SC Midlands</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits West Columbia opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Leeham News (Farnborough coverage)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>https://leehamnews.com/</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>National aerospace</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 rate confirmation at Farnborough Airshow</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>WFMY News 2 (Reynolds American)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfmynews2.com/</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>NC Triad</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Reynolds American Tobaccoville jobs (excluded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Hoodline (AdvanceTEC, RTP 3.0)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>NC Triangle/Triad</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>AdvanceTEC Johnston Co. groundbreaking; RTP 3.0 framework approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>journalnow.com (Winston-Salem Journal)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>https://journalnow.com/</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>NC Triad</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>ProKidney Greensboro plant withdrawal</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette (Cielo Digital Infrastructure)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Upstate SC</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Cielo Digital Infrastructure Cherokee Co. data center</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15327,7 +20474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15766,7 +20913,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -15786,7 +20933,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -15806,7 +20953,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -15826,7 +20973,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -15846,7 +20993,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -15866,7 +21013,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -15886,7 +21033,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -15906,7 +21053,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -15918,6 +21065,166 @@
         <v>77</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle (second consecutive quiet cycle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill School Board's 5-2 endorsement of the amended tax-share terms is genuine forward momentum without a new negative signal; Rock Hill City Council's outstanding vote remains the key risk — net +1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Headcount and active-hiring trend reconfirmed unchanged; a previously-cited 2026-07-29 hiring-event date could not be corroborated as genuinely 2026-dated and is now treated as unverified — no score impact since the broader hiring signal stands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; county incentive hearing is a procedural step, not a scale change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; sole dated milestone now sits exactly at the trailing-6-month window boundary — flagged for likely drop-out next cycle absent a new update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>State budget signed 2026-07-07 releases the previously-frozen $133.9M JDIG-linked funding (execution-certainty positive); hiring-ramp timeline itself unchanged — net +1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Unchanged; no new milestone this cycle.</t>
         </is>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-07-20  ·  Window 2026-01-20 to 2026-07-20  ·  NC + SC</t>
+          <t>Week of 2026-07-27  ·  Window 2026-01-27 to 2026-07-27  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20  (Week 4)</t>
+          <t>2026-07-27  (Week 4)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-01-20 to 2026-07-20  (trailing 6 months)</t>
+          <t>2026-01-27 to 2026-07-27  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 88 (+1) — Rock Hill School Board voted 5-2 to back the amended tax-share terms; Rock Hill City Council's own vote remains outstanding</t>
+          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 90 (+3) — Rock Hill City Council's unanimous 7-0 vote on 2026-07-23 (rezoning, land sale, tax-incentive resolution) resolves the deal's last major outstanding risk</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Second consecutive cycle with zero brand-new qualifying (500+ job / $100k+ wage) deals across all five sub-regions — all 8 ranked entries carry forward. JetZero gained an execution-certainty boost when Gov. Stein signed the FY2026-27 state budget (2026-07-07), releasing the previously-frozen $133.9M JDIG-linked funding. A data-quality correction: last week's Scout Motors '2026-07-29 hiring event' could not be corroborated as genuinely 2026-dated (it traces to matching 2025 wage/role details) and is now flagged unverified rather than carried forward as confirmed. Genentech's sole dated milestone (2026-01-20) now sits exactly at the trailing-6-month window boundary — watch for it to age out next cycle absent a new update. SC Ports' Leatherman Terminal pause remains on track for Aug. 1 with no reversal found.</t>
+          <t>Octapharma's Rock Hill City Council vote finally cleared 7-0 on 2026-07-23, fully closing out the region's most-watched pending approval. Citigroup's Ballantyne office is promoted to Ranked this cycle on the strength of a confirmed in-window hiring ramp (~400 of 510 roles filled) — the first tier promotion of a previously excluded deal since SMBC in Week 2. JetZero landed a non-binding EXIM Letter of Interest exploring up to $3B in federal financing, a modest positive that does not resolve its hiring-ramp delay. Two reversals: SC Ports' Leatherman Terminal pause is now confirmed effective Aug. 1 with no reopening timeline, and Pallidus's $443M Rock Hill semiconductor project was confirmed cancelled (37 laid off).</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-01-20 to 2026-07-20.</t>
+          <t>Trailing 6 months now runs 2026-01-27 to 2026-07-27.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Scout Motors' previously-reported 2026-07-29 pre-hire event could not be independently corroborated this cycle as a genuinely 2026-dated announcement — the wage/role details match 2025-07-10 and 2025-07-25 stories precisely. Treated as unverified/likely a dating error rather than confirmed. Two Watch-tier items (Snider Fleet Solutions, FN America) were dropped this cycle after 2-3 consecutive quiet cycles with zero forward movement; four new Watch-tier items were added (Isuzu North America, EPC Power Corp., BMW Plant Woodruff, Southern Glazer's Wine &amp; Spirits) — all clear the 500-job bar in Isuzu's/Southern Glazer's case but fail the $100k wage bar.</t>
+          <t>A prior-cycle fact was corrected: Scout Motors' '70+ maintenance-tech interview event beginning 7/29' traces to July 2025, not 2026 — no 2026 repeat was found, though independent April/June 2026 hiring and production milestones (Training Center opening, first vehicle body weld) confirm continued momentum. Two strong near-misses were added to Watch rather than Ranked: Aspida Financial (Durham, 1,000 jobs, $137,288 stated wage, but its only announcement predates the window) and VinFast (Chatham, job count cut to 1,400 with a stated wage well under $100k, now further complicated by a state lawsuit).</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>8 of 8 prior-ranked deals remain qualifying (none removed, none newly added); 1 gaining momentum (Octapharma, +1), 1 updated (AbbVie — county incentive hearing), 1 updated (JetZero, +1 — state budget funding release), 5 repeated (SMBC, Scout Motors, Capital Group, Genentech, Novartis).</t>
+          <t>8 of 8 prior-ranked deals remain qualifying; 1 promoted from Excluded to Ranked (Citigroup); 1 updated with a major positive resolution (Octapharma, +3); 1 updated (JetZero, non-binding financing signal, score flat); 1 gaining momentum (Scout Motors); 5 repeated (SMBC, AbbVie, Capital Group, Genentech, Novartis); none removed from Ranked. Watch tier: 1 removed as confirmed-stale (Snider Fleet Solutions); 3 new candidates added (BMW Woodruff, Aspida Financial, VinFast); Pallidus confirmed cancelled (stays in Excluded/Noise as a reversal).</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2083,7 +2083,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -2174,7 +2174,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -2265,7 +2265,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2356,7 +2356,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -2447,7 +2447,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
@@ -2538,7 +2538,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -2629,7 +2629,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -2720,7 +2720,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -2811,7 +2811,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Lease signed / active hiring milestone (unchanged)</t>
+          <t>Lease signed / active hiring milestone</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
@@ -2902,14 +2902,14 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (fully approved)</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -2956,27 +2956,27 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
+          <t>Fee-in-lieu-of-tax; Rock Hill forgoes ~85% of its project tax share; York County contributes 10% of its EDA fund revenue; ~$80M directed to Rock Hill Schools over 40 yrs</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill School Board endorsement of amended tax-share terms; City Council vote still outstanding</t>
+          <t>Final city + county approval (rezoning, land sale, tax-incentive resolution)</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/13/rock-hill-schools-board-urges-city-to-accept-county-tax-allocations/</t>
+          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Med (deal certainty)</t>
+          <t>High (facts); High (deal certainty — now fully approved)</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH. Approval removes the deal's last major execution risk.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
+          <t>Scout Motors — EV assembly plant (training center opens; first body weld)</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
+          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Hiring event announced; companywide headcount update</t>
+          <t>Training-center opening + production-validation milestone</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/scout-motors-plant-blythewood-update/101-c64d17ed-4b85-4fae-b866-e7e1a08021f1</t>
+          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
@@ -3084,7 +3084,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>County incentive hearing (procedural step, no scale change)</t>
+          <t>New facility (greenfield, 185 ac)</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>https://abc11.com/post/abbvie-pharmaceutical-project-moves-forward-durham/19500900/</t>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
@@ -3175,7 +3175,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Capital Group — East Coast operations hub</t>
+          <t>Capital Group — East Coast ops hub</t>
         </is>
       </c>
       <c r="H28" s="6" t="n">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+          <t>$194,141 avg (stated)</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Wage figure confirmed (stated, not inferred)</t>
+          <t>Lease commenced</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+          <t>https://businessnc.com/capital-group-picks-its-uptown-charlotte-spot-for-600-workers</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, 2025 tranche)</t>
+          <t>~$119,833 avg (stated, original 2025 tranche)</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B</t>
+          <t>~$2.0B (doubled from ~$700M)</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -3350,21 +3350,21 @@
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
         <v>7</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
+          <t>JetZero — aerospace plant (EXIM financing exploration)</t>
         </is>
       </c>
       <c r="H30" s="6" t="n">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
+          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr; EXIM exploring up to $3B financing (non-binding)</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
+          <t>Letter of Interest for federal financing</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/jetzero-exim-explore-3b-financing-manufacturing-campus</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
@@ -3441,14 +3441,14 @@
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
+          <t>Same long-run scale as prior cycles; the financing signal is a modest positive but does not resolve the hiring-ramp delay.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Novartis — API mfg building (investment increase)</t>
+          <t>Novartis — API mfg building</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>~$991M (incl. $220M API building)</t>
+          <t>~$991M (incl. $220M)</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>Part of original $771M package incentives</t>
+          <t>State/local incentive package (Wake/Durham)</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>New facility (unchanged)</t>
+          <t>Investment increase (prior cycle)</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
@@ -3532,7 +3532,98 @@
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in the Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Ballantyne regional office (grand opening + hiring ramp)</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Office — banking/financial services</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed in sources reviewed</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>Office grand opening + active hiring ramp</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (promotion basis)</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Strong suburban Class-A rental + move-up for-sale demand in Ballantyne/south Charlotte; $131,832 wage supports higher-income housing product.</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5325,7 +5416,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -5441,7 +5532,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5557,7 +5648,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5673,7 +5764,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5789,7 +5880,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -5905,7 +5996,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -6021,7 +6112,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6137,7 +6228,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -6253,7 +6344,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -6294,7 +6385,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Lease signed / active hiring milestone (unchanged)</t>
+          <t>Lease signed / active hiring milestone</t>
         </is>
       </c>
       <c r="K24" s="6" t="n">
@@ -6362,26 +6453,26 @@
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle (second consecutive quiet cycle); project remains on track for fall 2026 first arrivals.</t>
+          <t>No new in-window milestone found this cycle; project remains on track for fall 2026 first-worker arrivals.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Gaining Momentum</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
@@ -6400,7 +6491,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (fully approved)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -6410,7 +6501,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill School Board endorsement of amended tax-share terms; City Council vote still outstanding</t>
+          <t>Final city + county approval (rezoning, land sale, tax-incentive resolution)</t>
         </is>
       </c>
       <c r="K25" s="6" t="n">
@@ -6423,7 +6514,7 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
@@ -6438,27 +6529,27 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
+          <t>Fee-in-lieu-of-tax; Rock Hill forgoes ~85% of its project tax share; York County contributes 10% of its EDA fund revenue; ~$80M directed to Rock Hill Schools over 40 yrs</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>York County Council 3rd reading approved 2026-07-08 (4-3); Rock Hill School Board voted 5-2 on 2026-07-13 to back the amended tax-share structure and urge City Council to accept it; Rock Hill City Council has still not voted as of 2026-07-20 (unconfirmed reporting points to an Aug. 10, 2026 council agenda — not independently verified)</t>
+          <t>Rock Hill City Council approved 7-0 (rezoning, land sale, tax-incentive resolution) on 2026-07-23, following York County Council's 4-3 third-reading approval on 2026-07-08/09; construction could start late 2026, buildout ~10 yrs</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/13/rock-hill-schools-board-urges-city-to-accept-county-tax-allocations/</t>
+          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Med (deal certainty)</t>
+          <t>High (facts); High (deal certainty — now fully approved)</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -6473,24 +6564,24 @@
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH. Approval removes the deal's last major execution risk.</t>
         </is>
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>School board's 5-2 endorsement removes one point of local opposition, but Rock Hill City Council's outstanding vote on the amended tax-share terms remains the key unresolved risk; +1 for continued forward momentum with no new negative signal this cycle.</t>
+          <t>Rock Hill City Council's unanimous vote resolves the outstanding-vote risk flagged in the 2026-07-13 report; deal now fully approved at both city and county level. +3 vs prior cycle.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>Gaining Momentum</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
@@ -6516,7 +6607,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
+          <t>Scout Motors — EV assembly plant (training center opens; first body weld)</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -6526,7 +6617,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Hiring event announced; companywide headcount update</t>
+          <t>Training-center opening + production-validation milestone</t>
         </is>
       </c>
       <c r="K26" s="6" t="n">
@@ -6534,12 +6625,12 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Projected (~1,400 hired companywide; 600+ in SC)</t>
+          <t>Projected (600+ SC production hires)</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
+          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -6559,17 +6650,17 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>Companywide headcount holds at ~1,400 (~600 in SC), confirmed via WLTX and Scout's own blog as of mid-July 2026; production still targeted late 2027, customer deliveries trending 2028</t>
+          <t>Training Center opened 2026-04-20; first vehicle body weld completed June 2026 (validation build); customer deliveries trending toward 2028</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/scout-motors-plant-blythewood-update/101-c64d17ed-4b85-4fae-b866-e7e1a08021f1</t>
+          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -6594,19 +6685,19 @@
       </c>
       <c r="X26" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION: last week's report cited a 2026-07-29 pre-hire event for 70+ maintenance techs; this cycle's research found the wage/role details trace precisely to a 2025-07-10 WISTV story and a 2025-07-25 SC Daily Gazette story, with no distinctly-dated 2026 version found — that specific claim is now treated as unverified/likely a dating error and is not carried forward. Headcount and the active-hiring trend remain independently confirmed.</t>
+          <t>600+ hired at the SC production site as of April 2026 (~1,313 companywide per Revelio Labs, Dec 2025). Correction: the '70+ maintenance-tech interview event beginning 7/29' cited in the 2026-07-13 report is a July 2025 event, not 2026 — no 2026 repeat found. Feb 2026 reporting suggests customer deliveries may slip to summer 2028; company reaffirms 2027 initial production.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Repeated</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -6642,7 +6733,7 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>County incentive hearing (procedural step, no scale change)</t>
+          <t>New facility (greenfield, 185 ac)</t>
         </is>
       </c>
       <c r="K27" s="6" t="n">
@@ -6675,17 +6766,17 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>Durham County Board of Commissioners held a public hearing 2026-07-13 on a proposed $15M county incentive package (on top of the ~$26M state EIC incentive approved in April); no vote outcome reported yet</t>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>https://abc11.com/post/abbvie-pharmaceutical-project-moves-forward-durham/19500900/</t>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -6710,14 +6801,14 @@
       </c>
       <c r="X27" s="6" t="inlineStr">
         <is>
-          <t>Procedural incentive step, not a scale change; construction start still targeted this year.</t>
+          <t>No new in-window milestone found this cycle; project remains on track.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -6748,7 +6839,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Capital Group — East Coast operations hub</t>
+          <t>Capital Group — East Coast ops hub</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -6758,7 +6849,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Wage figure confirmed (stated, not inferred)</t>
+          <t>Lease commenced</t>
         </is>
       </c>
       <c r="K28" s="6" t="n">
@@ -6771,12 +6862,12 @@
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+          <t>$194,141 avg (stated)</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -6791,17 +6882,17 @@
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>12-yr JDIG term; lease term began 2026-05-22</t>
+          <t>16-yr lease at One Independence Center (196,940 sq ft) commenced 2026-05-22; hiring 2027-2031</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+          <t>https://businessnc.com/capital-group-picks-its-uptown-charlotte-spot-for-600-workers</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -6826,14 +6917,14 @@
       </c>
       <c r="X28" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle.</t>
+          <t>No new in-window milestone beyond the already-confirmed lease-commencement date; unchanged since 2026-07-13.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -6887,7 +6978,7 @@
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, 2025 tranche)</t>
+          <t>~$119,833 avg (stated, original 2025 tranche)</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
@@ -6897,7 +6988,7 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B</t>
+          <t>~$2.0B (doubled from ~$700M)</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
@@ -6937,19 +7028,19 @@
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay).</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle; the sole dated milestone (2026-01-20 investment doubling) sits exactly at this week's window boundary (2026-01-20 to 2026-07-20) — still inclusive, but flagged as at risk of aging out of the window next cycle absent a new update.</t>
+          <t>No new in-window milestone found this cycle. Some 2026 coverage references a total nearer 600 site jobs; unverified as a distinct dated milestone — flagged for next cycle.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -6961,7 +7052,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
@@ -6980,7 +7071,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
+          <t>JetZero — aerospace plant (EXIM financing exploration)</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -6990,7 +7081,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
+          <t>Letter of Interest for federal financing</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
@@ -7018,22 +7109,22 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
+          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr; EXIM exploring up to $3B financing (non-binding)</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking held 2026-06-15; zero jobs still projected for 2027; hiring ramp begins 2028-2029 (3,020 jobs by end 2029); full 14,500+ target due by 2037; Governor Stein signed the FY2026-27 state budget on 2026-07-07, releasing the previously-frozen $133.9M JDIG-linked infrastructure allocation (on top of $118.1M already allotted) — company communications called it 'all systems go'</t>
+          <t>EXIM Letter of Interest signed 2026-07-20 at the Farnborough Airshow to explore up to $3B in financing under EXIM's 'Make More in America' initiative; explicitly not a financing commitment, subject to due diligence and EXIM Board approval</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
+          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/jetzero-exim-explore-3b-financing-manufacturing-campus</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -7053,19 +7144,19 @@
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
+          <t>Same long-run scale as prior cycles; the financing signal is a modest positive but does not resolve the hiring-ramp delay.</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>+1 for confirmed release of state incentive funding (an execution-certainty signal), though the hiring-ramp timeline itself is unchanged from last cycle.</t>
+          <t>Non-binding financing exploration only; does not change the JDIG-amendment hiring ramp (zero jobs projected for 2027, full 14,500-job target due by 2037). Score held flat.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -7096,7 +7187,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Novartis — API mfg building (investment increase)</t>
+          <t>Novartis — API mfg building</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -7106,7 +7197,7 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>New facility (unchanged)</t>
+          <t>Investment increase (prior cycle)</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
@@ -7129,17 +7220,17 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>~$991M (incl. $220M API building)</t>
+          <t>~$991M (incl. $220M)</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Part of original $771M package incentives</t>
+          <t>State/local incentive package (Wake/Durham)</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>Facility opening targeted 2027-2028</t>
+          <t>Facilities opening 2027-2028</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -7169,12 +7260,128 @@
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in the Wake/Durham corridor.</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
         <is>
           <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>New (promoted from Excluded)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Ballantyne regional office (grand opening + hiring ramp)</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Office grand opening + active hiring ramp</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>Projected; ~400 hired to date</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed in sources reviewed</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Grand opening 2026-03-17; ~400 of 510 planned roles filled as of ~April 2026 (incl. 275 relocated internally); 3-floor, 90,000 sq ft building</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Med (promotion basis)</t>
+        </is>
+      </c>
+      <c r="U32" s="6" t="inlineStr">
+        <is>
+          <t>Office — banking/financial services</t>
+        </is>
+      </c>
+      <c r="V32" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W32" s="6" t="inlineStr">
+        <is>
+          <t>Strong suburban Class-A rental + move-up for-sale demand in Ballantyne/south Charlotte; $131,832 wage supports higher-income housing product.</t>
+        </is>
+      </c>
+      <c r="X32" s="6" t="inlineStr">
+        <is>
+          <t>Promoted from Excluded to Ranked this cycle: the in-window grand opening plus a confirmed hiring-ramp to ~400/510 roles is genuine forward-moving execution, not merely a delayed pre-window commitment (same logic used for SMBC's Week-2 promotion). Prior cycles excluded this deal; this reverses that call.</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10950,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -10805,7 +11012,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -10867,7 +11074,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -10929,7 +11136,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -10991,7 +11198,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -11053,7 +11260,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -11115,7 +11322,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -11177,7 +11384,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -11239,7 +11446,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -11301,7 +11508,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -11363,7 +11570,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -11425,7 +11632,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -11487,7 +11694,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -11549,7 +11756,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -11611,7 +11818,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -11673,7 +11880,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -11735,7 +11942,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -11797,7 +12004,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -11859,7 +12066,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -11921,7 +12128,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -11983,7 +12190,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -12045,7 +12252,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -12107,7 +12314,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -12169,7 +12376,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -12231,7 +12438,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -12293,7 +12500,7 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -12355,7 +12562,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -12417,7 +12624,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -12479,7 +12686,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -12541,7 +12748,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -12603,7 +12810,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -12665,7 +12872,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -12727,7 +12934,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -12789,7 +12996,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -12851,7 +13058,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -12913,7 +13120,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -12975,7 +13182,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -13037,7 +13244,7 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -13099,7 +13306,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -13161,7 +13368,7 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -13223,7 +13430,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -13285,7 +13492,7 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -13320,12 +13527,12 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>$24.50-$63/hr (stated; unchanged)</t>
+          <t>Not disclosed; $24.50-$63/hr stated range</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>Still just under 500 jobs; no threshold-crossing update found this cycle (high-priority check)</t>
+          <t>Still just under 500 jobs; facility now targeted to open April 2028 (later ramp than previously implied)</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
@@ -13335,7 +13542,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
+          <t>https://investors.usare.com/news-releases/news-release-details/usa-rare-earth-selects-cherokee-county-south-carolina-new-rare</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
@@ -13347,17 +13554,17 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg / I-26</t>
+          <t>Laurens Co.</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -13367,37 +13574,37 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Ferrara Candy — groundbreaking held</t>
+          <t>Suniva — solar-cell plant</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>1,000 (10 yr)</t>
+          <t>564</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>$675M</t>
+          <t>$350M</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; confectionery = workforce-tier</t>
+          <t>Stated $23-$53/hr = workforce-tier</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>No new milestone since May 2026 groundbreaking; first lines targeted Q1 2029</t>
+          <t>No update found; operations still targeted spring/summer 2027</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
+          <t>https://governor.sc.gov/news/2026-04/suniva-inc-selects-laurens-county-first-south-carolina-manufacturing-facility</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -13409,12 +13616,12 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Laurens Co.</t>
+          <t>Gray Court / Laurens Co.</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -13429,37 +13636,37 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Suniva — solar-cell plant</t>
+          <t>Aptiv Services US — Connexial Center</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>277</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>$350M</t>
+          <t>$120.8M</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Stated $23-$53/hr = workforce-tier</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle; operations targeted spring/summer 2027</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
+          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -13471,7 +13678,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -13506,22 +13713,22 @@
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+          <t>Not disclosed; Estimated/Inferred sub-$100k (security-tech corporate/sales mix)</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>Formal announcement confirmed 2026-03-24; 125,000 sq ft building, houses 500+ total employees incl. relocated staff, online by end of 2028</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
+          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
@@ -13533,7 +13740,7 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -13573,29 +13780,29 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>Ribbon-cutting/opening ceremony held late April 2026 for the 240,000 sq ft facility; production ramp still targeted mid-2028</t>
+          <t>Confirmed announcement date 2026-03-26 (240,000 sq ft indium-phosphide laser plant on former Qorvo site); production targeted mid-2028; no update since</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>https://myfox8.com/news/north-carolina/greensboro/lumentum-holdings-opens-new-manufacturing-facility-in-greensboro/</t>
+          <t>https://www.areadevelopment.com/newsitems/4-14-2026/lumentum-greensboro-north-carolina.shtml</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
@@ -13635,7 +13842,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>Now corroborated via official NC Commerce/Governor press releases dated 2026-05-26, resolving prior cycle's uncorroborated flag</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
@@ -13657,7 +13864,7 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -13692,17 +13899,17 @@
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>'high-tech, high-wage' but figure Not disclosed (Inferred mid-$60k-$80k)</t>
+          <t>Mixed band: current postings range $19.50/hr (Assembler) to $86k-$126k (LVA Mfg Supervisor)</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Eaton recruiting at WNC Career Expo 2026-04-16; confirmed as 7th Helene-recovery manufacturer expansion</t>
+          <t>No update found this cycle beyond confirmed wage-band detail</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
@@ -13719,7 +13926,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
@@ -13754,17 +13961,17 @@
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
+          <t>Not disclosed; Charlotte/Mecklenburg-specific split still unconfirmed</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle; Mecklenburg-specific allocation for this tranche remains unclear (conflated with a 2024 tranche in some coverage)</t>
+          <t>No update found; county-level job split still not disclosed despite renewed search</t>
         </is>
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
@@ -13774,19 +13981,19 @@
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>Med (totals uncertain)</t>
+          <t>High (totals); Low (wage/split)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / Wendell / Knightdale</t>
+          <t>Knightdale / Wendell</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -13821,12 +14028,12 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>New 101,000 sq ft Wendell facility coming online July 2026; Knightdale targeting 100 jobs by end 2026; expanded Wendell campus (+200 jobs) by 2028</t>
+          <t>New Wendell facility (101,000 sq ft, ~50 jobs) came online July 2026 as expected; Knightdale (131,000 sq ft, ~100 jobs) still targeting end of 2026</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
@@ -13843,7 +14050,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
@@ -13883,29 +14090,29 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>Reaffirmed 2026-01-28 via White House-linked event; construction underway on west campus, facility slated to open within the next year</t>
+          <t>Project reaffirmed via a White House social-media assist ~Jan 2026; construction underway on west campus; no further update this cycle</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>https://greensboro.com/news/local/business/development/article_f8077494-ba1d-526b-a82a-9d8425f0acbe.html</t>
+          <t>https://hpj.com/2026/01/28/deere-announces-two-new-u-s-plants</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -13945,29 +14152,29 @@
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>York County's nine-month data-center moratorium received FINAL passage 2026-07-14 (6-0); it bars new site plans/special exceptions/CUPs for data centers in unincorporated York Co. through ~April 2027 but explicitly exempts projects with vested rights — QTS's under-construction buildings are understood to be unaffected</t>
+          <t>York County's 9-month data-center moratorium passed final reading 2026-07-13 but does not affect QTS's already-permitted (2023) construction</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrhi.com/2026/07/york-county-council-approves-nine-month-data-center-moratorium-214184</t>
+          <t>https://www.wbtv.com/2026/06/17/york-county-weighs-9-month-moratorium-new-data-centers-what-we-know/</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
@@ -14007,17 +14214,17 @@
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle; original Oct. 2025 announcement remains the latest news</t>
+          <t>$9B investment now confirmed to cover the existing Berkeley County campus expansion plus two NEW Dorchester County campuses; no discrete permanent-job figure disclosed</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+          <t>https://www.charlestondigital.com/news/google-announces-new-usd9b-investment-in-south-carolina-through-2027</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr">
@@ -14029,17 +14236,17 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Pickens</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -14049,17 +14256,17 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>Siemens Smart Infrastructure</t>
+          <t>FN America — 2nd production facility</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>~150</t>
+          <t>~176</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>$165M</t>
+          <t>$33M</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
@@ -14069,59 +14276,59 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>Third consecutive quiet cycle with no movement — recommend removal next cycle absent an update</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Hamlet</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>AWS/Amazon — AI/cloud campus</t>
+          <t>Siemens Smart Infrastructure</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>~150</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>$10B</t>
+          <t>$165M</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
@@ -14131,39 +14338,39 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>Still unverified; outside this cycle's five assigned research regions — needs direct confirmation next cycle</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>verify</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>https://www.aboutamazon.com/</t>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr">
         <is>
-          <t>Low (needs verification)</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Wake Co. (aggregate)</t>
+          <t>Hamlet</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -14173,59 +14380,59 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+          <t>AWS/Amazon — AI/cloud campus</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>~11,000 (pipeline)</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>$11B</t>
+          <t>$10B</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>Mixed (office-skewed)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>RECONCILED this cycle: the previously-flagged second figure (~30 projects/8,000-10,800 jobs/$5.6B) is confirmed to be the closed, prior EDGE 6 campaign (concluded ~Sept 2024) — sequential, not duplicative, with the current $11B/11,000-job EDGE 7 pipeline</t>
+          <t>Still unverified; Richmond County falls outside all five assigned research sub-regions this dataset tracks — carried forward unchanged pending a dedicated check</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+          <t>https://www.aboutamazon.com/</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low (needs verification)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / SouthPark</t>
+          <t>Wake Co. (aggregate)</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -14235,54 +14442,54 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Chase — new office (1,000-employee bldg)</t>
+          <t>County jobs pipeline (EDGE 7)</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>400 new by 2028</t>
+          <t>~11,000 (pipeline); 60,000+ direct+indirect target</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$11B (pipeline); $3B (EDGE 7 target)</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>~$105k Estimated/Inferred (job-posting range)</t>
+          <t>Mixed (office-skewed)</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>Raleigh Chamber formally launched EDGE 7, a 5-year strategy succeeding the closed EDGE 6 campaign (37 projects/$5.6B/10,800 jobs); no new named mega-project beyond items already tracked</t>
         </is>
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+          <t>https://raleigh-wake.org/about-us/edge7</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Charlotte (CLT airport)</t>
+          <t>Charlotte / SouthPark</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -14297,37 +14504,37 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Averitt — logistics campus</t>
+          <t>JPMorgan Chase — new office</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>400 new (1,000 total on-site)</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>$81,769 avg (stated)</t>
+          <t>Estimated/Inferred ~$105k (unconfirmed)</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>New office at One Piedmont Town Center (5 floors, 145,000 sq ft) confirmed 2026-04-21; consolidates 600+ existing staff plus 400 new; move-in early 2028</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorganchase-charlotte-hiring-workforce-banking-competition</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
@@ -14339,17 +14546,17 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Rowan County</t>
+          <t>Charlotte (CLT airport)</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -14359,37 +14566,37 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters Inc. — "Project Rack" distribution hub (identity confirmed)</t>
+          <t>Averitt — logistics campus</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>200+ (per 2026-07-17 announcement; county incentive filing cited 258)</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>$41M</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>$57,351 avg for ~70 skilled roles (stated); bulk of the 200+ workforce likely lower (Estimated/Inferred)</t>
+          <t>$81,769 (stated)</t>
         </is>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>Company identity confirmed 2026-07-17: American Eagle Outfitters Inc., $41M, 472,890 sq ft distribution hub at Innovation Logistics Center, 1415 Peeler Road, Salisbury; Q1 2027 ops start unchanged</t>
+          <t>No update found this cycle; confirmed unchanged</t>
         </is>
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr">
@@ -14401,12 +14608,12 @@
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Rowan / Kannapolis</t>
+          <t>Rowan County</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -14421,59 +14628,59 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
+          <t>"Project Rack" (company undisclosed)</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$41M</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>$55k-$150k range (DHL postings)</t>
+          <t>Estimated/Inferred sub-$100k</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle; jobs still undisclosed</t>
+          <t>Rowan County Commissioners approved 3-year tax incentives 2026-06-05 for the still-undisclosed 'iconic American brand'; Q1 2027 operations start still targeted</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>https://www.salisburypost.com/2026/05/02/not-a-data-center-google-leases-rowan-county-side-kannapolis-industrial-site/</t>
+          <t>https://www.salisburypost.com/2026/06/05/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / North Hills</t>
+          <t>Rowan/Kannapolis</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -14483,59 +14690,59 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Ralliant Corp. — global HQ launch</t>
+          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>$2.1M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>$170k-$189k avg (stated)</t>
+          <t>$55k-$150k range (DHL postings)</t>
         </is>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>No update found; DHL actively hiring on-site but Kannapolis officials confirm no job total tied to the Google lease has been released</t>
         </is>
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
+          <t>https://www.wcnc.com/article/news/local/google-facility-planned-in-kannapolis</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Siler City</t>
+          <t>Raleigh / North Hills</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -14545,59 +14752,59 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Wolfspeed — silicon-carbide fab</t>
+          <t>Ralliant Corp. — global HQ launch</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>1,800 (proj.)</t>
+          <t>~150 on-site now (180 by 2029)</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>$5.0B</t>
+          <t>$2.1M</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>$77,753 avg (stated)</t>
+          <t>$170,531-$189,479 (stated)</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>Post-bankruptcy ramp described by the company as 'more measured/disciplined' — original full-occupancy March 2026 target appears to have slipped; SiC crystal growth/wafer shipments to Mohawk Valley (NY) underway</t>
+          <t>HQ formally opened 2026-03-05; state expects up to 180 high-paying jobs by 2029</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>2026-Q1 (10-Q)</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000895419/000089541926000030/wolf-20260329.htm</t>
+          <t>https://www.businesswire.com/news/home/20260305697057/en/Ralliant-Opens-Global-Headquarters-in-Raleigh-North-Carolina</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>Med (financial distress clouds trajectory)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Siler City</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -14607,59 +14814,59 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Vulcan Elements — magnet factory</t>
+          <t>Wolfspeed — silicon-carbide fab (layoffs announced; long-term target reaffirmed)</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>1,000 (proj.)</t>
+          <t>1,800 (proj., slower pace)</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>$918.4M</t>
+          <t>$5.0B</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>$81,932 avg (stated)</t>
+          <t>$77,753 (stated)</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>'Hundreds of workers already on site' per current coverage; JCC training cohorts begin summer 2026 as originally scheduled</t>
+          <t>Wolfspeed disclosed ~2026-06-09 it will lay off 73 Siler City employees (effective 2026-08-08) amid soft demand and cut FY2026 revenue guidance to $850M, but reaffirmed the full 1,800-job Siler City commitment at a slower pace</t>
         </is>
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>2026-summer (training start)</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/sponsored/fifth-third-bank/the-next-industrial-revolution-how-vulcan-elements-makes-nc-the-backbone-of-vital-global-market/</t>
+          <t>https://www.carolinajournal.com/wolfspeed-layoffs-at-its-siler-city-materials-factory/</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (facts); Low (timeline)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Wake County (statewide)</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -14669,37 +14876,37 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>WakeMed / Atrium Health — proposed merger</t>
+          <t>Vulcan Elements — magnet factory</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>3,300 (statewide, 5 yr)</t>
+          <t>1,000 (proj.)</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>$2.0B (Wake Co. portion)</t>
+          <t>$918.4M</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$81,932 (stated)</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>Vote still not scheduled as of 2026-07-20; the 90-day delay from 2026-05-04 points to early August 2026; opposition continues (Brown University School of Public Health cost-impact report, community groups)</t>
+          <t>No new in-window update found on hiring/construction progress this cycle</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04 (delay announced)</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/news/local/wakemed-atrium-merger-costs-opposition-july-2026/</t>
+          <t>https://www.wunc.org/economy/2025-11-18/vulcan-elements-worlds-largest-magnet-factory-outside-china-benson</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
@@ -14711,17 +14918,17 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Wake County (statewide)</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -14731,17 +14938,17 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+          <t>WakeMed / Atrium Health — proposed merger</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+          <t>3,300 (statewide, 5 yr)</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>~$50M (hangar, existing)</t>
+          <t>$2.0B (Wake Co. portion)</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
@@ -14751,39 +14958,39 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>No positive or negative movement found this cycle; hangar still largely idle, and the Dec. 31, 2026 500-employee deadline is now roughly five months away with no confirmed hiring progress</t>
+          <t>Wake Commissioners voted 2026-05-04 to delay the vote by 90 days, pushing a potential vote to ~2026-08-02 — just after this window closes; opposition continues to mount</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+          <t>https://www.wral.com/news/local/wakemed-atrium-health-planned-deal-state-auditor-calls-for-delay-may-2026/</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr">
         <is>
-          <t>High (risk)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Multi-site NC incl. Wilmington</t>
+          <t>RTP</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>New Hanover +</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -14793,59 +15000,59 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Amazon-Corning — fiber-optics partnership</t>
+          <t>Apple — RTP campus extension</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>1,000 (multi-site, unallocated)</t>
+          <t>3,000 originally proj.; ~600-990 added to date</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>Multi-billion (undisclosed NC-specific)</t>
+          <t>$552M-$1B+ (paused)</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>Avg salary &gt;$65,000 (newly disclosed; sub-$100k)</t>
+          <t>$187k (stated, 2021 award)</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>Wage now disclosed (exceeds $65k) but still sub-$100k; per-site (incl. Wilmington-specific) job allocation still not broken out</t>
+          <t>DATE CORRECTION: the 4-yr incentive-timeline extension was approved 2025-11-25 (not April 2026 as previously reported); no active construction restart found</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>https://www.corning.com/worldwide/en/about-us/news-events/news-releases/2026/06/amazon-announces-agreement-with-corning-to-boost-us-fiber-optics-manufacturing-creating-1000-advanced-manufacturing-jobs-in-north-carolina.html</t>
+          <t>https://9to5mac.com/2025/11/25/apple-granted-rare-timeline-extension-north-carolina-campus/</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Arden</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -14855,59 +15062,59 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>≤500 currently; must hit 500 by 12/31/26</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>$285M</t>
+          <t>~$50M (hangar)</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>$62,413 avg (stated)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>On track: first equipment arrival end of 2026, first parts production mid-2027, hiring ramp begins mid-2027</t>
+          <t>Risk continues escalating: hangar still largely idle per most recent coverage; no updated employee-count disclosure found; deadline now ~5 months out with no positive movement</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>2026 (equipment arrival timeline)</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/2026/04/rtx-says-gtf-groundings-are-coming-down-thanks-to-maintenance-ramp/</t>
+          <t>https://www.hoodline.com/2026/03/greensboro-s-50-million-supersonic-ghost-hangar-puts-state-on-the-clock</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Med (facts); Low (outlook)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Asheboro</t>
+          <t>Multi-site NC incl. Wilmington</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>New Hanover +</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -14917,59 +15124,59 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Environmental Air Systems</t>
+          <t>Amazon-Corning — fiber-optics partnership</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,000 (multi-site, unallocated)</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>$20M</t>
+          <t>Multi-billion (undisclosed NC-specific)</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>$55,133 avg (stated)</t>
+          <t>Avg &gt;$65,000 (disclosed; sub-$100k)</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle despite targeted searches</t>
+          <t>Deal confirmed 2026-06-08; per-site (Wilmington vs. Concord) allocation still not disclosed; distinct from the larger Corning-Meta $6B Hickory/Catawba deal</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>2025-11-25 (orig.)</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+          <t>https://www.wect.com/2026/06/08/amazons-data-center-push-fuels-1000-job-fiber-optic-agreement-with-corning/</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (facts); Low (allocation)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Wilmington</t>
+          <t>Arden</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>New Hanover</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -14979,141 +15186,141 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>325</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Not itemized</t>
+          <t>$285M</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$62,413 (stated)</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>GNF4 fuel fabrication began early 2026; lead-use assemblies scheduled for deployment in commercial reactors during 2026 — genuine in-window production milestones, jobs still undisclosed</t>
+          <t>No update found this cycle; on track for equipment arrival end 2026, first parts mid-2027</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>2026 (fabrication start)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/global-nuclear-fuel-unveils-new-gnf4-product</t>
+          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Woodruff / Spartanburg Co.</t>
+          <t>Asheboro</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>AIRSYS Cooling Technologies — global HQ</t>
+          <t>Environmental Air Systems</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>$40-60M</t>
+          <t>$20M</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Estimated/Mixed)</t>
+          <t>$55,133 (stated)</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>Manufacturing-operations start slipped from 2026 to early 2027; HQ campus itself already opened</t>
+          <t>No update found despite targeted searches — third consecutive quiet cycle</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>~2026 (HQ opening); early 2027 (mfg slip)</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/25/environmental-air-systems-expand-randolph-county-adding-300-jobs-and-20-million-investment</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Gray Court</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>New Hanover</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Aptiv Services US — Connexial Center</t>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>$120.8M</t>
+          <t>Not itemized ($50M+ cited)</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -15123,79 +15330,79 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>No update found; ~27 open GE Nuclear roles in Wilmington as of Feb 2026, but no discrete headcount figure disclosed for the GNF4 line</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
+          <t>https://www.wilmingtonbiz.com/more_news/2025/10/09/global_nuclear_fuel_to_fabricate_new_nuclear_fuel_product_in_wilmington</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Easley (Anderson/Pickens border)</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>Signature Foods USA</t>
+          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>5,100 (proj. total); 3,000+ employed</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>$13.9B</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+          <t>$62,234 (stated; below $100k)</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>Operations confirmed online as of April 2026</t>
+          <t>No new headcount milestone found beyond the previously reported 3,000+ figure; company still targets a new production line roughly every 4 months through decade's end</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+          <t>https://www.wfmynews2.com/article/news/local/major-milestone-over-3000-people-now-work-at-the-toyota-battery-plant/83-b192b700-91b7-42f4-837e-33d0c01ee96e</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr">
@@ -15207,17 +15414,17 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Woodruff (Spartanburg Co.)</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -15227,59 +15434,59 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
+          <t>215 (at full operation)</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>$40-60M</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>$500M (valuation, not capex)</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>No update on headcount found this cycle</t>
+          <t>Global HQ campus (264,000 sq ft) officially opened 2026-05-13; corporate teams now on-site, but manufacturing operations (bulk of production hiring) remain delayed to Q1 2027</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Easley (Anderson/Pickens border)</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -15289,59 +15496,59 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Boeing 787 — production-rate ramp</t>
+          <t>Signature Foods USA</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>1,000 (unchanged)</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>$1.0B (existing)</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mixed ($54-64k assemblers; eng. likely higher)</t>
+          <t>Estimated/Inferred sub-$50k</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>Rate confirmed holding steady at 8/month as of the Farnborough Airshow (mid-July 2026); 10/month target reaffirmed 'over the next year' — consistent with, not accelerating beyond, prior framing</t>
+          <t>No headcount update found beyond the previously confirmed April 2026 online-operations milestone</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>https://leehamnews.com/2026/07/16/bca-riding-recovery-momentum-into-farnborough-air-show/</t>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -15351,59 +15558,59 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>SC Ports Authority — Leatherman Terminal Phase 2 (OPERATIONS PAUSED)</t>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>400 direct + ~1,200 indirect (unchanged projection)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>$1.2B (terminal, existing)</t>
+          <t>$500M (valuation, not capex)</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Estimated mixed, some 6-figure specialist roles)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>No reversal found; pause remains on track for Aug. 1, 2026 start (~5% of container volume / 5 weekly MSC calls affected); cargo shifting to Wando Welch/North Charleston terminals; no operations-resumption timeline given</t>
+          <t>No headcount figure published yet; new detail found — SCRA $50,000 relocation grant + city $1,500/job development grants imply a modest near-term headcount, but no number confirmed</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+          <t>https://www.upstatescalliance.com/announcements/gnq-insilico-a-500m-biotech-innovator-moving-to-greenville/</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr">
         <is>
-          <t>High (risk)</t>
+          <t>Low (headcount unconfirmed)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Goose Creek</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Berkeley</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -15413,37 +15620,37 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>HII (Newport News Shipbuilding) — 1-yr anniversary</t>
+          <t>GE Vernova — gas turbine mfg</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>~250 (estimate, not re-confirmed)</t>
+          <t>650 total planned; ~200 hired 2025, ~300 more by end 2026</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$160M (Greenville)</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Estimated/Inferred mixed, bulk likely sub-$100k</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>One-year operations anniversary reached 2026-01-22; company reports exceeding production targets, but no updated job-count figure surfaced</t>
+          <t>No new hiring-ramp confirmation found this cycle beyond job-board listing activity</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
+          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr">
@@ -15455,79 +15662,79 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>North Charleston</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Charleston</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
+          <t>Boeing 787 — production-rate ramp</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>5,100 (proj. total); 3,000+ now employed</t>
+          <t>1,000 (unchanged)</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>$13.9B</t>
+          <t>$1.0B (existing)</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>$62,234 avg (stated; below $100k)</t>
+          <t>Estimated/Inferred mixed</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>NEW to Watch: employment crossed 3,000+ workers (Feb 2026 milestone); all-EV battery line targeted to launch later 2026, plug-in hybrid line mid-2027; scale of hiring velocity in a rural county may pressure workforce housing despite sub-$100k wage</t>
+          <t>No Q2/Q3 2026 rate update found; rate confirmed 8/month as of Jan 2026, full 10/month target still described as 'over the next year'</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>https://www.wfmynews2.com/article/news/local/major-milestone-over-3000-people-now-work-at-the-toyota-battery-plant/83-b192b700-91b7-42f4-837e-33d0c01ee96e</t>
+          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg (former Kohler plant)</t>
+          <t>North Charleston</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Charleston</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -15537,17 +15744,17 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>NorthMark Strategies "Project Moc-1" — AI/HPC data center</t>
+          <t>SC Ports Authority — Leatherman Terminal (OPERATIONS PAUSED, CONFIRMED)</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>~150 FT at full operation (revised up from ~27); 400-600 temporary construction</t>
+          <t>400 direct + ~1,200 indirect</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>$2.8B</t>
+          <t>$1.2B (existing)</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -15557,39 +15764,39 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>SCDES air-permit comment period remains open through 2026-07-31; residents and the SC Environmental Law Center filed a lawsuit challenging the county's 'minor development' approval (hearing scheduled 2026-07-30 in Columbia); Spartanburg County Council separately gave first-reading approval to a one-year moratorium on new data-center proposals</t>
+          <t>CONFIRMED REVERSAL: pause of container operations takes effect 2026-08-01 (decision announced 2026-06-25); cargo consolidates into Wando Welch and North Charleston terminals; no reopening timeline given, contingent on demand recovery</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/07/08/lawsuit-targets-spartanburg-county-data-center-project-demands-public-planning-review/</t>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr">
         <is>
-          <t>Med (contested/evolving; litigation adds new risk)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Goose Creek</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Berkeley</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -15599,37 +15806,37 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>GE Vernova — gas turbine mfg (AI/data-center power supply chain)</t>
+          <t>HII (Newport News Shipbuilding) — 1-yr+ operations</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>650 total planned; ~200 hired 2025, ~300 more targeted by end 2026</t>
+          <t>~250 (estimate)</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>$160M (Greenville); part of $600M multi-site plan</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mixed — production/technician roles ~$45-56k; specialist/eng. roles $91k-$226k (Glassdoor); bulk of new hires likely sub-$100k</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>NEW to Watch: in-window (2026-06-27) hiring-ramp confirmation; original Jan-2025 investment announcement was pre-window</t>
+          <t>One-year anniversary reconfirmed 2026-01-22 (first-unit delivery within 40 days of startup, 2025 targets exceeded); no updated headcount figure found this cycle</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
+          <t>https://www.hii.com/news/hii-marks-one-year-of-newport-news-shipbuilding-charleston-operations</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr">
@@ -15641,79 +15848,79 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>RTP</t>
+          <t>Spartanburg (former Kohler plant)</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Apple — RTP campus extension (incentive-timeline extension)</t>
+          <t>NorthMark "Project Moc-1" — AI/HPC data center</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>3,000 originally projected; only ~600-990 added to date</t>
+          <t>~150 FT at full operation</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>$552M-$1B+ (paused)</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>$187k avg (stated, original 2021 award)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>NEW to Watch: NC Economic Investment Committee granted a four-year extension on hiring/investment timelines (April 2026) restarting the 2021 deal (up to $845M in potential tax benefits if targets met); no active construction found</t>
+          <t>Contested public hearing held 2026-06-25; DES comment period on the air permit runs through 2026-07-31 (closes just after this window); permit now seeks 11 additional gas turbines, raising approved capacity from ~50MW to ~450MW; Spartanburg Co.'s new one-year data-center moratorium explicitly exempts this already-approved project</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>https://www.carolinajournal.com/apple-delays-construction-on-552-million-rtp-campus/</t>
+          <t>https://www.postandcourier.com/spartanburg/news/spartanburg-county-council-data-center-public-hearing/article_746815ab-5f55-48b4-915e-e8c20482aae5.html</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr">
         <is>
-          <t>Low-Med (long-delayed, no active construction)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Orangeburg / I-26</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Orangeburg</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -15723,59 +15930,59 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Isuzu North America Corp. — production facility (medium-duty trucks)</t>
+          <t>Ferrara Candy — new mfg + corporate site</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>700+</t>
+          <t>1,000 (10 yr)</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>$280M</t>
+          <t>$675M</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$100k (Assembly Operator postings $52k-$72k; Quality Eng. $66k-$85k)</t>
+          <t>Not disclosed; Estimated/Inferred sub-$100k (confectionery production)</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>$283M JBIC/MUFG construction loan disbursed 2026-06-30; direct-hire event for 150+ positions held 2026-07-08 at Greenville Tech; production starts 2027, capacity 50,000 units/yr by 2030</t>
+          <t>Groundbreaking held 2026-05-19/20 (Gov. McMaster, Rep. Clyburn attended); first production lines targeted early 2029</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/news/isuzu-secures-us283m-loan-for-south-carolina-plant/</t>
+          <t>https://www.wistv.com/2026/05/19/ferrara-candy-company-breaks-ground-orangeburg/</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Fountain Inn</t>
+          <t>Woodruff</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -15785,166 +15992,166 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>EPC Power Corp. — power-conversion/inverter manufacturing facility</t>
+          <t>BMW Group — Plant Woodruff high-voltage battery assembly</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>300 (part of $1.7B multi-year investment)</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (site-specific)</t>
+          <t>~$700M (Woodruff portion of $1.7B total)</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$100k (Mfg/Test/Eng Tech postings $47k-$66k; Production Mgr $95k-$120k)</t>
+          <t>Not disclosed; Estimated/Inferred sub-$100k (comparable BMW SC production/assembly wages typically $50k-$80k; battery-plant role mix may skew slightly higher but unconfirmed)</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>Facility opened 2026-07-15, ramping to full capacity within the month; serves AI data-center and grid-infrastructure customers</t>
+          <t>BMW announced completion of its $1.7B South Carolina investment 2026-06-30/07-02, including the new Plant Woodruff battery facility; first fully-electric US-built BMW (iX5) production slated late 2026</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/07/15/epc-power-opens-facility-upstate-produce-critical-ai-data-center-technology/</t>
+          <t>https://spectrumlocalnews.com/sc/south-carolina/news/2026/07/02/south-carolina-bmw-investiment</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (jobs/date); Low (wage)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Woodruff</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>BMW Group — Plant Woodruff high-voltage battery assembly</t>
+          <t>Aspida Financial Services — HQ expansion (pre-window; tracked for a converting milestone)</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>~300 (Woodruff-specific, part of $1.7B total)</t>
+          <t>1,000 (proj., hiring 2028-2032)</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>$700M (Woodruff portion of $1.7B)</t>
+          <t>$28M+</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$100k (~$43,169 avg per ZipRecruiter)</t>
+          <t>$137,288 avg (stated) — clears the $100k bar</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>Completion celebrated 2026-07-01/07-02 ('Home of X' event, new BMW X5 premiere); iX5 EV production starts late 2026</t>
+          <t>Meets the job-count and wage thresholds outright, but the only announcement (2025-11-19) and its $21.8M JDIG-style incentive predate the window; no in-window flagship-site-selection or groundbreaking milestone found this cycle — watching for one to convert to Ranked</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>https://www.press.bmwgroup.com/global/article/detail/T0458864EN/</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/financial-services-company-expand-durham-headquarters-1000-new-jobs</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); N/A (timing)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>West Columbia</t>
+          <t>Chatham County</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits — distribution facility</t>
+          <t>VinFast — EV plant (jobs cut; state suing to reclaim site)</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>500+ (stated)</t>
+          <t>1,400 (cut from 7,500 proj.)</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>$80M</t>
+          <t>$4.0B (orig.; incentive up to $1.2B if met)</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred sub-$100k (warehouse/distribution roles typically $35k-$55k)</t>
+          <t>~$51,096 avg (Estimated/Inferred; well under $100k)</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>412,500 sq ft facility on 85 acres opened 2026-02-10/02-11 (originally planned fall 2026, opened early)</t>
+          <t>MATERIAL RISK: on 2026-03-18 VinFast cut its job projection to 1,400 and said construction resumes in 2026 (production targeted 2028); on 2026-05-21 NC AG Jeff Jackson sued VinFast to reclaim the Chatham County site and recoup incentives after VinFast missed its Jan 2024 construction deadline, its July 2026 operations deadline, and the 1,750-jobs-by-end-2026 requirement</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/columbia/business/wine-liquor-distributor-facility-west-columbia/article_60829410-b73e-47b4-9f46-f9c2dc79317c.html</t>
+          <t>https://www.axios.com/local/raleigh/2026/05/21/north-carolina-sues-vinfast-to-take-back-control-of-chatham-county-land</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); wage sub-$100k disqualifies Ranked</t>
         </is>
       </c>
     </row>
@@ -15959,7 +16166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17991,7 +18198,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -18033,7 +18240,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -18075,7 +18282,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -18117,7 +18324,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -18159,7 +18366,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -18201,7 +18408,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -18243,7 +18450,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -18285,7 +18492,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -18327,7 +18534,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -18369,7 +18576,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -18411,7 +18618,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -18453,7 +18660,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -18495,7 +18702,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -18537,7 +18744,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -18579,7 +18786,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -18621,143 +18828,143 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Snider Fleet Solutions</t>
+          <t>Maersk North American HQ</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Indian Land</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Confirmed stale after 3 cycles tracked on Watch — all coverage traces to 2023 relocation, completed/operational by June 2023; no 2026 developments found — removed from Watch tier</t>
+          <t>Pre-window; NC's Economic Investment Committee formally approved (2026-02-24/25) shifting the hiring window to 2027-2029 — still a delay, not qualifying forward movement; wage $100,962 stated</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>FN America</t>
+          <t>Scout Motors HQ (Plaza Midwood)</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Liberty (Pickens)</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>~176</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Third consecutive quiet cycle with zero forward movement — removed from Watch tier per the report's 2-cycle flag</t>
+          <t>Pre-window; no confirmed dated in-window milestone found again this cycle (no groundbreaking/permit date located)</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
+          <t>https://www.detroitnews.com/story/business/autos/2025/11/14/scout-motors-rolls-into-charlotte-5-key-things-about-the-automaker/87270881007/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Reynolds American — Tobaccoville Operations Center</t>
+          <t>Pallidus (PROJECT CANCELLED)</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Tobaccoville (Forsyth)</t>
+          <t>Rock Hill / York Co.</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0 (was 405)</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Site-specific 200-job figure is pre-window (Dec 2025); a March 2026 $3.2B multi-site reinvestment announcement is in-window but not broken out by site; wage (~$47k-$55k) well under $100k regardless</t>
+          <t>REVERSAL: Pallidus scrapped its $443M Rock Hill/York Co. HQ-and-manufacturing relocation, laid off 37 employees (44% of workforce), and is pivoting back to Albany, NY amid weak silicon-carbide demand</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://www.wfmynews2.com/article/news/local/reynolds-announces-200-new-jobs-coming-tobaccoville-operations-center/83-230e6897-51d9-4eeb-83e2-f486f0a759c3</t>
+          <t>https://www.manufacturingdive.com/news/pallidus-cancel-rock-hill-south-carolina-semiconductor-plant-hq-relocation</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>AdvanceTEC</t>
+          <t>PSA Airlines</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Clayton/Smithfield (Johnston)</t>
+          <t>Charlotte (CLT)</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -18767,123 +18974,123 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>~400 (450+ on-site)</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>160 jobs below the 200-job Watch floor; wage ~$90,000 also below the $100k bar despite the in-window groundbreaking</t>
+          <t>Grand opening confirmed 2026-03-25; Charlotte-area average salary $44,638 — well under $100k (pilots average ~$107k but are a minority of roles)</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/07/french-cleanroom-giant-drops-160-high-paying-jobs-into-johnston-county/</t>
+          <t>https://www.qcnews.com/charlotte/psa-airlines-opens-charlotte-headquarters-bringing-400-jobs-and-boost-to-nc-economy</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>FUJIFILM Diosynth Biotechnologies expansion</t>
+          <t>IKO North America</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs (Wake)</t>
+          <t>Chester Co.</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>~180</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Recycled old news — original announcement dated 2024-04-11, well outside the 6-month window; no in-window update found</t>
+          <t>Grand opening (production start) held March 2026; jobs remain ~180 — still below the 200-job Watch floor</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2024/04/11/fujifilm-diosynth-biotechnologies-expands-holly-springs-facility-create-one-largest-end-end-cell</t>
+          <t>https://www.iko.com/na/iko-celebrates-grand-opening-of-new-fiberglass-and-fiberglass-mat-manufacturing-facilities-in-south-carolina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Cielo Digital Infrastructure "Project Kingfisher"</t>
+          <t>Compass Datacenters</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Gaffney (Cherokee)</t>
+          <t>Statesville (Iredell)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>~250</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>$2.1B capex but only 30 confirmed jobs — far below the 200-job Watch floor despite being described as the largest-ever Cherokee County investment</t>
+          <t>No new 2026 milestone found again this cycle</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/briefs/cherokee-county-inks-2-1b-deal-with-data-center-developer/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Multiple recycled Lowcountry items (Volvo Ridgeville XC60/hybrid expansion, Mercedes-Benz Ladson CKD expansion, Roper St. Francis $1.2B hospital campus)</t>
+          <t>Snider Fleet Solutions (REMOVED FROM WATCH)</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Berkeley/Dorchester/Charleston</t>
+          <t>Indian Land (Lancaster)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -18893,81 +19100,81 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>various (2025)</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>All trace to pre-window announcements (Sept 2025, Dec 2025, and June 2025 respectively) with no in-window milestone found despite active search this cycle</t>
+          <t>CONFIRMED STALE: original announcement dates to May 2023; no 2026 activity found in a dedicated re-check — removed from active Watch tracking this cycle</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://governor.sc.gov/news/2023-05/snider-fleet-solutions-relocating-headquarters-lancaster-county</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>ProKidney — Greensboro manufacturing plant (WITHDRAWN)</t>
+          <t>Bosch — Dorchester Co. electric motors</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Greensboro (Guilford)</t>
+          <t>Dorchester</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>330 (orig., never tracked)</t>
+          <t>n/d (workforce 1,500-&gt;1,800)</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Company ended its pursuit of the Greensboro plant and sold the site (June 2026) — closure/withdrawal noted for completeness only; never previously tracked since it never met the qualifying bar</t>
+          <t>Expansion remains paused amid EV demand downturn; no discrete new-jobs announcement or resumption found</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>https://journalnow.com/news/local/business/health-care/prokidney-greensboro-manufacturing-plant/article_e77df70a-d8c9-11ef-82c8-a347d4b0b442.html</t>
+          <t>https://www.postandcourier.com/business/bosch-dorchester-electric-vehicles-rivian-expansion/article_265b1c36-ab6c-11ef-b047-3b784368d210.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
+          <t>Southeastern Container</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Raleigh (Wake)</t>
+          <t>Enka-Candler (Buncombe)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -18977,39 +19184,39 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>1,500 (claimed)</t>
+          <t>12 (new)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Re-checked again this cycle across Barclays newsroom, NC Governor, Wake County, EDPNC, and NC Commerce — still no authoritative primary source, only recirculating non-authoritative blog/social posts</t>
+          <t>$31M modernization confirmed, but only 12 new jobs at $32.90/hr (~$68,400/yr) — below both the 200-job Watch floor and the wage bar</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/southeastern-container-expands-buncombe-county-headquarters-and-manufacturing-operations</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Frontier Scientific Solutions</t>
+          <t>Walmart — Mebane distribution center</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Wilmington (New Hanover)</t>
+          <t>Alamance</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -19019,22 +19226,1240 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>~80 (current)</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Current headcount (~80) is well below even the 200-job Watch floor; CEO's 'likely exceed 500' figure is a speculative, undated future-phase projection, not a confirmed commitment — noted for context only</t>
+          <t>Confirmed via current job postings: average pay ~$14.79/hr (~$30,700/yr) — well under $100k</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>https://www.wilmingtonbiz.com/more_news/2026/03/18/amazon_facility_regional_projects_forecast_to_bring_hundreds_of_jobs_to_wilmington_area/27315</t>
+          <t>https://www.ziprecruiter.com/Jobs/Walmart-Distribution-Center/-in-Mebane,NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>"3 medical textile manufacturers" (unnamed)</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Winston-Salem (Forsyth)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>600+ (aspirational)</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Still no companies named as a set; aggregate/speculative claim; best partial matches (GMAX Industries, Tex-Tech Industries) are both pre-window and sub-200 jobs individually</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh (Wake)</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (claimed)</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Re-checked again this cycle: still unverifiable — sole source is a non-authoritative relocation/SEO site (arcrelocation.com); no corroboration from Barclays, WRAL, Axios, NC Commerce, or the Governor's office</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>https://arcrelocation.com/companies-moving-to-raleigh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Novo Nordisk speculative Four Oaks expansion</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>~500 (speculative)</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>2025-10 (cancelled)</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Re-confirmed cancelled/shelved; company's active NC investment is concentrated in its separate Clayton (Johnston Co.) facility</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>https://jocoreport.com/major-four-oaks-pharmaceutical-project-cancelled/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Kempower (EV charger manufacturer)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>0 (was ~306 committed)</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>REVERSAL: company confirmed it will not meet its ~306-job Durham commitment; NC ended its tax incentives as a result</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.pressreader.com/usa/the-herald-sun/20260716/281560887555485</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Biogen $2B RTP manufacturing investment</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Durham/Wake (RTP)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window (30th-anniversary announcement); company gave no job-count estimate tied to the investment</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/biogen-manufacturing-2-billion-july-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Amgen (2nd facility)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs (Wake)</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; wage &gt;$91k but &lt;$100k; no in-window update found</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/story/amgen-to-add-370-jobs-as-part-of-1b-investment-in-holly-springs-nc-officials-say/21754490/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Fujifilm Diosynth Biotechnologies</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs (Wake)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; no in-window update found</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2024/04/11/fujifilm-diosynth-biotechnologies-expands-holly-springs-facility-create-one-largest-end-end-cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; sub-500 jobs regardless</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>https://investor.lilly.com/news-releases/news-release-details/lilly-plans-invest-additional-450-million-manufacturing-site</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Ypsomed</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs (Wake)</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200 jobs; well below Watch floor</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wake.gov/news/ypsomed-announces-plans-invest-1954-m-creating-62-new-jobs-holly-springs</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Audemars Piguet</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh (Wake)</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; sub-200 jobs and wage $92,376 (&lt;$100k)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/story/luxury-watch-brand-audemars-piguet-to-invest-22-million-and-create-105-jobs-in-raleigh/21202535/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>AdvanceTEC</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Johnston County</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>In-window groundbreaking confirmed, but 160 jobs remains below the 200-job Watch floor; wage $90k avg (&lt;$100k)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/07/french-cleanroom-giant-drops-160-high-paying-jobs-into-johnston-county/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Ziehl-Abegg Inc. — North American HQ</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Winston-Salem (Forsyth)</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>500+ (growing from ~200)</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Milestone timing (HQ opening / headcount crossing 500) could not be confirmed as falling inside this window — flagged for verification next cycle rather than asserted</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>https://fanpost.ziehl-abegg.com/en/detail/new-headquarters-with-high-tech-production-plant-and-hundreds-of-new-jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Rowan Co. (Salisbury)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>200+</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Distribution hub confirmed; best-paid roles (~70 mgmt/maintenance) average only $57,351 — low-wage-only despite clearing the 200-job floor</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.salisburypost.com/2026/07/17/fly-like-an-eagle-famous-outfitters-to-invest-41m-create-200-jobs-in-rowan-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Cheerwine / Piedmont Cheerwine Bottling</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Rowan Co.</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>~100</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200 jobs; no high-wage signal</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/06/cheerwine-s-7-million-salisbury-score-set-to-super-size-rowan-county-jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Huntington Bank Carolinas branch expansion</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Multi (Charlotte/Raleigh/Winston-Salem/Charleston/Columbia/Greenville)</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>NC/SC</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>~350 (multi-state)</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Vague/diffuse multi-state aggregate spanning 55 branches, not a single site/project; bank-branch roles unlikely to average $100k+</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/03/06/banks-branch-expansion-huntington</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Corvid Technologies</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Mooresville (Iredell)</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed stale/recycled 2018 announcement; no in-window update found</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mooresvilletribune.com/news/mooresville-chosen-for-367-job-headquarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Fort Mill (York Co.)</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Stale/recycled announcement from 2014; no in-window (2026) milestone found</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Costco</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Indian Land (Lancaster Co.)</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>Speculative; no official confirmation of a new warehouse/location found</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>JGA Space &amp; Defense</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Huntersville (Mecklenburg)</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>~40</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200 jobs</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Albemarle — Richburg lithium hydroxide plant</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co.</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Project remains paused since March 2024 due to falling lithium prices; no evidence of a resumed in-window milestone; also sub-500 jobs regardless</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2024/03/18/major-electric-vehicle-lithium-project-paused-in-south-carolina/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Bank of America / Wells Fargo / Truist</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>- (cuts)</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>LAYOFFS/job cuts (AI-driven headcount reduction) — excluded per rules (opposite of qualifying criteria)</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/01/16/bank-america-wells-fargo-ai-job-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Woodward, Inc. — aerospace actuation manufacturing</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Greer (Spartanburg Co.)</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>date conflict (2025-09 vs 2026-02, unresolved)</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Date conflict could not be resolved this cycle (SC Governor's office URL slug reads Sept. 2025, one search result suggested Feb. 2026); excluded pending verification rather than asserted either way</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2025-09/woodward-inc-selects-spartanburg-county-establish-new-manufacturing-site-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>ElringKlinger — EV battery components expansion</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Pickens Co.)</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window; no in-window update found</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/news/elringklinger-auto-supplier-easley-plant/article_d5a55a73-946a-44e3-a2c7-d47669288ac3.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Cielo Digital Infrastructure</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co.</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200 jobs; pre-window announcement/tax-break approval</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2025-06/cielo-digital-infrastructure-selects-cherokee-county-first-south-carolina-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Numerous sub-200-job items (Detpak USA, Fortified Solar, Idealworks, Shamrock Technologies, Advanced Metalworks, Eastern Engineered Wood, Hydrite Chemical, Coastal Precast, Peabody Engineering, KP Components, Xoted Biotechnology Labs, United Composite Materials)</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Various Upstate SC</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>13-151 each</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Below Watch floor regardless of window</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Numerous sub-200-job items (AVANTech, Eastover Chips, AVM Group, Hoffman &amp; Hoffman Lexington, WiJo Pouches North America, Techo-Bloc, ALLTAPE Adhesive Mfg, Leonardo DRS, Modus21)</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Various Midlands/Lowcountry</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>27-170 each</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Below Watch floor and/or recycled old news with no in-window update; Ritedose Corp (Richland) flagged but unverified before search budget exhausted</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Numerous sub-200-job items (Sumitomo Forestry America, Alamance Foods, Hoffman &amp; Hoffman Greensboro, Cascade Die Casting, Torvan Medical, Swamp Rider, Team LaunchPoint, GMAX Industries)</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Various Triad</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>12-135 each</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Below Watch floor and/or sub-$100k wage and/or pre-window</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Alzchem Group AG (new US production facility)</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Bushy Park / Goose Creek (Berkeley Co.)</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>~2026-07-20</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>Job count and investment figures not captured before this cycle's search budget was exhausted — flagged as a priority follow-up rather than scored on incomplete data</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Jewelers Mutual Insurance "Project Diamond" — innovation hub</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh (Wake)</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>200 (phased 2025-2029)</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Wage and precise announcement date could not be confirmed this cycle (source not independently fetchable) — flagged for a dedicated follow-up search next cycle rather than scored on incomplete data</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -19049,7 +20474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -20061,7 +21486,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Fort Mill Sun (Rock Hill school board)</t>
+          <t>Fort Mill Sun — Rock Hill City Council coverage</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -20071,51 +21496,51 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/13/</t>
+          <t>https://www.fortmillsun.com/</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Charlotte-metro SC (York Co.)</t>
+          <t>York Co. SC</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — Rock Hill School Board 5-2 endorsement</t>
+          <t>Octapharma final 7-0 city-council approval, 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>ABC11 / AOL / Yahoo News mirrors</t>
+          <t>Aviation Week / FlightGlobal</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>trade_journal</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>https://abc11.com/</t>
+          <t>https://aviationweek.com/</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>NC Triangle</t>
+          <t>National aerospace</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>AbbVie — Durham County incentive hearing</t>
+          <t>JetZero-EXIM $3B financing Letter of Interest</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Carolina Journal (state budget)</t>
+          <t>Hoodline</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -20125,186 +21550,186 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>https://www.carolinajournal.com/</t>
+          <t>https://hoodline.com/</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>NC statewide</t>
+          <t>NC/SC metro</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>JetZero — FY2026-27 budget signing, $133.9M JDIG funding release</t>
+          <t>Citigroup Ballantyne grand opening/hiring ramp; Boom Supersonic risk update</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>WLTX (Columbia)</t>
+          <t>Businesswire — Ralliant press release</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>company_primary</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>https://www.wltx.com/</t>
+          <t>https://www.businesswire.com/</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>SC Midlands</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — mid-July headcount reconfirmation</t>
+          <t>Ralliant global HQ opening, North Hills</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>NC Governor's Office (Rowan)</t>
+          <t>Axios Raleigh</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>state_primary</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>https://governor.nc.gov/news/press-releases/2026/07/17/</t>
+          <t>https://www.axios.com/local/raleigh/</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>NC statewide</t>
+          <t>NC Triangle</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters — Rowan Co. distribution hub (Project Rack identity)</t>
+          <t>WakeMed/Atrium delay; VinFast lawsuit; Aspida Durham HQ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>WRHI (York County moratorium)</t>
+          <t>Carolina Journal</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>regional_edo/journal</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrhi.com/</t>
+          <t>https://www.carolinajournal.com/</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>York Co. SC</t>
+          <t>NC statewide</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>York County data-center moratorium final passage</t>
+          <t>Wolfspeed Siler City layoffs</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Fox Carolina (Spartanburg litigation)</t>
+          <t>Manufacturing Dive</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>trade_journal</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/</t>
+          <t>https://www.manufacturingdive.com/</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Upstate SC</t>
+          <t>National mfg</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>NorthMark Project Moc-1 lawsuit; EPC Power opening</t>
+          <t>Pallidus project cancellation, Rock Hill/York Co.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Automotive World</t>
+          <t>Charleston Digital</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>trade_journal</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/</t>
+          <t>https://www.charlestondigital.com/</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>National automotive</t>
+          <t>SC Lowcountry</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Isuzu North America — Piedmont SC loan/hiring event</t>
+          <t>Google SC $9B data-center expansion detail</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>BMW Group press office</t>
+          <t>Spectrum Local News</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>company_primary</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>https://www.press.bmwgroup.com/</t>
+          <t>https://spectrumlocalnews.com/</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>NC/SC</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>BMW Plant Woodruff completion event</t>
+          <t>BMW $1.7B SC investment completion; AbbVie recap</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Post and Courier — Columbia bureau (Southern Glazer's)</t>
+          <t>Post and Courier — Spartanburg bureau</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -20314,78 +21739,78 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/columbia/</t>
+          <t>https://www.postandcourier.com/spartanburg/</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>SC Midlands</t>
+          <t>Upstate SC</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits West Columbia opening</t>
+          <t>NorthMark Project Moc-1 hearing; AIRSYS HQ opening</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Leeham News (Farnborough coverage)</t>
+          <t>WECT / WilmingtonBiz</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>trade_journal</t>
+          <t>journal</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>https://leehamnews.com/</t>
+          <t>https://www.wect.com/</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>National aerospace</t>
+          <t>New Hanover Co. NC</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Boeing 787 rate confirmation at Farnborough Airshow</t>
+          <t>Amazon-Corning fiber-optics Wilmington detail</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>WFMY News 2 (Reynolds American)</t>
+          <t>9to5Mac</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>trade_journal</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>https://www.wfmynews2.com/</t>
+          <t>https://9to5mac.com/</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>NC Triad</t>
+          <t>National tech</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Reynolds American Tobaccoville jobs (excluded)</t>
+          <t>Apple RTP incentive-extension date correction (2025-11-25)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Hoodline (AdvanceTEC, RTP 3.0)</t>
+          <t>SC Daily Gazette</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -20395,71 +21820,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/</t>
+          <t>https://scdailygazette.com/</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>NC Triangle/Triad</t>
+          <t>SC statewide</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>AdvanceTEC Johnston Co. groundbreaking; RTP 3.0 framework approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>journalnow.com (Winston-Salem Journal)</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>https://journalnow.com/</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>NC Triad</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>ProKidney Greensboro plant withdrawal</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>SC Daily Gazette (Cielo Digital Infrastructure)</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>https://scdailygazette.com/</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Upstate SC</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Cielo Digital Infrastructure Cherokee Co. data center</t>
+          <t>SC Ports Leatherman confirmed pause; Boeing 787 rate</t>
         </is>
       </c>
     </row>
@@ -20474,7 +21845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20913,7 +22284,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -20933,7 +22304,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -20953,7 +22324,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -20973,7 +22344,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -20993,7 +22364,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -21013,7 +22384,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -21033,7 +22404,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -21053,7 +22424,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -21073,7 +22444,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -21086,14 +22457,14 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; no new milestone this cycle (second consecutive quiet cycle).</t>
+          <t>Unchanged; no new milestone this cycle.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -21102,18 +22473,18 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill School Board's 5-2 endorsement of the amended tax-share terms is genuine forward momentum without a new negative signal; Rock Hill City Council's outstanding vote remains the key risk — net +1.</t>
+          <t>Rock Hill City Council's unanimous 7-0 approval (2026-07-23) resolves the outstanding city-vote risk that had discounted this deal for two consecutive cycles; +3 for the removal of that execution-certainty discount.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -21126,14 +22497,14 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Headcount and active-hiring trend reconfirmed unchanged; a previously-cited 2026-07-29 hiring-event date could not be corroborated as genuinely 2026-dated and is now treated as unverified — no score impact since the broader hiring signal stands.</t>
+          <t>Unchanged: Training Center opened, 600+ hired, first vehicle body weld completed — genuine hiring/construction progress — offset by continued signals that customer deliveries may slip toward 2028.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -21146,14 +22517,14 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; county incentive hearing is a procedural step, not a scale change.</t>
+          <t>Unchanged; no new milestone this cycle.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -21166,14 +22537,14 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; no new milestone this cycle.</t>
+          <t>Unchanged; lease-commencement date confirmed but not a new milestone.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -21186,14 +22557,14 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; sole dated milestone now sits exactly at the trailing-6-month window boundary — flagged for likely drop-out next cycle absent a new update.</t>
+          <t>Unchanged; no new milestone this cycle.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -21202,18 +22573,18 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>State budget signed 2026-07-07 releases the previously-frozen $133.9M JDIG-linked funding (execution-certainty positive); hiring-ramp timeline itself unchanged — net +1.</t>
+          <t>Unchanged: EXIM Letter of Interest for up to $3B in financing is a modest, explicitly non-binding positive signal that does not resolve the JDIG-amendment hiring-ramp delay; score held flat.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -21227,6 +22598,26 @@
       <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup (Charlotte/Ballantyne)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Ranked this cycle: 510 jobs, $131,832 stated wage, and a confirmed in-window hiring-ramp to ~400/510 roles constitute genuine forward execution (not merely a delayed pre-window commitment), reversing three cycles of exclusion; scored below other ranked deals given modest capex ($16.1M) and first-time-ranked low repeat-momentum.</t>
         </is>
       </c>
     </row>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-07-27  ·  Window 2026-01-27 to 2026-07-27  ·  NC + SC</t>
+          <t>Week of 2026-08-03  ·  Window 2026-02-03 to 2026-08-03  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27  (Week 4)</t>
+          <t>2026-08-03  (Week 4)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-01-27 to 2026-07-27  (trailing 6 months)</t>
+          <t>2026-02-03 to 2026-08-03  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 90 (+3) — Rock Hill City Council's unanimous 7-0 vote on 2026-07-23 (rezoning, land sale, tax-incentive resolution) resolves the deal's last major outstanding risk</t>
+          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 90 (+3) — Rock Hill City Council voted unanimously 7-0 on 2026-07-23 to approve the land sale and amended tax-incentive terms, closing out the deal on both county and city sides</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Octapharma's Rock Hill City Council vote finally cleared 7-0 on 2026-07-23, fully closing out the region's most-watched pending approval. Citigroup's Ballantyne office is promoted to Ranked this cycle on the strength of a confirmed in-window hiring ramp (~400 of 510 roles filled) — the first tier promotion of a previously excluded deal since SMBC in Week 2. JetZero landed a non-binding EXIM Letter of Interest exploring up to $3B in federal financing, a modest positive that does not resolve its hiring-ramp delay. Two reversals: SC Ports' Leatherman Terminal pause is now confirmed effective Aug. 1 with no reopening timeline, and Pallidus's $443M Rock Hill semiconductor project was confirmed cancelled (37 laid off).</t>
+          <t>No brand-new qualifying (500+ job / $100k+ wage) deal was found in any of the five sub-regions this cycle — all 8 ranked entries carry forward. Octapharma's Rock Hill City Council vote (unanimous, 7-0) resolves the prior cycle's biggest open risk. Two major reversals surfaced: SC Ports' Leatherman Terminal pause took effect as scheduled on Aug. 1, 2026, and Chatham County terminated its VinFast EV-megafactory incentive agreement (7,500-job target collapsed to ~1,400, then cancelled outright) on July 28, 2026. Aspida Financial Services (Durham, 1,000 jobs, $137,288 stated wage) is a strong near-miss on Watch pending an in-window milestone.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-01-27 to 2026-07-27.</t>
+          <t>Trailing 6 months now runs 2026-02-03 to 2026-08-03.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>A prior-cycle fact was corrected: Scout Motors' '70+ maintenance-tech interview event beginning 7/29' traces to July 2025, not 2026 — no 2026 repeat was found, though independent April/June 2026 hiring and production milestones (Training Center opening, first vehicle body weld) confirm continued momentum. Two strong near-misses were added to Watch rather than Ranked: Aspida Financial (Durham, 1,000 jobs, $137,288 stated wage, but its only announcement predates the window) and VinFast (Chatham, job count cut to 1,400 with a stated wage well under $100k, now further complicated by a state lawsuit).</t>
+          <t>Maersk (Charlotte, wage stated at $100,962) and Citigroup (Ballantyne, wage stated at $131,832) remain excluded for a second/third consecutive cycle for consistency with this dataset's established milestone rules — both clear job-count/wage thresholds but their only in-window 'movement' traces to a hiring delay or a pre-window commitment, not genuine forward progress.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>8 of 8 prior-ranked deals remain qualifying; 1 promoted from Excluded to Ranked (Citigroup); 1 updated with a major positive resolution (Octapharma, +3); 1 updated (JetZero, non-binding financing signal, score flat); 1 gaining momentum (Scout Motors); 5 repeated (SMBC, AbbVie, Capital Group, Genentech, Novartis); none removed from Ranked. Watch tier: 1 removed as confirmed-stale (Snider Fleet Solutions); 3 new candidates added (BMW Woodruff, Aspida Financial, VinFast); Pallidus confirmed cancelled (stays in Excluded/Noise as a reversal).</t>
+          <t>8 of 8 prior-ranked deals remain qualifying (none removed, none newly added); 2 gaining momentum (Octapharma, JetZero), 1 updated (Scout Motors, timeline slip confirmed), 5 repeated (SMBC, AbbVie, Capital Group, Genentech, Novartis). Watch tier: 2 removed as stale (Snider Fleet Solutions, FN America), ~10 new additions (incl. Aspida Financial Services, Lenovo Whitsett, EnerSys Greenville scope-cut, Ahold Delhaize/Food Lion Burlington).</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2083,7 +2083,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -2174,7 +2174,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -2265,7 +2265,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2356,7 +2356,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -2447,7 +2447,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
@@ -2538,7 +2538,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -2629,7 +2629,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -2720,7 +2720,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -2811,7 +2811,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Lease signed / active hiring milestone</t>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (fully approved)</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax; Rock Hill forgoes ~85% of its project tax share; York County contributes 10% of its EDA fund revenue; ~$80M directed to Rock Hill Schools over 40 yrs</t>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; land sale of 50 ac in Palmetto Research Park to Octapharma</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>Final city + county approval (rezoning, land sale, tax-incentive resolution)</t>
+          <t>City-level approval closes out the deal</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+          <t>https://www.wbtv.com/2026/07/23/rock-hills-octapharma-projects-moved-forward-what-we-know/</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>High (facts); High (deal certainty — now fully approved)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -2986,21 +2986,21 @@
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH. Approval removes the deal's last major execution risk.</t>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (training center opens; first body weld)</t>
+          <t>Scout Motors — EV assembly plant (active hiring ramp; timeline slips further)</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
+          <t>$30-$34/hr maintenance tech / $33.50-$37.50/hr senior maintenance tech (stated); salaried roles mixed/undisclosed</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Training-center opening + production-validation milestone</t>
+          <t>Hiring event held as scheduled; timeline confirmation</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
+          <t>https://www.wltx.com/article/news/local/scout-motors-hiring-maintenance-technicians-blythewood-plant/101-1ca4c9f6-a045-44a2-8c89-8a427cd766e2</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
@@ -3084,7 +3084,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -3175,7 +3175,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Capital Group — East Coast ops hub</t>
+          <t>Capital Group — East Coast operations hub</t>
         </is>
       </c>
       <c r="H28" s="6" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>$194,141 avg (stated)</t>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Lease commenced</t>
+          <t>Wage figure confirmed (stated, not inferred)</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/capital-group-picks-its-uptown-charlotte-spot-for-600-workers</t>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, original 2025 tranche)</t>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B (doubled from ~$700M)</t>
+          <t>~$2.0B</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -3350,21 +3350,21 @@
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay).</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
         <v>7</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (EXIM financing exploration)</t>
+          <t>JetZero — aerospace plant (EXIM financing Letter of Interest)</t>
         </is>
       </c>
       <c r="H30" s="6" t="n">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr; EXIM exploring up to $3B financing (non-binding)</t>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>Letter of Interest for federal financing</t>
+          <t>Financing milestone — EXIM Bank Letter of Interest</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/jetzero-exim-explore-3b-financing-manufacturing-campus</t>
+          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
@@ -3441,14 +3441,14 @@
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale as prior cycles; the financing signal is a modest positive but does not resolve the hiring-ramp delay.</t>
+          <t>Same long-run scale; a $3B EXIM financing pathway strengthens confidence the megaproject reaches its full build-out even as near-term hiring stays on the 2028-2029 ramp.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Novartis — API mfg building</t>
+          <t>Novartis — API mfg building (investment increase)</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>~$991M (incl. $220M)</t>
+          <t>~$991M (incl. $220M API building)</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>State/local incentive package (Wake/Durham)</t>
+          <t>Part of original $771M package incentives</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>Investment increase (prior cycle)</t>
+          <t>New facility (unchanged)</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
@@ -3532,98 +3532,7 @@
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>Reinforces sustained high-wage biomanufacturing hiring in the Wake/Durham corridor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Charlotte / Ballantyne</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Mecklenburg</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Citigroup — Ballantyne regional office (grand opening + hiring ramp)</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Office — banking/financial services</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>$131,832 avg (stated)</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated</t>
-        </is>
-      </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>$16.1M</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed in sources reviewed</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>Office grand opening + active hiring ramp</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>High (facts); Med (promotion basis)</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>Strong suburban Class-A rental + move-up for-sale demand in Ballantyne/south Charlotte; $131,832 wage supports higher-income housing product.</t>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5416,7 +5325,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -5532,7 +5441,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5648,7 +5557,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5764,7 +5673,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5880,7 +5789,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -5996,7 +5905,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -6112,7 +6021,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6228,7 +6137,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -6344,7 +6253,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -6385,7 +6294,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Lease signed / active hiring milestone</t>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
         </is>
       </c>
       <c r="K24" s="6" t="n">
@@ -6453,19 +6362,19 @@
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle; project remains on track for fall 2026 first-worker arrivals.</t>
+          <t>No new in-window milestone found this cycle; project remains on track for fall 2026 first arrivals.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Gaining Momentum</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -6491,7 +6400,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (fully approved)</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -6501,7 +6410,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Final city + county approval (rezoning, land sale, tax-incentive resolution)</t>
+          <t>City-level approval closes out the deal</t>
         </is>
       </c>
       <c r="K25" s="6" t="n">
@@ -6514,7 +6423,7 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated, county-presented figures)</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
@@ -6529,12 +6438,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax; Rock Hill forgoes ~85% of its project tax share; York County contributes 10% of its EDA fund revenue; ~$80M directed to Rock Hill Schools over 40 yrs</t>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; land sale of 50 ac in Palmetto Research Park to Octapharma</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council approved 7-0 (rezoning, land sale, tax-incentive resolution) on 2026-07-23, following York County Council's 4-3 third-reading approval on 2026-07-08/09; construction could start late 2026, buildout ~10 yrs</t>
+          <t>Rock Hill City Council voted UNANIMOUSLY 7-0 on 2026-07-23 to approve both the land sale and the amended tax-incentive agreement, resolving the prior cycle's single outstanding risk; deal is now fully closed on both county and city sides. No groundbreaking date set yet; construction expected to start 2027.</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -6544,12 +6453,12 @@
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+          <t>https://www.wbtv.com/2026/07/23/rock-hills-octapharma-projects-moved-forward-what-we-know/</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>High (facts); High (deal certainty — now fully approved)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -6564,31 +6473,31 @@
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH. Approval removes the deal's last major execution risk.</t>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
         </is>
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council's unanimous vote resolves the outstanding-vote risk flagged in the 2026-07-13 report; deal now fully approved at both city and county level. +3 vs prior cycle.</t>
+          <t>The prior cycle's key open question (Rock Hill City Council's vote) is now resolved unanimously in favor — execution-risk discount removed, score up +3. Council members publicly criticized York County over the tax-split fight during the same meeting, but the vote itself was 7-0 to proceed. Next milestone to watch: a groundbreaking date.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Gaining Momentum</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
@@ -6607,7 +6516,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (training center opens; first body weld)</t>
+          <t>Scout Motors — EV assembly plant (active hiring ramp; timeline slips further)</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -6617,7 +6526,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Training-center opening + production-validation milestone</t>
+          <t>Hiring event held as scheduled; timeline confirmation</t>
         </is>
       </c>
       <c r="K26" s="6" t="n">
@@ -6625,12 +6534,12 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Projected (600+ SC production hires)</t>
+          <t>Projected (~1,400 hired companywide; 600+ in SC)</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>$30-$37.50/hr line (stated, news); salaried higher</t>
+          <t>$30-$34/hr maintenance tech / $33.50-$37.50/hr senior maintenance tech (stated); salaried roles mixed/undisclosed</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -6650,17 +6559,17 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>Training Center opened 2026-04-20; first vehicle body weld completed June 2026 (validation build); customer deliveries trending toward 2028</t>
+          <t>Pre-hire/interview events for 70+ maintenance-tech roles proceeded as scheduled the week of 2026-07-29; Traveler production now explicitly targeted late 2027 with customer deliveries pushed to early 2028 (a further, more concrete slip vs. last cycle's softer 'trending toward 2028')</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>https://www.wistv.com/2026/04/20/scout-motors-hold-grand-opening-blythewood-area-training-center/</t>
+          <t>https://www.wltx.com/article/news/local/scout-motors-hiring-maintenance-technicians-blythewood-plant/101-1ca4c9f6-a045-44a2-8c89-8a427cd766e2</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -6685,14 +6594,14 @@
       </c>
       <c r="X26" s="6" t="inlineStr">
         <is>
-          <t>600+ hired at the SC production site as of April 2026 (~1,313 companywide per Revelio Labs, Dec 2025). Correction: the '70+ maintenance-tech interview event beginning 7/29' cited in the 2026-07-13 report is a July 2025 event, not 2026 — no 2026 repeat found. Feb 2026 reporting suggests customer deliveries may slip to summer 2028; company reaffirms 2027 initial production.</t>
+          <t>Hiring event proceeded on schedule (positive), but the customer-delivery timeline slip to 'early 2028' is now stated plainly rather than softly implied — net -1 for confirmed further timeline risk even as near-term hiring signal stays strong.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -6801,14 +6710,14 @@
       </c>
       <c r="X27" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle; project remains on track.</t>
+          <t>No new in-window milestone found this cycle.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -6839,7 +6748,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Capital Group — East Coast ops hub</t>
+          <t>Capital Group — East Coast operations hub</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -6849,7 +6758,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Lease commenced</t>
+          <t>Wage figure confirmed (stated, not inferred)</t>
         </is>
       </c>
       <c r="K28" s="6" t="n">
@@ -6862,7 +6771,7 @@
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>$194,141 avg (stated)</t>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
@@ -6882,17 +6791,17 @@
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>16-yr lease at One Independence Center (196,940 sq ft) commenced 2026-05-22; hiring 2027-2031</t>
+          <t>12-yr JDIG term; lease term began 2026-05-22</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/capital-group-picks-its-uptown-charlotte-spot-for-600-workers</t>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -6917,14 +6826,14 @@
       </c>
       <c r="X28" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone beyond the already-confirmed lease-commencement date; unchanged since 2026-07-13.</t>
+          <t>No new in-window milestone found this cycle; hiring doesn't begin until 2027.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -6978,7 +6887,7 @@
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, original 2025 tranche)</t>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
@@ -6988,7 +6897,7 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B (doubled from ~$700M)</t>
+          <t>~$2.0B</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
@@ -7028,31 +6937,31 @@
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake (Holly Springs/Apex/Fuquay).</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle. Some 2026 coverage references a total nearer 600 site jobs; unverified as a distinct dated milestone — flagged for next cycle.</t>
+          <t>No new in-window milestone found this cycle.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Gaining Momentum</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
@@ -7071,7 +6980,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (EXIM financing exploration)</t>
+          <t>JetZero — aerospace plant (EXIM financing Letter of Interest)</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -7081,7 +6990,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Letter of Interest for federal financing</t>
+          <t>Financing milestone — EXIM Bank Letter of Interest</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
@@ -7109,12 +7018,12 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to ~$1.02B / 37 yr; Guilford grant ~$75.9M / 20 yr; EXIM exploring up to $3B financing (non-binding)</t>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>EXIM Letter of Interest signed 2026-07-20 at the Farnborough Airshow to explore up to $3B in financing under EXIM's 'Make More in America' initiative; explicitly not a financing commitment, subject to due diligence and EXIM Board approval</t>
+          <t>JetZero and the U.S. Export-Import Bank signed a Letter of Interest on 2026-07-20 (at the Farnborough Airshow) to explore up to $3B in EXIM financing for the Greensboro campus — a capital-durability signal, not a jobs/wage change; hiring ramp still begins 2028-2029 per the prior JDIG amendment</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -7124,7 +7033,7 @@
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/jetzero-exim-explore-3b-financing-manufacturing-campus</t>
+          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -7144,19 +7053,19 @@
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale as prior cycles; the financing signal is a modest positive but does not resolve the hiring-ramp delay.</t>
+          <t>Same long-run scale; a $3B EXIM financing pathway strengthens confidence the megaproject reaches its full build-out even as near-term hiring stays on the 2028-2029 ramp.</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>Non-binding financing exploration only; does not change the JDIG-amendment hiring ramp (zero jobs projected for 2027, full 14,500-job target due by 2037). Score held flat.</t>
+          <t>Construction/financing momentum continues even though no new jobs/wage figures moved this cycle — +1 for reduced execution-certainty risk on the capital side.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -7187,7 +7096,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Novartis — API mfg building</t>
+          <t>Novartis — API mfg building (investment increase)</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -7197,7 +7106,7 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Investment increase (prior cycle)</t>
+          <t>New facility (unchanged)</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
@@ -7220,17 +7129,17 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>~$991M (incl. $220M)</t>
+          <t>~$991M (incl. $220M API building)</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>State/local incentive package (Wake/Durham)</t>
+          <t>Part of original $771M package incentives</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>Facilities opening 2027-2028</t>
+          <t>Facility opening targeted 2027-2028</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -7260,128 +7169,12 @@
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>Reinforces sustained high-wage biomanufacturing hiring in the Wake/Durham corridor.</t>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
         <is>
           <t>No new in-window milestone found this cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>New (promoted from Excluded)</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Charlotte / Ballantyne</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Mecklenburg</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Citigroup — Ballantyne regional office (grand opening + hiring ramp)</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Banking / financial services</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>Office grand opening + active hiring ramp</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>Projected; ~400 hired to date</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>$131,832 avg (stated)</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>$16.1M</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed in sources reviewed</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>Grand opening 2026-03-17; ~400 of 510 planned roles filled as of ~April 2026 (incl. 275 relocated internally); 3-floor, 90,000 sq ft building</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs</t>
-        </is>
-      </c>
-      <c r="T32" s="6" t="inlineStr">
-        <is>
-          <t>High (facts); Med (promotion basis)</t>
-        </is>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>Office — banking/financial services</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="W32" s="6" t="inlineStr">
-        <is>
-          <t>Strong suburban Class-A rental + move-up for-sale demand in Ballantyne/south Charlotte; $131,832 wage supports higher-income housing product.</t>
-        </is>
-      </c>
-      <c r="X32" s="6" t="inlineStr">
-        <is>
-          <t>Promoted from Excluded to Ranked this cycle: the in-window grand opening plus a confirmed hiring-ramp to ~400/510 roles is genuine forward-moving execution, not merely a delayed pre-window commitment (same logic used for SMBC's Week-2 promotion). Prior cycles excluded this deal; this reverses that call.</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10950,7 +10743,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -11012,7 +10805,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -11074,7 +10867,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -11136,7 +10929,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -11198,7 +10991,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -11260,7 +11053,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -11322,7 +11115,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -11384,7 +11177,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -11446,7 +11239,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -11508,7 +11301,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -11570,7 +11363,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -11632,7 +11425,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -11694,7 +11487,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -11756,7 +11549,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -11818,7 +11611,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -11880,7 +11673,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -11942,7 +11735,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -12004,7 +11797,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -12066,7 +11859,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -12128,7 +11921,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -12190,7 +11983,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -12252,7 +12045,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -12314,7 +12107,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -12376,7 +12169,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -12438,7 +12231,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -12500,7 +12293,7 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -12562,7 +12355,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -12624,7 +12417,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -12686,7 +12479,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -12748,7 +12541,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -12810,7 +12603,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -12872,7 +12665,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -12934,7 +12727,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -12996,7 +12789,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -13058,7 +12851,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -13120,7 +12913,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -13182,7 +12975,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -13244,7 +13037,7 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -13306,7 +13099,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -13368,7 +13161,7 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -13430,7 +13223,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -13492,7 +13285,7 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -13527,12 +13320,12 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; $24.50-$63/hr stated range</t>
+          <t>$24.50-$63/hr (stated)</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>Still just under 500 jobs; facility now targeted to open April 2028 (later ramp than previously implied)</t>
+          <t>Formal site-selection/investment announcement confirmed 2026-06-02; still just under 500 jobs, no threshold-crossing update found; commissioning now targeted ~2028</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
@@ -13542,7 +13335,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>https://investors.usare.com/news-releases/news-release-details/usa-rare-earth-selects-cherokee-county-south-carolina-new-rare</t>
+          <t>https://governor.sc.gov/news/2026-06/usa-rare-earth-inc-selects-cherokee-county-first-south-carolina-operation</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
@@ -13554,7 +13347,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -13589,12 +13382,12 @@
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>Stated $23-$53/hr = workforce-tier</t>
+          <t>Entry-level ~$23/hr; technicians $26-$36/hr (stated) — Estimated/Inferred blended avg ~$62k-$83k, below $100k</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>No update found; operations still targeted spring/summer 2027</t>
+          <t>Crosses 500 jobs but detailed wage-tier data confirms the bulk of roles fail the $100k bar; stays Watch. Operations still targeted 2027</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
@@ -13604,7 +13397,7 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2026-04/suniva-inc-selects-laurens-county-first-south-carolina-manufacturing-facility</t>
+          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -13616,17 +13409,17 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Gray Court / Laurens Co.</t>
+          <t>Columbia / BullStreet</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Richland</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -13636,22 +13429,22 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Aptiv Services US — Connexial Center</t>
+          <t>AMAROK — new HQ (perimeter security)</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>296</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>$120.8M</t>
+          <t>$69M</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -13661,12 +13454,12 @@
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
+          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -13678,79 +13471,79 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Columbia / BullStreet</t>
+          <t>Greensboro</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Richland</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>AMAROK — new HQ (perimeter security)</t>
+          <t>Lumentum — AI/data-center optics</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>~400</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>$69M</t>
+          <t>Hundreds of millions</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred sub-$100k (security-tech corporate/sales mix)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>Formal announcement confirmed 2026-03-24; 125,000 sq ft building, houses 500+ total employees incl. relocated staff, online by end of 2028</t>
+          <t>Ribbon-cutting confirmed 2026-04-29; production still targeted mid-2028; no further update this cycle</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+          <t>https://greensboro.com/news/local/business/development/article_be1b2ff0-8a3c-463e-904e-78472c59db7a.html</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Greensboro</t>
+          <t>Hendersonville</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -13760,59 +13553,59 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>Lumentum — AI/data-center optics</t>
+          <t>BorgWarner — vertical-integration expansion</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>~400</t>
+          <t>378</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Hundreds of millions</t>
+          <t>$100M</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$67,047 avg (stated; below $100k)</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>Confirmed announcement date 2026-03-26 (240,000 sq ft indium-phosphide laser plant on former Qorvo site); production targeted mid-2028; no update since</t>
+          <t>No new update found this cycle</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>https://www.areadevelopment.com/newsitems/4-14-2026/lumentum-greensboro-north-carolina.shtml</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Hendersonville</t>
+          <t>Asheville / Arden</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -13822,59 +13615,59 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>BorgWarner — vertical-integration expansion</t>
+          <t>Eaton — Low Voltage Assembly expansion</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>$100M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>$67,047 avg (stated; below $100k)</t>
+          <t>'high-wage' but figure Not disclosed (Inferred mid-$60k-$80k)</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>No new update found this cycle; remains 7th Helene-recovery manufacturer expansion</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (jobs); Low (wage)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Asheville / Arden</t>
+          <t>Kernersville</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Forsyth</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -13884,59 +13677,59 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Eaton — Low Voltage Assembly expansion</t>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>150+</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$70M</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>Mixed band: current postings range $19.50/hr (Assembler) to $86k-$126k (LVA Mfg Supervisor)</t>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle beyond confirmed wage-band detail</t>
+          <t>Construction underway on west campus; opening still targeted 'next year'</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+          <t>https://journalnow.com/news/local/business/development/article_b204fb94-5ff2-4618-9eba-6aee803fc2dc.html</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr">
         <is>
-          <t>High (jobs); Low (wage)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / Raleigh / Rural Hall</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -13946,59 +13739,59 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Siemens Energy — $421M NC expansion</t>
+          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>500 (statewide)</t>
+          <t>5,100 (proj. total); 3,000+ employed</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>$421M</t>
+          <t>$13.9B</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Charlotte/Mecklenburg-specific split still unconfirmed</t>
+          <t>$62,234 (stated; below $100k)</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>No update found; county-level job split still not disclosed despite renewed search</t>
+          <t>Continued active hiring (70+ open roles as of Aug 2026); no wage or NC-specific investment update found this cycle</t>
         </is>
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+          <t>https://allamerican.org/news/toyotas-north-carolina-battery-plant-brings-jobs/</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>High (totals); Low (wage/split)</t>
+          <t>High (jobs); Low (wage)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Knightdale / Wendell</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -14008,17 +13801,17 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Siemens AG — power devices for AI/data centers</t>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>≤500 currently; must hit 500 by 12/31/2026</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>part of $165M</t>
+          <t>~$50M (hangar)</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
@@ -14028,7 +13821,7 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>New Wendell facility (101,000 sq ft, ~50 jobs) came online July 2026 as expected; Knightdale (131,000 sq ft, ~100 jobs) still targeting end of 2026</t>
+          <t>No movement toward or away from the Dec 31, 2026 lease-default trigger found this cycle; hangar still described as largely idle; a July 2026 FAA supersonic-overland rulemaking (comment period closes 2026-08-17) is a regulatory tailwind, not a jobs signal</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
@@ -14038,29 +13831,29 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Kernersville</t>
+          <t>Multi-site incl. Wilmington</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Forsyth</t>
+          <t>New Hanover+</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -14070,151 +13863,151 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>John Deere — excavator plant (relocating from Japan)</t>
+          <t>Amazon-Corning — fiber-optics partnership</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>150+</t>
+          <t>1,000 (multi-site, unallocated)</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>$70M</t>
+          <t>Multi-billion (undisclosed NC-specific)</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Inferred skilled-mfg)</t>
+          <t>avg &gt;$65,000 (sub-$100k)</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>Project reaffirmed via a White House social-media assist ~Jan 2026; construction underway on west campus; no further update this cycle</t>
+          <t>Confirmed 2026-06-08; multi-year, multi-billion agreement; per-site allocation still not broken out</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>https://hpj.com/2026/01/28/deere-announces-two-new-u-s-plants</t>
+          <t>https://www.wect.com/2026/06/08/amazons-data-center-push-fuels-1000-job-fiber-optic-agreement-with-corning/</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>York Co.</t>
+          <t>Arden</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>QTS "Project Cobra" — data-center campus</t>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>~200 FTE (+~1,000 constr.)</t>
+          <t>325</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>up to $8B</t>
+          <t>$285M</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>~$80k median (stated)</t>
+          <t>$62,413 (stated)</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>York County's 9-month data-center moratorium passed final reading 2026-07-13 but does not affect QTS's already-permitted (2023) construction</t>
+          <t>On track: equipment arrival end-2026 target unchanged, first parts still mid-2027</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>https://www.wbtv.com/2026/06/17/york-county-weighs-9-month-moratorium-new-data-centers-what-we-know/</t>
+          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county/</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
-          <t>High (facts)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Berkeley / Dorchester</t>
+          <t>Asheboro</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Berkeley &amp; Dorchester</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Google — data-center expansion</t>
+          <t>Environmental Air Systems</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>~160 apprentices (FTE n/d)</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>$9B</t>
+          <t>$20M</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$55,133 (stated)</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>$9B investment now confirmed to cover the existing Berkeley County campus expansion plus two NEW Dorchester County campuses; no discrete permanent-job figure disclosed</t>
+          <t>No jobs/wage change; new incentive detail surfaced (~$5M total: $3.3M JDIG, $1.2M workforce training, $500K building re-use grant)</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
@@ -14224,49 +14017,49 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>https://www.charlestondigital.com/news/google-announces-new-usd9b-investment-in-south-carolina-through-2027</t>
+          <t>https://edpnc.com/news/environmental-air-systems-randolph-county/</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr">
         <is>
-          <t>High (capex)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Pickens</t>
+          <t>New Hanover</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>FN America — 2nd production facility</t>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>~176</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>$33M</t>
+          <t>Not itemized</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
@@ -14276,101 +14069,101 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>Third consecutive quiet cycle with no movement — recommend removal next cycle absent an update</t>
+          <t>GNF4 fabrication underway; new detail: GNF plans &gt;$50M in safety/quality/production investment across this year and next; first lead-use assemblies contracted for 2026 deployment</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
+          <t>https://www.wilmingtonbiz.com/more_news/2025/10/09/global_nuclear_fuel_to_fabricate_new_nuclear_fuel_product_in_wilmington/26920</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Whitsett</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Siemens Smart Infrastructure</t>
+          <t>NEW — Lenovo — server/AI manufacturing campus expansion</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>~150</t>
+          <t>~1,000 total target (up from ~600 current)</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>$165M</t>
+          <t>$145M (up from original $77M pledge)</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$66,770 (2025-stated; sub-$100k)</t>
         </is>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>Ribbon-cutting held 2026-07-24 at the 'NC Smart Campus,' Whitsett; facility doubled to 890,000 sq ft, 35% more manufacturing capacity, 20MW power infrastructure for AI/HPC</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+          <t>https://news.lenovo.com/pressroom/press-releases/lenovo-doubles-the-size-of-its-u-s-manufacturing-facility-in-north-carolina/</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Hamlet</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Guilford/Alamance</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -14380,49 +14173,49 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>AWS/Amazon — AI/cloud campus</t>
+          <t>NEW — Ahold Delhaize USA / Food Lion — "Project Titan" distribution center</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>505 (proj. by end of 2033)</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>$10B</t>
+          <t>$860M</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$60k-$62k avg (Estimated/Inferred; sub-$100k distribution-center wage)</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>Still unverified; Richmond County falls outside all five assigned research sub-regions this dataset tracks — carried forward unchanged pending a dedicated check</t>
+          <t>Guilford ($17.9M) and Burlington City ($21.5M) incentive packages approved; construction expected to begin 2026, operations 2029; crosses 500 jobs but wage clearly fails the higher-income-housing test</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>verify</t>
+          <t>2025-10 (approvals); 2026 construction start</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>https://www.aboutamazon.com/</t>
+          <t>https://greensboro.com/news/local/business/employment/article_ce55534b-c262-47cf-b949-8cfda5828bf7.html</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
         <is>
-          <t>Low (needs verification)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
@@ -14447,12 +14240,12 @@
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>~11,000 (pipeline); 60,000+ direct+indirect target</t>
+          <t>~11,000 (pipeline)</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>$11B (pipeline); $3B (EDGE 7 target)</t>
+          <t>$11B</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -14462,7 +14255,7 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>Raleigh Chamber formally launched EDGE 7, a 5-year strategy succeeding the closed EDGE 6 campaign (37 projects/$5.6B/10,800 jobs); no new named mega-project beyond items already tracked</t>
+          <t>2026 outlook reconfirms the ~$11B/11,000-job pipeline; ~25% of prospects foreign-HQ'd (Japan, Germany, Switzerland)</t>
         </is>
       </c>
       <c r="J114" s="6" t="inlineStr">
@@ -14472,7 +14265,7 @@
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>https://raleigh-wake.org/about-us/edge7</t>
+          <t>https://raleigh-wake.org/blog/2026-economic-development-outlook-forwake-county</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr">
@@ -14484,17 +14277,17 @@
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / SouthPark</t>
+          <t>Raleigh / Wendell / Knightdale</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -14504,37 +14297,37 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Chase — new office</t>
+          <t>Siemens AG — power devices for AI/data centers</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>400 new (1,000 total on-site)</t>
+          <t>350</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H115" s="6" t="inlineStr">
-        <is>
-          <t>Estimated/Inferred ~$105k (unconfirmed)</t>
-        </is>
-      </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>New office at One Piedmont Town Center (5 floors, 145,000 sq ft) confirmed 2026-04-21; consolidates 600+ existing staff plus 400 new; move-in early 2028</t>
+          <t>New 101,000-sf Wendell facility confirmed online July 2026 as previously flagged; Knightdale's 100-jobs-by-end-2026 target not yet confirmed met</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorganchase-charlotte-hiring-workforce-banking-competition</t>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
@@ -14546,17 +14339,17 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Charlotte (CLT airport)</t>
+          <t>Siler City</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -14566,59 +14359,59 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Averitt — logistics campus</t>
+          <t>Wolfspeed — silicon-carbide fab ("The JP")</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>1,800 (proj.)</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$5.0B</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>$81,769 (stated)</t>
+          <t>$77,753 (stated, 2025)</t>
         </is>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle; confirmed unchanged</t>
+          <t>Q2 FY26 earnings (reported 2026-02-04) show Siler City underutilization costs rising ($26M-&gt;$47M YoY); new CEO pursuing 'operational discipline' (optimize installed capacity) over aggressive ramp — a slower, more measured hiring trajectory than previously implied. Company separately shut down its legacy Durham 150mm line (see Excluded)</t>
         </is>
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
+          <t>https://www.investing.com/news/transcripts/earnings-call-transcript-wolfspeeds-q2-2026-results-disappoint-stock-dips-93CH-4486298</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Rowan County</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -14628,59 +14421,59 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>"Project Rack" (company undisclosed)</t>
+          <t>Vulcan Elements — magnet factory</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>1,000 (proj.)</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>$41M</t>
+          <t>$918.4M</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$100k</t>
+          <t>$81,932 (stated)</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>Rowan County Commissioners approved 3-year tax incentives 2026-06-05 for the still-undisclosed 'iconic American brand'; Q1 2027 operations start still targeted</t>
+          <t>Johnston Community College received a $3.6M GoldenLEAF grant; train-the-trainer instruction begins summer 2026 as scheduled; company secured a $620M federal loan plus a government equity stake, though a Feb-2026 site visit found the parking lot still largely empty ahead of a targeted Q1 2027 Benson-operations start</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>https://www.salisburypost.com/2026/06/05/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
+          <t>https://www.thewirechina.com/2026/03/15/the-magnet-makers-vulcan-elements-rare-earths/</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Rowan/Kannapolis</t>
+          <t>Wake County (statewide)</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -14690,54 +14483,54 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
+          <t>WakeMed / Atrium Health — proposed merger</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>$55k-$150k range (DHL postings)</t>
-        </is>
-      </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>No update found; DHL actively hiring on-site but Kannapolis officials confirm no job total tied to the Google lease has been released</t>
+          <t>Wake County Commissioners voted 2026-05-04 to delay their decision by 90 days, landing the vote at approximately 2026-08-02 — essentially coincident with this report's cutoff; no confirmed outcome located as of this report date. HIGHEST-PRIORITY recheck for next cycle</t>
         </is>
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>https://www.wcnc.com/article/news/local/google-facility-planned-in-kannapolis</t>
+          <t>https://www.wake.gov/news/wake-county-commission-delays-vote-legal-documents-related-wakemed-atrium-health-strategic-combination</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (timeline); Low (outcome)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / North Hills</t>
+          <t>RTP</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -14752,59 +14545,59 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Ralliant Corp. — global HQ launch</t>
+          <t>Apple — RTP campus extension</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>~150 on-site now (180 by 2029)</t>
+          <t>3,000 originally proj.; ~600-990 added to date</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>$2.1M</t>
+          <t>$552M-$1B+ (paused)</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>$170,531-$189,479 (stated)</t>
+          <t>$187k (stated, 2021 award)</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>HQ formally opened 2026-03-05; state expects up to 180 high-paying jobs by 2029</t>
+          <t>No active construction found this cycle; new hiring commitments restart 2027 under the incentive-timeline extension. (Note: this session's sources date the extension itself to late Nov. 2025, not April 2026 as in the prior baseline — flagged for reconciliation)</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11 (extension)</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260305697057/en/Ralliant-Opens-Global-Headquarters-in-Raleigh-North-Carolina</t>
+          <t>https://9to5mac.com/2025/11/25/apple-granted-rare-timeline-extension-north-carolina-campus/</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Siler City</t>
+          <t>Raleigh / North Hills</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -14814,59 +14607,59 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Wolfspeed — silicon-carbide fab (layoffs announced; long-term target reaffirmed)</t>
+          <t>Ralliant Corp. — global HQ launch</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>1,800 (proj., slower pace)</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>$5.0B</t>
+          <t>$2.1M</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>$77,753 (stated)</t>
+          <t>$170k-$189k (stated)</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>Wolfspeed disclosed ~2026-06-09 it will lay off 73 Siler City employees (effective 2026-08-08) amid soft demand and cut FY2026 revenue guidance to $850M, but reaffirmed the full 1,800-job Siler City commitment at a slower pace</t>
+          <t>HQ officially opened 2026-03-05; 150 of the 180 targeted jobs already filled; hiring continues through 2029</t>
         </is>
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>https://www.carolinajournal.com/wolfspeed-layoffs-at-its-siler-city-materials-factory/</t>
+          <t>https://www.wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Low (timeline)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -14876,54 +14669,54 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>Vulcan Elements — magnet factory</t>
+          <t>NEW — Aspida Financial Services — HQ expansion</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>1,000 (proj.)</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>$918.4M</t>
+          <t>$28M</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>$81,932 (stated)</t>
+          <t>$137,288 avg (stated; Durham Co. avg is $97,531)</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>No new in-window update found on hiring/construction progress this cycle</t>
+          <t>HIGH-PRIORITY WATCH ADD: numerically clears both the 500-job and $100k-wage bars, but the announcement itself is dated 2025-11-19 — before this window opens — and no in-window (Feb-Aug 2026) milestone (lease signing, groundbreaking, hiring event) was found this cycle. Recommend promoting to Ranked the moment a genuine forward-moving in-window milestone surfaces</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>https://www.wunc.org/economy/2025-11-18/vulcan-elements-worlds-largest-magnet-factory-outside-china-benson</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/financial-services-company-expand-durham-headquarters-1000-new-jobs</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (facts); N/A (in-window trigger)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Wake County (statewide)</t>
+          <t>Holly Springs</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -14938,59 +14731,59 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>WakeMed / Atrium Health — proposed merger</t>
+          <t>NEW — Amgen — biomanufacturing site (headcount target)</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>3,300 (statewide, 5 yr)</t>
+          <t>725 total by 2032 (site target)</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>$2.0B (Wake Co. portion)</t>
+          <t>~$1.57B (cumulative)</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$91,527 avg (stated, sub-$100k)</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>Wake Commissioners voted 2026-05-04 to delay the vote by 90 days, pushing a potential vote to ~2026-08-02 — just after this window closes; opposition continues to mount</t>
+          <t>No in-window milestone beyond the ongoing ramp toward the 2032 target</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-12 (original)</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/news/local/wakemed-atrium-health-planned-deal-state-auditor-calls-for-delay-may-2026/</t>
+          <t>https://www.ncbiotech.org/news/amgens-holly-springs-facilities-employ-more-700-2032</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>RTP</t>
+          <t>Clayton</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -15000,59 +14793,59 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Apple — RTP campus extension</t>
+          <t>NEW — Novo Nordisk — manufacturing campus</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>3,000 originally proj.; ~600-990 added to date</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>$552M-$1B+ (paused)</t>
+          <t>$4.1B</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>$187k (stated, 2021 award)</t>
+          <t>Estimated/Inferred $65k-$70k (sub-$100k; basis: company-disclosed range vs. ~$45k county avg)</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>DATE CORRECTION: the 4-yr incentive-timeline extension was approved 2025-11-25 (not April 2026 as previously reported); no active construction restart found</t>
+          <t>Construction phased 2027-2029; ~2,000 external contractors on-site for clearing/foundation work; no confirmed new 2026 milestone beyond ongoing construction</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025 (original); ongoing construction</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>https://9to5mac.com/2025/11/25/apple-granted-rare-timeline-extension-north-carolina-campus/</t>
+          <t>https://businessnc.com/novo-nordisk-investing-4-1b-adding-1000-jobs-in-johnston-county/</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Raleigh</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -15062,59 +14855,59 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+          <t>NEW — BuildOps Inc. — 3rd US hub</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>≤500 currently; must hit 500 by 12/31/26</t>
+          <t>291</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>~$50M (hangar)</t>
+          <t>$711,200</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$110,997 avg (stated; &gt;$100k, but sub-500 jobs)</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>Risk continues escalating: hangar still largely idle per most recent coverage; no updated employee-count disclosure found; deadline now ~5 months out with no positive movement</t>
+          <t>Announced 2025-06-24, pre-window; no confirmed in-window milestone found</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>https://www.hoodline.com/2026/03/greensboro-s-50-million-supersonic-ghost-hangar-puts-state-on-the-clock</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/24/governor-stein-announces-software-company-buildops-will-create-291-jobs-raleigh</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr">
         <is>
-          <t>Med (facts); Low (outlook)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Multi-site NC incl. Wilmington</t>
+          <t>Statesville</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>New Hanover +</t>
+          <t>Iredell</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -15124,59 +14917,59 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Amazon-Corning — fiber-optics partnership</t>
+          <t>Compass Datacenters</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>1,000 (multi-site, unallocated)</t>
+          <t>~250</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>Multi-billion (undisclosed NC-specific)</t>
+          <t>$1B+ (up to 500MW campus)</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>Avg &gt;$65,000 (disclosed; sub-$100k)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>Deal confirmed 2026-06-08; per-site (Wilmington vs. Concord) allocation still not disclosed; distinct from the larger Corning-Meta $6B Hickory/Catawba deal</t>
+          <t>Statesville rezoning for the ~340-acre, up to 500MW campus has been reported, but no precisely dated in-window 2026 milestone could be confirmed this cycle; operations still targeted 2028</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-08 (pre-window baseline)</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>https://www.wect.com/2026/06/08/amazons-data-center-push-fuels-1000-job-fiber-optic-agreement-with-corning/</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Low (allocation)</t>
+          <t>Low-Med</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Arden</t>
+          <t>Rowan County</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -15186,37 +14979,37 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+          <t>"Project Rack" (company undisclosed)</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>$285M</t>
+          <t>$41M</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>$62,413 (stated)</t>
+          <t>Estimated/Inferred sub-$100k</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle; on track for equipment arrival end 2026, first parts mid-2027</t>
+          <t>Rowan County Commissioners approved incentives 2026-06-06 (three-year tax incentives); Q1 2027 ops start still targeted</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county</t>
+          <t>https://www.salisburypost.com/2026/06/06/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr">
@@ -15228,17 +15021,17 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Asheboro</t>
+          <t>Rowan/Kannapolis</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -15248,121 +15041,121 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Environmental Air Systems</t>
+          <t>Google (via 3rd-party logistics operator) — warehouse lease</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>$20M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>$55,133 (stated)</t>
+          <t>$55k-$150k range (job-board postings)</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>No update found despite targeted searches — third consecutive quiet cycle</t>
+          <t>Lease publicly confirmed 2026-04-29: 729,872 sq ft at Overlook 85 Industrial Park, 88-month term; explicitly described as 'not a data center' — warehousing/logistics; jobs still undisclosed</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/25/environmental-air-systems-expand-randolph-county-adding-300-jobs-and-20-million-investment</t>
+          <t>https://www.wbtv.com/2026/04/29/google-leases-massive-facility-near-rowan-cabarrus-county-line/</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (lease); Low (jobs)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Wilmington</t>
+          <t>York Co.</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>New Hanover</t>
+          <t>York</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+          <t>QTS "Project Cobra" — data-center campus</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~200 FTE (+~1,000 constr.)</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Not itemized ($50M+ cited)</t>
+          <t>up to $8B</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$80k median (stated)</t>
         </is>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>No update found; ~27 open GE Nuclear roles in Wilmington as of Feb 2026, but no discrete headcount figure disclosed for the GNF4 line</t>
+          <t>York County Council passed its 9-month data-center moratorium on 3rd/final reading 2026-07-13; QTS's own site plans (9 buildings, various stages) are already vested and unaffected by the moratorium</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>https://www.wilmingtonbiz.com/more_news/2025/10/09/global_nuclear_fuel_to_fabricate_new_nuclear_fuel_product_in_wilmington</t>
+          <t>https://www.wrhi.com/2026/06/york-county-council-approves-data-center-moratorium-first-reading-advances-1-5-billion-biopharmaceutical-project-213500</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Charlotte / SouthPark</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -15372,99 +15165,99 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
+          <t>JPMorgan Chase — new office</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>5,100 (proj. total); 3,000+ employed</t>
+          <t>400 new by 2028</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>$13.9B</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>$62,234 (stated; below $100k)</t>
+          <t>~$105k Estimated/Inferred</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>No new headcount milestone found beyond the previously reported 3,000+ figure; company still targets a new production line roughly every 4 months through decade's end</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>https://www.wfmynews2.com/article/news/local/major-milestone-over-3000-people-now-work-at-the-toyota-battery-plant/83-b192b700-91b7-42f4-837e-33d0c01ee96e</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Woodruff (Spartanburg Co.)</t>
+          <t>Charlotte (CLT airport)</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>AIRSYS Cooling Technologies — global HQ</t>
+          <t>Averitt — logistics campus</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>215 (at full operation)</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>$40-60M</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$81,769 (stated)</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>Global HQ campus (264,000 sq ft) officially opened 2026-05-13; corporate teams now on-site, but manufacturing operations (bulk of production hiring) remain delayed to Q1 2027</t>
+          <t>No update found this cycle; construction 'expected to begin immediately' per original release, completion 2028</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr">
@@ -15476,79 +15269,79 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Easley (Anderson/Pickens border)</t>
+          <t>Mooresville</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Iredell</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Signature Foods USA</t>
+          <t>NEW — Corvid Technologies — HQ expansion</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>367</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>$28.9M</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$50k</t>
+          <t>Not disclosed; Estimated/Inferred a meaningful share of engineering roles clear $100k (basis: Glassdoor role-level data — Software Engineer ~$134,243, Computational Analyst ~$138,353, Senior Program Manager ~$176,995; company-wide avg ~$77,578)</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>No headcount update found beyond the previously confirmed April 2026 online-operations milestone</t>
+          <t>Defense/aerospace/biomedical/motorsports physics engineering firm expanding its existing Mooresville HQ; announced 2026-06-20</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+          <t>https://statesville.com/news/iredell-chosen-for-367-job-headquarters/article_e69950c5-7074-5f48-bbbc-a2c832f5bb1f.html</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Spartanburg (former Kohler plant)</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -15558,49 +15351,49 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+          <t>NorthMark "Project Moc-1" — AI/HPC data center</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
+          <t>~150 FT at full operation</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>$2.8B-$3.0B</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>$500M (valuation, not capex)</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>No headcount figure published yet; new detail found — SCRA $50,000 relocation grant + city $1,500/job development grants imply a modest near-term headcount, but no number confirmed</t>
+          <t>Contested public hearing held 2026-06-25; comment period closed 2026-07-31 with no permit decision yet issued (SCDES says review could take 'several months'); a new lawsuit was filed 2026-07-06 by local residents seeking Planning Commission review of the next construction phase; construction continues despite opposition</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-07-06 (lawsuit); 2026-07-31 (comment close)</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>https://www.upstatescalliance.com/announcements/gnq-insilico-a-500m-biotech-innovator-moving-to-greenville/</t>
+          <t>https://www.postandcourier.com/spartanburg/news/spartanburg-data-center-northmark-water-power/article_07cc2de8-9eb6-4711-ad7f-90ef8230b158.html</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr">
         <is>
-          <t>Low (headcount unconfirmed)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -15625,7 +15418,7 @@
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>650 total planned; ~200 hired 2025, ~300 more by end 2026</t>
+          <t>650 total planned (200 hired 2025; 300 more by end 2026)</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
@@ -15635,44 +15428,44 @@
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mixed, bulk likely sub-$100k</t>
+          <t>Estimated/Inferred mixed, bulk likely sub-$100k (basis: job-board postings $66k-$125k)</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>No new hiring-ramp confirmation found this cycle beyond job-board listing activity</t>
+          <t>Hiring-ramp progress confirmed 2026-06-27 (200 hired 2025, 300 more targeted by end of 2026), consistent with production ramping from 37 turbines (2025) toward 74 (2027)</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
+          <t>https://www.cnbc.com/2026/06/27/ge-vernova-gas-turbines-ai-data-centers.html</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Spartanburg / Roebuck</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -15682,59 +15475,59 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Boeing 787 — production-rate ramp</t>
+          <t>Siemens Smart Infrastructure</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>1,000 (unchanged)</t>
+          <t>~150</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>$1.0B (existing)</t>
+          <t>$165M</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mixed</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>No Q2/Q3 2026 rate update found; rate confirmed 8/month as of Jan 2026, full 10/month target still described as 'over the next year'</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/</t>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Woodruff</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -15744,17 +15537,17 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>SC Ports Authority — Leatherman Terminal (OPERATIONS PAUSED, CONFIRMED)</t>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>400 direct + ~1,200 indirect</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>$1.2B (existing)</t>
+          <t>$40-60M</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -15764,17 +15557,17 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>CONFIRMED REVERSAL: pause of container operations takes effect 2026-08-01 (decision announced 2026-06-25); cargo consolidates into Wando Welch and North Charleston terminals; no reopening timeline given, contingent on demand recovery</t>
+          <t>Grand opening of the new 264,000 sq ft, 60-acre HQ campus confirmed 2026-05-13; manufacturing-operations start still targeted early 2027 (previously slipped from 2026, no further slip found)</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+          <t>https://airsysnorthamerica.com/airsys-opens-global-headquarters-campus-in-south-carolina-to-meet-surging-global-demand-for-ai-and-data-center-cooling/</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr">
@@ -15786,17 +15579,17 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Goose Creek</t>
+          <t>Gray Court</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Berkeley</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -15806,59 +15599,59 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>HII (Newport News Shipbuilding) — 1-yr+ operations</t>
+          <t>Aptiv Services US — Connexial Center</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>~250 (estimate)</t>
+          <t>277</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>One-year anniversary reconfirmed 2026-01-22 (first-unit delivery within 40 days of startup, 2025 targets exceeded); no updated headcount figure found this cycle</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>https://www.hii.com/news/hii-marks-one-year-of-newport-news-shipbuilding-charleston-operations</t>
+          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg (former Kohler plant)</t>
+          <t>Easley</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -15868,59 +15661,59 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>NorthMark "Project Moc-1" — AI/HPC data center</t>
+          <t>Signature Foods USA</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>~150 FT at full operation</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>$2.8B</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Estimated/Inferred sub-$50k</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>Contested public hearing held 2026-06-25; DES comment period on the air permit runs through 2026-07-31 (closes just after this window); permit now seeks 11 additional gas turbines, raising approved capacity from ~50MW to ~450MW; Spartanburg Co.'s new one-year data-center moratorium explicitly exempts this already-approved project</t>
+          <t>Operations confirmed online; company still actively hiring</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/spartanburg/news/spartanburg-county-council-data-center-public-hearing/article_746815ab-5f55-48b4-915e-e8c20482aae5.html</t>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg / I-26</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -15930,59 +15723,59 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Ferrara Candy — new mfg + corporate site</t>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>1,000 (10 yr)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>$675M</t>
+          <t>$500M (valuation, not capex)</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred sub-$100k (confectionery production)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking held 2026-05-19/20 (Gov. McMaster, Rep. Clyburn attended); first production lines targeted early 2029</t>
+          <t>Formal in-window relocation confirmation (HQ + labs moving from California/Canada to Greenville, initial lab ops at Clemson's CUBEInC) dated 2026-05-21/23; job projections still 'developing' pending planned public listing (SPAC merger)</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>https://www.wistv.com/2026/05/19/ferrara-candy-company-breaks-ground-orangeburg/</t>
+          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr">
         <is>
-          <t>High (facts)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Woodruff</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -15992,166 +15785,414 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>BMW Group — Plant Woodruff high-voltage battery assembly</t>
+          <t>NEW — EnerSys — lithium-ion cell manufacturing (Augusta Grove)</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>300 (part of $1.7B multi-year investment)</t>
+          <t>Originally 500 (2024); scope materially reduced</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>~$700M (Woodruff portion of $1.7B total)</t>
+          <t>~$500M (net, incl. ~$150M DOE grant)</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred sub-$100k (comparable BMW SC production/assembly wages typically $50k-$80k; battery-plant role mix may skew slightly higher but unconfirmed)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>BMW announced completion of its $1.7B South Carolina investment 2026-06-30/07-02, including the new Plant Woodruff battery facility; first fully-electric US-built BMW (iX5) production slated late 2026</t>
+          <t>FLAG: 2026-07-23 scope revision cuts planned capacity ~75-80% (from ~4-5 GWh to ~1 GWh), refocused exclusively to aerospace/defense/specialized-industrial cells; construction now targeted 1H FY2028, full production ~2031 (a major slip from the original 2027 target). Original 500-job figure should be treated as stale pending a restated number</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>https://spectrumlocalnews.com/sc/south-carolina/news/2026/07/02/south-carolina-bmw-investiment</t>
+          <t>https://investor.enersys.com/news/news-details/2026/EnerSys-Refines-Plans-for-DefenseFocused-Lithium-Cell-Manufacturing-Facility-with-DOE-Support/default.aspx</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
-          <t>Med (jobs/date); Low (wage)</t>
+          <t>Med-High (scope cut); Low (current jobs figure)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Fountain Inn</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Aspida Financial Services — HQ expansion (pre-window; tracked for a converting milestone)</t>
+          <t>NEW — EPC Power — AI data-center power inverter mfg</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>1,000 (proj., hiring 2028-2032)</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>$28M+</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>$137,288 avg (stated) — clears the $100k bar</t>
+          <t>Estimated/Inferred sub-$100k (basis: job-board postings $47k-$64k/yr, $25-$35/hr)</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>Meets the job-count and wage thresholds outright, but the only announcement (2025-11-19) and its $21.8M JDIG-style incentive predate the window; no in-window flagship-site-selection or groundbreaking milestone found this cycle — watching for one to convert to Ranked</t>
+          <t>Grand opening/ribbon-cutting of the 167,000 sq ft facility (EPC Power's 3rd US site) held 2026-07-15</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/financial-services-company-expand-durham-headquarters-1000-new-jobs</t>
+          <t>https://www.foxcarolina.com/2026/07/15/epc-power-opens-facility-upstate-produce-critical-ai-data-center-technology/</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>High (facts); N/A (timing)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy — new mfg + corporate site</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone since the May 2026 groundbreaking; first lines still targeted Q1 2029</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>~160 apprentices (FTE n/d)</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; $9B figure traces to an Oct. 2025 announcement (pre-window)</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L142" s="6" t="inlineStr">
+        <is>
+          <t>High (capex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (unchanged)</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>$1.0B (existing)</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>Rate confirmed 8/month as of Jan 2026; CEO targets 10/month by end of 2026; the $1B expansion is designed to eventually support 16/month by 2028, a more ambitious framing than the prior cycle's '10/month by 2027'</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/</t>
+        </is>
+      </c>
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal (OPERATIONS PAUSED)</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B (existing)</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED: SC Ports paused all container operations at Leatherman effective 2026-08-01 (today), consolidating cargo to Wando Welch/North Charleston, citing an 'uncertain trade outlook' and high labor costs from the all-union workforce structure (Leatherman handled &lt;6% of SC Ports' container volume). No reopening date given; Phase 2 wharf construction ($88.5M) continues uninterrupted, targeted for 2027 completion. No confirmation found of ILA worker layoffs tied to the pause</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 (announced); 2026-08-01 (effective)</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>https://scspa.com/news/sc-ports-consolidating-container-operations-in-the-short-term/</t>
+        </is>
+      </c>
+      <c r="L144" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding)</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>~250 (estimate)</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>One-year anniversary (Jan 2026) confirmed exceeding production targets; hosted Australia's Minister for Defence Industry 2026-07-27 in connection with the AUKUS submarine partnership — a positive diplomatic/business-development signal, but no new jobs/investment figures disclosed</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>Chatham County</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>Chatham</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>VinFast — EV plant (jobs cut; state suing to reclaim site)</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>1,400 (cut from 7,500 proj.)</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr">
-        <is>
-          <t>$4.0B (orig.; incentive up to $1.2B if met)</t>
-        </is>
-      </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>~$51,096 avg (Estimated/Inferred; well under $100k)</t>
-        </is>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>MATERIAL RISK: on 2026-03-18 VinFast cut its job projection to 1,400 and said construction resumes in 2026 (production targeted 2028); on 2026-05-21 NC AG Jeff Jackson sued VinFast to reclaim the Chatham County site and recoup incentives after VinFast missed its Jan 2024 construction deadline, its July 2026 operations deadline, and the 1,750-jobs-by-end-2026 requirement</t>
-        </is>
-      </c>
-      <c r="J141" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="K141" s="6" t="inlineStr">
-        <is>
-          <t>https://www.axios.com/local/raleigh/2026/05/21/north-carolina-sues-vinfast-to-take-back-control-of-chatham-county-land</t>
-        </is>
-      </c>
-      <c r="L141" s="6" t="inlineStr">
-        <is>
-          <t>High (facts); wage sub-$100k disqualifies Ranked</t>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/07/27/3333932/0/en/hii-hosts-australian-minister-for-defence-industry-at-newport-news-shipbuilding-charleston-operations.html</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -16166,7 +16207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18198,7 +18239,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -18240,7 +18281,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -18282,7 +18323,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -18324,7 +18365,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -18366,7 +18407,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -18408,7 +18449,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -18450,7 +18491,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -18492,7 +18533,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -18534,7 +18575,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -18576,7 +18617,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -18618,7 +18659,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -18660,7 +18701,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -18702,7 +18743,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -18744,7 +18785,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -18786,7 +18827,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -18828,7 +18869,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -18858,7 +18899,7 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; NC's Economic Investment Committee formally approved (2026-02-24/25) shifting the hiring window to 2027-2029 — still a delay, not qualifying forward movement; wage $100,962 stated</t>
+          <t>Pre-window; no new forward movement found beyond the previously-noted 1-year hiring delay (now 2027-2029); wage remains stated at $100,962 but a delay is not qualifying forward movement per report rules</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -18870,17 +18911,17 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors HQ (Plaza Midwood)</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charlotte / Ballantyne</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -18890,71 +18931,71 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; no confirmed dated in-window milestone found again this cycle (no groundbreaking/permit date located)</t>
+          <t>Pre-window; the March 2026 grand-opening milestone remains tied to a pre-window (2025-07-08) commitment; no new increase or fresh milestone found this cycle</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>https://www.detroitnews.com/story/business/autos/2025/11/14/scout-motors-rolls-into-charlotte-5-key-things-about-the-automaker/87270881007/</t>
+          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Pallidus (PROJECT CANCELLED)</t>
+          <t>Scout Motors HQ (Plaza Midwood)</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co.</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>0 (was 405)</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>REVERSAL: Pallidus scrapped its $443M Rock Hill/York Co. HQ-and-manufacturing relocation, laid off 37 employees (44% of workforce), and is pivoting back to Albany, NY amid weak silicon-carbide demand</t>
+          <t>Pre-window; early job postings for the HQ (several six-figure roles) surfaced this cycle but do not amount to a formal milestone (lease signing, groundbreaking, or a announced hiring-ramp event) — recheck next cycle for a concrete trigger</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://www.manufacturingdive.com/news/pallidus-cancel-rock-hill-south-carolina-semiconductor-plant-hq-relocation</t>
+          <t>https://www.detroitnews.com/story/business/autos/2025/11/14/scout-motors-rolls-into-charlotte-5-key-things-about-the-automaker/87270881007/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -18974,39 +19015,39 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>~400 (450+ on-site)</t>
+          <t>~400-450 (mix reloc.+new; ~250 net new)</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Grand opening confirmed 2026-03-25; Charlotte-area average salary $44,638 — well under $100k (pilots average ~$107k but are a minority of roles)</t>
+          <t>Grand opening reconfirmed (450+ team members, ~80% of net-new hiring filled); net-new local roles (~250) remain well below the 500-job threshold and wage remains mixed/mostly sub-$100k except for pilots — no new in-window update changes this assessment</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>https://www.qcnews.com/charlotte/psa-airlines-opens-charlotte-headquarters-bringing-400-jobs-and-boost-to-nc-economy</t>
+          <t>https://psaairlines.com/psa-airlines-celebrates-grand-opening-of-charlotte-headquarters-underscoring-economic-and-workforce-impact-across-north-carolina/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>IKO North America</t>
+          <t>Bosch — Dorchester Co. electric motors</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Chester Co.</t>
+          <t>Dorchester</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -19016,29 +19057,29 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>~180</t>
+          <t>n/d (workforce 1,500-&gt;1,800)</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Grand opening (production start) held March 2026; jobs remain ~180 — still below the 200-job Watch floor</t>
+          <t>No 2026 confirmation of resumption found this cycle; status remains unresolved/paused pending an EV-demand recovery</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>https://www.iko.com/na/iko-celebrates-grand-opening-of-new-fiberglass-and-fiberglass-mat-manufacturing-facilities-in-south-carolina</t>
+          <t>https://www.postandcourier.com/business/bosch-dorchester-electric-vehicles-rivian-expansion/article_265b1c36-ab6c-11ef-b047-3b784368d210.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -19068,7 +19109,7 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>No new 2026 milestone found again this cycle</t>
+          <t>No precisely-dated in-window 2026 milestone could be confirmed this cycle despite reported rezoning progress; staying excluded pending a hard date</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -19080,12 +19121,12 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Snider Fleet Solutions (REMOVED FROM WATCH)</t>
+          <t>Snider Fleet Solutions (REMOVED)</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -19095,7 +19136,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -19110,29 +19151,29 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>CONFIRMED STALE: original announcement dates to May 2023; no 2026 activity found in a dedicated re-check — removed from active Watch tracking this cycle</t>
+          <t>REMOVED from tracking this cycle: confirmed stale for a third consecutive pass — all coverage traces to a May 2023 announcement with zero 2026 activity found</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2023-05/snider-fleet-solutions-relocating-headquarters-lancaster-county</t>
+          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Bosch — Dorchester Co. electric motors</t>
+          <t>FN America — 2nd production facility (REMOVED)</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Dorchester</t>
+          <t>Liberty (Pickens)</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -19142,39 +19183,39 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>n/d (workforce 1,500-&gt;1,800)</t>
+          <t>~176</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Expansion remains paused amid EV demand downturn; no discrete new-jobs announcement or resumption found</t>
+          <t>REMOVED from tracking this cycle: three consecutive quiet cycles with no 2026 news on hiring, production start, or facility completion found; all available coverage remains 2023-2024 era</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/business/bosch-dorchester-electric-vehicles-rivian-expansion/article_265b1c36-ab6c-11ef-b047-3b784368d210.html</t>
+          <t>https://governor.sc.gov/news/2023-04/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Southeastern Container</t>
+          <t>VinFast EV megafactory (Moncure megasite) — TERMINATED</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Enka-Candler (Buncombe)</t>
+          <t>Chatham Co.</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -19184,39 +19225,39 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>12 (new)</t>
+          <t>Target cut from 7,500 to ~1,400; failed to meet 1,750-job threshold</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>$31M modernization confirmed, but only 12 new jobs at $32.90/hr (~$68,400/yr) — below both the 200-job Watch floor and the wage bar</t>
+          <t>MAJOR REVERSAL: Chatham County Commissioners voted 2026-07-28 to terminate the $400M incentives agreement (site abandoned since late 2024, no construction contract, expired permits); NC AG separately sued (~2026-05-21) to force VinFast to sell back the land. A collapse, not a growth signal</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>https://www.ashevillechamber.org/news-events/press-releases/southeastern-container-expands-buncombe-county-headquarters-and-manufacturing-operations</t>
+          <t>https://www.wral.com/business/vinfast-agreement-canceled-chatham-county-north-carolina-july-2026/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Walmart — Mebane distribution center</t>
+          <t>Wolfspeed — Durham fab (150mm device line)</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Alamance</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -19226,81 +19267,81 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>N/A (shutdown)</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Confirmed via current job postings: average pay ~$14.79/hr (~$30,700/yr) — well under $100k</t>
+          <t>Closure of a legacy 150mm device-production line, completed ahead of schedule per Q2 FY26 earnings call — an explicit contraction, not a growth signal (Wolfspeed's Siler City project remains separately tracked in Watch)</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>https://www.ziprecruiter.com/Jobs/Walmart-Distribution-Center/-in-Mebane,NC</t>
+          <t>https://www.investing.com/news/transcripts/earnings-call-transcript-wolfspeeds-q2-2026-results-disappoint-stock-dips-93CH-4486298</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>"3 medical textile manufacturers" (unnamed)</t>
+          <t>TigerDC "Project Spero" (still withdrawn)</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Winston-Salem (Forsyth)</t>
+          <t>Spartanburg Co.</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>600+ (aspirational)</t>
+          <t>~50 FTE (Phase I)</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Still no companies named as a set; aggregate/speculative claim; best partial matches (GMAX Industries, Tex-Tech Industries) are both pre-window and sub-200 jobs individually</t>
+          <t>Confirmed still withdrawn this cycle; no revival evidence found</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://www.foxcarolina.com/2026/02/27/company-withdraws-ai-data-center-spartanburg-county-consideration/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
+          <t>Corvid Technologies (retained note)</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Raleigh (Wake)</t>
+          <t>Mooresville (Iredell)</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -19310,81 +19351,81 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>1,500 (claimed)</t>
+          <t>367</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Re-checked again this cycle: still unverifiable — sole source is a non-authoritative relocation/SEO site (arcrelocation.com); no corroboration from Barclays, WRAL, Axios, NC Commerce, or the Governor's office</t>
+          <t>Tracked in Watch tier this cycle (367 jobs, wage not officially stated) — noted here only to confirm it does NOT qualify for Ranked: sub-500 jobs</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>https://arcrelocation.com/companies-moving-to-raleigh/</t>
+          <t>https://statesville.com/news/iredell-chosen-for-367-job-headquarters/article_e69950c5-7074-5f48-bbbc-a2c832f5bb1f.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Novo Nordisk speculative Four Oaks expansion</t>
+          <t>Numerous sub-200-job items (Poly-America/Carolina Poly Chester, Element Designs Fort Mill, TTX Charlotte, RXO Ballantyne, Daimler Truck Financial Ballantyne, Red Bull/Rauch Concord, EG Group Charlotte [jobs undisclosed], Lowe's Mooresville [-600, layoffs])</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Various Charlotte metro</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NC/SC</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>~500 (speculative)</t>
+          <t>12-450 each (or layoffs)</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>2025-10 (cancelled)</t>
+          <t>2021-2026</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Re-confirmed cancelled/shelved; company's active NC investment is concentrated in its separate Clayton (Johnston Co.) facility</t>
+          <t>Below Watch floor, low-wage, recycled old news with no in-window update, or (Lowe's) a layoff rather than a growth signal</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>https://jocoreport.com/major-four-oaks-pharmaceutical-project-cancelled/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Kempower (EV charger manufacturer)</t>
+          <t>Numerous sub-200/recycled items (Corning/Meta Hickory [out of region], Skyeton Fayetteville [out of region], CorestemChemon Winston-Salem [vague], Herbalife Winston-Salem, GMAX Industries, Foster Caviness/ReAgent/Tex-Tech Winston-Salem, Wilmington Trade Center Phase 2 [speculative/unallocated], Honda Aircraft Greensboro, Hoffman &amp; Hoffman Greensboro, ImpactData Greensboro, Southeastern Container Enka-Candler)</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Various Triad/WNC/Coastal</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -19394,39 +19435,39 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>0 (was ~306 committed)</t>
+          <t>12-1,500 each</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2019-2026</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>REVERSAL: company confirmed it will not meet its ~306-job Durham commitment; NC ended its tax incentives as a result</t>
+          <t>Below Watch floor, out of region, vague/speculative, or recycled old news with no in-window update</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/usa/the-herald-sun/20260716/281560887555485</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Biogen $2B RTP manufacturing investment</t>
+          <t>Numerous sub-200/recycled items (Cisco RTP "550 jobs" [stale SEO content, actually 2014], Merck Durham "180 jobs" [~2011], Microsoft Wake "500 jobs" [2019], CITEL America Hillsborough, Innovative Construction Group Chatham, Ypsomed Holly Springs, Audemars Piguet Raleigh, Fujifilm RTP, AdvanceTEC Johnston [160 jobs/~$90k])</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Durham/Wake (RTP)</t>
+          <t>Various NC Triangle</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -19436,1028 +19477,104 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>62-550 each</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2011-2026 (mostly stale)</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Pre-window (30th-anniversary announcement); company gave no job-count estimate tied to the investment</t>
+          <t>Below Watch floor and/or recycled/stale old news falsely resurfacing in current searches; no in-window update</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/biogen-manufacturing-2-billion-july-2025/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Amgen (2nd facility)</t>
+          <t>Numerous sub-200-job items (Cielo Digital Infrastructure Cherokee [30 jobs/$2.1B], Oshkosh Defense Spartanburg [recycled 2021], Detpak USA Spartanburg, Fortified Solar Greenville, United Composite Materials Greenville, Advanced Metalworks Anderson, Southern Wall Products Anderson, Sargent Metal Fabricators Anderson, Eastern Engineered Wood Anderson, Sync.MD Anderson, Woodward Inc. Greer [~275 jobs, no in-window milestone])</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs (Wake)</t>
+          <t>Various Upstate SC</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>10-1,000 each</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2021-2026</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; wage &gt;$91k but &lt;$100k; no in-window update found</t>
+          <t>Below Watch floor regardless of window, capex-heavy with tiny headcount, or recycled old news with no in-window update</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/story/amgen-to-add-370-jobs-as-part-of-1b-investment-in-holly-springs-nc-officials-say/21754490/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Fujifilm Diosynth Biotechnologies</t>
+          <t>Numerous sub-200/incomplete items (AVANTech Richland, Mattress Warehouse Lexington, Hoffman &amp; Hoffman Lexington, Patten Seed Charleston, ZEB Metals Berkeley, Summerville warehouse Dorchester, TS Conductor Jasper [out of region], Delta Children's Orangeburg, ALLTAPE Adhesive Lexington [no figures], Southern Glazer's Wine &amp; Spirits Lexington [job count not found before search budget exhausted])</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs (Wake)</t>
+          <t>Various Midlands/Lowcountry</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>12-462 each (or undisclosed)</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2022-2026</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; no in-window update found</t>
+          <t>Below Watch floor, out of region, or insufficient data (no job/wage figures located) to assess against thresholds — flagged for a follow-up search next cycle where noted</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2024/04/11/fujifilm-diosynth-biotechnologies-expands-holly-springs-facility-create-one-largest-end-end-cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>RTP</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>100+</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>Pre-window; sub-500 jobs regardless</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>https://investor.lilly.com/news-releases/news-release-details/lilly-plans-invest-additional-450-million-manufacturing-site</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Ypsomed</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Holly Springs (Wake)</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Sub-200 jobs; well below Watch floor</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wake.gov/news/ypsomed-announces-plans-invest-1954-m-creating-62-new-jobs-holly-springs</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>Audemars Piguet</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Raleigh (Wake)</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>Pre-window; sub-200 jobs and wage $92,376 (&lt;$100k)</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wral.com/story/luxury-watch-brand-audemars-piguet-to-invest-22-million-and-create-105-jobs-in-raleigh/21202535/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>AdvanceTEC</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Johnston County</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>In-window groundbreaking confirmed, but 160 jobs remains below the 200-job Watch floor; wage $90k avg (&lt;$100k)</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>https://hoodline.com/2026/07/french-cleanroom-giant-drops-160-high-paying-jobs-into-johnston-county/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>Ziehl-Abegg Inc. — North American HQ</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>Winston-Salem (Forsyth)</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>500+ (growing from ~200)</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>unconfirmed</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>Milestone timing (HQ opening / headcount crossing 500) could not be confirmed as falling inside this window — flagged for verification next cycle rather than asserted</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>https://fanpost.ziehl-abegg.com/en/detail/new-headquarters-with-high-tech-production-plant-and-hundreds-of-new-jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>American Eagle Outfitters</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Rowan Co. (Salisbury)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>200+</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>Distribution hub confirmed; best-paid roles (~70 mgmt/maintenance) average only $57,351 — low-wage-only despite clearing the 200-job floor</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>https://www.salisburypost.com/2026/07/17/fly-like-an-eagle-famous-outfitters-to-invest-41m-create-200-jobs-in-rowan-county</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Cheerwine / Piedmont Cheerwine Bottling</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Rowan Co.</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>~100</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>Sub-200 jobs; no high-wage signal</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>https://hoodline.com/2026/06/cheerwine-s-7-million-salisbury-score-set-to-super-size-rowan-county-jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Huntington Bank Carolinas branch expansion</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Multi (Charlotte/Raleigh/Winston-Salem/Charleston/Columbia/Greenville)</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>NC/SC</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>~350 (multi-state)</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>Vague/diffuse multi-state aggregate spanning 55 branches, not a single site/project; bank-branch roles unlikely to average $100k+</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>https://www.axios.com/local/charlotte/2026/03/06/banks-branch-expansion-huntington</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Corvid Technologies</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Mooresville (Iredell)</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed stale/recycled 2018 announcement; no in-window update found</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>https://www.mooresvilletribune.com/news/mooresville-chosen-for-367-job-headquarters</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>LPL Financial</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Fort Mill (York Co.)</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>Stale/recycled announcement from 2014; no in-window (2026) milestone found</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>Costco</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Indian Land (Lancaster Co.)</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>unconfirmed</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>Speculative; no official confirmation of a new warehouse/location found</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>JGA Space &amp; Defense</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>Huntersville (Mecklenburg)</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>~40</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>Sub-200 jobs</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Albemarle — Richburg lithium hydroxide plant</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>Chester Co.</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>Project remains paused since March 2024 due to falling lithium prices; no evidence of a resumed in-window milestone; also sub-500 jobs regardless</t>
-        </is>
-      </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>https://scdailygazette.com/2024/03/18/major-electric-vehicle-lithium-project-paused-in-south-carolina/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Bank of America / Wells Fargo / Truist</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>- (cuts)</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>LAYOFFS/job cuts (AI-driven headcount reduction) — excluded per rules (opposite of qualifying criteria)</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>https://www.axios.com/local/charlotte/2026/01/16/bank-america-wells-fargo-ai-job-cuts</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Woodward, Inc. — aerospace actuation manufacturing</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Greer (Spartanburg Co.)</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>date conflict (2025-09 vs 2026-02, unresolved)</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>Date conflict could not be resolved this cycle (SC Governor's office URL slug reads Sept. 2025, one search result suggested Feb. 2026); excluded pending verification rather than asserted either way</t>
-        </is>
-      </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.sc.gov/news/2025-09/woodward-inc-selects-spartanburg-county-establish-new-manufacturing-site-south</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>ElringKlinger — EV battery components expansion</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Easley (Pickens Co.)</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>Pre-window; no in-window update found</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>https://www.postandcourier.com/greenville/news/elringklinger-auto-supplier-easley-plant/article_d5a55a73-946a-44e3-a2c7-d47669288ac3.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>Cielo Digital Infrastructure</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>Cherokee Co.</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>Sub-200 jobs; pre-window announcement/tax-break approval</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.sc.gov/news/2025-06/cielo-digital-infrastructure-selects-cherokee-county-first-south-carolina-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Numerous sub-200-job items (Detpak USA, Fortified Solar, Idealworks, Shamrock Technologies, Advanced Metalworks, Eastern Engineered Wood, Hydrite Chemical, Coastal Precast, Peabody Engineering, KP Components, Xoted Biotechnology Labs, United Composite Materials)</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Various Upstate SC</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>13-151 each</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Below Watch floor regardless of window</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>Numerous sub-200-job items (AVANTech, Eastover Chips, AVM Group, Hoffman &amp; Hoffman Lexington, WiJo Pouches North America, Techo-Bloc, ALLTAPE Adhesive Mfg, Leonardo DRS, Modus21)</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>Various Midlands/Lowcountry</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>27-170 each</t>
-        </is>
-      </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>Below Watch floor and/or recycled old news with no in-window update; Ritedose Corp (Richland) flagged but unverified before search budget exhausted</t>
-        </is>
-      </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Numerous sub-200-job items (Sumitomo Forestry America, Alamance Foods, Hoffman &amp; Hoffman Greensboro, Cascade Die Casting, Torvan Medical, Swamp Rider, Team LaunchPoint, GMAX Industries)</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>Various Triad</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>12-135 each</t>
-        </is>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>Below Watch floor and/or sub-$100k wage and/or pre-window</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Alzchem Group AG (new US production facility)</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>Bushy Park / Goose Creek (Berkeley Co.)</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>~2026-07-20</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>Job count and investment figures not captured before this cycle's search budget was exhausted — flagged as a priority follow-up rather than scored on incomplete data</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>Jewelers Mutual Insurance "Project Diamond" — innovation hub</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>Raleigh (Wake)</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>200 (phased 2025-2029)</t>
-        </is>
-      </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>unconfirmed</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>Wage and precise announcement date could not be confirmed this cycle (source not independently fetchable) — flagged for a dedicated follow-up search next cycle rather than scored on incomplete data</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -20474,7 +19591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -21483,357 +20600,6 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Fort Mill Sun — Rock Hill City Council coverage</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>https://www.fortmillsun.com/</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>York Co. SC</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Octapharma final 7-0 city-council approval, 2026-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Aviation Week / FlightGlobal</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>trade_journal</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>https://aviationweek.com/</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>National aerospace</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>JetZero-EXIM $3B financing Letter of Interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Hoodline</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>https://hoodline.com/</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>NC/SC metro</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Citigroup Ballantyne grand opening/hiring ramp; Boom Supersonic risk update</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Businesswire — Ralliant press release</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>company_primary</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>https://www.businesswire.com/</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Ralliant global HQ opening, North Hills</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Axios Raleigh</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>https://www.axios.com/local/raleigh/</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>NC Triangle</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>WakeMed/Atrium delay; VinFast lawsuit; Aspida Durham HQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Carolina Journal</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>https://www.carolinajournal.com/</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>NC statewide</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Wolfspeed Siler City layoffs</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Manufacturing Dive</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>trade_journal</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>https://www.manufacturingdive.com/</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>National mfg</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Pallidus project cancellation, Rock Hill/York Co.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Charleston Digital</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>https://www.charlestondigital.com/</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>SC Lowcountry</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Google SC $9B data-center expansion detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Spectrum Local News</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>https://spectrumlocalnews.com/</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>NC/SC</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>BMW $1.7B SC investment completion; AbbVie recap</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Post and Courier — Spartanburg bureau</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>https://www.postandcourier.com/spartanburg/</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Upstate SC</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>NorthMark Project Moc-1 hearing; AIRSYS HQ opening</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>WECT / WilmingtonBiz</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wect.com/</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>New Hanover Co. NC</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Amazon-Corning fiber-optics Wilmington detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>9to5Mac</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>trade_journal</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>https://9to5mac.com/</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>National tech</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Apple RTP incentive-extension date correction (2025-11-25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>SC Daily Gazette</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>https://scdailygazette.com/</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>SC statewide</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>SC Ports Leatherman confirmed pause; Boeing 787 rate</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21845,7 +20611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22284,7 +21050,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -22304,7 +21070,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -22324,7 +21090,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -22344,7 +21110,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -22364,7 +21130,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -22384,7 +21150,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -22404,7 +21170,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -22424,7 +21190,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -22444,7 +21210,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -22464,7 +21230,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -22477,14 +21243,14 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council's unanimous 7-0 approval (2026-07-23) resolves the outstanding city-vote risk that had discounted this deal for two consecutive cycles; +3 for the removal of that execution-certainty discount.</t>
+          <t>Rock Hill City Council voted unanimously 7-0 (2026-07-23) to approve the land sale and amended tax-incentive agreement, closing out the prior cycle's single outstanding risk (the city-level vote). Deal is now fully cleared on both county and city sides; +3 for removed execution-risk discount.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -22493,18 +21259,18 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Unchanged: Training Center opened, 600+ hired, first vehicle body weld completed — genuine hiring/construction progress — offset by continued signals that customer deliveries may slip toward 2028.</t>
+          <t>Hiring event proceeded on schedule (positive) but the customer-delivery timeline slip to 'early 2028' is now stated explicitly rather than softly implied; net -1 for confirmed further timeline risk.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -22524,7 +21290,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -22537,14 +21303,14 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; lease-commencement date confirmed but not a new milestone.</t>
+          <t>Unchanged; no new milestone this cycle.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -22564,7 +21330,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -22573,18 +21339,18 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Unchanged: EXIM Letter of Interest for up to $3B in financing is a modest, explicitly non-binding positive signal that does not resolve the JDIG-amendment hiring-ramp delay; score held flat.</t>
+          <t>EXIM Bank Letter of Interest (2026-07-20) to explore up to $3B in financing strengthens capital/project-certainty even though no new jobs/wage figures moved; +1.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -22598,26 +21364,6 @@
       <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Unchanged; no new milestone this cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Citigroup (Charlotte/Ballantyne)</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>NEW to Ranked this cycle: 510 jobs, $131,832 stated wage, and a confirmed in-window hiring-ramp to ~400/510 roles constitute genuine forward execution (not merely a delayed pre-window commitment), reversing three cycles of exclusion; scored below other ranked deals given modest capex ($16.1M) and first-time-ranked low repeat-momentum.</t>
         </is>
       </c>
     </row>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-08-03  ·  Window 2026-02-03 to 2026-08-03  ·  NC + SC</t>
+          <t>Week of 2026-08-10  ·  Window 2026-02-10 to 2026-08-10  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03  (Week 4)</t>
+          <t>2026-08-10  (Week 4)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-02-03 to 2026-08-03  (trailing 6 months)</t>
+          <t>2026-02-10 to 2026-08-10  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 90 (+3) — Rock Hill City Council voted unanimously 7-0 on 2026-07-23 to approve the land sale and amended tax-incentive terms, closing out the deal on both county and city sides</t>
+          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 90 (+3) — Rock Hill City Council voted 7-0 on 2026-07-23 to approve amended tax-share terms, resolving the deal's last outstanding governmental hurdle; deal now described as fully finalized</t>
         </is>
       </c>
     </row>
@@ -634,43 +634,55 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>No brand-new qualifying (500+ job / $100k+ wage) deal was found in any of the five sub-regions this cycle — all 8 ranked entries carry forward. Octapharma's Rock Hill City Council vote (unanimous, 7-0) resolves the prior cycle's biggest open risk. Two major reversals surfaced: SC Ports' Leatherman Terminal pause took effect as scheduled on Aug. 1, 2026, and Chatham County terminated its VinFast EV-megafactory incentive agreement (7,500-job target collapsed to ~1,400, then cancelled outright) on July 28, 2026. Aspida Financial Services (Durham, 1,000 jobs, $137,288 stated wage) is a strong near-miss on Watch pending an in-window milestone.</t>
+          <t>Octapharma is now a closed deal, not a pending one. Scout Motors' Charlotte global HQ (distinct from its Blythewood, SC EV plant) is newly Ranked on an in-window land-development filing for a second office building. JetZero has moved from ceremonial groundbreaking to an active general contractor physically building the first facility. Two negative reversals hit the NC Triangle (VinFast incentive terminated in Chatham Co.; Kempower's JDIG cancelled in Durham/RTP).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Window note</t>
+          <t>Coverage gap — READ</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-02-03 to 2026-08-03.</t>
+          <t>This session's shared web-search tool budget (200 calls) was exhausted before the SC Midlands/Lowcountry research pass could run at all, and before the Upstate SC pass could complete more than 4 of its planned ~25 searches. Every SC Midlands/Lowcountry entry (Scout Motors' Blythewood plant, SC Ports Leatherman Terminal, AMAROK, Ferrara Candy, Boeing 787, HII, Google) and several Upstate SC watch items are carried forward from 2026-07-13 UNVERIFIED this cycle — flagged in both the report and this workbook. No numbers were invented; see the report's Appendix for full detail.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Data-quality note</t>
+          <t>Window note</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Maersk (Charlotte, wage stated at $100,962) and Citigroup (Ballantyne, wage stated at $131,832) remain excluded for a second/third consecutive cycle for consistency with this dataset's established milestone rules — both clear job-count/wage thresholds but their only in-window 'movement' traces to a hiring delay or a pre-window commitment, not genuine forward progress.</t>
+          <t>Trailing 6 months now runs 2026-02-10 to 2026-08-10.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>Data-quality note</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SC Ports' announced Aug. 1, 2026 pause of Leatherman Terminal operations (reported 2026-06-25) could not be confirmed as having taken effect this cycle due to the coverage gap above — this is the #1 priority recheck for next cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Week-over-week</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>8 of 8 prior-ranked deals remain qualifying (none removed, none newly added); 2 gaining momentum (Octapharma, JetZero), 1 updated (Scout Motors, timeline slip confirmed), 5 repeated (SMBC, AbbVie, Capital Group, Genentech, Novartis). Watch tier: 2 removed as stale (Snider Fleet Solutions, FN America), ~10 new additions (incl. Aspida Financial Services, Lenovo Whitsett, EnerSys Greenville scope-cut, Ahold Delhaize/Food Lion Burlington).</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>8 of 8 prior-ranked deals remain qualifying, plus 1 new (Scout Motors Global HQ, Charlotte) — 9 total. 1 updated/resolved (Octapharma, +3), 1 updated (JetZero, +1), 5 repeated (SMBC, AbbVie, Capital Group, Genentech, Novartis), 1 repeated-but-unverified (Scout Motors EV plant, Blythewood). None removed from Ranked. Snider Fleet Solutions removed from Watch (confirmed stale).</t>
         </is>
       </c>
     </row>
@@ -685,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2083,7 +2095,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -2174,7 +2186,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -2265,7 +2277,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2356,7 +2368,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -2447,7 +2459,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
@@ -2538,7 +2550,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -2629,7 +2641,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -2720,7 +2732,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -2811,7 +2823,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -2902,7 +2914,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -2928,7 +2940,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (finalized)</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
@@ -2956,12 +2968,12 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; land sale of 50 ac in Palmetto Research Park to Octapharma</t>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools; NEW: $65M SC Coordinating Council Closing Fund grant to York County</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>City-level approval closes out the deal</t>
+          <t>Rock Hill City Council final approval (unanimous); deal finalized</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
@@ -2971,7 +2983,7 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>https://www.wbtv.com/2026/07/23/rock-hills-octapharma-projects-moved-forward-what-we-know/</t>
+          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
@@ -2993,14 +3005,14 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -3019,7 +3031,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (active hiring ramp; timeline slips further)</t>
+          <t>Scout Motors — EV assembly plant (carried forward, not rechecked)</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -3032,7 +3044,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>$30-$34/hr maintenance tech / $33.50-$37.50/hr senior maintenance tech (stated); salaried roles mixed/undisclosed</t>
+          <t>$30-$37.50/hr line (stated, per 2026-07-13); salaried higher</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -3052,22 +3064,22 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Hiring event held as scheduled; timeline confirmation</t>
+          <t>Hiring event announced; companywide headcount update (as of 2026-07-13)</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>https://www.wltx.com/article/news/local/scout-motors-hiring-maintenance-technicians-blythewood-plant/101-1ca4c9f6-a045-44a2-8c89-8a427cd766e2</t>
+          <t>https://www.postandcourier.com/columbia/business/scout-motors-blythewood-factory-construction-sc/article_66a10144-3603-47f1-9b23-2f8415835b8f.html</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (not independently rechecked)</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -3084,7 +3096,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -3175,7 +3187,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -3234,7 +3246,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Wage figure confirmed (stated, not inferred)</t>
+          <t>New facility / operations hub (unchanged)</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -3266,7 +3278,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -3277,12 +3289,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs / SW Wake</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -3292,55 +3304,55 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Genentech — biomanufacturing expansion</t>
+          <t>JetZero — aerospace plant (construction underway)</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>500</v>
+        <v>14500</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Aerospace mfg + eng.</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, 2025 tranche)</t>
+          <t>$89,340 avg (stated, 2025)</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>N/A — stated (2025)</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B</t>
+          <t>$4.7B</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>Expansion of committed project</t>
+          <t>General contractor on site; physical construction start on Phase 1</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+          <t>https://www.hitt.com/news-hub/jetzero-greensboro-groundbreaking/</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); Low (timeline)</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -3350,14 +3362,14 @@
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+          <t>Same long-run scale; near-term construction-phase hiring (GC + subcontractors) is a modest, earlier housing-demand signal ahead of the 2028-2029 direct-hire ramp.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -3368,12 +3380,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Holly Springs / SW Wake</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -3383,55 +3395,55 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (EXIM financing Letter of Interest)</t>
+          <t>Genentech — biomanufacturing expansion</t>
         </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>14500</v>
+        <v>500</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Aerospace mfg + eng.</t>
+          <t>Adv. biomanufacturing</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>$89,340 avg (stated, 2025)</t>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated (2025)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>$4.7B</t>
+          <t>~$2.0B</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>Financing milestone — EXIM Bank Letter of Interest</t>
+          <t>Expansion of committed project</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Low (timeline)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -3441,96 +3453,187 @@
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale; a $3B EXIM financing pathway strengthens confidence the megaproject reaches its full build-out even as near-term hiring stays on the 2028-2029 ramp.</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
         <v>8</v>
       </c>
       <c r="C31" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Durham / Morrisville</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Durham &amp; Wake</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Novartis — API mfg building (investment increase)</t>
         </is>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H32" s="6" t="n">
         <v>700</v>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>Adv. mfg / API production</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>$111,161 avg (stated)</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr">
+      <c r="K32" s="6" t="inlineStr">
         <is>
           <t>N/A — stated</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>~$991M (incl. $220M API building)</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>Part of original $771M package incentives</t>
         </is>
       </c>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>New facility (unchanged)</t>
         </is>
       </c>
-      <c r="O31" s="6" t="inlineStr">
+      <c r="O32" s="6" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="P31" s="6" t="inlineStr">
+      <c r="P32" s="6" t="inlineStr">
         <is>
           <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>Suburban</t>
         </is>
       </c>
-      <c r="S31" s="6" t="inlineStr">
+      <c r="S32" s="6" t="inlineStr">
         <is>
           <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
         </is>
@@ -3547,7 +3650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5325,7 +5428,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -5441,7 +5544,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5557,7 +5660,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5673,7 +5776,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5789,7 +5892,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -5905,7 +6008,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -6021,7 +6124,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6137,7 +6240,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -6253,7 +6356,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -6362,19 +6465,19 @@
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle; project remains on track for fall 2026 first arrivals.</t>
+          <t>Third consecutive quiet cycle; no new in-window milestone but nothing has slipped either.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Gaining Momentum</t>
+          <t>Updated (resolved)</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -6400,7 +6503,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (finalized)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -6410,7 +6513,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>City-level approval closes out the deal</t>
+          <t>Rock Hill City Council final approval (unanimous); deal finalized</t>
         </is>
       </c>
       <c r="K25" s="6" t="n">
@@ -6438,12 +6541,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; land sale of 50 ac in Palmetto Research Park to Octapharma</t>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools; NEW: $65M SC Coordinating Council Closing Fund grant to York County</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council voted UNANIMOUSLY 7-0 on 2026-07-23 to approve both the land sale and the amended tax-incentive agreement, resolving the prior cycle's single outstanding risk; deal is now fully closed on both county and city sides. No groundbreaking date set yet; construction expected to start 2027.</t>
+          <t>Rock Hill City Council voted 7-0 on 2026-07-23 to approve amended tax-share terms — all governmental approvals now complete; land closing expected in coming months; construction as early as 2027; operations targeted mid-2030s</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -6453,7 +6556,7 @@
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>https://www.wbtv.com/2026/07/23/rock-hills-octapharma-projects-moved-forward-what-we-know/</t>
+          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -6478,26 +6581,26 @@
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>The prior cycle's key open question (Rock Hill City Council's vote) is now resolved unanimously in favor — execution-risk discount removed, score up +3. Council members publicly criticized York County over the tax-split fight during the same meeting, but the vote itself was 7-0 to proceed. Next milestone to watch: a groundbreaking date.</t>
+          <t>Rock Hill City Council's previously outstanding vote is now resolved unanimously; deal described by multiple outlets as fully 'finalized'/'inked' as of late July 2026 — removes the deal-certainty discount that had held the score down.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Repeated (unverified this cycle)</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
@@ -6516,7 +6619,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (active hiring ramp; timeline slips further)</t>
+          <t>Scout Motors — EV assembly plant (carried forward, not rechecked)</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -6526,7 +6629,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Hiring event held as scheduled; timeline confirmation</t>
+          <t>Hiring event announced; companywide headcount update (as of 2026-07-13)</t>
         </is>
       </c>
       <c r="K26" s="6" t="n">
@@ -6534,12 +6637,12 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Projected (~1,400 hired companywide; 600+ in SC)</t>
+          <t>Projected (~1,400 hired companywide, per 2026-07-13)</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>$30-$34/hr maintenance tech / $33.50-$37.50/hr senior maintenance tech (stated); salaried roles mixed/undisclosed</t>
+          <t>$30-$37.50/hr line (stated, per 2026-07-13); salaried higher</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -6559,22 +6662,22 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>Pre-hire/interview events for 70+ maintenance-tech roles proceeded as scheduled the week of 2026-07-29; Traveler production now explicitly targeted late 2027 with customer deliveries pushed to early 2028 (a further, more concrete slip vs. last cycle's softer 'trending toward 2028')</t>
+          <t>Pre-hire/interview events for 70+ maintenance-tech roles were scheduled to begin 2026-07-29 (per 2026-07-13 report); not independently reconfirmed this cycle</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>https://www.wltx.com/article/news/local/scout-motors-hiring-maintenance-technicians-blythewood-plant/101-1ca4c9f6-a045-44a2-8c89-8a427cd766e2</t>
+          <t>https://www.postandcourier.com/columbia/business/scout-motors-blythewood-factory-construction-sc/article_66a10144-3603-47f1-9b23-2f8415835b8f.html</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (not independently rechecked)</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -6594,14 +6697,14 @@
       </c>
       <c r="X26" s="6" t="inlineStr">
         <is>
-          <t>Hiring event proceeded on schedule (positive), but the customer-delivery timeline slip to 'early 2028' is now stated plainly rather than softly implied — net -1 for confirmed further timeline risk even as near-term hiring signal stays strong.</t>
+          <t>SC Midlands/Lowcountry research pass could not run this cycle (session web-search budget exhausted before this region's agent began); carried forward unverified from 2026-07-13 — top-priority recheck next cycle.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -6717,7 +6820,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -6758,7 +6861,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Wage figure confirmed (stated, not inferred)</t>
+          <t>New facility / operations hub (unchanged)</t>
         </is>
       </c>
       <c r="K28" s="6" t="n">
@@ -6826,19 +6929,19 @@
       </c>
       <c r="X28" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle; hiring doesn't begin until 2027.</t>
+          <t>No new in-window milestone found this cycle.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -6849,12 +6952,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs / SW Wake</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -6864,70 +6967,70 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Genentech — biomanufacturing expansion</t>
+          <t>JetZero — aerospace plant (construction underway)</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Aerospace / advanced manufacturing</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Expansion of committed project</t>
+          <t>General contractor on site; physical construction start on Phase 1</t>
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>500</v>
+        <v>14500</v>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Projected (site total)</t>
+          <t>Projected</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, 2025 tranche)</t>
+          <t>$89,340 avg (stated, 2025)</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>N/A — stated (2025)</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B</t>
+          <t>$4.7B</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>Operational by 2029</t>
+          <t>HITT Contracting confirmed as general contractor on the NC Composite Center (NC3, 150,000 sf); construction physically underway beyond the June groundbreaking ceremony; first deliveries described as 'early 2030s', full run-rate 'late 2030s' — consistent with the 2037 full-target timeline</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+          <t>https://www.hitt.com/news-hub/jetzero-greensboro-groundbreaking/</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); Low (timeline)</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Aerospace mfg + eng.</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
@@ -6937,24 +7040,24 @@
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+          <t>Same long-run scale; near-term construction-phase hiring (GC + subcontractors) is a modest, earlier housing-demand signal ahead of the 2028-2029 direct-hire ramp.</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle.</t>
+          <t>Trade press (HITT, ENR, CompositesWorld, Aviation Week) confirms an active general contractor building the first facility — more concrete than a ceremonial groundbreaking alone; no new JDIG amendment found this cycle.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Gaining Momentum</t>
+          <t>Repeated</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
@@ -6965,12 +7068,12 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Holly Springs / SW Wake</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -6980,70 +7083,70 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (EXIM financing Letter of Interest)</t>
+          <t>Genentech — biomanufacturing expansion</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Aerospace / advanced manufacturing</t>
+          <t>Adv. biomanufacturing</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Financing milestone — EXIM Bank Letter of Interest</t>
+          <t>Expansion of committed project</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>14500</v>
+        <v>500</v>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>Projected</t>
+          <t>Projected (site total)</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>$89,340 avg (stated, 2025)</t>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated (2025)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>$4.7B</t>
+          <t>~$2.0B</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>JetZero and the U.S. Export-Import Bank signed a Letter of Interest on 2026-07-20 (at the Farnborough Airshow) to explore up to $3B in EXIM financing for the Greensboro campus — a capital-durability signal, not a jobs/wage change; hiring ramp still begins 2028-2029 per the prior JDIG amendment</t>
+          <t>Operational by 2029</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Low (timeline)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>Aerospace mfg + eng.</t>
+          <t>Adv. biomanufacturing</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
@@ -7053,126 +7156,242 @@
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale; a $3B EXIM financing pathway strengthens confidence the megaproject reaches its full build-out even as near-term hiring stays on the 2028-2029 ramp.</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>Construction/financing momentum continues even though no new jobs/wage figures moved this cycle — +1 for reduced execution-certainty risk on the capital side.</t>
+          <t>No new in-window milestone found this cycle.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D31" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Automotive (EV) — corporate HQ</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Projected (365 relocating + 835 new local hires)</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>1st ~150,000 sf building move-in ~mid-2026; 2nd building's land-development plan filed March 2026, construction start targeted H1 2027</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="V31" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr">
+        <is>
+          <t>Reclassified from Excluded (2026-07-13 report cited 'no confirmed in-window milestone') after identifying the March 2026 land-development filing for a 2nd office building tied explicitly to Scout's HQ job growth. Distinct project from the Blythewood, SC EV assembly plant (also separately ranked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Durham / Morrisville</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Durham &amp; Wake</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Novartis — API mfg building (investment increase)</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>Adv. mfg / API production</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>New facility (unchanged)</t>
         </is>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K32" s="6" t="n">
         <v>700</v>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>Projected (part of pre-window deal)</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>$111,161 avg (stated)</t>
         </is>
       </c>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>N/A — stated</t>
         </is>
       </c>
-      <c r="O31" s="6" t="inlineStr">
+      <c r="O32" s="6" t="inlineStr">
         <is>
           <t>~$991M (incl. $220M API building)</t>
         </is>
       </c>
-      <c r="P31" s="6" t="inlineStr">
+      <c r="P32" s="6" t="inlineStr">
         <is>
           <t>Part of original $771M package incentives</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>Facility opening targeted 2027-2028</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="S31" s="6" t="inlineStr">
+      <c r="S32" s="6" t="inlineStr">
         <is>
           <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
         </is>
       </c>
-      <c r="T31" s="6" t="inlineStr">
+      <c r="T32" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U31" s="6" t="inlineStr">
+      <c r="U32" s="6" t="inlineStr">
         <is>
           <t>Adv. mfg / API production</t>
         </is>
       </c>
-      <c r="V31" s="6" t="inlineStr">
+      <c r="V32" s="6" t="inlineStr">
         <is>
           <t>Suburban</t>
         </is>
       </c>
-      <c r="W31" s="6" t="inlineStr">
+      <c r="W32" s="6" t="inlineStr">
         <is>
           <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
         </is>
       </c>
-      <c r="X31" s="6" t="inlineStr">
+      <c r="X32" s="6" t="inlineStr">
         <is>
           <t>No new in-window milestone found this cycle.</t>
         </is>
@@ -7189,7 +7408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10743,7 +10962,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -10805,7 +11024,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -10867,7 +11086,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -10929,7 +11148,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -10991,7 +11210,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -11053,7 +11272,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -11115,7 +11334,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -11177,7 +11396,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -11239,7 +11458,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -11301,7 +11520,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -11363,7 +11582,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -11425,7 +11644,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -11487,7 +11706,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -11549,7 +11768,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -11611,7 +11830,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -11673,7 +11892,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -11735,7 +11954,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -11797,7 +12016,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -11859,7 +12078,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -11921,7 +12140,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -11983,7 +12202,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -12045,7 +12264,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -12107,7 +12326,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -12169,7 +12388,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -12231,7 +12450,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -12293,7 +12512,7 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -12355,7 +12574,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -12417,7 +12636,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -12479,7 +12698,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -12541,7 +12760,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -12603,7 +12822,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -12665,7 +12884,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -12727,7 +12946,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -12789,7 +13008,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -12851,7 +13070,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -12913,7 +13132,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -12975,7 +13194,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -13037,7 +13256,7 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -13099,7 +13318,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -13161,7 +13380,7 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -13223,7 +13442,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -13285,17 +13504,17 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Cherokee Co. / Blacksburg</t>
+          <t>North Charleston</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Cherokee</t>
+          <t>Charleston</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -13305,12 +13524,12 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>USA Rare Earth — rare-earth magnet plant</t>
+          <t>SC Ports Authority — Leatherman Terminal (PAUSE STATUS UNCONFIRMED)</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>~490</t>
+          <t>400 direct + ~1,200 indirect</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -13320,44 +13539,44 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>$24.50-$63/hr (stated)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>Formal site-selection/investment announcement confirmed 2026-06-02; still just under 500 jobs, no threshold-crossing update found; commissioning now targeted ~2028</t>
+          <t>TOP PRIORITY GAP: as of 2026-07-13, SC Ports announced it would pause ALL Leatherman operations starting 2026-08-01 (today is 2026-08-10); this cycle could not confirm whether the pause took effect or any reopening timeline — not rechecked (SC Midlands/Lowcountry gap)</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25 (last verified)</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2026-06/usa-rare-earth-inc-selects-cherokee-county-first-south-carolina-operation</t>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (risk, not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Laurens Co.</t>
+          <t>Cherokee Co. / Blacksburg</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Cherokee</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -13367,37 +13586,37 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Suniva — solar-cell plant</t>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>~490</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>$350M</t>
+          <t>$1.2B</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>Entry-level ~$23/hr; technicians $26-$36/hr (stated) — Estimated/Inferred blended avg ~$62k-$83k, below $100k</t>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>Crosses 500 jobs but detailed wage-tier data confirms the bulk of roles fail the $100k bar; stays Watch. Operations still targeted 2027</t>
+          <t>Still just under 500 jobs; commissioning now framed as targeting 2028; no threshold-crossing update</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
+          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -13409,17 +13628,17 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Columbia / BullStreet</t>
+          <t>Spartanburg (former Kohler plant)</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Richland</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -13429,59 +13648,59 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>AMAROK — new HQ (perimeter security)</t>
+          <t>NorthMark "Project Moc-1" — AI/HPC data center</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>~150 FT at full operation</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>$69M</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>SCDES public-comment period on the air-construction permit closed 2026-07-31; approval/denial outcome could not be determined this cycle</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-31 (comment period close)</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
+          <t>https://www.foxcarolina.com/2026/05/01/spartanburg-co-residents-say-they-were-misled-about-data-center-project/</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (outcome pending)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Greensboro</t>
+          <t>Wake County (statewide)</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -13491,17 +13710,17 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Lumentum — AI/data-center optics</t>
+          <t>WakeMed / Atrium Health — proposed merger</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>~400</t>
+          <t>3,300 (statewide, 5 yr)</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>Hundreds of millions</t>
+          <t>$2.0B (Wake Co. portion)</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
@@ -13511,39 +13730,39 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>Ribbon-cutting confirmed 2026-04-29; production still targeted mid-2028; no further update this cycle</t>
+          <t>Vote delayed again: public hearing set 2026-08-17; earliest possible Commissioners vote now 2026-09-08 (past this window); commissioners reportedly 'feeling much better' after private briefings, drawing transparency criticism</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>https://greensboro.com/news/local/business/development/article_be1b2ff0-8a3c-463e-904e-78472c59db7a.html</t>
+          <t>https://www.northcarolinahealthnews.org/2026/08/07/wakemed-atrium-leaders-brief-wake-commissioners/</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Hendersonville</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -13553,59 +13772,59 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>BorgWarner — vertical-integration expansion</t>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>$100M</t>
+          <t>~$50M (hangar)</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>$67,047 avg (stated; below $100k)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>No new update found this cycle</t>
+          <t>RISK ESCALATING FURTHER: hangar still largely idle; only ~19 open roles as of Aug. 2026 — nowhere near a 500-employee surge with the deadline now under 5 months away</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08 (job-posting check)</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (risk)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Asheville / Arden</t>
+          <t>Rowan County</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -13615,59 +13834,59 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Eaton — Low Voltage Assembly expansion</t>
+          <t>American Eagle Outfitters (formerly code-named "Project Rack" — identity now confirmed)</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200+ (state figure; county vote cited 258)</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$41M</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>'high-wage' but figure Not disclosed (Inferred mid-$60k-$80k)</t>
+          <t>$57,351 avg (stated)</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>No new update found this cycle; remains 7th Helene-recovery manufacturer expansion</t>
+          <t>Company identity officially confirmed via Governor Stein announcement 2026-07-17; Q1 2027 ops start still targeted</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
         <is>
-          <t>High (jobs); Low (wage)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Kernersville</t>
+          <t>Charlotte (CLT airport)</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Forsyth</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -13677,121 +13896,121 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>John Deere — excavator plant (relocating from Japan)</t>
+          <t>Averitt — logistics campus</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>150+</t>
+          <t>~230 (revised from 211)</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>$70M</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Inferred skilled-mfg)</t>
+          <t>$81,769 avg (stated)</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Construction underway on west campus; opening still targeted 'next year'</t>
+          <t>Jobs figure revised in some coverage; Planning Commission recommended rezoning 6-0 on 2026-04-13; final City Council vote not confirmed as completed</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>https://journalnow.com/news/local/business/development/article_b204fb94-5ff2-4618-9eba-6aee803fc2dc.html</t>
+          <t>https://hoodline.com/2026/04/averitt-s-230-job-truck-campus-poised-to-rev-up-clt-s-cargo-corridor/</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>York Co.</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>York</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
+          <t>QTS "Project Cobra" — data-center campus</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>5,100 (proj. total); 3,000+ employed</t>
+          <t>~200 FTE (+~1,000 constr.)</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>$13.9B</t>
+          <t>up to $8B</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>$62,234 (stated; below $100k)</t>
+          <t>~$80k median (stated)</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>Continued active hiring (70+ open roles as of Aug 2026); no wage or NC-specific investment update found this cycle</t>
+          <t>York County's 9-month data-center moratorium passed final reading 6-0 on 2026-07-13; QTS's 9 buildings have vested site-plan rights predating the ordinance and are unaffected</t>
         </is>
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>https://allamerican.org/news/toyotas-north-carolina-battery-plant-brings-jobs/</t>
+          <t>https://www.wrhi.com/2026/07/york-county-council-approves-nine-month-data-center-moratorium-214184</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>High (jobs); Low (wage)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Burlington / Alamance-Guilford line</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Alamance</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -13801,59 +14020,59 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+          <t>NEW — Ahold Delhaize USA (Food Lion parent) — distribution center</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>≤500 currently; must hit 500 by 12/31/2026</t>
+          <t>500-505</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>~$50M (hangar)</t>
+          <t>$860M</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>No movement toward or away from the Dec 31, 2026 lease-default trigger found this cycle; hangar still described as largely idle; a July 2026 FAA supersonic-overland rulemaking (comment period closes 2026-08-17) is a regulatory tailwind, not a jobs signal</t>
+          <t>Groundbreaking held 2026-02-16 (in-window); construction underway, opening targeted 2029</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+          <t>https://www.globenewswire.com/news-release/2026/02/16/3238762/0/en/Ahold-Delhaize-USA-Breaks-Ground-on-New-860-Million-Distribution-Center-in-Burlington-N-C.html</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Multi-site incl. Wilmington</t>
+          <t>Pender / New Hanover</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>New Hanover+</t>
+          <t>Pender (+New Hanover)</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -13863,59 +14082,59 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Amazon-Corning — fiber-optics partnership</t>
+          <t>NEW — Amazon — robotics fulfillment center</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>1,000 (multi-site, unallocated)</t>
+          <t>1,000+</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Multi-billion (undisclosed NC-specific)</t>
+          <t>$350M</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>avg &gt;$65,000 (sub-$100k)</t>
+          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>Confirmed 2026-06-08; multi-year, multi-billion agreement; per-site allocation still not broken out</t>
+          <t>Opening targeted Q3 2026; largest Amazon site in NC; county allocation between Pender/New Hanover uncertain</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026 (Q3 opening)</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>https://www.wect.com/2026/06/08/amazons-data-center-push-fuels-1000-job-fiber-optic-agreement-with-corning/</t>
+          <t>https://businessnc.com/amazon-adding-1000-jobs-at-new-pender-county-center/</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Arden</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -13925,59 +14144,59 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+          <t>NEW — Aspida Financial Services — HQ expansion</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1,000 (proj.)</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>$285M</t>
+          <t>$28M+</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>$62,413 (stated)</t>
+          <t>$137,288 avg (stated)</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>On track: equipment arrival end-2026 target unchanged, first parts still mid-2027</t>
+          <t>Meets Ranked-tier job/wage bar, but the real-estate commitment (Dec. 2025 lease) predates the window; a Q4 2026 move-in is the likely next in-window milestone</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-12 (lease, pre-window)</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county/</t>
+          <t>https://rebusinessonline.com/drawbridge-realty-signs-aspida-to-89770-sf-office-lease-in-durham/</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); pre-window</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Asheboro</t>
+          <t>Wake Co. (aggregate)</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -13987,59 +14206,59 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Environmental Air Systems</t>
+          <t>County jobs pipeline (EDGE 7)</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>~11,000 (pipeline)</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>$20M</t>
+          <t>$11B</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>$55,133 (stated)</t>
+          <t>Mixed (office-skewed)</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>No jobs/wage change; new incentive detail surfaced (~$5M total: $3.3M JDIG, $1.2M workforce training, $500K building re-use grant)</t>
+          <t>Reconfirmed; no material change to the aggregate figure</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>https://edpnc.com/news/environmental-air-systems-randolph-county/</t>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Wilmington</t>
+          <t>Charlotte / SouthPark</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>New Hanover</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -14049,59 +14268,59 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+          <t>JPMorgan Chase — new office (1,000-employee bldg)</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
+          <t>400 new by 2028</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>Not itemized</t>
-        </is>
-      </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~$105k Estimated/Inferred</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>GNF4 fabrication underway; new detail: GNF plans &gt;$50M in safety/quality/production investment across this year and next; first lead-use assemblies contracted for 2026 deployment</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>https://www.wilmingtonbiz.com/more_news/2025/10/09/global_nuclear_fuel_to_fabricate_new_nuclear_fuel_product_in_wilmington/26920</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Whitsett</t>
+          <t>Raleigh / North Hills</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -14111,37 +14330,37 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>NEW — Lenovo — server/AI manufacturing campus expansion</t>
+          <t>Ralliant Corp. — global HQ launch</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>~1,000 total target (up from ~600 current)</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>$145M (up from original $77M pledge)</t>
+          <t>$2.1M</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>$66,770 (2025-stated; sub-$100k)</t>
+          <t>$170k-$189k avg (stated)</t>
         </is>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>Ribbon-cutting held 2026-07-24 at the 'NC Smart Campus,' Whitsett; facility doubled to 890,000 sq ft, 35% more manufacturing capacity, 20MW power infrastructure for AI/HPC</t>
+          <t>HQ officially opened 2026-03-05 with ~150 staff on-site, hiring toward the 180-job commitment through 2029</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>https://news.lenovo.com/pressroom/press-releases/lenovo-doubles-the-size-of-its-u-s-manufacturing-facility-in-north-carolina/</t>
+          <t>https://investors.ralliant.com/news-events/press-releases/detail/121/ralliant-opens-global-headquarters-in-raleigh-north-carolina</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr">
@@ -14153,17 +14372,17 @@
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Burlington</t>
+          <t>Raleigh / North Hills</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Guilford/Alamance</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -14173,54 +14392,54 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>NEW — Ahold Delhaize USA / Food Lion — "Project Titan" distribution center</t>
+          <t>NEW — Jewelers Mutual Group</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>505 (proj. by end of 2033)</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>$860M</t>
+          <t>$5.85M</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>~$60k-$62k avg (Estimated/Inferred; sub-$100k distribution-center wage)</t>
+          <t>$169,592 avg (stated)</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>Guilford ($17.9M) and Burlington City ($21.5M) incentive packages approved; construction expected to begin 2026, operations 2029; crosses 500 jobs but wage clearly fails the higher-income-housing test</t>
+          <t>High wage but only 200 jobs (Watch floor); in-window office-opening date unconfirmed</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>2025-10 (approvals); 2026 construction start</t>
+          <t>2024-08-13 (orig. announcement)</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>https://greensboro.com/news/local/business/employment/article_ce55534b-c262-47cf-b949-8cfda5828bf7.html</t>
+          <t>https://businessnc.com/jewelers-mutual-coming-to-raleigh-with-200-jobs-averaging-169k/</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Wake Co. (aggregate)</t>
+          <t>Garner</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -14235,37 +14454,37 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>County jobs pipeline (EDGE 7)</t>
+          <t>NEW — Gregory Poole Equipment Co. — HQ relocation</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>~11,000 (pipeline)</t>
+          <t>500+ (5 yr)</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>$11B</t>
+          <t>$347M</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>Mixed (office-skewed)</t>
+          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>2026 outlook reconfirms the ~$11B/11,000-job pipeline; ~25% of prospects foreign-HQ'd (Japan, Germany, Switzerland)</t>
+          <t>500+ jobs but company-wide wage clearly sub-$100k; no 2026 groundbreaking found</t>
         </is>
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-10-16 (pre-window)</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>https://raleigh-wake.org/blog/2026-economic-development-outlook-forwake-county</t>
+          <t>https://www.cbs17.com/news/local-news/wake-county-news/gregory-poole-equipment-caterpillar-dealer-moving-headquarters-to-garner/</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr">
@@ -14277,17 +14496,17 @@
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / Wendell / Knightdale</t>
+          <t>Siler City</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -14297,59 +14516,59 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Siemens AG — power devices for AI/data centers</t>
+          <t>Wolfspeed — silicon-carbide fab</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1,800 (proj.)</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>part of $165M</t>
+          <t>$5.0B</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$77,753 avg (stated)</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>New 101,000-sf Wendell facility confirmed online July 2026 as previously flagged; Knightdale's 100-jobs-by-end-2026 target not yet confirmed met</t>
+          <t>Post-bankruptcy ramp remains 'measured/disciplined'; completed 150mm-&gt;200mm transition; received ~$700M in Section 48D tax refunds; no new Chatham headcount figures</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-05 (Q3 earnings call)</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+          <t>https://mgrid.org/2026/04/22/wolfspeeds-200mm-silicon-carbide-wafer-capacity-is-the-single-biggest-2026-bottleneck-on-solid-state-transformer-production/</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Siler City</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -14359,59 +14578,59 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Wolfspeed — silicon-carbide fab ("The JP")</t>
+          <t>Vulcan Elements — magnet factory</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>1,800 (proj.)</t>
+          <t>1,000 (proj.)</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>$5.0B</t>
+          <t>$918.4M</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>$77,753 (stated, 2025)</t>
+          <t>$81,932 avg (stated)</t>
         </is>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>Q2 FY26 earnings (reported 2026-02-04) show Siler City underutilization costs rising ($26M-&gt;$47M YoY); new CEO pursuing 'operational discipline' (optimize installed capacity) over aggressive ramp — a slower, more measured hiring trajectory than previously implied. Company separately shut down its legacy Durham 150mm line (see Excluded)</t>
+          <t>JCC's Golden LEAF-funded training pipeline now active: train-the-trainer begins summer 2026; production-employee training runs Aug. 2026-Dec. 2030</t>
         </is>
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026 (training start)</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>https://www.investing.com/news/transcripts/earnings-call-transcript-wolfspeeds-q2-2026-results-disappoint-stock-dips-93CH-4486298</t>
+          <t>https://www.johnstoncc.edu/news/vulcangoldenleafgrant.php</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Multi-site NC incl. Wilmington</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>New Hanover +</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -14421,59 +14640,59 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Vulcan Elements — magnet factory</t>
+          <t>Amazon-Corning — fiber-optics partnership</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>1,000 (proj.)</t>
+          <t>1,000 (multi-site, unallocated)</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>$918.4M</t>
+          <t>Multi-billion (undisclosed NC-specific)</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>$81,932 (stated)</t>
+          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>Johnston Community College received a $3.6M GoldenLEAF grant; train-the-trainer instruction begins summer 2026 as scheduled; company secured a $620M federal loan plus a government equity stake, though a Feb-2026 site visit found the parking lot still largely empty ahead of a targeted Q1 2027 Benson-operations start</t>
+          <t>No update; per-site Wilmington allocation still not broken out</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>https://www.thewirechina.com/2026/03/15/the-magnet-makers-vulcan-elements-rare-earths/</t>
+          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Wake County (statewide)</t>
+          <t>Arden</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -14483,59 +14702,59 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>WakeMed / Atrium Health — proposed merger</t>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>3,300 (statewide, 5 yr)</t>
+          <t>325</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>$2.0B (Wake Co. portion)</t>
+          <t>$285M</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$62,413 avg (stated)</t>
         </is>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>Wake County Commissioners voted 2026-05-04 to delay their decision by 90 days, landing the vote at approximately 2026-08-02 — essentially coincident with this report's cutoff; no confirmed outcome located as of this report date. HIGHEST-PRIORITY recheck for next cycle</t>
+          <t>On track: equipment arrival end 2026, first parts mid-2027</t>
         </is>
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026 (timeline confirm)</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>https://www.wake.gov/news/wake-county-commission-delays-vote-legal-documents-related-wakemed-atrium-health-strategic-combination</t>
+          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county/</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
         <is>
-          <t>High (timeline); Low (outcome)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>RTP</t>
+          <t>Asheville / Arden</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -14545,59 +14764,59 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Apple — RTP campus extension</t>
+          <t>Eaton — Low Voltage Assembly expansion</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>3,000 originally proj.; ~600-990 added to date</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>$552M-$1B+ (paused)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>$187k (stated, 2021 award)</t>
+          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>No active construction found this cycle; new hiring commitments restart 2027 under the incentive-timeline extension. (Note: this session's sources date the extension itself to late Nov. 2025, not April 2026 as in the prior baseline — flagged for reconciliation)</t>
+          <t>No update found; company now employs ~1,500 across Buncombe sites</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>2025-11 (extension)</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>https://9to5mac.com/2025/11/25/apple-granted-rare-timeline-extension-north-carolina-campus/</t>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (jobs); Low (wage)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / North Hills</t>
+          <t>Hendersonville</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -14607,37 +14826,37 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Ralliant Corp. — global HQ launch</t>
+          <t>BorgWarner — vertical-integration expansion</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>378</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>$2.1M</t>
+          <t>$100M</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>$170k-$189k (stated)</t>
+          <t>$67,047 avg (stated; below $100k)</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>HQ officially opened 2026-03-05; 150 of the 180 targeted jobs already filled; hiring continues through 2029</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
@@ -14649,17 +14868,17 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Greensboro</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -14669,59 +14888,59 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>NEW — Aspida Financial Services — HQ expansion</t>
+          <t>Lumentum — AI/data-center optics</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>~400</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>$28M</t>
+          <t>Hundreds of millions</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>$137,288 avg (stated; Durham Co. avg is $97,531)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>HIGH-PRIORITY WATCH ADD: numerically clears both the 500-job and $100k-wage bars, but the announcement itself is dated 2025-11-19 — before this window opens — and no in-window (Feb-Aug 2026) milestone (lease signing, groundbreaking, hiring event) was found this cycle. Recommend promoting to Ranked the moment a genuine forward-moving in-window milestone surfaces</t>
+          <t>No update found; production still targeted mid-2028</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/19/financial-services-company-expand-durham-headquarters-1000-new-jobs</t>
+          <t>https://www.areadevelopment.com/newsitems/4-14-2026/lumentum-greensboro-north-carolina.shtml</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>High (facts); N/A (in-window trigger)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs</t>
+          <t>Kernersville</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Forsyth</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -14731,59 +14950,59 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>NEW — Amgen — biomanufacturing site (headcount target)</t>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>725 total by 2032 (site target)</t>
+          <t>150+</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>~$1.57B (cumulative)</t>
+          <t>$70M</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>~$91,527 avg (stated, sub-$100k)</t>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>No in-window milestone beyond the ongoing ramp toward the 2032 target</t>
+          <t>Reaffirmed Jan. 2026; construction underway on west campus</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>2024-12 (original)</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>https://www.ncbiotech.org/news/amgens-holly-springs-facilities-employ-more-700-2032</t>
+          <t>https://greensboro.com/news/local/business/development/article_f8077494-ba1d-526b-a82a-9d8425f0acbe.html</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Clayton</t>
+          <t>Asheboro</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -14793,37 +15012,37 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>NEW — Novo Nordisk — manufacturing campus</t>
+          <t>Environmental Air Systems</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>$4.1B</t>
+          <t>$20M</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred $65k-$70k (sub-$100k; basis: company-disclosed range vs. ~$45k county avg)</t>
+          <t>$55,133 avg (stated)</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>Construction phased 2027-2029; ~2,000 external contractors on-site for clearing/foundation work; no confirmed new 2026 milestone beyond ongoing construction</t>
+          <t>No update found despite targeted searches</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>2025 (original); ongoing construction</t>
+          <t>2025-11-25 (orig.)</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/novo-nordisk-investing-4-1b-adding-1000-jobs-in-johnston-county/</t>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr">
@@ -14835,17 +15054,17 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>New Hanover</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -14855,59 +15074,59 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>NEW — BuildOps Inc. — 3rd US hub</t>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>$711,200</t>
+          <t>Not itemized</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>$110,997 avg (stated; &gt;$100k, but sub-500 jobs)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>Announced 2025-06-24, pre-window; no confirmed in-window milestone found</t>
+          <t>GNF4 fabrication underway; company plans $50M+ further investment this year and next; jobs still undisclosed</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026 (ongoing)</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2025/06/24/governor-stein-announces-software-company-buildops-will-create-291-jobs-raleigh</t>
+          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low-Med</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Statesville</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Iredell</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -14917,54 +15136,54 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Compass Datacenters</t>
+          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>~250</t>
+          <t>5,100 (proj. total); 3,000+ employed</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>$1B+ (up to 500MW campus)</t>
+          <t>$13.9B</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$62,234 avg (stated; below $100k)</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>Statesville rezoning for the ~340-acre, up to 500MW campus has been reported, but no precisely dated in-window 2026 milestone could be confirmed this cycle; operations still targeted 2028</t>
+          <t>Grand opening reconfirmed with 4 of 14 planned production lines operating; $10B additional 5-yr investment pledge reconfirmed</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>2025-08 (pre-window baseline)</t>
+          <t>2025-11 (reconfirmed 2026)</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://rebusinessonline.com/toyota-begins-production-at-13-9b-battery-plant-in-north-carolina-pledges-additional-10b-investment-over-next-five-years/</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr">
         <is>
-          <t>Low-Med</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Rowan County</t>
+          <t>Rowan / Kannapolis</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -14979,59 +15198,59 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>"Project Rack" (company undisclosed)</t>
+          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>$41M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$100k</t>
+          <t>$55k-$150k range (DHL postings)</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>Rowan County Commissioners approved incentives 2026-06-06 (three-year tax incentives); Q1 2027 ops start still targeted</t>
+          <t>No update; jobs still undisclosed</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>https://www.salisburypost.com/2026/06/06/rowan-county-approves-project-rack-incentives-for-258-job-distribution-site/</t>
+          <t>https://www.wbtv.com/2026/04/29/google-leases-massive-facility-near-rowan-cabarrus-county-line/</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Rowan/Kannapolis</t>
+          <t>RTP</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -15041,121 +15260,121 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Google (via 3rd-party logistics operator) — warehouse lease</t>
+          <t>Apple — RTP campus extension (incentive-timeline extension)</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$552M-$1B+ (paused)</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>$55k-$150k range (job-board postings)</t>
+          <t>$187k avg (stated, original 2021 award)</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>Lease publicly confirmed 2026-04-29: 729,872 sq ft at Overlook 85 Industrial Park, 88-month term; explicitly described as 'not a data center' — warehousing/logistics; jobs still undisclosed</t>
+          <t>No active construction found; permits obtained but final building-approval paperwork not yet resubmitted to Wake County</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026 (ongoing)</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>https://www.wbtv.com/2026/04/29/google-leases-massive-facility-near-rowan-cabarrus-county-line/</t>
+          <t>https://www.cbs17.com/news/local-news/wake-county-news/construction-on-apple-campus-set-to-start-2026-new-documents-show-plans-for-traffic/</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
         <is>
-          <t>High (lease); Low (jobs)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>York Co.</t>
+          <t>Charlotte / Raleigh / Rural Hall</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Multi</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>QTS "Project Cobra" — data-center campus</t>
+          <t>Siemens Energy — $421M NC expansion</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>~200 FTE (+~1,000 constr.)</t>
+          <t>500 (statewide)</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>up to $8B</t>
+          <t>$421M</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>~$80k median (stated)</t>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
         </is>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>York County Council passed its 9-month data-center moratorium on 3rd/final reading 2026-07-13; QTS's own site plans (9 buildings, various stages) are already vested and unaffected by the moratorium</t>
+          <t>No update found; one unverified headline references a possible 2nd Rural Hall (Forsyth) expansion — flagged for priority recheck</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrhi.com/2026/06/york-county-council-approves-data-center-moratorium-first-reading-advances-1-5-billion-biopharmaceutical-project-213500</t>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (totals uncertain)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / SouthPark</t>
+          <t>Raleigh / Wendell / Knightdale</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -15165,37 +15384,37 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Chase — new office</t>
+          <t>Siemens AG — power devices for AI/data centers</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>400 new by 2028</t>
+          <t>350</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H129" s="6" t="inlineStr">
-        <is>
-          <t>~$105k Estimated/Inferred</t>
-        </is>
-      </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>Breakdown clarified (100 Knightdale by YE2026; 50 new + 200 existing Wendell by 2028); new Wendell facility's online status unconfirmed</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr">
@@ -15207,17 +15426,17 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Charlotte (CLT airport)</t>
+          <t>Hamlet</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -15227,121 +15446,121 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Averitt — logistics campus</t>
+          <t>AWS/Amazon — AI/cloud campus</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$10B</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>$81,769 (stated)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle; construction 'expected to begin immediately' per original release, completion 2028</t>
+          <t>Still unverified; outside all five assigned research regions again this cycle</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
+          <t>https://www.aboutamazon.com/</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low (needs verification)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Mooresville</t>
+          <t>Orangeburg / I-26</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Iredell</t>
+          <t>Orangeburg</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>NEW — Corvid Technologies — HQ expansion</t>
+          <t>Ferrara Candy — groundbreaking held</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1,000 (10 yr)</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>$28.9M</t>
+          <t>$675M</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; Estimated/Inferred a meaningful share of engineering roles clear $100k (basis: Glassdoor role-level data — Software Engineer ~$134,243, Computational Analyst ~$138,353, Senior Program Manager ~$176,995; company-wide avg ~$77,578)</t>
+          <t>Not disclosed; confectionery = workforce-tier</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>Defense/aerospace/biomedical/motorsports physics engineering firm expanding its existing Mooresville HQ; announced 2026-06-20</t>
+          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward — first lines still targeted Q1 2029</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-20 (last verified)</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>https://statesville.com/news/iredell-chosen-for-367-job-headquarters/article_e69950c5-7074-5f48-bbbc-a2c832f5bb1f.html</t>
+          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>High (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg (former Kohler plant)</t>
+          <t>Columbia / BullStreet</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Richland</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -15351,59 +15570,59 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>NorthMark "Project Moc-1" — AI/HPC data center</t>
+          <t>AMAROK — new HQ (perimeter security)</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>~150 FT at full operation</t>
+          <t>296</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>$2.8B-$3.0B</t>
+          <t>$69M</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>Contested public hearing held 2026-06-25; comment period closed 2026-07-31 with no permit decision yet issued (SCDES says review could take 'several months'); a new lawsuit was filed 2026-07-06 by local residents seeking Planning Commission review of the next construction phase; construction continues despite opposition</t>
+          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06 (lawsuit); 2026-07-31 (comment close)</t>
+          <t>2026-03-03 (last verified)</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/spartanburg/news/spartanburg-data-center-northmark-water-power/article_07cc2de8-9eb6-4711-ad7f-90ef8230b158.html</t>
+          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>North Charleston</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Charleston</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -15413,59 +15632,59 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>GE Vernova — gas turbine mfg</t>
+          <t>Boeing 787 — production-rate ramp</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>650 total planned (200 hired 2025; 300 more by end 2026)</t>
+          <t>1,000 (unchanged)</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>$160M (Greenville)</t>
+          <t>$1.0B (existing)</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mixed, bulk likely sub-$100k (basis: job-board postings $66k-$125k)</t>
+          <t>Estimated/Inferred mixed ($54-64k assemblers; eng. likely higher)</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>Hiring-ramp progress confirmed 2026-06-27 (200 hired 2025, 300 more targeted by end of 2026), consistent with production ramping from 37 turbines (2025) toward 74 (2027)</t>
+          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-01-27 (last verified)</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/06/27/ge-vernova-gas-turbines-ai-data-centers.html</t>
+          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Med (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg / Roebuck</t>
+          <t>Goose Creek</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Berkeley</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -15475,17 +15694,17 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Siemens Smart Infrastructure</t>
+          <t>HII (Newport News Shipbuilding) — 1-yr anniversary</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>~150</t>
+          <t>~250 (estimate, not re-confirmed)</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>$165M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -15495,39 +15714,39 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-22 (last verified)</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Low (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Woodruff</t>
+          <t>Berkeley / Dorchester</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Berkeley &amp; Dorchester</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -15537,17 +15756,17 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>AIRSYS Cooling Technologies — global HQ</t>
+          <t>Google — data-center expansion</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>~160 apprentices (FTE n/d)</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>$40-60M</t>
+          <t>$9B</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -15557,39 +15776,39 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>Grand opening of the new 264,000 sq ft, 60-acre HQ campus confirmed 2026-05-13; manufacturing-operations start still targeted early 2027 (previously slipped from 2026, no further slip found)</t>
+          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-13 (last verified)</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>https://airsysnorthamerica.com/airsys-opens-global-headquarters-campus-in-south-carolina-to-meet-surging-global-demand-for-ai-and-data-center-cooling/</t>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (capex, not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Gray Court</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -15599,17 +15818,17 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Aptiv Services US — Connexial Center</t>
+          <t>Siemens Smart Infrastructure</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>~150</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>$120.8M</t>
+          <t>$165M</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -15619,39 +15838,39 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03-18 (last verified)</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Easley</t>
+          <t>Woodruff / Spartanburg Co.</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -15661,59 +15880,59 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Signature Foods USA</t>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>$40-60M</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$50k</t>
+          <t>Not disclosed (Estimated/Mixed)</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>Operations confirmed online; company still actively hiring</t>
+          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05-13 (last verified)</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+          <t>https://www.airsysnorthamerica.com/</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Gray Court</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -15723,59 +15942,59 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+          <t>Aptiv Services US — Connexial Center</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>$500M (valuation, not capex)</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>Formal in-window relocation confirmation (HQ + labs moving from California/Canada to Greenville, initial lab ops at Clemson's CUBEInC) dated 2026-05-21/23; job projections still 'developing' pending planned public listing (SPAC merger)</t>
+          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-20 (last verified)</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
+          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Easley (Anderson/Pickens border)</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -15785,54 +16004,54 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>NEW — EnerSys — lithium-ion cell manufacturing (Augusta Grove)</t>
+          <t>Signature Foods USA</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>Originally 500 (2024); scope materially reduced</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>~$500M (net, incl. ~$150M DOE grant)</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>FLAG: 2026-07-23 scope revision cuts planned capacity ~75-80% (from ~4-5 GWh to ~1 GWh), refocused exclusively to aerospace/defense/specialized-industrial cells; construction now targeted 1H FY2028, full production ~2031 (a major slip from the original 2027 target). Original 500-job figure should be treated as stale pending a restated number</t>
+          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04 (last verified)</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>https://investor.enersys.com/news/news-details/2026/EnerSys-Refines-Plans-for-DefenseFocused-Lithium-Cell-Manufacturing-Facility-with-DOE-Support/default.aspx</t>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
-          <t>Med-High (scope cut); Low (current jobs figure)</t>
+          <t>High (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Fountain Inn</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -15847,59 +16066,59 @@
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>NEW — EPC Power — AI data-center power inverter mfg</t>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>Estimated/Inferred sub-$100k (basis: job-board postings $47k-$64k/yr, $25-$35/hr)</t>
-        </is>
-      </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>Grand opening/ribbon-cutting of the 167,000 sq ft facility (EPC Power's 3rd US site) held 2026-07-15</t>
+          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05 (last verified)</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/07/15/epc-power-opens-facility-upstate-produce-critical-ai-data-center-technology/</t>
+          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg / I-26</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -15909,59 +16128,59 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>Ferrara Candy — new mfg + corporate site</t>
+          <t>GE Vernova — gas turbine mfg (AI/data-center power supply chain)</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>1,000 (10 yr)</t>
+          <t>650 total planned</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>$675M</t>
+          <t>$160M (Greenville)</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; confectionery = workforce-tier</t>
+          <t>Estimated/Inferred mixed (bulk likely sub-$100k)</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>No new milestone since the May 2026 groundbreaking; first lines still targeted Q1 2029</t>
+          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-27 (last verified)</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
+          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med (not rechecked)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Berkeley / Dorchester</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Berkeley &amp; Dorchester</t>
+          <t>Pickens</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -15971,17 +16190,17 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Google — data-center expansion</t>
+          <t>FN America — 2nd production facility</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>~160 apprentices (FTE n/d)</t>
+          <t>~176</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>$9B</t>
+          <t>$33M</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -15991,208 +16210,22 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle; $9B figure traces to an Oct. 2025 announcement (pre-window)</t>
+          <t>Not rechecked this cycle; third consecutive cycle with no confirmed momentum — recommend removal next cycle absent an update</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026 (last verified)</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr">
         <is>
-          <t>High (capex)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>North Charleston</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>Charleston</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>Boeing 787 — production-rate ramp</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>1,000 (unchanged)</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="inlineStr">
-        <is>
-          <t>$1.0B (existing)</t>
-        </is>
-      </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>Estimated/Inferred mixed</t>
-        </is>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>Rate confirmed 8/month as of Jan 2026; CEO targets 10/month by end of 2026; the $1B expansion is designed to eventually support 16/month by 2028, a more ambitious framing than the prior cycle's '10/month by 2027'</t>
-        </is>
-      </c>
-      <c r="J143" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="K143" s="6" t="inlineStr">
-        <is>
-          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/</t>
-        </is>
-      </c>
-      <c r="L143" s="6" t="inlineStr">
-        <is>
-          <t>Med-High</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>North Charleston</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>Charleston</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>SC Ports Authority — Leatherman Terminal (OPERATIONS PAUSED)</t>
-        </is>
-      </c>
-      <c r="F144" s="6" t="inlineStr">
-        <is>
-          <t>400 direct + ~1,200 indirect</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr">
-        <is>
-          <t>$1.2B (existing)</t>
-        </is>
-      </c>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>CONFIRMED: SC Ports paused all container operations at Leatherman effective 2026-08-01 (today), consolidating cargo to Wando Welch/North Charleston, citing an 'uncertain trade outlook' and high labor costs from the all-union workforce structure (Leatherman handled &lt;6% of SC Ports' container volume). No reopening date given; Phase 2 wharf construction ($88.5M) continues uninterrupted, targeted for 2027 completion. No confirmation found of ILA worker layoffs tied to the pause</t>
-        </is>
-      </c>
-      <c r="J144" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-25 (announced); 2026-08-01 (effective)</t>
-        </is>
-      </c>
-      <c r="K144" s="6" t="inlineStr">
-        <is>
-          <t>https://scspa.com/news/sc-ports-consolidating-container-operations-in-the-short-term/</t>
-        </is>
-      </c>
-      <c r="L144" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>Goose Creek</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>Berkeley</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>HII (Newport News Shipbuilding)</t>
-        </is>
-      </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
-          <t>~250 (estimate)</t>
-        </is>
-      </c>
-      <c r="G145" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="H145" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>One-year anniversary (Jan 2026) confirmed exceeding production targets; hosted Australia's Minister for Defence Industry 2026-07-27 in connection with the AUKUS submarine partnership — a positive diplomatic/business-development signal, but no new jobs/investment figures disclosed</t>
-        </is>
-      </c>
-      <c r="J145" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="K145" s="6" t="inlineStr">
-        <is>
-          <t>https://www.globenewswire.com/news-release/2026/07/27/3333932/0/en/hii-hosts-australian-minister-for-defence-industry-at-newport-news-shipbuilding-charleston-operations.html</t>
-        </is>
-      </c>
-      <c r="L145" s="6" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18239,7 +18272,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -18281,7 +18314,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -18323,7 +18356,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -18365,7 +18398,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -18407,7 +18440,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -18449,7 +18482,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -18491,7 +18524,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -18533,7 +18566,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -18575,7 +18608,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -18617,7 +18650,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -18659,7 +18692,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -18701,7 +18734,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -18743,7 +18776,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -18785,7 +18818,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -18827,7 +18860,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -18869,17 +18902,17 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Maersk North American HQ</t>
+          <t>VinFast (INCENTIVE TERMINATED)</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chatham Co.</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -18889,39 +18922,39 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>1,400 (scaled back from 7,500)</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-07-27 to 07-31</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; no new forward movement found beyond the previously-noted 1-year hiring delay (now 2027-2029); wage remains stated at $100,962 but a delay is not qualifying forward movement per report rules</t>
+          <t>NEW REVERSAL: Chatham County commissioners voted to terminate the $400M incentive agreement after VinFast failed to hit its 1,750-job/~$700M-invested threshold; state separately suing to reclaim the Moncure site; no production has begun</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+          <t>https://www.wral.com/business/vinfast-agreement-canceled-chatham-county-north-carolina-july-2026/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Kempower (JDIG CANCELLED)</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / Ballantyne</t>
+          <t>Durham/RTP</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -18931,34 +18964,34 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>306 (pledge; only ~100 employed)</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07 (mid-July)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; the March 2026 grand-opening milestone remains tied to a pre-window (2025-07-08) commitment; no new increase or fresh milestone found this cycle</t>
+          <t>NEW REVERSAL: NC Commerce cancelled Kempower's JDIG after the company missed hiring targets (156 jobs required by end-2025); company continues operating at reduced scale, citing loss of federal EV tax credits and softer US EV demand</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs/</t>
+          <t>https://hoodline.com/2026/07/durham-ev-plant-slams-brakes-on-hiring-as-state-yanks-job-grant/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors HQ (Plaza Midwood)</t>
+          <t>Maersk North American HQ</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -18973,39 +19006,39 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; early job postings for the HQ (several six-figure roles) surfaced this cycle but do not amount to a formal milestone (lease signing, groundbreaking, or a announced hiring-ramp event) — recheck next cycle for a concrete trigger</t>
+          <t>Pre-window; in-window milestone remains a 1-year hiring delay (2027-2029); rechecked this cycle, no new forward movement found</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://www.detroitnews.com/story/business/autos/2025/11/14/scout-motors-rolls-into-charlotte-5-key-things-about-the-automaker/87270881007/</t>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>PSA Airlines</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Charlotte (CLT)</t>
+          <t>Charlotte / Ballantyne</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -19015,81 +19048,81 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>~400-450 (mix reloc.+new; ~250 net new)</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Grand opening reconfirmed (450+ team members, ~80% of net-new hiring filled); net-new local roles (~250) remain well below the 500-job threshold and wage remains mixed/mostly sub-$100k except for pilots — no new in-window update changes this assessment</t>
+          <t>Pre-window; rechecked this cycle — office headcount grew from ~350 to ~860 by April 2026, but this is continued execution of the pre-window commitment, not a new 500+ award</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>https://psaairlines.com/psa-airlines-celebrates-grand-opening-of-charlotte-headquarters-underscoring-economic-and-workforce-impact-across-north-carolina/</t>
+          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Bosch — Dorchester Co. electric motors</t>
+          <t>Compass Datacenters</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Dorchester</t>
+          <t>Statesville (Iredell)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>n/d (workforce 1,500-&gt;1,800)</t>
+          <t>~250</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>No 2026 confirmation of resumption found this cycle; status remains unresolved/paused pending an EV-demand recovery</t>
+          <t>Rechecked this cycle; no 2026 milestone found; remains pre-window</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/business/bosch-dorchester-electric-vehicles-rivian-expansion/article_265b1c36-ab6c-11ef-b047-3b784368d210.html</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Compass Datacenters</t>
+          <t>PSA Airlines</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Statesville (Iredell)</t>
+          <t>Charlotte (CLT)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -19099,39 +19132,39 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>~250</t>
+          <t>~400</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>No precisely-dated in-window 2026 milestone could be confirmed this cycle despite reported rezoning progress; staying excluded pending a hard date</t>
+          <t>Rechecked this cycle; grand opening remains the only milestone and ties to a pre-window relocation commitment</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://psaairlines.com/psa-airlines-celebrates-grand-opening-of-charlotte-headquarters-underscoring-economic-and-workforce-impact-across-north-carolina/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Snider Fleet Solutions (REMOVED)</t>
+          <t>EG Group global HQ relocation</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Indian Land (Lancaster)</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -19141,81 +19174,81 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>REMOVED from tracking this cycle: confirmed stale for a third consecutive pass — all coverage traces to a May 2023 announcement with zero 2026 activity found</t>
+          <t>Pre-window; no disclosed job count or capex for the Charlotte component</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
+          <t>https://www.aol.com/news/scout-motors-midst-launching-charlotte-090500610.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>FN America — 2nd production facility (REMOVED)</t>
+          <t>Daimler Truck Financial Services USA</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Liberty (Pickens)</t>
+          <t>Ballantyne (Charlotte)</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>~176</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>REMOVED from tracking this cycle: three consecutive quiet cycles with no 2026 news on hiring, production start, or facility completion found; all available coverage remains 2023-2024 era</t>
+          <t>Pre-window; sub-500; no in-window update</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>https://governor.sc.gov/news/2023-04/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>VinFast EV megafactory (Moncure megasite) — TERMINATED</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Chatham Co.</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -19225,81 +19258,81 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Target cut from 7,500 to ~1,400; failed to meet 1,750-job threshold</t>
+          <t>216</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>MAJOR REVERSAL: Chatham County Commissioners voted 2026-07-28 to terminate the $400M incentives agreement (site abandoned since late 2024, no construction contract, expired permits); NC AG separately sued (~2026-05-21) to force VinFast to sell back the land. A collapse, not a growth signal</t>
+          <t>Pre-window; wage $89,769 (&lt;$100k)</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/vinfast-agreement-canceled-chatham-county-north-carolina-july-2026/</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Wolfspeed — Durham fab (150mm device line)</t>
+          <t>Albemarle "Mega-Flex" lithium plant</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Chester Co.</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>N/A (shutdown)</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02 (earnings call)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Closure of a legacy 150mm device-production line, completed ahead of schedule per Q2 FY26 earnings call — an explicit contraction, not a growth signal (Wolfspeed's Siler City project remains separately tracked in Watch)</t>
+          <t>Confirmed still paused per CEO's Feb. 2026 earnings-call comments citing depressed lithium prices — no construction, engineering work stopped</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>https://www.investing.com/news/transcripts/earnings-call-transcript-wolfspeeds-q2-2026-results-disappoint-stock-dips-93CH-4486298</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TigerDC "Project Spero" (still withdrawn)</t>
+          <t>E&amp;J Gallo Winery</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg Co.</t>
+          <t>Chester Co.</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -19309,39 +19342,39 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>~50 FTE (Phase I)</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Confirmed still withdrawn this cycle; no revival evidence found</t>
+          <t>Recycled 2021 news; no in-window update found</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/02/27/company-withdraws-ai-data-center-spartanburg-county-consideration/</t>
+          <t>https://governor.sc.gov/news/2021-06/e-j-gallo-winery-establishing-new-east-coast-facility-chester-county</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Corvid Technologies (retained note)</t>
+          <t>Honeywell HQ</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Mooresville (Iredell)</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -19351,59 +19384,59 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Tracked in Watch tier this cycle (367 jobs, wage not officially stated) — noted here only to confirm it does NOT qualify for Ranked: sub-500 jobs</t>
+          <t>Long-completed 2018 announcement; no relevance to the window</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>https://statesville.com/news/iredell-chosen-for-367-job-headquarters/article_e69950c5-7074-5f48-bbbc-a2c832f5bb1f.html</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Numerous sub-200-job items (Poly-America/Carolina Poly Chester, Element Designs Fort Mill, TTX Charlotte, RXO Ballantyne, Daimler Truck Financial Ballantyne, Red Bull/Rauch Concord, EG Group Charlotte [jobs undisclosed], Lowe's Mooresville [-600, layoffs])</t>
+          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Various Charlotte metro</t>
+          <t>Raleigh (Wake)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>NC/SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>12-450 each (or layoffs)</t>
+          <t>1,500 (claimed)</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>2021-2026</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Below Watch floor, low-wage, recycled old news with no in-window update, or (Lowe's) a layoff rather than a growth signal</t>
+          <t>Re-checked this cycle: traces to a 2024 Instagram post about existing NC card-services operations, not a 2026 relocation — still unverifiable, no authoritative source found</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -19415,17 +19448,17 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Numerous sub-200/recycled items (Corning/Meta Hickory [out of region], Skyeton Fayetteville [out of region], CorestemChemon Winston-Salem [vague], Herbalife Winston-Salem, GMAX Industries, Foster Caviness/ReAgent/Tex-Tech Winston-Salem, Wilmington Trade Center Phase 2 [speculative/unallocated], Honda Aircraft Greensboro, Hoffman &amp; Hoffman Greensboro, ImpactData Greensboro, Southeastern Container Enka-Candler)</t>
+          <t>Novo Nordisk speculative Four Oaks expansion</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Various Triad/WNC/Coastal</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -19435,17 +19468,17 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>12-1,500 each</t>
+          <t>~500 (speculative)</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>2019-2026</t>
+          <t>2025-10 (cancelled)</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Below Watch floor, out of region, vague/speculative, or recycled old news with no in-window update</t>
+          <t>Confirmed still cancelled after an annexation vote in Oct. 2025; also pre-window</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -19457,17 +19490,17 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Numerous sub-200/recycled items (Cisco RTP "550 jobs" [stale SEO content, actually 2014], Merck Durham "180 jobs" [~2011], Microsoft Wake "500 jobs" [2019], CITEL America Hillsborough, Innovative Construction Group Chatham, Ypsomed Holly Springs, Audemars Piguet Raleigh, Fujifilm RTP, AdvanceTEC Johnston [160 jobs/~$90k])</t>
+          <t>Fujifilm Diosynth</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Various NC Triangle</t>
+          <t>Holly Springs (Wake)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -19477,17 +19510,17 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>62-550 each</t>
+          <t>680 (2024 expansion)</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>2011-2026 (mostly stale)</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Below Watch floor and/or recycled/stale old news falsely resurfacing in current searches; no in-window update</t>
+          <t>Grand opening was Sept. 2025, pre-window; no in-window update found</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -19499,37 +19532,37 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Numerous sub-200-job items (Cielo Digital Infrastructure Cherokee [30 jobs/$2.1B], Oshkosh Defense Spartanburg [recycled 2021], Detpak USA Spartanburg, Fortified Solar Greenville, United Composite Materials Greenville, Advanced Metalworks Anderson, Southern Wall Products Anderson, Sargent Metal Fabricators Anderson, Eastern Engineered Wood Anderson, Sync.MD Anderson, Woodward Inc. Greer [~275 jobs, no in-window milestone])</t>
+          <t>Amgen (2nd facility)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Various Upstate SC</t>
+          <t>Holly Springs (Wake)</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>10-1,000 each</t>
+          <t>370</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>2021-2026</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Below Watch floor regardless of window, capex-heavy with tiny headcount, or recycled old news with no in-window update</t>
+          <t>Pre-window; sub-500 jobs</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -19541,40 +19574,166 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Numerous sub-200/incomplete items (AVANTech Richland, Mattress Warehouse Lexington, Hoffman &amp; Hoffman Lexington, Patten Seed Charleston, ZEB Metals Berkeley, Summerville warehouse Dorchester, TS Conductor Jasper [out of region], Delta Children's Orangeburg, ALLTAPE Adhesive Lexington [no figures], Southern Glazer's Wine &amp; Spirits Lexington [job count not found before search budget exhausted])</t>
+          <t>Science 37</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Various Midlands/Lowcountry</t>
+          <t>Morrisville (Wake)</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Company being acquired/taken private (~$375M sale) — reversal-adjacent, not a growth signal</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Snider Fleet Solutions (REMOVED from Watch)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Indian Land (Lancaster)</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>12-462 each (or undisclosed)</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>2022-2026</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>Below Watch floor, out of region, or insufficient data (no job/wage figures located) to assess against thresholds — flagged for a follow-up search next cycle where noted</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed stale 2023 item; no developments found in 3+ years despite repeated rechecks — removed from active Watch tracking this cycle</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic "Rolls-Royce engine partnership collapse" (rumor, debunked)</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>An AI-summarized search result implied this was a 2026 event; underlying sources trace to 2022 — not a current development, excluded as a data-quality catch</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200-job items (AdvanceTEC/Clayton, Innovative Construction Group/Siler City, CITEL/Hillsborough, GMAX Industries/Forsyth, Superion/Guilford, Walmart Gaston, Fit Precast)</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Various NC</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>36-300 each</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>Below Watch floor and/or wage well under $100k regardless of window</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -19591,7 +19750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -20600,6 +20759,384 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Fort Mill Sun — Rock Hill Council 7-0 vote</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>York Co. SC</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma final Rock Hill City Council resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>WFAE</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte metro &amp; Triangle</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma finalization; WakeMed/Atrium merger transparency coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>SC statewide</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma finalization; USA Rare Earth; SC Ports Leatherman (last verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Hoodline</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>NC (Charlotte/Triad/Triangle)</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors HQ 2nd building filing; Averitt rezoning; Kempower JDIG cancellation; Novartis Morrisville API facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Crosland Southeast</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.croslandsoutheast.com/</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte NC</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors HQ Commonwealth development detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>HITT Contracting / ENR / CompositesWorld / Aviation Week</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hitt.com/news-hub/jetzero-greensboro-groundbreaking/</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>National aerospace/construction</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>JetZero NC3 construction-start confirmation, general contractor detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>North Carolina Health News / WFAE / CBS17 / ABC11</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.northcarolinahealthnews.org/</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>NC Triangle</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed/Atrium merger vote-delay tracking (public hearing Aug. 17, earliest vote Sept. 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>rebusinessonline</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>https://rebusinessonline.com/</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>National CRE</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Durham lease; Toyota Battery NC grand-opening detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Johnston Community College</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>regional_edo</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.johnstoncc.edu/</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Johnston Co. NC</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements training-pipeline detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Business NC — Jewelers Mutual / Amazon Pender</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>NC Triangle &amp; Coastal</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Jewelers Mutual Raleigh; Amazon Pender/New Hanover fulfillment center</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>GlobeNewswire — Ahold Delhaize</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Alamance Co. NC</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize/Food Lion Burlington distribution center groundbreaking</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>WRAL — VinFast termination</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/vinfast-agreement-canceled-chatham-county-north-carolina-july-2026/</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Co. NC</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>VinFast incentive termination</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Fox Carolina — Project Moc-1</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark Project Moc-1 SCDES comment-period status</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>CBS17 — Gregory Poole / Apple RTP</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.cbs17.com/</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. NC</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Gregory Poole Garner HQ; Apple RTP construction status</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20611,7 +21148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21050,7 +21587,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -21070,7 +21607,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -21090,7 +21627,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -21110,7 +21647,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -21130,7 +21667,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -21150,7 +21687,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -21170,7 +21707,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -21190,7 +21727,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -21210,7 +21747,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -21223,14 +21760,14 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; no new milestone this cycle.</t>
+          <t>Unchanged; no new milestone this cycle (third consecutive quiet cycle).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -21243,34 +21780,34 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council voted unanimously 7-0 (2026-07-23) to approve the land sale and amended tax-incentive agreement, closing out the prior cycle's single outstanding risk (the city-level vote). Deal is now fully cleared on both county and city sides; +3 for removed execution-risk discount.</t>
+          <t>Rock Hill City Council voted 7-0 to approve amended tax-share terms (2026-07-23), resolving the deal's chief outstanding execution risk; SC awarded a $65M Closing Fund grant to York County; deal now described as fully finalized — net +3 for removed deal-certainty discount.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors (Blythewood)</t>
+          <t>Scout Motors — EV plant (Blythewood)</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Hiring event proceeded on schedule (positive) but the customer-delivery timeline slip to 'early 2028' is now stated explicitly rather than softly implied; net -1 for confirmed further timeline risk.</t>
+          <t>Carried forward unchanged — this cycle's SC Midlands/Lowcountry recheck could not be completed due to web-search tool-budget exhaustion; no negative signal found, but also not independently reverified this cycle.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -21290,7 +21827,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -21310,12 +21847,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Genentech (Holly Springs)</t>
+          <t>JetZero (Greensboro)</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -21323,19 +21860,19 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; no new milestone this cycle.</t>
+          <t>Physical construction now confirmed underway (NC Composite Center, HITT Contracting as general contractor) beyond the groundbreaking ceremony already credited last cycle; net +1 for reduced execution-risk discount, still capped by the extended hiring ramp (full target 2037).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>JetZero (Greensboro)</t>
+          <t>Genentech (Holly Springs)</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
@@ -21343,25 +21880,45 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>EXIM Bank Letter of Interest (2026-07-20) to explore up to $3B in financing strengthens capital/project-certainty even though no new jobs/wage figures moved; +1.</t>
+          <t>Unchanged; no new milestone this cycle.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>Scout Motors — Global HQ (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>New to Ranked: 1,200 jobs + stated $153,978 wage (well above county avg) + urban Plaza Midwood fit; discounted for Med confidence (in-window milestone is a preliminary land-development filing, not a permit or groundbreaking) and zero repeat-momentum as a first-time-ranked entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>Novartis (Durham/Morrisville)</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C42" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Unchanged; no new milestone this cycle.</t>
         </is>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-08-10  ·  Window 2026-02-10 to 2026-08-10  ·  NC + SC</t>
+          <t>Week of 2026-07-20  ·  Window 2026-01-20 to 2026-07-20  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10  (Week 4)</t>
+          <t>2026-07-20  (Week 4)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10 to 2026-08-10  (trailing 6 months)</t>
+          <t>2026-01-20 to 2026-07-20  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 90 (+3) — Rock Hill City Council voted 7-0 on 2026-07-23 to approve amended tax-share terms, resolving the deal's last outstanding governmental hurdle; deal now described as fully finalized</t>
+          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 88 (+1) — Rock Hill School Board voted 5-2 to back the amended tax-share terms; Rock Hill City Council's own vote remains outstanding</t>
         </is>
       </c>
     </row>
@@ -634,55 +634,43 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Octapharma is now a closed deal, not a pending one. Scout Motors' Charlotte global HQ (distinct from its Blythewood, SC EV plant) is newly Ranked on an in-window land-development filing for a second office building. JetZero has moved from ceremonial groundbreaking to an active general contractor physically building the first facility. Two negative reversals hit the NC Triangle (VinFast incentive terminated in Chatham Co.; Kempower's JDIG cancelled in Durham/RTP).</t>
+          <t>Second consecutive cycle with zero brand-new qualifying (500+ job / $100k+ wage) deals across all five sub-regions — all 8 ranked entries carry forward. JetZero gained an execution-certainty boost when Gov. Stein signed the FY2026-27 state budget (2026-07-07), releasing the previously-frozen $133.9M JDIG-linked funding. A data-quality correction: last week's Scout Motors '2026-07-29 hiring event' could not be corroborated as genuinely 2026-dated (it traces to matching 2025 wage/role details) and is now flagged unverified rather than carried forward as confirmed. Genentech's sole dated milestone (2026-01-20) now sits exactly at the trailing-6-month window boundary — watch for it to age out next cycle absent a new update. SC Ports' Leatherman Terminal pause remains on track for Aug. 1 with no reversal found.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Coverage gap — READ</t>
+          <t>Window note</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>This session's shared web-search tool budget (200 calls) was exhausted before the SC Midlands/Lowcountry research pass could run at all, and before the Upstate SC pass could complete more than 4 of its planned ~25 searches. Every SC Midlands/Lowcountry entry (Scout Motors' Blythewood plant, SC Ports Leatherman Terminal, AMAROK, Ferrara Candy, Boeing 787, HII, Google) and several Upstate SC watch items are carried forward from 2026-07-13 UNVERIFIED this cycle — flagged in both the report and this workbook. No numbers were invented; see the report's Appendix for full detail.</t>
+          <t>Trailing 6 months now runs 2026-01-20 to 2026-07-20.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Window note</t>
+          <t>Data-quality note</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-02-10 to 2026-08-10.</t>
+          <t>Scout Motors' previously-reported 2026-07-29 pre-hire event could not be independently corroborated this cycle as a genuinely 2026-dated announcement — the wage/role details match 2025-07-10 and 2025-07-25 stories precisely. Treated as unverified/likely a dating error rather than confirmed. Two Watch-tier items (Snider Fleet Solutions, FN America) were dropped this cycle after 2-3 consecutive quiet cycles with zero forward movement; four new Watch-tier items were added (Isuzu North America, EPC Power Corp., BMW Plant Woodruff, Southern Glazer's Wine &amp; Spirits) — all clear the 500-job bar in Isuzu's/Southern Glazer's case but fail the $100k wage bar.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Data-quality note</t>
+          <t>Week-over-week</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SC Ports' announced Aug. 1, 2026 pause of Leatherman Terminal operations (reported 2026-06-25) could not be confirmed as having taken effect this cycle due to the coverage gap above — this is the #1 priority recheck for next cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Week-over-week</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>8 of 8 prior-ranked deals remain qualifying, plus 1 new (Scout Motors Global HQ, Charlotte) — 9 total. 1 updated/resolved (Octapharma, +3), 1 updated (JetZero, +1), 5 repeated (SMBC, AbbVie, Capital Group, Genentech, Novartis), 1 repeated-but-unverified (Scout Motors EV plant, Blythewood). None removed from Ranked. Snider Fleet Solutions removed from Watch (confirmed stale).</t>
+          <t>8 of 8 prior-ranked deals remain qualifying (none removed, none newly added); 1 gaining momentum (Octapharma, +1), 1 updated (AbbVie — county incentive hearing), 1 updated (JetZero, +1 — state budget funding release), 5 repeated (SMBC, Scout Motors, Capital Group, Genentech, Novartis).</t>
         </is>
       </c>
     </row>
@@ -697,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2095,7 +2083,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -2186,7 +2174,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -2277,7 +2265,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2368,7 +2356,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -2459,7 +2447,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
@@ -2550,7 +2538,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -2641,7 +2629,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -2732,7 +2720,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -2823,7 +2811,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -2914,14 +2902,14 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
@@ -2940,7 +2928,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (finalized)</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
@@ -2968,27 +2956,27 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools; NEW: $65M SC Coordinating Council Closing Fund grant to York County</t>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council final approval (unanimous); deal finalized</t>
+          <t>Rock Hill School Board endorsement of amended tax-share terms; City Council vote still outstanding</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+          <t>https://www.fortmillsun.com/2026/07/13/rock-hill-schools-board-urges-city-to-accept-county-tax-allocations/</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); Med (deal certainty)</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -3005,7 +2993,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -3031,7 +3019,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (carried forward, not rechecked)</t>
+          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -3044,7 +3032,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>$30-$37.50/hr line (stated, per 2026-07-13); salaried higher</t>
+          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -3064,22 +3052,22 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Hiring event announced; companywide headcount update (as of 2026-07-13)</t>
+          <t>Hiring event announced; companywide headcount update</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/columbia/business/scout-motors-blythewood-factory-construction-sc/article_66a10144-3603-47f1-9b23-2f8415835b8f.html</t>
+          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/scout-motors-plant-blythewood-update/101-c64d17ed-4b85-4fae-b866-e7e1a08021f1</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>Med (not independently rechecked)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -3096,7 +3084,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -3155,17 +3143,17 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>New facility (greenfield, 185 ac)</t>
+          <t>County incentive hearing (procedural step, no scale change)</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+          <t>https://abc11.com/post/abbvie-pharmaceutical-project-moves-forward-durham/19500900/</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
@@ -3187,7 +3175,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -3231,7 +3219,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -3246,7 +3234,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>New facility / operations hub (unchanged)</t>
+          <t>Wage figure confirmed (stated, not inferred)</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -3278,7 +3266,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -3289,12 +3277,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Holly Springs / SW Wake</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -3304,55 +3292,55 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (construction underway)</t>
+          <t>Genentech — biomanufacturing expansion</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>14500</v>
+        <v>500</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Aerospace mfg + eng.</t>
+          <t>Adv. biomanufacturing</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>$89,340 avg (stated, 2025)</t>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated (2025)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>$4.7B</t>
+          <t>~$2.0B</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>General contractor on site; physical construction start on Phase 1</t>
+          <t>Expansion of committed project</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>https://www.hitt.com/news-hub/jetzero-greensboro-groundbreaking/</t>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Low (timeline)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -3362,14 +3350,14 @@
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale; near-term construction-phase hiring (GC + subcontractors) is a modest, earlier housing-demand signal ahead of the 2028-2029 direct-hire ramp.</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -3380,12 +3368,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs / SW Wake</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -3395,55 +3383,55 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Genentech — biomanufacturing expansion</t>
+          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
         </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>500</v>
+        <v>14500</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Aerospace mfg + eng.</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, 2025 tranche)</t>
+          <t>$89,340 avg (stated, 2025)</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>N/A — stated (2025)</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B</t>
+          <t>$4.7B</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>Expansion of committed project</t>
+          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); Low (timeline)</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -3453,30 +3441,30 @@
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
         <v>8</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / Plaza Midwood</t>
+          <t>Durham / Morrisville</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Durham &amp; Wake</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -3486,20 +3474,20 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+          <t>Novartis — API mfg building (investment increase)</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Corporate HQ / professional</t>
+          <t>Adv. mfg / API production</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>$153,978 avg (stated)</t>
+          <t>$111,161 avg (stated)</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -3509,131 +3497,40 @@
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>$206.9M</t>
+          <t>~$991M (incl. $220M API building)</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+          <t>Part of original $771M package incentives</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>Preliminary land-development plan filed for 2nd office building</t>
+          <t>New facility (unchanged)</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>Med (facts High; milestone stage early)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Suburban</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Durham / Morrisville</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Durham &amp; Wake</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Novartis — API mfg building (investment increase)</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>700</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Adv. mfg / API production</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>$111,161 avg (stated)</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated</t>
-        </is>
-      </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>~$991M (incl. $220M API building)</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>Part of original $771M package incentives</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>New facility (unchanged)</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
         <is>
           <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
         </is>
@@ -3650,7 +3547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5428,7 +5325,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -5544,7 +5441,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5660,7 +5557,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5776,7 +5673,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5892,7 +5789,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -6008,7 +5905,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -6124,7 +6021,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6240,7 +6137,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -6356,7 +6253,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -6465,26 +6362,26 @@
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>Third consecutive quiet cycle; no new in-window milestone but nothing has slipped either.</t>
+          <t>No new in-window milestone found this cycle (second consecutive quiet cycle); project remains on track for fall 2026 first arrivals.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Updated (resolved)</t>
+          <t>Gaining Momentum</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
@@ -6503,7 +6400,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (finalized)</t>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -6513,7 +6410,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council final approval (unanimous); deal finalized</t>
+          <t>Rock Hill School Board endorsement of amended tax-share terms; City Council vote still outstanding</t>
         </is>
       </c>
       <c r="K25" s="6" t="n">
@@ -6541,27 +6438,27 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools; NEW: $65M SC Coordinating Council Closing Fund grant to York County</t>
+          <t>Fee-in-lieu-of-tax, assessment ratio cut to 4%; ~85% of Rock Hill's tax share redirected mostly to Rock Hill Schools</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council voted 7-0 on 2026-07-23 to approve amended tax-share terms — all governmental approvals now complete; land closing expected in coming months; construction as early as 2027; operations targeted mid-2030s</t>
+          <t>York County Council 3rd reading approved 2026-07-08 (4-3); Rock Hill School Board voted 5-2 on 2026-07-13 to back the amended tax-share structure and urge City Council to accept it; Rock Hill City Council has still not voted as of 2026-07-20 (unconfirmed reporting points to an Aug. 10, 2026 council agenda — not independently verified)</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+          <t>https://www.fortmillsun.com/2026/07/13/rock-hill-schools-board-urges-city-to-accept-county-tax-allocations/</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); Med (deal certainty)</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -6581,19 +6478,19 @@
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council's previously outstanding vote is now resolved unanimously; deal described by multiple outlets as fully 'finalized'/'inked' as of late July 2026 — removes the deal-certainty discount that had held the score down.</t>
+          <t>School board's 5-2 endorsement removes one point of local opposition, but Rock Hill City Council's outstanding vote on the amended tax-share terms remains the key unresolved risk; +1 for continued forward momentum with no new negative signal this cycle.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Repeated (unverified this cycle)</t>
+          <t>Repeated</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
@@ -6619,7 +6516,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV assembly plant (carried forward, not rechecked)</t>
+          <t>Scout Motors — EV assembly plant (active hiring ramp)</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -6629,7 +6526,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Hiring event announced; companywide headcount update (as of 2026-07-13)</t>
+          <t>Hiring event announced; companywide headcount update</t>
         </is>
       </c>
       <c r="K26" s="6" t="n">
@@ -6637,12 +6534,12 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Projected (~1,400 hired companywide, per 2026-07-13)</t>
+          <t>Projected (~1,400 hired companywide; 600+ in SC)</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>$30-$37.50/hr line (stated, per 2026-07-13); salaried higher</t>
+          <t>$30-$37.50/hr line (stated; senior maintenance techs to $37.50/hr); salaried higher</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -6662,22 +6559,22 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>Pre-hire/interview events for 70+ maintenance-tech roles were scheduled to begin 2026-07-29 (per 2026-07-13 report); not independently reconfirmed this cycle</t>
+          <t>Companywide headcount holds at ~1,400 (~600 in SC), confirmed via WLTX and Scout's own blog as of mid-July 2026; production still targeted late 2027, customer deliveries trending 2028</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/columbia/business/scout-motors-blythewood-factory-construction-sc/article_66a10144-3603-47f1-9b23-2f8415835b8f.html</t>
+          <t>https://www.wltx.com/article/news/local/midlands/building-the-midlands/scout-motors-plant-blythewood-update/101-c64d17ed-4b85-4fae-b866-e7e1a08021f1</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>Med (not independently rechecked)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -6697,19 +6594,19 @@
       </c>
       <c r="X26" s="6" t="inlineStr">
         <is>
-          <t>SC Midlands/Lowcountry research pass could not run this cycle (session web-search budget exhausted before this region's agent began); carried forward unverified from 2026-07-13 — top-priority recheck next cycle.</t>
+          <t>CORRECTION: last week's report cited a 2026-07-29 pre-hire event for 70+ maintenance techs; this cycle's research found the wage/role details trace precisely to a 2025-07-10 WISTV story and a 2025-07-25 SC Daily Gazette story, with no distinctly-dated 2026 version found — that specific claim is now treated as unverified/likely a dating error and is not carried forward. Headcount and the active-hiring trend remain independently confirmed.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -6745,7 +6642,7 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>New facility (greenfield, 185 ac)</t>
+          <t>County incentive hearing (procedural step, no scale change)</t>
         </is>
       </c>
       <c r="K27" s="6" t="n">
@@ -6778,17 +6675,17 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+          <t>Durham County Board of Commissioners held a public hearing 2026-07-13 on a proposed $15M county incentive package (on top of the ~$26M state EIC incentive approved in April); no vote outcome reported yet</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+          <t>https://abc11.com/post/abbvie-pharmaceutical-project-moves-forward-durham/19500900/</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -6813,14 +6710,14 @@
       </c>
       <c r="X27" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle.</t>
+          <t>Procedural incentive step, not a scale change; construction start still targeted this year.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -6861,7 +6758,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>New facility / operations hub (unchanged)</t>
+          <t>Wage figure confirmed (stated, not inferred)</t>
         </is>
       </c>
       <c r="K28" s="6" t="n">
@@ -6879,7 +6776,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>N/A — now stated (was Estimated/Inferred ~$190k)</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -6936,12 +6833,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Repeated</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -6952,12 +6849,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Holly Springs / SW Wake</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -6967,70 +6864,70 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>JetZero — aerospace plant (construction underway)</t>
+          <t>Genentech — biomanufacturing expansion</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Aerospace / advanced manufacturing</t>
+          <t>Adv. biomanufacturing</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>General contractor on site; physical construction start on Phase 1</t>
+          <t>Expansion of committed project</t>
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>14500</v>
+        <v>500</v>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Projected</t>
+          <t>Projected (site total)</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>$89,340 avg (stated, 2025)</t>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated (2025)</t>
+          <t>N/A — stated</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>$4.7B</t>
+          <t>~$2.0B</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period 2028-2037 (unchanged)</t>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>HITT Contracting confirmed as general contractor on the NC Composite Center (NC3, 150,000 sf); construction physically underway beyond the June groundbreaking ceremony; first deliveries described as 'early 2030s', full run-rate 'late 2030s' — consistent with the 2037 full-target timeline</t>
+          <t>Operational by 2029</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>https://www.hitt.com/news-hub/jetzero-greensboro-groundbreaking/</t>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>High (facts); Low (timeline)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>Aerospace mfg + eng.</t>
+          <t>Adv. biomanufacturing</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
@@ -7040,24 +6937,24 @@
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>Same long-run scale; near-term construction-phase hiring (GC + subcontractors) is a modest, earlier housing-demand signal ahead of the 2028-2029 direct-hire ramp.</t>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
         <is>
-          <t>Trade press (HITT, ENR, CompositesWorld, Aviation Week) confirms an active general contractor building the first facility — more concrete than a ceremonial groundbreaking alone; no new JDIG amendment found this cycle.</t>
+          <t>No new in-window milestone found this cycle; the sole dated milestone (2026-01-20 investment doubling) sits exactly at this week's window boundary (2026-01-20 to 2026-07-20) — still inclusive, but flagged as at risk of aging out of the window next cycle absent a new update.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
@@ -7068,12 +6965,12 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Holly Springs / SW Wake</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -7083,70 +6980,70 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Genentech — biomanufacturing expansion</t>
+          <t>JetZero — aerospace plant (groundbreaking held; hiring pushed further)</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Aerospace / advanced manufacturing</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Expansion of committed project</t>
+          <t>Groundbreaking ceremony + JDIG base-period amendment</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>500</v>
+        <v>14500</v>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>Projected (site total)</t>
+          <t>Projected</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>~$119,833 avg (stated, 2025 tranche)</t>
+          <t>$89,340 avg (stated, 2025)</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>N/A — stated</t>
+          <t>N/A — stated (2025)</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>~$2.0B</t>
+          <t>$4.7B</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; base period shifted to 2028-2037</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>Operational by 2029</t>
+          <t>Groundbreaking held 2026-06-15; zero jobs still projected for 2027; hiring ramp begins 2028-2029 (3,020 jobs by end 2029); full 14,500+ target due by 2037; Governor Stein signed the FY2026-27 state budget on 2026-07-07, releasing the previously-frozen $133.9M JDIG-linked infrastructure allocation (on top of $118.1M already allotted) — company communications called it 'all systems go'</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+          <t>https://www.carolinajournal.com/state-budget-allocates-133-9m-for-delayed-jetzero-project/</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (facts); Low (timeline)</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>Adv. biomanufacturing</t>
+          <t>Aerospace mfg + eng.</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
@@ -7156,40 +7053,40 @@
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+          <t>Same long-run scale, but full-target timeline has slipped a further year (2036-&gt;2037); construction is real and tangible even as hiring pushes out.</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>No new in-window milestone found this cycle.</t>
+          <t>+1 for confirmed release of state incentive funding (an execution-certainty signal), though the hiring-ramp timeline itself is unchanged from last cycle.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeated</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / Plaza Midwood</t>
+          <t>Durham / Morrisville</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Durham &amp; Wake</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -7199,30 +7096,30 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+          <t>Novartis — API mfg building (investment increase)</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Automotive (EV) — corporate HQ</t>
+          <t>Adv. mfg / API production</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Preliminary land-development plan filed for 2nd office building</t>
+          <t>New facility (unchanged)</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Projected (365 relocating + 835 new local hires)</t>
+          <t>Projected (part of pre-window deal)</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>$153,978 avg (stated)</t>
+          <t>$111,161 avg (stated)</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
@@ -7232,166 +7129,50 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>$206.9M</t>
+          <t>~$991M (incl. $220M API building)</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+          <t>Part of original $771M package incentives</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>1st ~150,000 sf building move-in ~mid-2026; 2nd building's land-development plan filed March 2026, construction start targeted H1 2027</t>
+          <t>Facility opening targeted 2027-2028</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>Med (facts High; milestone stage early)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
         <is>
-          <t>Corporate HQ / professional</t>
+          <t>Adv. mfg / API production</t>
         </is>
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Suburban</t>
         </is>
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
-        <is>
-          <t>Reclassified from Excluded (2026-07-13 report cited 'no confirmed in-window milestone') after identifying the March 2026 land-development filing for a 2nd office building tied explicitly to Scout's HQ job growth. Distinct project from the Blythewood, SC EV assembly plant (also separately ranked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Repeated</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Durham / Morrisville</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Durham &amp; Wake</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Novartis — API mfg building (investment increase)</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Adv. mfg / API production</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>New facility (unchanged)</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>700</v>
-      </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>Projected (part of pre-window deal)</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>$111,161 avg (stated)</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>N/A — stated</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>~$991M (incl. $220M API building)</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>Part of original $771M package incentives</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>Facility opening targeted 2027-2028</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
-        </is>
-      </c>
-      <c r="T32" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>Adv. mfg / API production</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>Suburban</t>
-        </is>
-      </c>
-      <c r="W32" s="6" t="inlineStr">
-        <is>
-          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
-        </is>
-      </c>
-      <c r="X32" s="6" t="inlineStr">
         <is>
           <t>No new in-window milestone found this cycle.</t>
         </is>
@@ -7408,7 +7189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10962,7 +10743,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -11024,7 +10805,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -11086,7 +10867,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -11148,7 +10929,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -11210,7 +10991,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -11272,7 +11053,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -11334,7 +11115,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -11396,7 +11177,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -11458,7 +11239,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -11520,7 +11301,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -11582,7 +11363,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -11644,7 +11425,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -11706,7 +11487,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -11768,7 +11549,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -11830,7 +11611,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -11892,7 +11673,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -11954,7 +11735,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -12016,7 +11797,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -12078,7 +11859,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -12140,7 +11921,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -12202,7 +11983,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -12264,7 +12045,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -12326,7 +12107,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -12388,7 +12169,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -12450,7 +12231,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -12512,7 +12293,7 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -12574,7 +12355,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -12636,7 +12417,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -12698,7 +12479,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -12760,7 +12541,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -12822,7 +12603,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -12884,7 +12665,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -12946,7 +12727,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -13008,7 +12789,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -13070,7 +12851,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -13132,7 +12913,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -13194,7 +12975,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -13256,7 +13037,7 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -13318,7 +13099,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -13380,7 +13161,7 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -13442,7 +13223,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -13504,17 +13285,17 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Cherokee Co. / Blacksburg</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Cherokee</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -13524,12 +13305,12 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>SC Ports Authority — Leatherman Terminal (PAUSE STATUS UNCONFIRMED)</t>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>400 direct + ~1,200 indirect</t>
+          <t>~490</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -13539,44 +13320,44 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>TOP PRIORITY GAP: as of 2026-07-13, SC Ports announced it would pause ALL Leatherman operations starting 2026-08-01 (today is 2026-08-10); this cycle could not confirm whether the pause took effect or any reopening timeline — not rechecked (SC Midlands/Lowcountry gap)</t>
+          <t>Still just under 500 jobs; no threshold-crossing update found this cycle (high-priority check)</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25 (last verified)</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>High (risk, not rechecked)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Cherokee Co. / Blacksburg</t>
+          <t>Orangeburg / I-26</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Cherokee</t>
+          <t>Orangeburg</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -13586,37 +13367,37 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>USA Rare Earth — rare-earth magnet plant</t>
+          <t>Ferrara Candy — groundbreaking held</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>~490</t>
+          <t>1,000 (10 yr)</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>$1.2B</t>
+          <t>$675M</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>$24.50-$63/hr (stated; unchanged)</t>
+          <t>Not disclosed; confectionery = workforce-tier</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>Still just under 500 jobs; commissioning now framed as targeting 2028; no threshold-crossing update</t>
+          <t>No new milestone since May 2026 groundbreaking; first lines targeted Q1 2029</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
+          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -13628,17 +13409,17 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg (former Kohler plant)</t>
+          <t>Laurens Co.</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -13648,99 +13429,99 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>NorthMark "Project Moc-1" — AI/HPC data center</t>
+          <t>Suniva — solar-cell plant</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>~150 FT at full operation</t>
+          <t>564</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>$2.8B</t>
+          <t>$350M</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Stated $23-$53/hr = workforce-tier</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>SCDES public-comment period on the air-construction permit closed 2026-07-31; approval/denial outcome could not be determined this cycle</t>
+          <t>No update found this cycle; operations targeted spring/summer 2027</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31 (comment period close)</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/05/01/spartanburg-co-residents-say-they-were-misled-about-data-center-project/</t>
+          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
         <is>
-          <t>Med (outcome pending)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Wake County (statewide)</t>
+          <t>Columbia / BullStreet</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Richland</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>WakeMed / Atrium Health — proposed merger</t>
+          <t>AMAROK — new HQ (perimeter security)</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>3,300 (statewide, 5 yr)</t>
+          <t>296</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>$2.0B (Wake Co. portion)</t>
+          <t>$69M</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>Vote delayed again: public hearing set 2026-08-17; earliest possible Commissioners vote now 2026-09-08 (past this window); commissioners reportedly 'feeling much better' after private briefings, drawing transparency criticism</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>https://www.northcarolinahealthnews.org/2026/08/07/wakemed-atrium-leaders-brief-wake-commissioners/</t>
+          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
@@ -13752,12 +13533,12 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Greensboro / PTI Airport</t>
+          <t>Greensboro</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -13772,17 +13553,17 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+          <t>Lumentum — AI/data-center optics</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>&lt;=500 currently; must hit 500 by 12/31/26</t>
+          <t>~400</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>~$50M (hangar)</t>
+          <t>Hundreds of millions</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
@@ -13792,39 +13573,39 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>RISK ESCALATING FURTHER: hangar still largely idle; only ~19 open roles as of Aug. 2026 — nowhere near a 500-employee surge with the deadline now under 5 months away</t>
+          <t>Ribbon-cutting/opening ceremony held late April 2026 for the 240,000 sq ft facility; production ramp still targeted mid-2028</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>2026-08 (job-posting check)</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+          <t>https://myfox8.com/news/north-carolina/greensboro/lumentum-holdings-opens-new-manufacturing-facility-in-greensboro/</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
-          <t>High (risk)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Rowan County</t>
+          <t>Hendersonville</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -13834,37 +13615,37 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters (formerly code-named "Project Rack" — identity now confirmed)</t>
+          <t>BorgWarner — vertical-integration expansion</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>200+ (state figure; county vote cited 258)</t>
+          <t>378</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>$41M</t>
+          <t>$100M</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>$57,351 avg (stated)</t>
+          <t>$67,047 avg (stated; below $100k)</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>Company identity officially confirmed via Governor Stein announcement 2026-07-17; Q1 2027 ops start still targeted</t>
+          <t>Now corroborated via official NC Commerce/Governor press releases dated 2026-05-26, resolving prior cycle's uncorroborated flag</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
@@ -13876,17 +13657,17 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Charlotte (CLT airport)</t>
+          <t>Asheville / Arden</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -13896,121 +13677,121 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Averitt — logistics campus</t>
+          <t>Eaton — Low Voltage Assembly expansion</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>~230 (revised from 211)</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>$81,769 avg (stated)</t>
+          <t>'high-tech, high-wage' but figure Not disclosed (Inferred mid-$60k-$80k)</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Jobs figure revised in some coverage; Planning Commission recommended rezoning 6-0 on 2026-04-13; final City Council vote not confirmed as completed</t>
+          <t>Eaton recruiting at WNC Career Expo 2026-04-16; confirmed as 7th Helene-recovery manufacturer expansion</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/04/averitt-s-230-job-truck-campus-poised-to-rev-up-clt-s-cargo-corridor/</t>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (jobs); Low (wage)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>York Co.</t>
+          <t>Charlotte / Raleigh / Rural Hall</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Multi</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>QTS "Project Cobra" — data-center campus</t>
+          <t>Siemens Energy — $421M NC expansion</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>~200 FTE (+~1,000 constr.)</t>
+          <t>500 (statewide)</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>up to $8B</t>
+          <t>$421M</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>~$80k median (stated)</t>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>York County's 9-month data-center moratorium passed final reading 6-0 on 2026-07-13; QTS's 9 buildings have vested site-plan rights predating the ordinance and are unaffected</t>
+          <t>No update found this cycle; Mecklenburg-specific allocation for this tranche remains unclear (conflated with a 2024 tranche in some coverage)</t>
         </is>
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrhi.com/2026/07/york-county-council-approves-nine-month-data-center-moratorium-214184</t>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Med (totals uncertain)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Burlington / Alamance-Guilford line</t>
+          <t>Raleigh / Wendell / Knightdale</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Alamance</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -14020,37 +13801,37 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>NEW — Ahold Delhaize USA (Food Lion parent) — distribution center</t>
+          <t>Siemens AG — power devices for AI/data centers</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>500-505</t>
+          <t>350</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>$860M</t>
+          <t>part of $165M</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>Groundbreaking held 2026-02-16 (in-window); construction underway, opening targeted 2029</t>
+          <t>New 101,000 sq ft Wendell facility coming online July 2026; Knightdale targeting 100 jobs by end 2026; expanded Wendell campus (+200 jobs) by 2028</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/02/16/3238762/0/en/Ahold-Delhaize-USA-Breaks-Ground-on-New-860-Million-Distribution-Center-in-Burlington-N-C.html</t>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr">
@@ -14062,17 +13843,17 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Pender / New Hanover</t>
+          <t>Kernersville</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Pender (+New Hanover)</t>
+          <t>Forsyth</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -14082,210 +13863,210 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>NEW — Amazon — robotics fulfillment center</t>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>1,000+</t>
+          <t>150+</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>$350M</t>
+          <t>$70M</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>Opening targeted Q3 2026; largest Amazon site in NC; county allocation between Pender/New Hanover uncertain</t>
+          <t>Reaffirmed 2026-01-28 via White House-linked event; construction underway on west campus, facility slated to open within the next year</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>2026 (Q3 opening)</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/amazon-adding-1000-jobs-at-new-pender-county-center/</t>
+          <t>https://greensboro.com/news/local/business/development/article_f8077494-ba1d-526b-a82a-9d8425f0acbe.html</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>York Co.</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>York</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>NEW — Aspida Financial Services — HQ expansion</t>
+          <t>QTS "Project Cobra" — data-center campus</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>1,000 (proj.)</t>
+          <t>~200 FTE (+~1,000 constr.)</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>$28M+</t>
+          <t>up to $8B</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>$137,288 avg (stated)</t>
+          <t>~$80k median (stated)</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>Meets Ranked-tier job/wage bar, but the real-estate commitment (Dec. 2025 lease) predates the window; a Q4 2026 move-in is the likely next in-window milestone</t>
+          <t>York County's nine-month data-center moratorium received FINAL passage 2026-07-14 (6-0); it bars new site plans/special exceptions/CUPs for data centers in unincorporated York Co. through ~April 2027 but explicitly exempts projects with vested rights — QTS's under-construction buildings are understood to be unaffected</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>2025-12 (lease, pre-window)</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>https://rebusinessonline.com/drawbridge-realty-signs-aspida-to-89770-sf-office-lease-in-durham/</t>
+          <t>https://www.wrhi.com/2026/07/york-county-council-approves-nine-month-data-center-moratorium-214184</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
-          <t>High (facts); pre-window</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Wake Co. (aggregate)</t>
+          <t>Berkeley / Dorchester</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Berkeley &amp; Dorchester</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>County jobs pipeline (EDGE 7)</t>
+          <t>Google — data-center expansion</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>~11,000 (pipeline)</t>
+          <t>~160 apprentices (FTE n/d)</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>$11B</t>
+          <t>$9B</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>Mixed (office-skewed)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>Reconfirmed; no material change to the aggregate figure</t>
+          <t>No new in-window milestone found this cycle; original Oct. 2025 announcement remains the latest news</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High (capex)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / SouthPark</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Chase — new office (1,000-employee bldg)</t>
+          <t>Siemens Smart Infrastructure</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>400 new by 2028</t>
+          <t>~150</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H111" s="6" t="inlineStr">
-        <is>
-          <t>~$105k Estimated/Inferred</t>
-        </is>
-      </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
           <t>No update found this cycle</t>
@@ -14293,12 +14074,12 @@
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
@@ -14310,17 +14091,17 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / North Hills</t>
+          <t>Hamlet</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -14330,54 +14111,54 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Ralliant Corp. — global HQ launch</t>
+          <t>AWS/Amazon — AI/cloud campus</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>$2.1M</t>
+          <t>$10B</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>$170k-$189k avg (stated)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>HQ officially opened 2026-03-05 with ~150 staff on-site, hiring toward the 180-job commitment through 2029</t>
+          <t>Still unverified; outside this cycle's five assigned research regions — needs direct confirmation next cycle</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>https://investors.ralliant.com/news-events/press-releases/detail/121/ralliant-opens-global-headquarters-in-raleigh-north-carolina</t>
+          <t>https://www.aboutamazon.com/</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low (needs verification)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / North Hills</t>
+          <t>Wake Co. (aggregate)</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -14392,59 +14173,59 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>NEW — Jewelers Mutual Group</t>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>~11,000 (pipeline)</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>$5.85M</t>
+          <t>$11B</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>$169,592 avg (stated)</t>
+          <t>Mixed (office-skewed)</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>High wage but only 200 jobs (Watch floor); in-window office-opening date unconfirmed</t>
+          <t>RECONCILED this cycle: the previously-flagged second figure (~30 projects/8,000-10,800 jobs/$5.6B) is confirmed to be the closed, prior EDGE 6 campaign (concluded ~Sept 2024) — sequential, not duplicative, with the current $11B/11,000-job EDGE 7 pipeline</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>2024-08-13 (orig. announcement)</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/jewelers-mutual-coming-to-raleigh-with-200-jobs-averaging-169k/</t>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Garner</t>
+          <t>Charlotte / SouthPark</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -14454,59 +14235,59 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>NEW — Gregory Poole Equipment Co. — HQ relocation</t>
+          <t>JPMorgan Chase — new office (1,000-employee bldg)</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>500+ (5 yr)</t>
+          <t>400 new by 2028</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>$347M</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
+          <t>~$105k Estimated/Inferred (job-posting range)</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>500+ jobs but company-wide wage clearly sub-$100k; no 2026 groundbreaking found</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16 (pre-window)</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>https://www.cbs17.com/news/local-news/wake-county-news/gregory-poole-equipment-caterpillar-dealer-moving-headquarters-to-garner/</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Siler City</t>
+          <t>Charlotte (CLT airport)</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -14516,59 +14297,59 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Wolfspeed — silicon-carbide fab</t>
+          <t>Averitt — logistics campus</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>1,800 (proj.)</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>$5.0B</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>$77,753 avg (stated)</t>
+          <t>$81,769 avg (stated)</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>Post-bankruptcy ramp remains 'measured/disciplined'; completed 150mm-&gt;200mm transition; received ~$700M in Section 48D tax refunds; no new Chatham headcount figures</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>2026-05-05 (Q3 earnings call)</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>https://mgrid.org/2026/04/22/wolfspeeds-200mm-silicon-carbide-wafer-capacity-is-the-single-biggest-2026-bottleneck-on-solid-state-transformer-production/</t>
+          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Rowan County</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -14578,59 +14359,59 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Vulcan Elements — magnet factory</t>
+          <t>American Eagle Outfitters Inc. — "Project Rack" distribution hub (identity confirmed)</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>1,000 (proj.)</t>
+          <t>200+ (per 2026-07-17 announcement; county incentive filing cited 258)</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>$918.4M</t>
+          <t>$41M</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>$81,932 avg (stated)</t>
+          <t>$57,351 avg for ~70 skilled roles (stated); bulk of the 200+ workforce likely lower (Estimated/Inferred)</t>
         </is>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>JCC's Golden LEAF-funded training pipeline now active: train-the-trainer begins summer 2026; production-employee training runs Aug. 2026-Dec. 2030</t>
+          <t>Company identity confirmed 2026-07-17: American Eagle Outfitters Inc., $41M, 472,890 sq ft distribution hub at Innovation Logistics Center, 1415 Peeler Road, Salisbury; Q1 2027 ops start unchanged</t>
         </is>
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>2026 (training start)</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>https://www.johnstoncc.edu/news/vulcangoldenleafgrant.php</t>
+          <t>https://governor.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Multi-site NC incl. Wilmington</t>
+          <t>Rowan / Kannapolis</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>New Hanover +</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -14640,37 +14421,37 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Amazon-Corning — fiber-optics partnership</t>
+          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>1,000 (multi-site, unallocated)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Multi-billion (undisclosed NC-specific)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
+          <t>$55k-$150k range (DHL postings)</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>No update; per-site Wilmington allocation still not broken out</t>
+          <t>No update found this cycle; jobs still undisclosed</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
+          <t>https://www.salisburypost.com/2026/05/02/not-a-data-center-google-leases-rowan-county-side-kannapolis-industrial-site/</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
@@ -14682,17 +14463,17 @@
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Arden</t>
+          <t>Raleigh / North Hills</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -14702,59 +14483,59 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+          <t>Ralliant Corp. — global HQ launch</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>$285M</t>
+          <t>$2.1M</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>$62,413 avg (stated)</t>
+          <t>$170k-$189k avg (stated)</t>
         </is>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>On track: equipment arrival end 2026, first parts mid-2027</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>2026 (timeline confirm)</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county/</t>
+          <t>https://www.wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Asheville / Arden</t>
+          <t>Siler City</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Buncombe</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -14764,59 +14545,59 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Eaton — Low Voltage Assembly expansion</t>
+          <t>Wolfspeed — silicon-carbide fab</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,800 (proj.)</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$5.0B</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
+          <t>$77,753 avg (stated)</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>No update found; company now employs ~1,500 across Buncombe sites</t>
+          <t>Post-bankruptcy ramp described by the company as 'more measured/disciplined' — original full-occupancy March 2026 target appears to have slipped; SiC crystal growth/wafer shipments to Mohawk Valley (NY) underway</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-Q1 (10-Q)</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000895419/000089541926000030/wolf-20260329.htm</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>High (jobs); Low (wage)</t>
+          <t>Med (financial distress clouds trajectory)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Hendersonville</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -14826,59 +14607,59 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>BorgWarner — vertical-integration expansion</t>
+          <t>Vulcan Elements — magnet factory</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>1,000 (proj.)</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>$100M</t>
+          <t>$918.4M</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>$67,047 avg (stated; below $100k)</t>
+          <t>$81,932 avg (stated)</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>No update found this cycle</t>
+          <t>'Hundreds of workers already on site' per current coverage; JCC training cohorts begin summer 2026 as originally scheduled</t>
         </is>
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-summer (training start)</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+          <t>https://www.wral.com/sponsored/fifth-third-bank/the-next-industrial-revolution-how-vulcan-elements-makes-nc-the-backbone-of-vital-global-market/</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Greensboro</t>
+          <t>Wake County (statewide)</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -14888,17 +14669,17 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>Lumentum — AI/data-center optics</t>
+          <t>WakeMed / Atrium Health — proposed merger</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>~400</t>
+          <t>3,300 (statewide, 5 yr)</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>Hundreds of millions</t>
+          <t>$2.0B (Wake Co. portion)</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -14908,17 +14689,17 @@
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>No update found; production still targeted mid-2028</t>
+          <t>Vote still not scheduled as of 2026-07-20; the 90-day delay from 2026-05-04 points to early August 2026; opposition continues (Brown University School of Public Health cost-impact report, community groups)</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-04 (delay announced)</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>https://www.areadevelopment.com/newsitems/4-14-2026/lumentum-greensboro-north-carolina.shtml</t>
+          <t>https://www.wral.com/news/local/wakemed-atrium-merger-costs-opposition-july-2026/</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
@@ -14930,17 +14711,17 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Kernersville</t>
+          <t>Greensboro / PTI Airport</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Forsyth</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -14950,59 +14731,59 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>John Deere — excavator plant (relocating from Japan)</t>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>150+</t>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>$70M</t>
+          <t>~$50M (hangar, existing)</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Inferred skilled-mfg)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>Reaffirmed Jan. 2026; construction underway on west campus</t>
+          <t>No positive or negative movement found this cycle; hangar still largely idle, and the Dec. 31, 2026 500-employee deadline is now roughly five months away with no confirmed hiring progress</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>https://greensboro.com/news/local/business/development/article_f8077494-ba1d-526b-a82a-9d8425f0acbe.html</t>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High (risk)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Asheboro</t>
+          <t>Multi-site NC incl. Wilmington</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>New Hanover +</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -15012,37 +14793,37 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Environmental Air Systems</t>
+          <t>Amazon-Corning — fiber-optics partnership</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,000 (multi-site, unallocated)</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>$20M</t>
+          <t>Multi-billion (undisclosed NC-specific)</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>$55,133 avg (stated)</t>
+          <t>Avg salary &gt;$65,000 (newly disclosed; sub-$100k)</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>No update found despite targeted searches</t>
+          <t>Wage now disclosed (exceeds $65k) but still sub-$100k; per-site (incl. Wilmington-specific) job allocation still not broken out</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>2025-11-25 (orig.)</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+          <t>https://www.corning.com/worldwide/en/about-us/news-events/news-releases/2026/06/amazon-announces-agreement-with-corning-to-boost-us-fiber-optics-manufacturing-creating-1000-advanced-manufacturing-jobs-in-north-carolina.html</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr">
@@ -15054,17 +14835,17 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Wilmington</t>
+          <t>Arden</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>New Hanover</t>
+          <t>Buncombe</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -15074,54 +14855,54 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>325</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>Not itemized</t>
+          <t>$285M</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$62,413 avg (stated)</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>GNF4 fabrication underway; company plans $50M+ further investment this year and next; jobs still undisclosed</t>
+          <t>On track: first equipment arrival end of 2026, first parts production mid-2027, hiring ramp begins mid-2027</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>2026 (ongoing)</t>
+          <t>2026 (equipment arrival timeline)</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
+          <t>https://www.flightglobal.com/engines/2026/04/rtx-says-gtf-groundings-are-coming-down-thanks-to-maintenance-ramp/</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr">
         <is>
-          <t>Low-Med</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Asheboro</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -15136,59 +14917,59 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
+          <t>Environmental Air Systems</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>5,100 (proj. total); 3,000+ employed</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>$13.9B</t>
+          <t>$20M</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>$62,234 avg (stated; below $100k)</t>
+          <t>$55,133 avg (stated)</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>Grand opening reconfirmed with 4 of 14 planned production lines operating; $10B additional 5-yr investment pledge reconfirmed</t>
+          <t>No update found this cycle despite targeted searches</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>2025-11 (reconfirmed 2026)</t>
+          <t>2025-11-25 (orig.)</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>https://rebusinessonline.com/toyota-begins-production-at-13-9b-battery-plant-in-north-carolina-pledges-additional-10b-investment-over-next-five-years/</t>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr">
         <is>
-          <t>Med-High</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Rowan / Kannapolis</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>New Hanover</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -15198,7 +14979,7 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Google (via DHL) — 730k sq ft warehouse lease</t>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
@@ -15208,27 +14989,27 @@
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>$55k-$150k range (DHL postings)</t>
-        </is>
-      </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>No update; jobs still undisclosed</t>
+          <t>GNF4 fuel fabrication began early 2026; lead-use assemblies scheduled for deployment in commercial reactors during 2026 — genuine in-window production milestones, jobs still undisclosed</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026 (fabrication start)</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>https://www.wbtv.com/2026/04/29/google-leases-massive-facility-near-rowan-cabarrus-county-line/</t>
+          <t>https://www.world-nuclear-news.org/articles/global-nuclear-fuel-unveils-new-gnf4-product</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr">
@@ -15240,223 +15021,223 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>RTP</t>
+          <t>Woodruff / Spartanburg Co.</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Apple — RTP campus extension (incentive-timeline extension)</t>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>3,000 originally projected; only ~600-990 added to date</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>$552M-$1B+ (paused)</t>
+          <t>$40-60M</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>$187k avg (stated, original 2021 award)</t>
+          <t>Not disclosed (Estimated/Mixed)</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>No active construction found; permits obtained but final building-approval paperwork not yet resubmitted to Wake County</t>
+          <t>Manufacturing-operations start slipped from 2026 to early 2027; HQ campus itself already opened</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>2026 (ongoing)</t>
+          <t>~2026 (HQ opening); early 2027 (mfg slip)</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>https://www.cbs17.com/news/local-news/wake-county-news/construction-on-apple-campus-set-to-start-2026-new-documents-show-plans-for-traffic/</t>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / Raleigh / Rural Hall</t>
+          <t>Gray Court</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Siemens Energy — $421M NC expansion</t>
+          <t>Aptiv Services US — Connexial Center</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>500 (statewide)</t>
+          <t>277</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>$421M</t>
+          <t>$120.8M</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>No update found; one unverified headline references a possible 2nd Rural Hall (Forsyth) expansion — flagged for priority recheck</t>
+          <t>No update found this cycle</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr">
         <is>
-          <t>Med (totals uncertain)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Raleigh / Wendell / Knightdale</t>
+          <t>Easley (Anderson/Pickens border)</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>Siemens AG — power devices for AI/data centers</t>
+          <t>Signature Foods USA</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>part of $165M</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>Breakdown clarified (100 Knightdale by YE2026; 50 new + 200 existing Wendell by 2028); new Wendell facility's online status unconfirmed</t>
+          <t>Operations confirmed online as of April 2026</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Hamlet</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>AWS/Amazon — AI/cloud campus</t>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>$10B</t>
+          <t>$500M (valuation, not capex)</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -15466,39 +15247,39 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>Still unverified; outside all five assigned research regions again this cycle</t>
+          <t>No update on headcount found this cycle</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>verify</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>https://www.aboutamazon.com/</t>
+          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr">
         <is>
-          <t>Low (needs verification)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg / I-26</t>
+          <t>North Charleston</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Orangeburg</t>
+          <t>Charleston</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -15508,59 +15289,59 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Ferrara Candy — groundbreaking held</t>
+          <t>Boeing 787 — production-rate ramp</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>1,000 (10 yr)</t>
+          <t>1,000 (unchanged)</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>$675M</t>
+          <t>$1.0B (existing)</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; confectionery = workforce-tier</t>
+          <t>Estimated/Inferred mixed ($54-64k assemblers; eng. likely higher)</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward — first lines still targeted Q1 2029</t>
+          <t>Rate confirmed holding steady at 8/month as of the Farnborough Airshow (mid-July 2026); 10/month target reaffirmed 'over the next year' — consistent with, not accelerating beyond, prior framing</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20 (last verified)</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
+          <t>https://leehamnews.com/2026/07/16/bca-riding-recovery-momentum-into-farnborough-air-show/</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr">
         <is>
-          <t>High (not rechecked)</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Columbia / BullStreet</t>
+          <t>North Charleston</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Richland</t>
+          <t>Charleston</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -15570,59 +15351,59 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>AMAROK — new HQ (perimeter security)</t>
+          <t>SC Ports Authority — Leatherman Terminal Phase 2 (OPERATIONS PAUSED)</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>400 direct + ~1,200 indirect (unchanged projection)</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>$69M</t>
+          <t>$1.2B (terminal, existing)</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+          <t>Not disclosed (Estimated mixed, some 6-figure specialist roles)</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
+          <t>No reversal found; pause remains on track for Aug. 1, 2026 start (~5% of container volume / 5 weekly MSC calls affected); cargo shifting to Wando Welch/North Charleston terminals; no operations-resumption timeline given</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>2026-03-03 (last verified)</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/columbia/business/columbia-sc-bullstreet-amarok-headquarters/article_73ea5904-fe8c-4048-b0a3-10417d1af35e.html</t>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr">
         <is>
-          <t>High (not rechecked)</t>
+          <t>High (risk)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>North Charleston</t>
+          <t>Goose Creek</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Berkeley</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -15632,121 +15413,121 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>Boeing 787 — production-rate ramp</t>
+          <t>HII (Newport News Shipbuilding) — 1-yr anniversary</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>1,000 (unchanged)</t>
+          <t>~250 (estimate, not re-confirmed)</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>$1.0B (existing)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mixed ($54-64k assemblers; eng. likely higher)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
+          <t>One-year operations anniversary reached 2026-01-22; company reports exceeding production targets, but no updated job-count figure surfaced</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27 (last verified)</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/2026/01/27/boeing-looks-to-build-on-momentum-at-sc-dreamliner-plant/</t>
+          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr">
         <is>
-          <t>Med (not rechecked)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Goose Creek</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Berkeley</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>HII (Newport News Shipbuilding) — 1-yr anniversary</t>
+          <t>Toyota Battery Manufacturing NC (TBMNC) — EV/hybrid battery megaplant</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>~250 (estimate, not re-confirmed)</t>
+          <t>5,100 (proj. total); 3,000+ now employed</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$13.9B</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>$62,234 avg (stated; below $100k)</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
+          <t>NEW to Watch: employment crossed 3,000+ workers (Feb 2026 milestone); all-EV battery line targeted to launch later 2026, plug-in hybrid line mid-2027; scale of hiring velocity in a rural county may pressure workforce housing despite sub-$100k wage</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22 (last verified)</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>https://www.live5news.com/2026/01/22/defense-provider-celebrates-one-year-operations-lowcountry/</t>
+          <t>https://www.wfmynews2.com/article/news/local/major-milestone-over-3000-people-now-work-at-the-toyota-battery-plant/83-b192b700-91b7-42f4-837e-33d0c01ee96e</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr">
         <is>
-          <t>Low (not rechecked)</t>
+          <t>Med-High</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Berkeley / Dorchester</t>
+          <t>Spartanburg (former Kohler plant)</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Berkeley &amp; Dorchester</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -15756,17 +15537,17 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>Google — data-center expansion</t>
+          <t>NorthMark Strategies "Project Moc-1" — AI/HPC data center</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>~160 apprentices (FTE n/d)</t>
+          <t>~150 FT at full operation (revised up from ~27); 400-600 temporary construction</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>$9B</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -15776,39 +15557,39 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (SC Midlands/Lowcountry gap); carried forward unchanged</t>
+          <t>SCDES air-permit comment period remains open through 2026-07-31; residents and the SC Environmental Law Center filed a lawsuit challenging the county's 'minor development' approval (hearing scheduled 2026-07-30 in Columbia); Spartanburg County Council separately gave first-reading approval to a one-year moratorium on new data-center proposals</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>2025-10-13 (last verified)</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+          <t>https://www.foxcarolina.com/2026/07/08/lawsuit-targets-spartanburg-county-data-center-project-demands-public-planning-review/</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr">
         <is>
-          <t>High (capex, not rechecked)</t>
+          <t>Med (contested/evolving; litigation adds new risk)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -15818,121 +15599,121 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Siemens Smart Infrastructure</t>
+          <t>GE Vernova — gas turbine mfg (AI/data-center power supply chain)</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>~150</t>
+          <t>650 total planned; ~200 hired 2025, ~300 more targeted by end 2026</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>$165M</t>
+          <t>$160M (Greenville); part of $600M multi-site plan</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Estimated/Inferred mixed — production/technician roles ~$45-56k; specialist/eng. roles $91k-$226k (Glassdoor); bulk of new hires likely sub-$100k</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
+          <t>NEW to Watch: in-window (2026-06-27) hiring-ramp confirmation; original Jan-2025 investment announcement was pre-window</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18 (last verified)</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr">
         <is>
-          <t>Med (not rechecked)</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Woodruff / Spartanburg Co.</t>
+          <t>RTP</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>AIRSYS Cooling Technologies — global HQ</t>
+          <t>Apple — RTP campus extension (incentive-timeline extension)</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>$40-60M</t>
+          <t>$552M-$1B+ (paused)</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed (Estimated/Mixed)</t>
+          <t>$187k avg (stated, original 2021 award)</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
+          <t>NEW to Watch: NC Economic Investment Committee granted a four-year extension on hiring/investment timelines (April 2026) restarting the 2021 deal (up to $845M in potential tax benefits if targets met); no active construction found</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13 (last verified)</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>https://www.airsysnorthamerica.com/</t>
+          <t>https://www.carolinajournal.com/apple-delays-construction-on-552-million-rtp-campus/</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr">
         <is>
-          <t>Medium (not rechecked)</t>
+          <t>Low-Med (long-delayed, no active construction)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Gray Court</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -15942,59 +15723,59 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Aptiv Services US — Connexial Center</t>
+          <t>Isuzu North America Corp. — production facility (medium-duty trucks)</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>700+</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>$120.8M</t>
+          <t>$280M</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Estimated/Inferred sub-$100k (Assembly Operator postings $52k-$72k; Quality Eng. $66k-$85k)</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
+          <t>$283M JBIC/MUFG construction loan disbursed 2026-06-30; direct-hire event for 150+ positions held 2026-07-08 at Greenville Tech; production starts 2027, capacity 50,000 units/yr by 2030</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20 (last verified)</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
+          <t>https://www.automotiveworld.com/news/isuzu-secures-us283m-loan-for-south-carolina-plant/</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr">
         <is>
-          <t>High (not rechecked)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Easley (Anderson/Pickens border)</t>
+          <t>Fountain Inn</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -16004,59 +15785,59 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>Signature Foods USA</t>
+          <t>EPC Power Corp. — power-conversion/inverter manufacturing facility</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>Not disclosed (site-specific)</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+          <t>Estimated/Inferred sub-$100k (Mfg/Test/Eng Tech postings $47k-$66k; Production Mgr $95k-$120k)</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
+          <t>Facility opened 2026-07-15, ramping to full capacity within the month; serves AI data-center and grid-infrastructure customers</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>2026-04 (last verified)</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+          <t>https://www.foxcarolina.com/2026/07/15/epc-power-opens-facility-upstate-produce-critical-ai-data-center-technology/</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
-          <t>High (not rechecked)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Woodruff</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Spartanburg</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -16066,59 +15847,59 @@
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+          <t>BMW Group — Plant Woodruff high-voltage battery assembly</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>~300 (Woodruff-specific, part of $1.7B total)</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>$500M (valuation, not capex)</t>
+          <t>$700M (Woodruff portion of $1.7B)</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Estimated/Inferred sub-$100k (~$43,169 avg per ZipRecruiter)</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
+          <t>Completion celebrated 2026-07-01/07-02 ('Home of X' event, new BMW X5 premiere); iX5 EV production starts late 2026</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>2026-05 (last verified)</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
+          <t>https://www.press.bmwgroup.com/global/article/detail/T0458864EN/</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>Med (not rechecked)</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>West Columbia</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -16128,104 +15909,42 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>GE Vernova — gas turbine mfg (AI/data-center power supply chain)</t>
+          <t>Southern Glazer's Wine &amp; Spirits — distribution facility</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>650 total planned</t>
+          <t>500+ (stated)</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>$160M (Greenville)</t>
+          <t>$80M</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>Estimated/Inferred mixed (bulk likely sub-$100k)</t>
+          <t>Not disclosed; Estimated/Inferred sub-$100k (warehouse/distribution roles typically $35k-$55k)</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>Not rechecked this cycle (Upstate SC research budget exhausted); carried forward unchanged</t>
+          <t>412,500 sq ft facility on 85 acres opened 2026-02-10/02-11 (originally planned fall 2026, opened early)</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27 (last verified)</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>https://scbiz.com/ge-vernova-to-invest-160m-create-650-jobs-with-greenville-expansion/</t>
+          <t>https://www.postandcourier.com/columbia/business/wine-liquor-distributor-facility-west-columbia/article_60829410-b73e-47b4-9f46-f9c2dc79317c.html</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr">
         <is>
-          <t>Med (not rechecked)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>Liberty</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>Pickens</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>FN America — 2nd production facility</t>
-        </is>
-      </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>~176</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>$33M</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>Not rechecked this cycle; third consecutive cycle with no confirmed momentum — recommend removal next cycle absent an update</t>
-        </is>
-      </c>
-      <c r="J142" s="6" t="inlineStr">
-        <is>
-          <t>2026 (last verified)</t>
-        </is>
-      </c>
-      <c r="K142" s="6" t="inlineStr">
-        <is>
-          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
-        </is>
-      </c>
-      <c r="L142" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16240,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18272,7 +17991,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -18314,7 +18033,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -18356,7 +18075,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -18398,7 +18117,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -18440,7 +18159,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -18482,7 +18201,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -18524,7 +18243,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -18566,7 +18285,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -18608,7 +18327,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -18650,7 +18369,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -18692,7 +18411,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -18734,7 +18453,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -18776,7 +18495,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -18818,7 +18537,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -18860,7 +18579,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -18902,101 +18621,101 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>VinFast (INCENTIVE TERMINATED)</t>
+          <t>Snider Fleet Solutions</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Chatham Co.</t>
+          <t>Indian Land</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>1,400 (scaled back from 7,500)</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 to 07-31</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>NEW REVERSAL: Chatham County commissioners voted to terminate the $400M incentive agreement after VinFast failed to hit its 1,750-job/~$700M-invested threshold; state separately suing to reclaim the Moncure site; no production has begun</t>
+          <t>Confirmed stale after 3 cycles tracked on Watch — all coverage traces to 2023 relocation, completed/operational by June 2023; no 2026 developments found — removed from Watch tier</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/vinfast-agreement-canceled-chatham-county-north-carolina-july-2026/</t>
+          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Kempower (JDIG CANCELLED)</t>
+          <t>FN America</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Durham/RTP</t>
+          <t>Liberty (Pickens)</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>306 (pledge; only ~100 employed)</t>
+          <t>~176</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>2026-07 (mid-July)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>NEW REVERSAL: NC Commerce cancelled Kempower's JDIG after the company missed hiring targets (156 jobs required by end-2025); company continues operating at reduced scale, citing loss of federal EV tax credits and softer US EV demand</t>
+          <t>Third consecutive quiet cycle with zero forward movement — removed from Watch tier per the report's 2-cycle flag</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/07/durham-ev-plant-slams-brakes-on-hiring-as-state-yanks-job-grant/</t>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Maersk North American HQ</t>
+          <t>Reynolds American — Tobaccoville Operations Center</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Tobaccoville (Forsyth)</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -19006,39 +18725,39 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; in-window milestone remains a 1-year hiring delay (2027-2029); rechecked this cycle, no new forward movement found</t>
+          <t>Site-specific 200-job figure is pre-window (Dec 2025); a March 2026 $3.2B multi-site reinvestment announcement is in-window but not broken out by site; wage (~$47k-$55k) well under $100k regardless</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+          <t>https://www.wfmynews2.com/article/news/local/reynolds-announces-200-new-jobs-coming-tobaccoville-operations-center/83-230e6897-51d9-4eeb-83e2-f486f0a759c3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>AdvanceTEC</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Charlotte / Ballantyne</t>
+          <t>Clayton/Smithfield (Johnston)</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -19048,39 +18767,39 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; rechecked this cycle — office headcount grew from ~350 to ~860 by April 2026, but this is continued execution of the pre-window commitment, not a new 500+ award</t>
+          <t>160 jobs below the 200-job Watch floor; wage ~$90,000 also below the $100k bar despite the in-window groundbreaking</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/03/stein-hits-ballantyne-as-citi-bets-big-on-charlotte-jobs/</t>
+          <t>https://hoodline.com/2026/07/french-cleanroom-giant-drops-160-high-paying-jobs-into-johnston-county/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Compass Datacenters</t>
+          <t>FUJIFILM Diosynth Biotechnologies expansion</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Statesville (Iredell)</t>
+          <t>Holly Springs (Wake)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -19090,123 +18809,123 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>~250</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Rechecked this cycle; no 2026 milestone found; remains pre-window</t>
+          <t>Recycled old news — original announcement dated 2024-04-11, well outside the 6-month window; no in-window update found</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://governor.nc.gov/news/press-releases/2024/04/11/fujifilm-diosynth-biotechnologies-expands-holly-springs-facility-create-one-largest-end-end-cell</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>PSA Airlines</t>
+          <t>Cielo Digital Infrastructure "Project Kingfisher"</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Charlotte (CLT)</t>
+          <t>Gaffney (Cherokee)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>~400</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Rechecked this cycle; grand opening remains the only milestone and ties to a pre-window relocation commitment</t>
+          <t>$2.1B capex but only 30 confirmed jobs — far below the 200-job Watch floor despite being described as the largest-ever Cherokee County investment</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>https://psaairlines.com/psa-airlines-celebrates-grand-opening-of-charlotte-headquarters-underscoring-economic-and-workforce-impact-across-north-carolina/</t>
+          <t>https://scdailygazette.com/briefs/cherokee-county-inks-2-1b-deal-with-data-center-developer/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>EG Group global HQ relocation</t>
+          <t>Multiple recycled Lowcountry items (Volvo Ridgeville XC60/hybrid expansion, Mercedes-Benz Ladson CKD expansion, Roper St. Francis $1.2B hospital campus)</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Berkeley/Dorchester/Charleston</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>various (2025)</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; no disclosed job count or capex for the Charlotte component</t>
+          <t>All trace to pre-window announcements (Sept 2025, Dec 2025, and June 2025 respectively) with no in-window milestone found despite active search this cycle</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>https://www.aol.com/news/scout-motors-midst-launching-charlotte-090500610.html</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Daimler Truck Financial Services USA</t>
+          <t>ProKidney — Greensboro manufacturing plant (WITHDRAWN)</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Ballantyne (Charlotte)</t>
+          <t>Greensboro (Guilford)</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -19216,39 +18935,39 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>330 (orig., never tracked)</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; sub-500; no in-window update</t>
+          <t>Company ended its pursuit of the Greensboro plant and sold the site (June 2026) — closure/withdrawal noted for completeness only; never previously tracked since it never met the qualifying bar</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://journalnow.com/news/local/business/health-care/prokidney-greensboro-manufacturing-plant/article_e77df70a-d8c9-11ef-82c8-a347d4b0b442.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Raleigh (Wake)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -19258,17 +18977,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>1,500 (claimed)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Pre-window; wage $89,769 (&lt;$100k)</t>
+          <t>Re-checked again this cycle across Barclays newsroom, NC Governor, Wake County, EDPNC, and NC Commerce — still no authoritative primary source, only recirculating non-authoritative blog/social posts</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
@@ -19280,462 +18999,42 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Albemarle "Mega-Flex" lithium plant</t>
+          <t>Frontier Scientific Solutions</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Chester Co.</t>
+          <t>Wilmington (New Hanover)</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>~80 (current)</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>2026-02 (earnings call)</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Confirmed still paused per CEO's Feb. 2026 earnings-call comments citing depressed lithium prices — no construction, engineering work stopped</t>
+          <t>Current headcount (~80) is well below even the 200-job Watch floor; CEO's 'likely exceed 500' figure is a speculative, undated future-phase projection, not a confirmed commitment — noted for context only</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>E&amp;J Gallo Winery</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Chester Co.</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Recycled 2021 news; no in-window update found</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>https://governor.sc.gov/news/2021-06/e-j-gallo-winery-establishing-new-east-coast-facility-chester-county</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Honeywell HQ</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Long-completed 2018 announcement; no relevance to the window</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>"Barclays 1,500 jobs, North Hills" (unverified)</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Raleigh (Wake)</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>1,500 (claimed)</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>Re-checked this cycle: traces to a 2024 Instagram post about existing NC card-services operations, not a 2026 relocation — still unverifiable, no authoritative source found</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>Novo Nordisk speculative Four Oaks expansion</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Johnston</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>~500 (speculative)</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>2025-10 (cancelled)</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed still cancelled after an annexation vote in Oct. 2025; also pre-window</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>Fujifilm Diosynth</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Holly Springs (Wake)</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>680 (2024 expansion)</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>Grand opening was Sept. 2025, pre-window; no in-window update found</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>Amgen (2nd facility)</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Holly Springs (Wake)</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>Pre-window; sub-500 jobs</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>Science 37</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Morrisville (Wake)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>Company being acquired/taken private (~$375M sale) — reversal-adjacent, not a growth signal</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>Snider Fleet Solutions (REMOVED from Watch)</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Indian Land (Lancaster)</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed stale 2023 item; no developments found in 3+ years despite repeated rechecks — removed from active Watch tracking this cycle</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>https://www.qcnews.com/news/u-s/lancaster-county/major-manufacturing-company-moving-to-indian-land/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Boom Supersonic "Rolls-Royce engine partnership collapse" (rumor, debunked)</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Greensboro</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>An AI-summarized search result implied this was a 2026 event; underlying sources trace to 2022 — not a current development, excluded as a data-quality catch</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>Sub-200-job items (AdvanceTEC/Clayton, Innovative Construction Group/Siler City, CITEL/Hillsborough, GMAX Industries/Forsyth, Superion/Guilford, Walmart Gaston, Fit Precast)</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Various NC</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>36-300 each</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>Below Watch floor and/or wage well under $100k regardless of window</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/03/18/amazon_facility_regional_projects_forecast_to_bring_hundreds_of_jobs_to_wilmington_area/27315</t>
         </is>
       </c>
     </row>
@@ -19750,7 +19049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -20762,7 +20061,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Fort Mill Sun — Rock Hill Council 7-0 vote</t>
+          <t>Fort Mill Sun (Rock Hill school board)</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -20772,24 +20071,24 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+          <t>https://www.fortmillsun.com/2026/07/13/</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>York Co. SC</t>
+          <t>Charlotte-metro SC (York Co.)</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Octapharma final Rock Hill City Council resolution</t>
+          <t>Octapharma — Rock Hill School Board 5-2 endorsement</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>WFAE</t>
+          <t>ABC11 / AOL / Yahoo News mirrors</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -20799,24 +20098,24 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>https://www.wfae.org/</t>
+          <t>https://abc11.com/</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Charlotte metro &amp; Triangle</t>
+          <t>NC Triangle</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Octapharma finalization; WakeMed/Atrium merger transparency coverage</t>
+          <t>AbbVie — Durham County incentive hearing</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>SC Daily Gazette</t>
+          <t>Carolina Journal (state budget)</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -20826,24 +20125,24 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>https://scdailygazette.com/</t>
+          <t>https://www.carolinajournal.com/</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>SC statewide</t>
+          <t>NC statewide</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Octapharma finalization; USA Rare Earth; SC Ports Leatherman (last verified)</t>
+          <t>JetZero — FY2026-27 budget signing, $133.9M JDIG funding release</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Hoodline</t>
+          <t>WLTX (Columbia)</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -20853,78 +20152,78 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>https://hoodline.com/</t>
+          <t>https://www.wltx.com/</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>NC (Charlotte/Triad/Triangle)</t>
+          <t>SC Midlands</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors HQ 2nd building filing; Averitt rezoning; Kempower JDIG cancellation; Novartis Morrisville API facility</t>
+          <t>Scout Motors — mid-July headcount reconfirmation</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Crosland Southeast</t>
+          <t>NC Governor's Office (Rowan)</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>company_primary</t>
+          <t>state_primary</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>https://www.croslandsoutheast.com/</t>
+          <t>https://governor.nc.gov/news/press-releases/2026/07/17/</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Charlotte NC</t>
+          <t>NC statewide</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors HQ Commonwealth development detail</t>
+          <t>American Eagle Outfitters — Rowan Co. distribution hub (Project Rack identity)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>HITT Contracting / ENR / CompositesWorld / Aviation Week</t>
+          <t>WRHI (York County moratorium)</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>trade_journal</t>
+          <t>regional_edo/journal</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>https://www.hitt.com/news-hub/jetzero-greensboro-groundbreaking/</t>
+          <t>https://www.wrhi.com/</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>National aerospace/construction</t>
+          <t>York Co. SC</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>JetZero NC3 construction-start confirmation, general contractor detail</t>
+          <t>York County data-center moratorium final passage</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>North Carolina Health News / WFAE / CBS17 / ABC11</t>
+          <t>Fox Carolina (Spartanburg litigation)</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -20934,24 +20233,24 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>https://www.northcarolinahealthnews.org/</t>
+          <t>https://www.foxcarolina.com/</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>NC Triangle</t>
+          <t>Upstate SC</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>WakeMed/Atrium merger vote-delay tracking (public hearing Aug. 17, earliest vote Sept. 8)</t>
+          <t>NorthMark Project Moc-1 lawsuit; EPC Power opening</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>rebusinessonline</t>
+          <t>Automotive World</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -20961,51 +20260,51 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>https://rebusinessonline.com/</t>
+          <t>https://www.automotiveworld.com/</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>National CRE</t>
+          <t>National automotive</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Aspida Financial Durham lease; Toyota Battery NC grand-opening detail</t>
+          <t>Isuzu North America — Piedmont SC loan/hiring event</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Johnston Community College</t>
+          <t>BMW Group press office</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>regional_edo</t>
+          <t>company_primary</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>https://www.johnstoncc.edu/</t>
+          <t>https://www.press.bmwgroup.com/</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Johnston Co. NC</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Vulcan Elements training-pipeline detail</t>
+          <t>BMW Plant Woodruff completion event</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Business NC — Jewelers Mutual / Amazon Pender</t>
+          <t>Post and Courier — Columbia bureau (Southern Glazer's)</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -21015,51 +20314,51 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>https://businessnc.com/</t>
+          <t>https://www.postandcourier.com/columbia/</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>NC Triangle &amp; Coastal</t>
+          <t>SC Midlands</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Jewelers Mutual Raleigh; Amazon Pender/New Hanover fulfillment center</t>
+          <t>Southern Glazer's Wine &amp; Spirits West Columbia opening</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>GlobeNewswire — Ahold Delhaize</t>
+          <t>Leeham News (Farnborough coverage)</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>company_primary</t>
+          <t>trade_journal</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/</t>
+          <t>https://leehamnews.com/</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Alamance Co. NC</t>
+          <t>National aerospace</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Ahold Delhaize/Food Lion Burlington distribution center groundbreaking</t>
+          <t>Boeing 787 rate confirmation at Farnborough Airshow</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>WRAL — VinFast termination</t>
+          <t>WFMY News 2 (Reynolds American)</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -21069,24 +20368,24 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>https://www.wral.com/business/vinfast-agreement-canceled-chatham-county-north-carolina-july-2026/</t>
+          <t>https://www.wfmynews2.com/</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Chatham Co. NC</t>
+          <t>NC Triad</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>VinFast incentive termination</t>
+          <t>Reynolds American Tobaccoville jobs (excluded)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Fox Carolina — Project Moc-1</t>
+          <t>Hoodline (AdvanceTEC, RTP 3.0)</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -21096,24 +20395,24 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>https://www.foxcarolina.com/</t>
+          <t>https://hoodline.com/</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Spartanburg Co. SC</t>
+          <t>NC Triangle/Triad</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>NorthMark Project Moc-1 SCDES comment-period status</t>
+          <t>AdvanceTEC Johnston Co. groundbreaking; RTP 3.0 framework approval</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>CBS17 — Gregory Poole / Apple RTP</t>
+          <t>journalnow.com (Winston-Salem Journal)</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -21123,17 +20422,44 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>https://www.cbs17.com/</t>
+          <t>https://journalnow.com/</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Wake Co. NC</t>
+          <t>NC Triad</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Gregory Poole Garner HQ; Apple RTP construction status</t>
+          <t>ProKidney Greensboro plant withdrawal</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette (Cielo Digital Infrastructure)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Upstate SC</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Cielo Digital Infrastructure Cherokee Co. data center</t>
         </is>
       </c>
     </row>
@@ -21148,7 +20474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21587,7 +20913,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -21607,7 +20933,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -21627,7 +20953,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -21647,7 +20973,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -21667,7 +20993,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -21687,7 +21013,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -21707,7 +21033,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -21727,7 +21053,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -21747,7 +21073,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -21760,14 +21086,14 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; no new milestone this cycle (third consecutive quiet cycle).</t>
+          <t>Unchanged; no new milestone this cycle (second consecutive quiet cycle).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -21776,23 +21102,23 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Rock Hill City Council voted 7-0 to approve amended tax-share terms (2026-07-23), resolving the deal's chief outstanding execution risk; SC awarded a $65M Closing Fund grant to York County; deal now described as fully finalized — net +3 for removed deal-certainty discount.</t>
+          <t>Rock Hill School Board's 5-2 endorsement of the amended tax-share terms is genuine forward momentum without a new negative signal; Rock Hill City Council's outstanding vote remains the key risk — net +1.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — EV plant (Blythewood)</t>
+          <t>Scout Motors (Blythewood)</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
@@ -21800,14 +21126,14 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Carried forward unchanged — this cycle's SC Midlands/Lowcountry recheck could not be completed due to web-search tool-budget exhaustion; no negative signal found, but also not independently reverified this cycle.</t>
+          <t>Headcount and active-hiring trend reconfirmed unchanged; a previously-cited 2026-07-29 hiring-event date could not be corroborated as genuinely 2026-dated and is now treated as unverified — no score impact since the broader hiring signal stands.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -21820,14 +21146,14 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; no new milestone this cycle.</t>
+          <t>Unchanged; county incentive hearing is a procedural step, not a scale change.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -21847,12 +21173,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>JetZero (Greensboro)</t>
+          <t>Genentech (Holly Springs)</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -21860,19 +21186,19 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Physical construction now confirmed underway (NC Composite Center, HITT Contracting as general contractor) beyond the groundbreaking ceremony already credited last cycle; net +1 for reduced execution-risk discount, still capped by the extended hiring ramp (full target 2037).</t>
+          <t>Unchanged; sole dated milestone now sits exactly at the trailing-6-month window boundary — flagged for likely drop-out next cycle absent a new update.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Genentech (Holly Springs)</t>
+          <t>JetZero (Greensboro)</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
@@ -21880,45 +21206,25 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Unchanged; no new milestone this cycle.</t>
+          <t>State budget signed 2026-07-07 releases the previously-frozen $133.9M JDIG-linked funding (execution-certainty positive); hiring-ramp timeline itself unchanged — net +1.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Scout Motors — Global HQ (Charlotte)</t>
+          <t>Novartis (Durham/Morrisville)</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>New to Ranked: 1,200 jobs + stated $153,978 wage (well above county avg) + urban Plaza Midwood fit; discounted for Med confidence (in-window milestone is a preliminary land-development filing, not a permit or groundbreaking) and zero repeat-momentum as a first-time-ranked entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Novartis (Durham/Morrisville)</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Unchanged; no new milestone this cycle.</t>
         </is>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-08-10  ·  Window 2026-02-10 to 2026-08-10  ·  NC + SC</t>
+          <t>Week of 2026-08-17  ·  Window 2026-02-17 to 2026-08-17  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10  (Week 4)</t>
+          <t>2026-08-17  (Week 5)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10 to 2026-08-10  (trailing 6 months)</t>
+          <t>2026-02-17 to 2026-08-17  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Rock Hill / York Co. (SC) — Octapharma 'Project Palmetto Rock', score 90 (+3) — Rock Hill City Council voted 7-0 on 2026-07-23 to approve amended tax-share terms, resolving the deal's last outstanding governmental hurdle; deal now described as fully finalized</t>
+          <t>North Charleston (Charleston Co., SC) — SC Ports Authority Leatherman Terminal pause CONFIRMED in effect as of Aug. 1, 2026 (phasing through mid-Sept.), resolving the report's single largest open question across the last two cycles; no reopening date set</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Octapharma is now a closed deal, not a pending one. Scout Motors' Charlotte global HQ (distinct from its Blythewood, SC EV plant) is newly Ranked on an in-window land-development filing for a second office building. JetZero has moved from ceremonial groundbreaking to an active general contractor physically building the first facility. Two negative reversals hit the NC Triangle (VinFast incentive terminated in Chatham Co.; Kempower's JDIG cancelled in Durham/RTP).</t>
+          <t>This cycle closed out the prior two-cycle SC Midlands/Lowcountry and Upstate SC research gap with a full recheck of both regions. Biggest miss corrected: Suniva's $350M/564-job Laurens Co. solar-cell plant (announced April 2026) had never been tracked. Scout Motors' Blythewood EV plant got its first independent recheck in 5 weeks — the previously-carried ~1,400-employee figure could not be corroborated (best-supported figure is 600+), and delivery-timeline risk is newly flagged, so its score was trimmed 3 points. Aspida Financial Services (Durham, 1,000 jobs, $137,288 wage) is newly Ranked on a confirmed building-renovation milestone. HII (Goose Creek, SC) and JetZero (Greensboro) both show genuine forward momentum.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Coverage gap — READ</t>
+          <t>Coverage note</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>This session's shared web-search tool budget (200 calls) was exhausted before the SC Midlands/Lowcountry research pass could run at all, and before the Upstate SC pass could complete more than 4 of its planned ~25 searches. Every SC Midlands/Lowcountry entry (Scout Motors' Blythewood plant, SC Ports Leatherman Terminal, AMAROK, Ferrara Candy, Boeing 787, HII, Google) and several Upstate SC watch items are carried forward from 2026-07-13 UNVERIFIED this cycle — flagged in both the report and this workbook. No numbers were invented; see the report's Appendix for full detail.</t>
+          <t>All five regions received a full research pass this cycle (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) — no region was skipped. Several news-site domains returned EGRESS_BLOCKED on direct WebFetch; findings from those domains rely on WebSearch-result snippets citing the same named URLs rather than full-page fetches, flagged per-item where this applies. No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-02-10 to 2026-08-10.</t>
+          <t>Trailing 6 months now runs 2026-02-17 to 2026-08-17.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SC Ports' announced Aug. 1, 2026 pause of Leatherman Terminal operations (reported 2026-06-25) could not be confirmed as having taken effect this cycle due to the coverage gap above — this is the #1 priority recheck for next cycle.</t>
+          <t>SC Ports' Leatherman Terminal pause (announced 2026-06-25, targeted for Aug. 1, 2026) is now confirmed to have taken effect, phasing in gradually through roughly mid-Sept. 2026; no reopening timeline exists. Separately, Scout Motors' Blythewood headcount figure was corrected — the previously-carried ~1,400 employees could not be corroborated this cycle; 600+ (Apr. 2026) is the best-supported current figure.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>8 of 8 prior-ranked deals remain qualifying, plus 1 new (Scout Motors Global HQ, Charlotte) — 9 total. 1 updated/resolved (Octapharma, +3), 1 updated (JetZero, +1), 5 repeated (SMBC, AbbVie, Capital Group, Genentech, Novartis), 1 repeated-but-unverified (Scout Motors EV plant, Blythewood). None removed from Ranked. Snider Fleet Solutions removed from Watch (confirmed stale).</t>
+          <t>9 of 9 prior-ranked deals remain qualifying, plus 1 new (Aspida Financial Services, Durham) — 10 total. 1 updated with a downward correction (Scout Motors EV plant, -3), 1 updated positively (JetZero, +1), 7 repeated unchanged (SMBC, Octapharma, AbbVie, Capital Group, Genentech, Scout Motors HQ, Novartis). None removed from Ranked. FN America removed from Watch (4th consecutive stale cycle); PSA Airlines reclassified from Excluded to Watch (was mis-scoped as pre-window); 3 new Watch items (Suniva, Isuzu North America, Redwood Materials).</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2095,7 +2095,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -2186,7 +2186,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -2277,7 +2277,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2368,7 +2368,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -2459,7 +2459,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
@@ -2550,7 +2550,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -2641,7 +2641,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -2732,7 +2732,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -3636,6 +3636,916 @@
       <c r="S32" s="6" t="inlineStr">
         <is>
           <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (finalized; pre-closing)</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>Both governmental approvals finalized; property sale pending</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (first independent recheck in 5 weeks)</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>Body Shop + Paint Shop construction milestones; prior headcount figure corrected</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/july-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (site prep + financing milestone)</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr (unchanged)</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>Mass grading set to begin; EXIM Bank financing LOI signed</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>https://avioradar.net/en/jetzero-explores-up-to-3-billion-in-financing-for-new-north-carolina-manufacturing-campus/</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; a $3B EXIM financing exploration reduces execution-risk uncertainty ahead of the 2028-2037 hiring ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Office — financial services/insurance</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>$137,288 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>$28M+ (incl. $10M Imperial Tower renovation)</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>Lease executed; building renovation underway</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-10-million-durham-revival/</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; move-in date not yet company-confirmed)</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>1,000 high-wage financial-services jobs concentrated in downtown Durham support Class-A urban rental and close-in for-sale demand.</t>
         </is>
       </c>
     </row>
@@ -3650,7 +4560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5428,7 +6338,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -5544,7 +6454,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5660,7 +6570,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5776,7 +6686,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5892,7 +6802,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -6008,7 +6918,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -6124,7 +7034,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6240,7 +7150,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -7394,6 +8304,1166 @@
       <c r="X32" s="6" t="inlineStr">
         <is>
           <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Leased former One Wells Fargo Center; hiring 70+ roles; first workers fall 2026</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W33" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X33" s="6" t="inlineStr">
+        <is>
+          <t>Fourth consecutive quiet cycle; actively hiring per job-board postings; on track for fall 2026 first-worker arrivals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (finalized; pre-closing)</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Both governmental approvals finalized; property sale pending</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Property sale expected to close 'in coming months'; construction as early as 2027</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fortmillsun.com/2026/07/23/rock-hill-council-clears-octapharma-deal-in-7-0-votes-as-members-blast-york-county-over-incentive-fight/</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U34" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V34" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W34" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X34" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle beyond continued finalized status; property-sale closing is the next concrete step to watch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V35" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W35" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X35" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; project remains on track.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (first independent recheck in 5 weeks)</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Body Shop + Paint Shop construction milestones; prior headcount figure corrected</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Projected (600+ hired as of Apr 2026; 200-300 more planned in 2026)</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>First Traveler body welded (Jun 2026); Paint Shop near completion, systems testing (Jul 2026); customer deliveries at risk of slipping toward summer 2028</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/july-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="U36" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V36" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W36" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X36" s="6" t="inlineStr">
+        <is>
+          <t>First independent recheck since 2026-07-13. The previously-carried ~1,400-employee figure could not be corroborated this cycle — best-supported current figure is 600+ hired (Apr 2026) with 200-300 more planned in 2026; treat the prior figure as an overstatement, not a layoff (no reduction signal found). Multiple trade outlets (CarsDirect, TFLcar, FITSNews) report EREV powertrain/cost pressure pushing customer deliveries toward summer 2028; Scout has publicly denied a formal delay. Score reduced 3 pts for headcount-certainty and timeline-risk discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>12-yr JDIG term; lease term began 2026-05-22</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U37" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V37" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W37" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+      <c r="X37" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (site prep + financing milestone)</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Mass grading set to begin; EXIM Bank financing LOI signed</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr (unchanged)</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Mass grading of the 600+ acre, 8M sq ft site expected to begin Aug/Sept 2026, running ~1 yr before vertical construction; JetZero signed a Letter of Interest with the Export-Import Bank of the US to explore up to $3B in financing (signed at the Farnborough Airshow, ~Jul 2026)</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>https://avioradar.net/en/jetzero-explores-up-to-3-billion-in-financing-for-new-north-carolina-manufacturing-campus/</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High (facts); Low (timeline)</t>
+        </is>
+      </c>
+      <c r="U38" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V38" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W38" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; a $3B EXIM financing exploration reduces execution-risk uncertainty ahead of the 2028-2037 hiring ramp.</t>
+        </is>
+      </c>
+      <c r="X38" s="6" t="inlineStr">
+        <is>
+          <t>Site-prep timeline and a large potential financing package are incremental positive signals beyond last cycle's 'general contractor on site' milestone; +1 for reduced execution-risk discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Expansion of committed project</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Operational by 2029</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gene.com/media/press-releases/15096/2026-01-20/genentech-more-than-doubles-investment-i</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U39" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V39" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W39" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake.</t>
+        </is>
+      </c>
+      <c r="X39" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Automotive (EV) — corporate HQ</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Projected (365 relocating + 835 new local hires)</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>1st ~150,000 sf building move-in ~mid-2026; 2nd building's land-development plan filed March 2026, construction start targeted H1 2027</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="T40" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="U40" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="V40" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W40" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+      <c r="X40" s="6" t="inlineStr">
+        <is>
+          <t>No new permit/construction-progress news found this cycle; still at preliminary land-development-filing stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Facility opening targeted 2027-2028</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U41" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V41" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W41" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X41" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Financial services / insurance HQ</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>Lease executed; building renovation underway</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>$137,288 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>$28M+ (incl. $10M Imperial Tower renovation)</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>89,770 sf lease (top 3 floors, Imperial Tower, 4820 Emperor Blvd); Drawbridge Realty's $10M building renovation targeted to complete summer 2026; move-in expected Q4 2026</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-10-million-durham-revival/</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; move-in date not yet company-confirmed)</t>
+        </is>
+      </c>
+      <c r="U42" s="6" t="inlineStr">
+        <is>
+          <t>Office — financial services/insurance</t>
+        </is>
+      </c>
+      <c r="V42" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W42" s="6" t="inlineStr">
+        <is>
+          <t>1,000 high-wage financial-services jobs concentrated in downtown Durham support Class-A urban rental and close-in for-sale demand.</t>
+        </is>
+      </c>
+      <c r="X42" s="6" t="inlineStr">
+        <is>
+          <t>Reclassified from Markets to Watch: the Dec. 2025 lease predates the window, but this cycle confirms an in-window construction milestone (building renovation on track for summer 2026 completion) corroborating the expected Q4 2026 move-in flagged last cycle.</t>
         </is>
       </c>
     </row>
@@ -7408,7 +9478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10962,7 +13032,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -11024,7 +13094,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -11086,7 +13156,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -11148,7 +13218,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -11210,7 +13280,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -11272,7 +13342,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -11334,7 +13404,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -11396,7 +13466,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -11458,7 +13528,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -11520,7 +13590,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -11582,7 +13652,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -11644,7 +13714,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -11706,7 +13776,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -11768,7 +13838,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -11830,7 +13900,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -11892,7 +13962,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -11954,7 +14024,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -12016,7 +14086,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -12078,7 +14148,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -12140,7 +14210,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -12202,7 +14272,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -12264,7 +14334,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -12326,7 +14396,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -12388,7 +14458,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -12450,7 +14520,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -12512,7 +14582,7 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -12574,7 +14644,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -12636,7 +14706,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -12698,7 +14768,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -12760,7 +14830,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -12822,7 +14892,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -12884,7 +14954,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -12946,7 +15016,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -13008,7 +15078,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -13070,7 +15140,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -13132,7 +15202,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -13194,7 +15264,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -13256,7 +15326,7 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -13318,7 +15388,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -13380,7 +15450,7 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -13442,7 +15512,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -16226,6 +18296,2858 @@
       <c r="L142" s="6" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal (PAUSE CONFIRMED IN EFFECT)</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>RESOLVED (top-priority item): the Aug. 1, 2026 pause did take effect, phasing in gradually over ~6 weeks (full wind-down ~mid-Sept 2026); no reopening date or reversal found — SC Ports CEO says reopening depends on cargo volumes and making Leatherman's ILA labor costs more competitive</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (pause confirmed underway)</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>https://www.dcvelocity.com/transportation/maritime-ocean/sc-ports-will-close-a-container-terminal</t>
+        </is>
+      </c>
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed this cycle; still just under 500 jobs, commissioning still targeted 2028, no threshold-crossing update</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
+        </is>
+      </c>
+      <c r="L144" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara "Project Moc-1" — AI/HPC data center</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>~150 FT at full operation (one source cites ~27 FT — discrepancy flagged, not resolved)</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>$2.8B</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>Permit decision still pending past the 2026-07-31 comment-period close; litigation escalating (SELC lawsuit; SC Public Service Commission held oral arguments 2026-08-05 on whether the project needs full state siting review); Spartanburg Co. Council gave 1st-reading approval to a 1-yr data-center moratorium (does not affect Moc-1, which predates it); special county 'fact-finding' session held 2026-08-12</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/08/12/fact-finding-journey-spartanburg-county-holds-special-meeting-data-centers/</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>Med (contested/evolving)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — proposed merger</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>Public hearing held as scheduled 2026-08-17 at the Wake County Justice Center; no vote taken same night; earliest possible Commissioners vote remains Sept. 8, 2026 (past this window)</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wakemed-atrium-health-possible-deal-public-meeting-monday-august-17-2026/</t>
+        </is>
+      </c>
+      <c r="L146" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar)</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>No positive movement found; hangar still described as largely idle nearly 2 years after ribbon-cutting; CEO says production start is 'about two years out'; ~19 open roles nationally on job boards, same as last cycle — deadline now ~4.5 months out with no visible hiring inflection</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (job-posting check)</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/greensboro-s-50-million-supersonic-ghost-hangar-puts-state-on-the-clock/</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>High (risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>200+ (state figure; county vote cited 258)</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>$57,351 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; Q1 2027 ops start still targeted</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+        </is>
+      </c>
+      <c r="L148" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>211 (confirmed; earlier 230 figure not reconfirmed)</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>City Council approved up to $2.9M in incentives over 5 yrs (~June 2026, one dissent citing engagement concerns); construction reported to begin immediately — resolves last cycle's 'pending final vote' status</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>2026-06 (Council approval)</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>https://www.charlottenc.gov/City-News/Averitt-Announces-New-Commitment-to-Charlotte</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>York Co.</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>QTS "Project Cobra" — data-center campus</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>~200 FTE (+~1,000 constr.)</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>up to $8B</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>~$80k median (stated)</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>No change; York Co.'s 9-month data-center moratorium (final reading 2026-07-13) explicitly exempts QTS's 9 vested-rights buildings</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/data-center-york-chester-qts-construction/article_1f68a2a7-8190-49df-b518-23aa5babd587.html</t>
+        </is>
+      </c>
+      <c r="L150" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>Burlington / Alamance-Guilford line</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>Alamance</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize USA (Food Lion parent) — distribution center</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>500-505</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>$860M</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone; construction underway post-Feb. groundbreaking, opening still targeted 2029</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/02/16/3238762/0/en/Ahold-Delhaize-USA-Breaks-Ground-on-New-860-Million-Distribution-Center-in-Burlington-N-C.html</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>Pender / New Hanover</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>Pender (+New Hanover)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>Amazon — robotics fulfillment center</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>1,000+</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>Building shell complete, robotics outfitting underway; active hiring campaign confirmed (WilmingtonBiz, 2026-08-10); opening now described as 'fall 2026' (slight slip from Q3 2026)</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/08/10/amazon_begins_hiring_as_local_facilities_near_completion/27737</t>
+        </is>
+      </c>
+      <c r="L152" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed; no material change to the aggregate figure</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L153" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — SouthPark consolidated office</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>400 new + ~600 relocated = 1,000 total on-site</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred (not independently reconfirmed)</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>Lease detail confirmed: 145,000 sf across 5 floors at One Piedmont Town Center; move-in early 2028</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/04/21/jpmorgan-chase-open-1000-employee-charlotte-office-add-400-jobs/</t>
+        </is>
+      </c>
+      <c r="L154" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/lease); Med (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant Corp. — global HQ launch</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>$170k-$189k avg (stated)</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>HQ open since March 2026; ~150 of 180 target staff now on-site, hiring continues through 2029</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>https://investors.ralliant.com/news-events/press-releases/detail/121/ralliant-opens-global-headquarters-in-raleigh-north-carolina</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>Jewelers Mutual Group</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>$5.85M</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>$169,592 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>~50 employees now in 31,000 sf at One North Hills Tower; 55 open roles found on job boards — modest hiring-ramp progress, still sub-500 jobs</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (job-posting check)</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/jewelers-mutual-coming-to-raleigh-with-200-jobs-averaging-169k/</t>
+        </is>
+      </c>
+      <c r="L156" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>Garner</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>Gregory Poole Equipment Co. — HQ relocation</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>500+ (5 yr)</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>$347M</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>No 2026 groundbreaking found this cycle</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-16 (pre-window)</t>
+        </is>
+      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>https://www.cbs17.com/news/local-news/wake-county-news/gregory-poole-equipment-caterpillar-dealer-moving-headquarters-to-garner/</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Siler City</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed — silicon-carbide fab (RISK FLAG)</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>1,800 (proj.)</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>$5.0B</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>$77,753 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>Financial strain deepening: Q2 FY26 capex cut 90% YoY company-wide, underutilization charges at Siler City specifically cited; Durham 150mm fab shutdown to focus capital on Mohawk Valley, NY; unverified headline suggests Siler City layoffs — Q4 FY26 earnings call scheduled 2026-08-19 (2 days after this report) is the next material data point</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19 (earnings call scheduled)</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>https://www.stocktitan.net/news/WOLF/wolfspeed-inc-announces-date-of-fiscal-fourth-quarter-earnings-call-n4d9mnhs19j2.html</t>
+        </is>
+      </c>
+      <c r="L158" s="6" t="inlineStr">
+        <is>
+          <t>Med (softening; recheck after 8/19 earnings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>No update found beyond the training-pipeline detail already tracked; no confirmation yet that on-site groundbreaking has occurred</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-18 (orig.)</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>https://www.johnstoncc.edu/news/vulcangoldenleafgrant.php</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed NC-specific)</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>No update; per-site Wilmington allocation explicitly still not broken out per company statements</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
+        </is>
+      </c>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>No update; equipment arrival still targeted end 2026, first parts mid-2027</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t>2026 (timeline confirm)</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/pratt-whitney-expands-in-asheville/</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>No update; noted as the 7th significant post-Helene expansion in Buncombe Co.</t>
+        </is>
+      </c>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>https://wlos.com/news/local/eaton-buncombe-county-300-jobs-asheville-advanced-manufacturing-expansion-arden-avery-creek-power-management-company</t>
+        </is>
+      </c>
+      <c r="L162" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>Ribbon-cutting held late April 2026 (with NVIDIA government-affairs presence) confirming the retrofitted facility is now active; production still targeted mid-2028</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>2026-04 (ribbon-cutting)</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/red-hot-lumentum-plans-400-worker-greensboro-plant/</t>
+        </is>
+      </c>
+      <c r="L164" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>No new construction-progress detail found; both NC and IN facilities still 'expected to open within the next year'</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>https://businessfacilities.com/john-deere-builds-new-facilities-in-north-carolina-indiana/</t>
+        </is>
+      </c>
+      <c r="L165" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>$20M</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>$55,133 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>No update found despite targeted searches</t>
+        </is>
+      </c>
+      <c r="J166" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25 (orig.)</t>
+        </is>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+        </is>
+      </c>
+      <c r="L166" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>Still no jobs figure disclosed; ~41 open GE Nuclear roles in Wilmington on job boards (informational only)</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr">
+        <is>
+          <t>2026 (ongoing)</t>
+        </is>
+      </c>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
+        </is>
+      </c>
+      <c r="L167" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery Manufacturing NC (TBMNC)</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>5,100 (proj. total); 3,000+ employed</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>$13.9B</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>$62,234 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone; production ramp continuing on prior trajectory</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>2025-11 (reconfirmed 2026)</t>
+        </is>
+      </c>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t>https://rebusinessonline.com/toyota-begins-production-at-13-9b-battery-plant-in-north-carolina-pledges-additional-10b-investment-over-next-five-years/</t>
+        </is>
+      </c>
+      <c r="L168" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>Google — 730k sq ft warehouse lease (3rd-party logistics operator; "DHL" attribution unconfirmed this cycle)</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (job-board postings)</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>No update; jobs still undisclosed; the previously-carried 'DHL' operator attribution could not be re-verified this cycle — recommend re-checking rather than carrying it forward as confirmed</t>
+        </is>
+      </c>
+      <c r="J169" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>https://www.qcnews.com/news/u-s/north-carolina/kannapolis/google-signs-multi-year-lease-to-move-into-730000-square-foot-warehouse-in-kannapolis/</t>
+        </is>
+      </c>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>No active Apple-specific construction found; RTP companies/landowners unanimously approved the park-wide 'RTP 3.0' long-range land-use framework (June 2026), which could eventually enable Apple's build-out but is not an Apple-specific milestone</t>
+        </is>
+      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>2026-06 (RTP 3.0 approval)</t>
+        </is>
+      </c>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t>https://www.rtp.org/2026/06/research-triangle-park-approves-3-0/</t>
+        </is>
+      </c>
+      <c r="L170" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>The 'possible 2nd Rural Hall expansion' headline flagged last cycle is confirmed real — this Feb. 2026 $421M announcement is reported as the 2nd Rural Hall/Winston Technology Center expansion in four months; per-site (Forsyth) job count still not broken out</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="K171" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+        </is>
+      </c>
+      <c r="L171" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals uncertain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="K172" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L172" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>Still unverified; outside all five assigned research regions again this cycle</t>
+        </is>
+      </c>
+      <c r="J173" s="6" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="K173" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aboutamazon.com/</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>Low (needs verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>Independently reconfirmed this cycle: groundbreaking held May 19-20, 2026; first lines still targeted Q1 2029</t>
+        </is>
+      </c>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19/20</t>
+        </is>
+      </c>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wrdw.com/2026/05/20/ferrara-candy-company-breaks-ground-orangeburg/</t>
+        </is>
+      </c>
+      <c r="L174" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>Independently reconfirmed this cycle: announcement date 2026-03-24, first phase in service by end of 2026, full buildout by ~2028</t>
+        </is>
+      </c>
+      <c r="J175" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/03/24/</t>
+        </is>
+      </c>
+      <c r="L175" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>1,000+ new jobs over 5 yrs (unchanged); campus total now 8,200+</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>$1B+ (existing)</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (production ~$70-85k; eng. above $100k)</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone; Nov. 2025 groundbreaking (2,500 construction workers, new ~1.2M sf final-assembly building targeted online early 2027) predates window and continues on prior trajectory</t>
+        </is>
+      </c>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-07 (pre-window; ongoing)</t>
+        </is>
+      </c>
+      <c r="K176" s="6" t="inlineStr">
+        <is>
+          <t>https://boeing.mediaroom.com/2025-11-07-Boeing-South-Carolina-Breaks-Ground-on-787-Site-Expansion</t>
+        </is>
+      </c>
+      <c r="L176" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — GAINING MOMENTUM</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>~475 employees (up from ~250 estimate)</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>Meaningful growth confirmed: HII discloses site production increased more than 50% under its ownership; 2026-07-13 media day highlighted expanded submarine/carrier production; 2026-07-27/28 HII hosted Australia's Defence Industry Minister and won the AUKUS-linked Australian Submarine Supplier Qualification (AUSSQ) contract, expected to grow the workforce further</t>
+        </is>
+      </c>
+      <c r="J177" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27/28</t>
+        </is>
+      </c>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/07/27</t>
+        </is>
+      </c>
+      <c r="L177" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>~160 apprentices (FTE n/d)</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window construction/hiring update found despite an active search this cycle — unusual for a project this size; recommend a dedicated recheck next cycle</t>
+        </is>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-13 (last verified)</t>
+        </is>
+      </c>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>Med (unexpected quiet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>Avg $78,811/yr ($37.89/hr); 90th pct ~$100k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>Independently reconfirmed this cycle; no material update since March 2026 announcement</t>
+        </is>
+      </c>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>$40-60M</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>Eng. roles $69-93k; assembly $34-46k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>Corporate teams now operating on-site; manufacturing still scheduled Q1 2027</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>https://www.spartanweeklyonline.com/news/local-news/airsys-opens-global-headquarters-campus-in-woodruff-bringing-215-jobs</t>
+        </is>
+      </c>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>~$49-76k technician range (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J181" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>https://www.golaurens.com/news/laurens-county-welcomes-277-jobs-and-120-million-from-aptiv/article_a0c4713d-b677-40d3-b3a7-c68779533f7c.html</t>
+        </is>
+      </c>
+      <c r="L181" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>Operations online, still actively hiring; no material update since April 2026</t>
+        </is>
+      </c>
+      <c r="J182" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K182" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L182" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>No jobs-figure disclosure found; relocation to downtown Greenville + Clemson CUBEInC lab space at Prisma's Patewood campus proceeding; pursuing SPAC IPO via IB Acquisition Corp.</t>
+        </is>
+      </c>
+      <c r="J183" s="6" t="inlineStr">
+        <is>
+          <t>2026-05 (last verified)</t>
+        </is>
+      </c>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t>https://www.upstatescalliance.com/announcements/gnq-insilico-a-500m-biotech-innovator-moving-to-greenville/</t>
+        </is>
+      </c>
+      <c r="L183" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (GAINING MOMENTUM)</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired past yr, ~300 more targeted by end 2026</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville); part of $600M multi-site plan</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed — production/technician ~$44-65k; engineering plausibly $85k-$115k+</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>CNBC on-the-ground feature (2026-06-27) confirms the hiring ramp is real and accelerating, directly tied to hyperscaler (Amazon/Google/Microsoft/Oracle) demand for gas turbines to power AI data centers</t>
+        </is>
+      </c>
+      <c r="J184" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="K184" s="6" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/06/27/ge-vernova-gas-turbines-ai-data-centers.html</t>
+        </is>
+      </c>
+      <c r="L184" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. (Laurens)</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>NEW — Suniva Inc. — solar-cell manufacturing plant</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred: entry ~$23/hr (~$48k), technicians $26-36/hr, line mgrs up to $53/hr (~$110k) — blended sub-$100k, 3rd-largest investment in Laurens Co. history</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>First U.S.-owned SC solar-cell facility; lease of 620,000 sf building; opening spring/summer 2027; will bring Suniva's total US capacity to 5.5+ GW/yr. Largest single new finding this cycle — missed entirely during the prior two-cycle SC Midlands/Upstate research gap</t>
+        </is>
+      </c>
+      <c r="J185" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-04/suniva-inc-selects-laurens-county-first-south-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="L185" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>NEW — Isuzu North America — truck assembly plant</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred: assembly $35-56k, engineers $79-108k — blended sub-$100k</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>Original announcement (Feb. 2025) and groundbreaking (Oct. 2025) predate the window, but a 2026-07-08 hiring event at Greenville Tech (filling ~150 of 700 planned roles) is a genuine in-window milestone; production launch still targeted 2027</t>
+        </is>
+      </c>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ccjdigital.com/business/article/15767928/isuzu-building-280m-truck-plant-in-south-carolina-creating-700-jobs</t>
+        </is>
+      </c>
+      <c r="L186" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>Ridgeville / Camp Hall</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>NEW — Redwood Materials — battery-materials recycling campus</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (over coming years)</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>$27-75/hr stated (~$56k-156k) — some of the highest wages in Berkeley Co.; upper tier clears $100k</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>Operations began late 2025 (just before window); despite targeted searches, no in-window (Feb-Aug 2026) phase-two, hiring-ramp, or expansion news was found — flagged as a standing gap for next cycle given the project's scale and wage profile</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr">
+        <is>
+          <t>2025 (pre-window; no in-window update found)</t>
+        </is>
+      </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/business/redwood-materials-battery-recycling-berkeley</t>
+        </is>
+      </c>
+      <c r="L187" s="6" t="inlineStr">
+        <is>
+          <t>Med (no in-window update found)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>NEW (reclassified from Excluded) — PSA Airlines — Charlotte headquarters</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>~400 (450+ total team members at HQ)</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Inferred mixed corporate/admin/ops, likely sub-$100k blended)</t>
+        </is>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>Grand opening 2026-03-19 (in-window) at Water Ridge Pkwy; economic-impact estimate $228M annual output, $10M state/local tax revenue; reclassified from Excluded — job count (~400) and unconfirmed wage keep it in Watch rather than Ranked, but it was mis-scoped as pre-window last cycle</t>
+        </is>
+      </c>
+      <c r="J188" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="K188" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/19/governor-stein-celebrates-psa-airlines-headquarters-grand-opening-charlotte-highlights-only</t>
+        </is>
+      </c>
+      <c r="L188" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -16240,7 +21162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18272,7 +23194,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -18314,7 +23236,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -18356,7 +23278,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -18398,7 +23320,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -18440,7 +23362,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -18482,7 +23404,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -18524,7 +23446,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -18566,7 +23488,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -18608,7 +23530,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -18650,7 +23572,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -18692,7 +23614,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -18734,7 +23656,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -18776,7 +23698,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -18818,7 +23740,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -18860,7 +23782,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -19734,6 +24656,594 @@
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>FN America (REMOVED from Watch)</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Liberty (Pickens)</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>~176</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>2026 (last verified)</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Fourth consecutive quiet cycle with no confirmed momentum despite repeated rechecks — removed from active Watch tracking this cycle per last cycle's flag</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sccommerce.com/news/fn-america-llc-expanding-south-carolina-footprint-pickens-county-second-production-facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Maersk North American HQ</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Rechecked this cycle: wage newly confirmed at $100,962 avg (just above $100k, via NC Economic Investment Committee filing) for future tracking, but the only in-window milestone is a NEGATIVE one — the Committee approved a 1-year hiring delay (2027-2029) on 2026-02-24/25; not a new growth signal, so kept excluded rather than promoted</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>VinFast (incentive terminated)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Co.</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>1,400 (scaled back from 7,500)</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27 to 07-31</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Rechecked this cycle; confirmed still terminated, no reversal found; state lawsuit to reclaim the Moncure site remains in progress</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/vinfast-agreement-canceled-chatham-county-north-carolina-july-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Kempower (JDIG cancelled)</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Durham/RTP</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>306 (pledge; ~100 employed)</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>2026-07 (mid-July)</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Rechecked this cycle; confirmed still cancelled, company continuing at reduced scale, no reversal found</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/07/durham-ev-plant-slams-brakes-on-hiring-as-state-yanks-job-grant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Electrolux/Midea Anderson retooling (washer/dryer JV)</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>~1,200 (eventual, gradual 2027-2028)</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Follows ~1,255 layoffs at the same plant (announced April 2026); average wage only ~$16/hr (~$33k/yr) — fails wage/income criterion and is fundamentally a layoff-then-partial-rehire story, not net new high-wage growth</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>BMW $1.7B Spartanburg/Woodruff investment ("completion")</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>~200-300 net new</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Original commitment dates to 2022; only a completion-ceremony milestone falls in-window; average pay (~$43k/yr) is well under the $100k threshold regardless</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Lockheed Martin Greenville hiring event</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Search returned only 2022-vintage articles despite an active search this cycle; no genuine 2026 hiring-event coverage could be verified — worth a targeted follow-up next cycle given Lockheed's F-16 backlog is real</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Prysmian North America — Lexington Co. expansion</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor; no wage stated; fiber-optic cable capacity expansion for the data-center market</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Alzchem Group AG — Bushy Park propellant plant</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>~45</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Well under the 200-job threshold; construction not starting until 2027</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Venom EV — Summerville golf-cart/EV manufacturing</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Dorchester</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Well under the 200-job threshold; $645k investment</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Vans / Bosch electric-motor plant</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>~350 (Bosch, 2022 figure)</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>2022-10 / 2023-2024</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Recycled 2022-2023 announcements; only a non-job-related MBV '20th anniversary' note and a Dec. 2025 (pre-window) CKD-line launch found this cycle — no qualifying in-window job/investment news</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>STERIS plc — Sanford Chemistries Mfg Center of Excellence</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Lee Co.</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Outside the six defined Triangle counties (Lee Co. is ~20 miles SW of Chatham/Wake) AND wage ($68,704 stated) is well under $100k — largest new central-NC announcement found this cycle, but fails both region and threshold criteria</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/08/05/leading-health-care-company-chooses-sanford-600-million-center-excellence</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Live Oak Bank</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington (New Hanover)</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Below the 500-job Ranked threshold; a May 2026 report shows the company pulled out of its state incentive program citing a projected hiring shortfall — a negative in-window update, not a growth signal</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>ElringKlinger — automotive supplier expansion</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Pickens</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Found only via an aggregated search-engine snippet (businessfacilities.com); could not independently fetch/verify a primary source this cycle — flagged as an unverified lead for next cycle rather than reported with a confidence rating</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -19750,7 +25260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -21137,6 +26647,330 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>DC Velocity / WorldCargoNews / gCaptain</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.dcvelocity.com/</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>SC Lowcountry</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Leatherman Terminal pause confirmation (Aug. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors company blog — July 2026 update</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors Blythewood Paint Shop/production-testing milestone; headcount correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>GlobeNewswire / StockTitan — HII</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley Co. SC</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>HII Goose Creek production increase, AUKUS/AUSSQ contract win</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Governor's Office (SC) — Suniva</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>state_primary</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. SC</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Suniva solar-cell plant announcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>CNBC — GE Vernova</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Greenville Co. SC</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova hyperscaler-driven hiring-ramp feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Fox Carolina — Spartanburg data-center fact-finding session</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara Project Moc-1 permit/litigation status</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>CCJ Digital — Isuzu North America</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ccjdigital.com/</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Greenville Co. SC</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu Piedmont truck-plant hiring event</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>WilmingtonBiz — Amazon Pender hiring</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Pender/New Hanover Co. NC</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Amazon robotics fulfillment center hiring campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>RTP.org</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>regional_edo</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.rtp.org/</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Wake/Durham Co. NC</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>RTP 3.0 park-wide land-use framework approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>StockTitan — Wolfspeed earnings</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>https://www.stocktitan.net/</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Co. NC</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed Q4 FY26 earnings-call scheduling; financial-strain signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Post and Courier — Redwood Materials</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley Co. SC</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials Camp Hall/Ridgeville battery-recycling campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>NC Governor's Office — PSA Airlines / STERIS</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>state_primary</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg &amp; Lee Co. NC</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>PSA Airlines grand opening; STERIS Sanford announcement</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21148,7 +26982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21587,7 +27421,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -21607,7 +27441,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -21627,7 +27461,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -21647,7 +27481,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -21667,7 +27501,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -21687,7 +27521,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -21707,7 +27541,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -21727,7 +27561,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -21921,6 +27755,206 @@
       <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle (fourth consecutive quiet cycle), actively hiring per job postings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; both governmental approvals remain final, property sale not yet closed — no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV plant (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>First independent recheck in 5 weeks: Body Shop/Paint Shop construction milestones confirmed positive, but the previously-carried ~1,400-employee figure could not be corroborated (best-supported current figure is 600+ hired) and multiple trade outlets flag EREV powertrain/cost pressure pushing customer deliveries toward summer 2028 — net -3 for headcount-certainty and timeline-risk discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Mass grading set to begin Aug/Sept 2026 and a signed EXIM Bank financing LOI (up to $3B) are incremental positive signals beyond last cycle's 'general contractor on site' milestone — net +1 for reduced execution-risk discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new permit/construction-progress news found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services (Durham)</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>New to Ranked (reclassified from Watch): 1,000 jobs + stated $137,288 wage + $10M Imperial Tower renovation confirmed on track for summer 2026 completion, corroborating the expected Q4 2026 move-in; capped below longer-tenured entries by Medium confidence (move-in date not yet company-confirmed) and zero repeat-momentum as a first-time-ranked entry.</t>
         </is>
       </c>
     </row>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-08-17  ·  Window 2026-02-17 to 2026-08-17  ·  NC + SC</t>
+          <t>Week of 2026-08-24  ·  Window 2026-02-24 to 2026-08-24  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17  (Week 5)</t>
+          <t>2026-08-24  (Week 6)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-02-17 to 2026-08-17  (trailing 6 months)</t>
+          <t>2026-02-24 to 2026-08-24  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>North Charleston (Charleston Co., SC) — SC Ports Authority Leatherman Terminal pause CONFIRMED in effect as of Aug. 1, 2026 (phasing through mid-Sept.), resolving the report's single largest open question across the last two cycles; no reopening date set</t>
+          <t>Holly Springs / SW Wake (Wake Co., NC) — Genentech's Aug. 18, 2026 structural topping-out ceremony (final beam raised on the ~700,000 sf, ~$2B facility) is the cycle's clearest, best-corroborated in-window construction milestone, moving the entry's score up 2 points and above Capital Group and JetZero in this cycle's ranking</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>This cycle closed out the prior two-cycle SC Midlands/Lowcountry and Upstate SC research gap with a full recheck of both regions. Biggest miss corrected: Suniva's $350M/564-job Laurens Co. solar-cell plant (announced April 2026) had never been tracked. Scout Motors' Blythewood EV plant got its first independent recheck in 5 weeks — the previously-carried ~1,400-employee figure could not be corroborated (best-supported figure is 600+), and delivery-timeline risk is newly flagged, so its score was trimmed 3 points. Aspida Financial Services (Durham, 1,000 jobs, $137,288 wage) is newly Ranked on a confirmed building-renovation milestone. HII (Goose Creek, SC) and JetZero (Greensboro) both show genuine forward momentum.</t>
+          <t>This was largely a verification cycle rather than a discovery cycle: all five regions plus two targeted follow-up passes (SC Midlands/Lowcountry, NC Triad/WNC/Coastal) were run, but no new Ranked- or Watch-tier company/project announcement was found dated inside 2026-08-17 to 2026-08-24 — a genuinely quiet week for fresh 500+/200+-job announcements across the footprint. Two previously-unconfirmed leads were run to ground and debunked as stale, misdated articles rather than real 2026 developments: a claimed SC Ports Leatherman Terminal reopening (the underlying article was from Sept. 2024) and a claimed new HII South Carolina acquisition (the underlying deal closed in Jan. 2025). One long-running unverified item, AWS/Amazon's Hamlet 'Project Blue Marlin' data-center campus (Richmond Co., NC — 500 jobs, $10B), was independently verified this cycle via Amazon's own newsroom plus a confirmed ~June 20, 2026 groundbreaking. NorthMark/Valara 'Project Moc-1' (Spartanburg, SC) saw its regulatory/legal risk escalate materially, with a SC Public Service Commission ruling due Sept. 4, 2026 and an SELC injunction motion filed Aug. 20 seeking to halt construction. Wolfspeed's Aug. 19 Q4 FY26 earnings call delivered a genuinely mixed signal for Siler City: the site reached 'production readiness,' but underutilization costs kept rising as customer demand has not caught up to capacity.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>All five regions received a full research pass this cycle (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) — no region was skipped. Several news-site domains returned EGRESS_BLOCKED on direct WebFetch; findings from those domains rely on WebSearch-result snippets citing the same named URLs rather than full-page fetches, flagged per-item where this applies. No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
+          <t>All five regions received a full research pass this cycle, plus two additional targeted follow-up passes to close gaps left by search-budget exhaustion in the SC Midlands/Lowcountry and NC Triad/WNC/Coastal passes (Boeing, Redwood Materials, Google data center, AMAROK, Ferrara Candy, and ten Triad/WNC/Coastal Watch items were all successfully rechecked in the follow-up passes). WebFetch (direct page retrieval) returned EGRESS_BLOCKED for essentially every news/gov domain attempted across all agents this cycle; every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries. No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-02-17 to 2026-08-17.</t>
+          <t>Trailing 6 months now runs 2026-02-24 to 2026-08-24.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SC Ports' Leatherman Terminal pause (announced 2026-06-25, targeted for Aug. 1, 2026) is now confirmed to have taken effect, phasing in gradually through roughly mid-Sept. 2026; no reopening timeline exists. Separately, Scout Motors' Blythewood headcount figure was corrected — the previously-carried ~1,400 employees could not be corroborated this cycle; 600+ (Apr. 2026) is the best-supported current figure.</t>
+          <t>Two previously-surfaced leads were investigated and debunked this cycle as stale/misdated articles, not 2026 developments: a claimed SC Ports Leatherman Terminal reopening (actual article dated Sept. 2024) and a claimed new HII South Carolina acquisition (actual deal closed Jan. 2025). NorthMark/Valara's jobs figure was reconciled down to 27 FT (the consistently-cited incentive-basis figure) from a previously-carried ~150 estimate. AWS/Amazon's Hamlet, NC data-center campus, carried for multiple cycles as 'unverified,' is now confirmed via a primary Amazon source and a dated groundbreaking.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>9 of 9 prior-ranked deals remain qualifying, plus 1 new (Aspida Financial Services, Durham) — 10 total. 1 updated with a downward correction (Scout Motors EV plant, -3), 1 updated positively (JetZero, +1), 7 repeated unchanged (SMBC, Octapharma, AbbVie, Capital Group, Genentech, Scout Motors HQ, Novartis). None removed from Ranked. FN America removed from Watch (4th consecutive stale cycle); PSA Airlines reclassified from Excluded to Watch (was mis-scoped as pre-window); 3 new Watch items (Suniva, Isuzu North America, Redwood Materials).</t>
+          <t>10 of 10 prior-ranked deals remain qualifying — none removed, none newly added. 2 updated positively (Octapharma +1 to 91 on a site-plan-design milestone; Genentech +2 to 82 on a structural topping-out ceremony), 1 updated with offsetting context and no net score change (Scout Motors EV plant, funding veto vs. community-relations friction), 7 repeated unchanged (SMBC, AbbVie, Capital Group, JetZero, Scout Motors HQ, Novartis, Aspida). Watch tier: no new items added and none removed; AWS/Amazon Hamlet upgraded from unverified to confirmed; Wolfspeed and NorthMark/Valara both saw material updates; two leads (SC Ports reopening, HII acquisition) were investigated and debunked rather than added as new information.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4549,6 +4549,916 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (site-plan design milestone)</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>Public site-plan renderings presented at regional summit; property sale still pending</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (funding, litigation, and framing update)</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>State funding for site cost-overrun secured; new community-relations friction; delivery-timeline framing shifted</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/08/17/sc-governor-vetoes-delay-on-paying-agency-overruns-at-scout-motors-site/</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (topping-out milestone)</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>Structural topping-out ceremony</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake; a topping-out milestone moves the 2029 hiring ramp from planned to physically materializing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (site prep + financing milestone)</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr (unchanged)</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking (Jun 2026) + EXIM financing LOI (Jul 2026) — both confirmed, no new in-window milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (current grading status)</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; groundbreaking and EXIM LOI both independently reconfirmed with primary-source URLs this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building (unchanged)</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Office — financial services/insurance</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>$137,288 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>$28M+ (incl. $10M Imperial Tower renovation)</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>Lease executed; building renovation underway (unchanged)</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-10-million-durham-revival/</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; move-in date not yet company-confirmed)</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>1,000 high-wage financial-services jobs concentrated in downtown Durham support Class-A urban rental and close-in for-sale demand.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4560,7 +5470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9467,6 +10377,1166 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Leased former One Wells Fargo Center; hiring 70+ roles; first workers fall 2026</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U43" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V43" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W43" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X43" s="6" t="inlineStr">
+        <is>
+          <t>Fifth consecutive quiet cycle; no new in-window milestone found despite a dedicated Charlotte-metro research pass this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus (site-plan design milestone)</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Public site-plan renderings presented at regional summit; property sale still pending</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma COO Alice Stewart presented proposed site-plan renderings for the Rock Hill HQ/mfg campus at the SC I-77 Alliance's Annual Economic Development Summit (Richburg, SC); operations still expected to begin in the 2030s; property sale not yet confirmed closed</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U44" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V44" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W44" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X44" s="6" t="inlineStr">
+        <is>
+          <t>First in-window forward-planning milestone since the two council votes finalized in July: public site-plan renderings move the project from 'approved on paper' toward a visible design phase, even though the property sale itself has still not been confirmed closed. +1 for reduced execution-risk discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>New facility (greenfield, 185 ac)</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>https://news.abbvie.com/2026-04-22-AbbVie-Selects-North-Carolina-for-New-1-4-Billion-Manufacturing-Campus</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U45" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V45" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W45" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X45" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; Durham County was reported to be considering an additional local incentive package (~$15M) tied to the project, but the exact hearing date could not be pinned down this cycle — flagged for confirmation next cycle, not scored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (funding, litigation, and framing update)</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>State funding for site cost-overrun secured; new community-relations friction; delivery-timeline framing shifted</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Projected (600+ hired as of Apr 2026; 200-300 more planned in 2026)</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Body Shop now has 700+ robots installed; Paint Shop near completion; Gov. McMaster's Aug. 17, 2026 budget veto clears a $150M state payment for site cost overruns (was at risk of being held pending a Dec. 2026 audit); Scout and outlets now describe total site employment as ~5,000 (folding in the ~1,000-job supplier park) vs. the standard 4,000 figure, and increasingly frame full production as 'completed in 2028' rather than 2027</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/08/17/sc-governor-vetoes-delay-on-paying-agency-overruns-at-scout-motors-site/</t>
+        </is>
+      </c>
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="U46" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V46" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W46" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X46" s="6" t="inlineStr">
+        <is>
+          <t>No fresher aggregate headcount than the April 2026 600+ figure was found despite a dedicated recheck. Two developments cut in opposite directions: the Aug. 17 veto is a genuine positive (removes a funding-hold risk on the state's $150M site-overrun payment), while an elderly-couple lawsuit alleging blasting/septic/stormwater damage (filed ~Aug 7-12) and Scout's declined request to sign a Community Benefits Agreement (SC For All coalition, Aug 13) are modest community-friction negatives. Net score held flat at 83 — the positive and negative developments offset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (topping-out milestone)</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Structural topping-out ceremony</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Final structural beam raised Aug. 18, 2026 at the ~700,000 sq ft CaMP Helix Business Park facility; operational target 2029 unchanged</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="T47" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V47" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W47" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake; a topping-out milestone moves the 2029 hiring ramp from planned to physically materializing.</t>
+        </is>
+      </c>
+      <c r="X47" s="6" t="inlineStr">
+        <is>
+          <t>First genuine in-window construction milestone since the Jan. 2026 investment-doubling announcement — a topping-out ceremony one day after the prior report's cutoff is a concrete, low-execution-risk signal. +2 for reduced execution-risk discount, moving this entry above Capital Group and JetZero in this cycle's ranking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>12-yr JDIG term; lease term began 2026-05-22</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T48" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U48" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V48" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W48" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+      <c r="X48" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (site prep + financing milestone)</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking (Jun 2026) + EXIM financing LOI (Jul 2026) — both confirmed, no new in-window milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr (unchanged)</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking confirmed held 2026-06-15; EXIM Bank Letter of Interest (up to $3B financing) confirmed signed 2026-07-20 at the Farnborough Airshow; could not confirm a dated report of mass-grading physical progress within the 8/17-8/24 sub-window despite a dedicated recheck</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (current grading status)</t>
+        </is>
+      </c>
+      <c r="U49" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V49" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W49" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; groundbreaking and EXIM LOI both independently reconfirmed with primary-source URLs this cycle.</t>
+        </is>
+      </c>
+      <c r="X49" s="6" t="inlineStr">
+        <is>
+          <t>No score change; both previously-credited milestones were independently reconfirmed but no new milestone appeared in the strict recheck window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Automotive (EV) — corporate HQ</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building (unchanged)</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>Projected (365 relocating + 835 new local hires)</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>1st ~150,000 sf building move-in ~mid-2026; 2nd building's land-development plan filed March 2026, construction start targeted H1 2027</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="T50" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="U50" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W50" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+      <c r="X50" s="6" t="inlineStr">
+        <is>
+          <t>No new permit/construction-progress news found this cycle despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (investment increase)</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>New facility (unchanged)</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Facility opening targeted 2027-2028</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T51" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U51" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V51" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W51" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X51" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Financial services / insurance HQ</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>Lease executed; building renovation underway (unchanged)</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>$137,288 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>$28M+ (incl. $10M Imperial Tower renovation)</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>89,770 sf lease (top 3 floors, Imperial Tower, 4820 Emperor Blvd); Drawbridge Realty's $10M building renovation still tracking to complete summer 2026; move-in still expected Q4 2026</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-10-million-durham-revival/</t>
+        </is>
+      </c>
+      <c r="T52" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; move-in date not yet company-confirmed)</t>
+        </is>
+      </c>
+      <c r="U52" s="6" t="inlineStr">
+        <is>
+          <t>Office — financial services/insurance</t>
+        </is>
+      </c>
+      <c r="V52" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W52" s="6" t="inlineStr">
+        <is>
+          <t>1,000 high-wage financial-services jobs concentrated in downtown Durham support Class-A urban rental and close-in for-sale demand.</t>
+        </is>
+      </c>
+      <c r="X52" s="6" t="inlineStr">
+        <is>
+          <t>No confirmation found this cycle that the renovation has actually completed — status remains 'on track,' not yet verified complete.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9478,7 +11548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L188"/>
+  <dimension ref="A1:L234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21151,6 +23221,2858 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal (pause remains in effect)</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>No reopening date found this cycle. A search result titled 'Leatherman Terminal reopening with major weekly Asia service' was run down and confirmed to be a stale, misdated article about a September 2024 ILA-labor-dispute reopening (unrelated ZIM Asia service) — debunked, not a 2026 development. SC Ports' position (reopening tied to cargo-volume recovery, no date set) is unchanged</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19 (Breakfast Briefing at Leatherman, no reopening announced)</t>
+        </is>
+      </c>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+        </is>
+      </c>
+      <c r="L189" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; still just under 500 jobs, commissioning still targeted 2028</t>
+        </is>
+      </c>
+      <c r="J190" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-02 (last verified)</t>
+        </is>
+      </c>
+      <c r="K190" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
+        </is>
+      </c>
+      <c r="L190" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara "Project Moc-1" — AI/HPC data center (litigation/regulatory risk escalating)</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>27 FT confirmed on incentive filings (company's own ~150-at-full-operation claim not independently corroborated)</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>$2.8B</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>Jobs figure reconciled DOWN this cycle — 27 FT is the consistently-cited incentive-basis figure across multiple sources; the ~150 figure is Valara's own longer-horizon claim, unconfirmed. Regulatory/legal risk escalated materially: SC PSC held oral arguments 2026-08-05 on whether the ~450-457MW on-site gas plant needs full state siting review and must rule by 2026-09-04; Spartanburg Co. Council delayed the moratorium's 3rd/final reading to 2026-09-21; SELC filed for a temporary injunction to halt construction on 2026-08-20 (no ruling yet); construction reported continuing as of the filing</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/08/20/environmental-group-files-court-order-stop-spartanburg-county-data-center-project/</t>
+        </is>
+      </c>
+      <c r="L191" s="6" t="inlineStr">
+        <is>
+          <t>Med (contested/evolving; jobs count corrected down)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — proposed merger</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>No update since the 2026-08-17 public hearing (no vote taken); earliest possible Commissioners vote remains Sept. 8, 2026</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17 (last verified)</t>
+        </is>
+      </c>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wakemed-atrium-health-possible-deal-public-meeting-monday-august-17-2026/</t>
+        </is>
+      </c>
+      <c r="L192" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar)</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>No positive movement found; a Prism News feature describes the Greensboro factory as still sitting largely idle roughly two years after the hangar's completion, having 'yet to produce a single aircraft,' with NC having invested $50M+; deadline now ~4 months out with no confirmed current headcount or hiring inflection found</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (Prism News feature)</t>
+        </is>
+      </c>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+        </is>
+      </c>
+      <c r="L193" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>200+ (state figure; county vote cited 258)</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>$57,351 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; Q1 2027 ops start still targeted</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17 (last verified)</t>
+        </is>
+      </c>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+        </is>
+      </c>
+      <c r="L194" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>211 (confirmed)</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J195" s="6" t="inlineStr">
+        <is>
+          <t>2026-06 (last verified)</t>
+        </is>
+      </c>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>https://www.charlottenc.gov/City-News/Averitt-Announces-New-Commitment-to-Charlotte</t>
+        </is>
+      </c>
+      <c r="L195" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>York Co.</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>QTS "Project Cobra" — data-center campus</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>~200 FTE (+~1,000 constr.)</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>up to $8B</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>~$80k median (stated)</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13 (last verified)</t>
+        </is>
+      </c>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/data-center-york-chester-qts-construction/article_1f68a2a7-8190-49df-b518-23aa5babd587.html</t>
+        </is>
+      </c>
+      <c r="L196" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>Burlington / Alamance-Guilford line</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>Alamance</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize USA (Food Lion parent) — distribution center</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>500-505</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>$860M</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; opening still targeted 2029</t>
+        </is>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-16 (last verified)</t>
+        </is>
+      </c>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/02/16/3238762/0/en/Ahold-Delhaize-USA-Breaks-Ground-on-New-860-Million-Distribution-Center-in-Burlington-N-C.html</t>
+        </is>
+      </c>
+      <c r="L197" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>Pender / New Hanover</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>Pender (+New Hanover)</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>Amazon — robotics fulfillment center</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>1,000+</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>No update strictly within 8/17-8/24; the most recent confirmed status (2026-08-10) has both the fulfillment center and a nearby delivery station on track for a fall 2026 opening, portions near completion but certificates of occupancy not yet issued</t>
+        </is>
+      </c>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10 (last verified)</t>
+        </is>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/08/10/amazon_begins_hiring_as_local_facilities_near_completion/27737</t>
+        </is>
+      </c>
+      <c r="L198" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
+          <t>2026-02 (last verified)</t>
+        </is>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — SouthPark consolidated office</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>400 new + ~600 relocated = 1,000 total on-site</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred — basis not independently confirmed this cycle (JPMorgan has not disclosed a wage figure in any source found)</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; move-in still targeted early 2028</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21 (last verified)</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/04/21/jpmorgan-chase-open-1000-employee-charlotte-office-add-400-jobs/</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/lease); Low (wage basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant Corp. — global HQ launch</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>$170k-$189k avg (stated)</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; ~150 of 180 target staff remain on-site</t>
+        </is>
+      </c>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-05 (last verified)</t>
+        </is>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>https://investors.ralliant.com/news-events/press-releases/detail/121/ralliant-opens-global-headquarters-in-raleigh-north-carolina</t>
+        </is>
+      </c>
+      <c r="L201" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>Jewelers Mutual Group</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>$5.85M</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>$169,592 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (last verified)</t>
+        </is>
+      </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/jewelers-mutual-coming-to-raleigh-with-200-jobs-averaging-169k/</t>
+        </is>
+      </c>
+      <c r="L202" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>Garner</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>Gregory Poole Equipment Co. — HQ relocation</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>500+ (5 yr)</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>$347M</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>Clarifying (pre-window) detail found: a voluntary annexation petition ('Project Cougar,' ~128 acres) was heard by the Town of Garner on 2026-05-19 — progress, but not the groundbreaking milestone this entry is watching for; no groundbreaking found this cycle</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19 (annexation hearing; pre-window)</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>https://www.garnernc.gov/Home/Components/News/News/2344/17</t>
+        </is>
+      </c>
+      <c r="L203" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>Siler City</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed — silicon-carbide fab (Q4 FY26 earnings reported 8/19 — mixed signal)</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>1,800 (proj.)</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>$5.0B</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>$77,753 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>Q4 FY26 results (2026-08-19): revenue $149.6M (-24% YoY, below Street consensus); FY26 revenue $468.3M (+138% YoY); FY26 net loss $415.8M. Siler City capacity expansion reached 'production readiness,' but underutilization costs rose to $47M in Q4 (from $26M in Q1 FY26) as customer demand has not caught up to installed capacity. AI data-center revenue more than doubled YoY, partly offsetting soft automotive SiC demand. Shares fell ~7.5% same-day, ~10.5% more after-hours. The previously-flagged 'unverified layoffs headline' is now confirmed to reference 2025-dated WARN notices (June and March 2025), not a new 2026 action — that flag is resolved as stale, not current</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260819859398/en/Wolfspeed-Reports-Financial-Results-for-the-Fourth-Quarter-of-Fiscal-2026</t>
+        </is>
+      </c>
+      <c r="L204" s="6" t="inlineStr">
+        <is>
+          <t>Med (facility now production-ready; demand/utilization risk remains open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; still no confirmation that on-site groundbreaking has occurred, though smelter construction is reportedly still targeted to start by year-end 2026</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-18 (orig.)</t>
+        </is>
+      </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/18/governor-stein-announces-vulcan-elements-selects-johnston-county-1000-job-magnet-factory-investing</t>
+        </is>
+      </c>
+      <c r="L205" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed NC-specific)</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; per-site Wilmington allocation still not broken out (all sources describe the 1,000 jobs across Corning's Concord and Wilmington sites collectively)</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08 (last verified)</t>
+        </is>
+      </c>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
+        </is>
+      </c>
+      <c r="L206" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; equipment arrival still targeted end 2026, first parts now expected mid-2027</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>2026 (last verified)</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/pratt-whitney-expands-in-asheville/</t>
+        </is>
+      </c>
+      <c r="L207" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle despite a dedicated recheck</t>
+        </is>
+      </c>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08 (last verified)</t>
+        </is>
+      </c>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t>https://wlos.com/news/local/eaton-buncombe-county-300-jobs-asheville-advanced-manufacturing-expansion-arden-avery-creek-power-management-company</t>
+        </is>
+      </c>
+      <c r="L208" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26 (last verified)</t>
+        </is>
+      </c>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L209" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the April 2026 ribbon-cutting already on record; production still targeted mid-2028</t>
+        </is>
+      </c>
+      <c r="J210" s="6" t="inlineStr">
+        <is>
+          <t>2026-04 (last verified)</t>
+        </is>
+      </c>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/red-hot-lumentum-plans-400-worker-greensboro-plant/</t>
+        </is>
+      </c>
+      <c r="L210" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>No construction-progress or opening-date update found this cycle; the completed facility received a 2026 Metal Architecture design award (recognition only, not an operational milestone)</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="inlineStr">
+        <is>
+          <t>2026 (design award)</t>
+        </is>
+      </c>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>https://businessfacilities.com/john-deere-builds-new-facilities-in-north-carolina-indiana/</t>
+        </is>
+      </c>
+      <c r="L211" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>$20M</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>$55,133 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle despite targeted searches</t>
+        </is>
+      </c>
+      <c r="J212" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25 (orig.)</t>
+        </is>
+      </c>
+      <c r="K212" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+        </is>
+      </c>
+      <c r="L212" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t>Still no jobs figure disclosed; open GE/GE Vernova roles in Castle Hayne, NC now number roughly 25-53 across job boards (varies by search term) — similar hiring intensity to last cycle, no material change</t>
+        </is>
+      </c>
+      <c r="J213" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (job-posting check)</t>
+        </is>
+      </c>
+      <c r="K213" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
+        </is>
+      </c>
+      <c r="L213" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery Manufacturing NC (TBMNC)</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>5,100 (proj. total); 3,000+ employed</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>$13.9B</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>$62,234 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle</t>
+        </is>
+      </c>
+      <c r="J214" s="6" t="inlineStr">
+        <is>
+          <t>2025-11 (last verified)</t>
+        </is>
+      </c>
+      <c r="K214" s="6" t="inlineStr">
+        <is>
+          <t>https://rebusinessonline.com/toyota-begins-production-at-13-9b-battery-plant-in-north-carolina-pledges-additional-10b-investment-over-next-five-years/</t>
+        </is>
+      </c>
+      <c r="L214" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>Google — 730k sq ft warehouse lease (3rd-party logistics operator)</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (job-board postings)</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; jobs still undisclosed</t>
+        </is>
+      </c>
+      <c r="J215" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29 (last verified)</t>
+        </is>
+      </c>
+      <c r="K215" s="6" t="inlineStr">
+        <is>
+          <t>https://www.qcnews.com/news/u-s/north-carolina/kannapolis/google-signs-multi-year-lease-to-move-into-730000-square-foot-warehouse-in-kannapolis/</t>
+        </is>
+      </c>
+      <c r="L215" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H216" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I216" s="6" t="inlineStr">
+        <is>
+          <t>No Apple-specific construction or hiring update found this cycle</t>
+        </is>
+      </c>
+      <c r="J216" s="6" t="inlineStr">
+        <is>
+          <t>2026-06 (last verified)</t>
+        </is>
+      </c>
+      <c r="K216" s="6" t="inlineStr">
+        <is>
+          <t>https://www.rtp.org/2026/06/research-triangle-park-approves-3-0/</t>
+        </is>
+      </c>
+      <c r="L216" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; clarifying detail confirmed: the Rural Hall/Winston Technology Center (Tobaccoville) site currently employs ~400 people making gas-turbine parts, one piece of the statewide 500-job/$421M plan; per-site job count still not broken out</t>
+        </is>
+      </c>
+      <c r="J217" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (Rural Hall headcount context)</t>
+        </is>
+      </c>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+        </is>
+      </c>
+      <c r="L217" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals uncertain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the previously-confirmed breakdown (Knightdale 131,000 sf targeting 100 jobs by YE2026; Wendell 101,000 sf targeting 50 new + 200 additional jobs at the existing campus by 2028); total figure is Carolinas-wide, not NC-only</t>
+        </is>
+      </c>
+      <c r="J218" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17 (last verified)</t>
+        </is>
+      </c>
+      <c r="K218" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L218" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus "Project Blue Marlin" (STATUS UPGRADED: VERIFIED)</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>500 permanent (confirmed)</t>
+        </is>
+      </c>
+      <c r="G219" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>No longer unverified — confirmed via Amazon's own newsroom and independent local/trade coverage: groundbreaking held ~2026-06-20 at Cole Auditorium in Hamlet, NC with state and congressional officials present; ~800 acres at the Energy Way Industrial Park (adjacent to Duke Energy's Smith Energy Complex); up to 20-21 buildings at ~200,000-225,000 sf each; described as the largest single capital project in NC history. Aug. 2026 investigative coverage (NC Newsline, Inside Climate News) raises transparency/environmental concerns (secretive deal process, ~650 diesel backup generators pending permits) — noted as context, not a jobs/capex change</t>
+        </is>
+      </c>
+      <c r="J219" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-20 (groundbreaking)</t>
+        </is>
+      </c>
+      <c r="K219" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aboutamazon.com/news/aws/amazon-data-centers-locations-news?p=amazon-connects-with-future-data-center-talent-in-hamlet-north-carolina</t>
+        </is>
+      </c>
+      <c r="L219" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (verified this cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the May 2026 groundbreaking; first lines still targeted Q1 2029</t>
+        </is>
+      </c>
+      <c r="J220" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19/20 (last verified)</t>
+        </is>
+      </c>
+      <c r="K220" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/04/22/ferrara-candy-company-build-675m-orangeburg-county-plant-create-1000-jobs-officials-say/</t>
+        </is>
+      </c>
+      <c r="L220" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G221" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H221" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; first phase still targeted in service by end of 2026</t>
+        </is>
+      </c>
+      <c r="J221" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-24 (last verified)</t>
+        </is>
+      </c>
+      <c r="K221" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+        </is>
+      </c>
+      <c r="L221" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>1,000+ new jobs over 5 yrs (unchanged); campus total 8,200+</t>
+        </is>
+      </c>
+      <c r="G222" s="6" t="inlineStr">
+        <is>
+          <t>$1B+ (existing)</t>
+        </is>
+      </c>
+      <c r="H222" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (production ~$70-85k; eng. above $100k)</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found strictly within 8/17-8/24; SC Governor McMaster proclaimed 'Boeing 787 Dreamliner Day' on 2026-08-07 (honorific, not operational)</t>
+        </is>
+      </c>
+      <c r="J222" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07 (proclamation, context only)</t>
+        </is>
+      </c>
+      <c r="K222" s="6" t="inlineStr">
+        <is>
+          <t>https://boeing.mediaroom.com/2025-11-07-Boeing-South-Carolina-Breaks-Ground-on-787-Site-Expansion</t>
+        </is>
+      </c>
+      <c r="L222" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — no new momentum this cycle</t>
+        </is>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>~475 employees (unchanged)</t>
+        </is>
+      </c>
+      <c r="G223" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H223" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="inlineStr">
+        <is>
+          <t>A search lead suggesting a new HII acquisition of a SC 'advanced metal fabricator' was run down and confirmed to be stale — that acquisition (W International SC / Vivid Empire SC, Goose Creek) was announced Dec. 2024 and closed Jan. 2025, well before this report's tracking window; no 2026 follow-up found. No fresher headcount than ~475 found this cycle</t>
+        </is>
+      </c>
+      <c r="J223" s="6" t="inlineStr">
+        <is>
+          <t>2025-01-27 (acquisition closing; pre-window, debunked as new)</t>
+        </is>
+      </c>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hii.com/news/hii-closes-on-asset-acquisition-to-expand-shipbuilding-capacity</t>
+        </is>
+      </c>
+      <c r="L223" s="6" t="inlineStr">
+        <is>
+          <t>Med (prior-cycle momentum stands; nothing new confirmed this cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>~160 apprentices (FTE n/d)</t>
+        </is>
+      </c>
+      <c r="G224" s="6" t="inlineStr">
+        <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t>Standing gap continues for a 4th consecutive cycle — a dedicated follow-up search found only a Google/SC Office of Resilience $1M Habitat for Humanity weatherization grant (2026-08-03), unrelated to data-center jobs or construction; no hiring/construction update for the data-center project itself found despite repeated dedicated searches</t>
+        </is>
+      </c>
+      <c r="J224" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03 (unrelated grant; no project-specific update found)</t>
+        </is>
+      </c>
+      <c r="K224" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L224" s="6" t="inlineStr">
+        <is>
+          <t>Med (unexpected persistent quiet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G225" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H225" s="6" t="inlineStr">
+        <is>
+          <t>Avg $78,811/yr ($37.89/hr); 90th pct ~$100k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J225" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-18 (last verified)</t>
+        </is>
+      </c>
+      <c r="K225" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L225" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t>$40-60M</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>Eng. roles $69-93k; assembly $34-46k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>Minor update: HQ formally opened with corporate teams now on-site at the 60-acre, 264,000 sf Woodruff campus; manufacturing/3D-printing operations remain under construction, still targeted early 2027</t>
+        </is>
+      </c>
+      <c r="J226" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (HQ opening confirmed)</t>
+        </is>
+      </c>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+        </is>
+      </c>
+      <c r="L226" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G227" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H227" s="6" t="inlineStr">
+        <is>
+          <t>~$49-76k technician range (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J227" s="6" t="inlineStr">
+        <is>
+          <t>2026-07 (last verified)</t>
+        </is>
+      </c>
+      <c r="K227" s="6" t="inlineStr">
+        <is>
+          <t>https://growlaurenscounty.com/news/article/momentum-continues-at-the-connexial-center-with-aptivs-investment</t>
+        </is>
+      </c>
+      <c r="L227" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G228" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; operations remain online</t>
+        </is>
+      </c>
+      <c r="J228" s="6" t="inlineStr">
+        <is>
+          <t>2026-04 (last verified)</t>
+        </is>
+      </c>
+      <c r="K228" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L228" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+        </is>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H229" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I229" s="6" t="inlineStr">
+        <is>
+          <t>No jobs-figure disclosure found; new context: GNQ is pursuing a public listing via SPAC merger with IB Acquisition Corp. (NASDAQ: IBAC) and has generated $20M+ contracted revenue since a Sept. 2025 launch — company-financial context, not a jobs/capex update</t>
+        </is>
+      </c>
+      <c r="J229" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (SPAC context)</t>
+        </is>
+      </c>
+      <c r="K229" s="6" t="inlineStr">
+        <is>
+          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
+        </is>
+      </c>
+      <c r="L229" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (momentum continues)</t>
+        </is>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired past yr, ~300 more targeted by end 2026</t>
+        </is>
+      </c>
+      <c r="G230" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville)</t>
+        </is>
+      </c>
+      <c r="H230" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (bulk likely sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I230" s="6" t="inlineStr">
+        <is>
+          <t>107 active open GE Vernova postings in Greenville confirmed as of 2026-08-18 (Gas Turbine Assembler Apprentices, Test Operators, Engineers), consistent with the hiring ramp already on record; no new discrete announcement this cycle</t>
+        </is>
+      </c>
+      <c r="J230" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18 (job-posting check)</t>
+        </is>
+      </c>
+      <c r="K230" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/ge-vernova-greenville-sc-manufacturing-new-jobs/article_7ef2b156-de75-11ef-b98b-b7f96e0e5f82.html</t>
+        </is>
+      </c>
+      <c r="L230" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. (Laurens)</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>Suniva Inc. — solar-cell manufacturing plant</t>
+        </is>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H231" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k blended</t>
+        </is>
+      </c>
+      <c r="I231" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond a clarifying detail: opening is specifically timed to Q2 2027 (consistent with prior 'spring/summer 2027' framing)</t>
+        </is>
+      </c>
+      <c r="J231" s="6" t="inlineStr">
+        <is>
+          <t>2026 (timeline clarification)</t>
+        </is>
+      </c>
+      <c r="K231" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
+        </is>
+      </c>
+      <c r="L231" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu North America — truck assembly plant</t>
+        </is>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="G232" s="6" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="H232" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred: assembly $35-56k, engineers $79-108k — blended sub-$100k</t>
+        </is>
+      </c>
+      <c r="I232" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the July 8, 2026 hiring event already on record; production launch still targeted 2027</t>
+        </is>
+      </c>
+      <c r="J232" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08 (last verified)</t>
+        </is>
+      </c>
+      <c r="K232" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ccjdigital.com/business/article/15767928/isuzu-building-280m-truck-plant-in-south-carolina-creating-700-jobs</t>
+        </is>
+      </c>
+      <c r="L232" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Ridgeville / Camp Hall</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials — battery-materials recycling campus</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (over coming years)</t>
+        </is>
+      </c>
+      <c r="G233" s="6" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H233" s="6" t="inlineStr">
+        <is>
+          <t>$27-75/hr stated (~$56k-156k) — upper tier clears $100k</t>
+        </is>
+      </c>
+      <c r="I233" s="6" t="inlineStr">
+        <is>
+          <t>Standing gap continues for a 4th consecutive cycle. A dedicated follow-up search of Redwood's own newsroom, Camp Hall's news page, and regional press confirmed every substantive SC-specific update predates the report window (operations-start milestone dated Nov. 2025; a company site-visit recap dated Feb. 2025) — no 2026 hiring-progress or milestone news exists for this site despite repeated targeted searching</t>
+        </is>
+      </c>
+      <c r="J233" s="6" t="inlineStr">
+        <is>
+          <t>2025-11 (last confirmed; no in-window update exists)</t>
+        </is>
+      </c>
+      <c r="K233" s="6" t="inlineStr">
+        <is>
+          <t>https://www.redwoodmaterials.com/news/redwood-begins-critical-materials-recovery-in-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L233" s="6" t="inlineStr">
+        <is>
+          <t>Med (confirmed no in-window update, not merely unfound)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>PSA Airlines — Charlotte headquarters</t>
+        </is>
+      </c>
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>~400 (450+ total team members at HQ)</t>
+        </is>
+      </c>
+      <c r="G234" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H234" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Inferred mixed corporate/admin/ops, likely sub-$100k blended)</t>
+        </is>
+      </c>
+      <c r="I234" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle</t>
+        </is>
+      </c>
+      <c r="J234" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-19 (last verified)</t>
+        </is>
+      </c>
+      <c r="K234" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/19/governor-stein-celebrates-psa-airlines-headquarters-grand-opening-charlotte-highlights-only</t>
+        </is>
+      </c>
+      <c r="L234" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21162,7 +26084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25249,6 +30171,426 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Prysmian Group — Claremont expansion</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Claremont</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Out of geography — Catawba County is not one of the seven defined Charlotte-metro NC counties; a large ($1B) in-window announcement but outside this report's footprint</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>BioAgilytix — Durham HQ expansion</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Jobs figure clears 500 but wage is undisclosed in every source found and the announcement date could not be confirmed as falling inside the 2026-02-24 to 2026-08-24 window before the research pass's search budget was exhausted — flagged for date/wage verification next cycle rather than promoted on an unconfirmed basis</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>"BCBSNC 3,000-job Raleigh tower" / "Energizer HQ to Apex" / "Lowe's 2,000-job Raleigh tech hub"</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Wake (claimed)</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Investigated and DEBUNKED this cycle: all three claims traced to a single low-credibility blog with no corroboration. BCBS NC's HQ remains in Durham; Energizer's HQ remains in Clayton, MO (its only NC project is an unrelated 144-job Asheboro expansion); Lowe's 2,000-job tech tower is confirmed to be in Charlotte's South End, not Raleigh. Excluded as unreliable/false rather than carried forward</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>UFP Packaging — new Cherokee County operation</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch-tier floor; wood/steel packaging is a low-wage industry</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-08/ufp-packaging-grows-south-carolina-footprint-new-cherokee-county-operation</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Fortified Solar — Greenville expansion</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (unverified exact date)</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch-tier floor</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/fortified-solar-expansion-greenville-sc-jobs/article_a50209bb-e5e1-47c3-8d49-428d923eeced.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Tyger River Industrial Park data center</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>2026-02 (rejected)</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>A separate, distinct $3B data-center proposal (not to be confused with NorthMark/Valara Project Moc-1) that Spartanburg County Council REJECTED in February 2026 — a negative/closed signal, not a qualifying announcement</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Unnamed global industrial automation technology company — first SC operation</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>162 (over 5 yrs)</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>2026 (unverified exact date)</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch-tier floor; jobs phased over 5 years is a weak near-term signal; company name not disclosed in source found</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Xoted Biotechnology Labs</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>2026 (unverified exact date)</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Far below the 200-job Watch-tier floor</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>MetOx International — Chatham County superconductor facility</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>2024 (last verified)</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>Below the 500-job Ranked threshold and no in-window (2026) update could be found this cycle despite a dedicated recheck — recycled/stale rather than newly excluded</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>NC Rural Infrastructure Authority grants (Aug. 20, 2026 round) — in-footprint line items only</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Guilford / Alamance / Buncombe</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>131 / 94 / 48 (individually, per project)</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>The statewide $1B+/342-job announcement includes several in-footprint projects, but each is individually below the 200-job Watch floor (Hoffman &amp; Hoffman reuse grant in Guilford also originally announced Dec. 2025, pre-window) — excluded on job-count grounds</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/08/20/governor-stein-announces-more-1-billion-private-investment-and-342-new-jobs-rural-north-carolina</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25260,7 +30602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -26971,6 +32313,222 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Post and Courier — York County</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>York Co. SC</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma Aug. 19 site-plan reveal at SC I-77 Alliance summit</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Pharma Manufacturing / BioSpace / rebusinessonline</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.pharmamanufacturing.com/</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. NC</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Genentech Holly Springs topping-out ceremony (Aug. 18, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette — budget/Scout</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Gov. McMaster's Aug. 17 veto clearing $150M Scout Motors site cost-overrun payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Post and Courier / Fox Carolina — Spartanburg data-center litigation</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara Project Moc-1: PSC oral arguments, SELC injunction filing, moratorium delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>BusinessWire / Nasdaq — Wolfspeed Q4 FY26 earnings</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Co. NC</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed Q4 FY2026 financial results (Aug. 19, 2026 earnings call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>About Amazon — AWS Hamlet</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aboutamazon.com/</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Richmond Co. NC</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon Hamlet 'Project Blue Marlin' data-center campus verification + groundbreaking</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Prism News — Boom Supersonic</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prismnews.com/</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co. NC</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic Greensboro factory idle-status feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Post and Courier — Redwood Materials / Google follow-up</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>https://www.redwoodmaterials.com/</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley Co. SC</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials + Google Berkeley/Dorchester standing-gap dedicated recheck</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26982,7 +32540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27958,6 +33516,206 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle (fifth consecutive quiet cycle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Public site-plan renderings presented at the SC I-77 Alliance summit (Aug. 19) is a genuine forward-planning milestone, moving the project from 'approved on paper' toward a visible design phase — net +1 for reduced execution-risk discount, even though the property sale itself is still not confirmed closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV plant (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Two offsetting in-window developments: Gov. McMaster's Aug. 17 budget veto clears a $150M state payment for site cost overruns (positive, removes a funding-hold risk), while a resident lawsuit over blasting/septic damage and Scout's declined Community Benefits Agreement request are modest community-friction negatives. Net score held flat — no fresher aggregate headcount than April's 600+ figure was found despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Structural topping-out ceremony held Aug. 18, 2026 (final beam raised on the ~700,000 sf, ~$2B facility) is a concrete, low-risk construction milestone — net +2 for reduced execution-risk discount, moving this entry above Capital Group and JetZero this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; both previously-credited milestones (June groundbreaking, July EXIM financing LOI) were independently reconfirmed with primary-source URLs, but no new milestone appeared within the strict 8/17-8/24 recheck window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new permit/construction-progress news found this cycle despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services (Durham)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; the Imperial Tower renovation remains 'on track for summer 2026' but no source found this cycle confirms it has actually completed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-08-24  ·  Window 2026-02-24 to 2026-08-24  ·  NC + SC</t>
+          <t>Week of 2026-08-31  ·  Window 2026-02-28 to 2026-08-31  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24  (Week 6)</t>
+          <t>2026-08-31  (Week 7)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-02-24 to 2026-08-24  (trailing 6 months)</t>
+          <t>2026-02-28 to 2026-08-31  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Holly Springs / SW Wake (Wake Co., NC) — Genentech's Aug. 18, 2026 structural topping-out ceremony (final beam raised on the ~700,000 sf, ~$2B facility) is the cycle's clearest, best-corroborated in-window construction milestone, moving the entry's score up 2 points and above Capital Group and JetZero in this cycle's ranking</t>
+          <t>Durham / RTP (Durham Co., NC) — AbbVie's ~$15.45M Durham County incentive package, flagged as unconfirmed last cycle, is now confirmed (BOCC approval July 13, 2026), moving the entry's score up 1 point to 85 and above Scout Motors' EV plant in this cycle's ranking; the biggest single de-risking event this cycle is NorthMark/Valara's Aug. 27 SC Public Service Commission ruling (Watch tier), which found the Spartanburg data center is not subject to state utility-siting review</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>This was largely a verification cycle rather than a discovery cycle: all five regions plus two targeted follow-up passes (SC Midlands/Lowcountry, NC Triad/WNC/Coastal) were run, but no new Ranked- or Watch-tier company/project announcement was found dated inside 2026-08-17 to 2026-08-24 — a genuinely quiet week for fresh 500+/200+-job announcements across the footprint. Two previously-unconfirmed leads were run to ground and debunked as stale, misdated articles rather than real 2026 developments: a claimed SC Ports Leatherman Terminal reopening (the underlying article was from Sept. 2024) and a claimed new HII South Carolina acquisition (the underlying deal closed in Jan. 2025). One long-running unverified item, AWS/Amazon's Hamlet 'Project Blue Marlin' data-center campus (Richmond Co., NC — 500 jobs, $10B), was independently verified this cycle via Amazon's own newsroom plus a confirmed ~June 20, 2026 groundbreaking. NorthMark/Valara 'Project Moc-1' (Spartanburg, SC) saw its regulatory/legal risk escalate materially, with a SC Public Service Commission ruling due Sept. 4, 2026 and an SELC injunction motion filed Aug. 20 seeking to halt construction. Wolfspeed's Aug. 19 Q4 FY26 earnings call delivered a genuinely mixed signal for Siler City: the site reached 'production readiness,' but underutilization costs kept rising as customer demand has not caught up to capacity.</t>
+          <t>This cycle broke a run of quiet weeks with one genuinely new Ranked-tier find: Citigroup's Ballantyne office (Mecklenburg, NC) — 510 jobs, a stated $131,832 average wage, and a facility that has already held its grand opening — was surfaced by a dedicated Charlotte-metro pass as a previously-untracked qualifying deal, joining the Ranked table at score 78. Four new Watch-tier items were also added: Maersk's North American HQ (Charlotte/Steele Creek, 520 jobs, $100,962 stated wage, held at Watch only because its lone dateable milestone falls 4 days before the window opens), Jabil's Rowan County advanced-manufacturing plant (1,181 jobs, sub-$100k wage), Forge Nano's Morrisville battery-gigafactory groundbreaking (Aug. 19, DOE-backed), and Protocase/45Drives' Wilmington precision-manufacturing campus. On the existing roster, AbbVie's previously-unconfirmed Durham County incentive package is now confirmed; NorthMark/Valara's Spartanburg data center cleared a major state-level regulatory hurdle (PSC ruling, Aug. 27) even as a county-permitting lawsuit remains open; AWS/Amazon's Hamlet campus cleared final air-quality permitting (Aug. 28); Boeing announced a North Charleston apprenticeship-program expansion; and Wolfspeed's Siler City site saw a genuinely new, real 2026 WARN layoff notice (73 employees) that reinforces the underutilization-cost signal from its Aug. 19 earnings call. VinFast's $400M Chatham County incentive agreement was confirmed terminated (Excluded, negative signal) and Electrolux's Anderson, SC plant recorded a 1,255-worker temporary layoff (Excluded, negative signal, with a speculative future Midea-JV rehire not yet scored).</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>All five regions received a full research pass this cycle, plus two additional targeted follow-up passes to close gaps left by search-budget exhaustion in the SC Midlands/Lowcountry and NC Triad/WNC/Coastal passes (Boeing, Redwood Materials, Google data center, AMAROK, Ferrara Candy, and ten Triad/WNC/Coastal Watch items were all successfully rechecked in the follow-up passes). WebFetch (direct page retrieval) returned EGRESS_BLOCKED for essentially every news/gov domain attempted across all agents this cycle; every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries. No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
+          <t>All five regions (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) received a full research pass this cycle via parallel dedicated research agents. WebFetch (direct page retrieval) again returned EGRESS_BLOCKED for essentially every news/gov domain attempted across all agents; every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries. Each region's WebSearch budget was exhausted before every conceivable follow-up query could be run (flagged per-region: Charlotte metro could not complete a York/Lancaster/Chester-county-specific sweep or verify one incomplete lead — AssetMark, ~252 jobs, held out of this week's tables pending confirmation; NC Triangle could not resolve a minor date discrepancy on Genentech's topping-out ceremony; Upstate SC and SC Midlands/Lowcountry both completed full required rechecks within budget). No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-02-24 to 2026-08-24.</t>
+          <t>Trailing 6 months now runs 2026-02-28 to 2026-08-31.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Two previously-surfaced leads were investigated and debunked this cycle as stale/misdated articles, not 2026 developments: a claimed SC Ports Leatherman Terminal reopening (actual article dated Sept. 2024) and a claimed new HII South Carolina acquisition (actual deal closed Jan. 2025). NorthMark/Valara's jobs figure was reconciled down to 27 FT (the consistently-cited incentive-basis figure) from a previously-carried ~150 estimate. AWS/Amazon's Hamlet, NC data-center campus, carried for multiple cycles as 'unverified,' is now confirmed via a primary Amazon source and a dated groundbreaking.</t>
+          <t>AbbVie's previously-flagged 'unconfirmed' ~$15M Durham County incentive is now confirmed at a not-to-exceed $15,450,000 (two independent sources). NorthMark/Valara's jobs figure remains 27 FT confirmed; its regulatory risk profile improved materially this cycle (SC PSC ruled in the project's favor Aug. 27) even as a separate county-permitting lawsuit remains open. Boeing's North Charleston campus headcount is reconciled to 9,059 (from a previously-carried 8,200+), based on a 2025 year-end payroll figure (+800 hires, ~10% YoY). One prior 'unverified layoffs' item for Wolfspeed is now superseded by a genuinely new, dated 2026 WARN notice (73 employees, Siler City) — distinct from the stale 2025 notices debunked two cycles ago.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>10 of 10 prior-ranked deals remain qualifying — none removed, none newly added. 2 updated positively (Octapharma +1 to 91 on a site-plan-design milestone; Genentech +2 to 82 on a structural topping-out ceremony), 1 updated with offsetting context and no net score change (Scout Motors EV plant, funding veto vs. community-relations friction), 7 repeated unchanged (SMBC, AbbVie, Capital Group, JetZero, Scout Motors HQ, Novartis, Aspida). Watch tier: no new items added and none removed; AWS/Amazon Hamlet upgraded from unverified to confirmed; Wolfspeed and NorthMark/Valara both saw material updates; two leads (SC Ports reopening, HII acquisition) were investigated and debunked rather than added as new information.</t>
+          <t>11 of 10 prior-ranked deals carry forward (all 10 remain qualifying; none removed) plus 1 new entry (Citigroup, Ballantyne). 1 updated positively (AbbVie +1 to 85 on a confirmed Durham County incentive package), 9 repeated unchanged (SMBC, Octapharma, Scout Motors EV plant, Genentech, Capital Group, JetZero, Scout Motors HQ, Novartis, Aspida). Watch tier: 4 new items added (Maersk, Jabil, Forge Nano, Protocase/45Drives), none removed; NorthMark/Valara, AWS/Amazon Hamlet, Boeing 787, and Wolfspeed all received material updates this cycle; Signature Foods' status was clarified from 'targeted' to 'operating.' Two negative/closed signals were newly logged in Excluded/Noise: VinFast's Chatham County incentive agreement (terminated) and Electrolux's Anderson, SC temporary layoff (1,255 workers).</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5459,6 +5459,1007 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county; Durham Co. performance-based award confirmed not-to-exceed $15,450,000 ("Project Glass")</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>Local incentive package confirmed</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>https://www.einpresswire.com/article/926805248/board-of-county-commissioners-regular-session-highlights-from-july-13</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant (no fresh in-window milestone)</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (+$25M training center)</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; Aug. 17 veto clears $150M cost-overrun payment (not yet confirmed disbursed)</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>Funding cleared to pay; litigation and headcount unchanged</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/08/17/sc-governor-vetoes-delay-on-paying-agency-overruns-at-scout-motors-site/</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake; a topping-out milestone moves the 2029 hiring ramp from planned to physically materializing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility</t>
+        </is>
+      </c>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (unchanged)</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr (unchanged)</t>
+        </is>
+      </c>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (current grading status)</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; no change in housing-demand framing this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building (unchanged)</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+ 